--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Polymarket" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kalshi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin of Victory" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voter Turnout" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PA Seat Count" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Polls" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast &amp; Aggregators" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campaign Finance" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venue Comparison" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Sources" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Charts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Distributions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Polymarket" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kalshi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Margin of Victory" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Voter Turnout" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PA Seat Count" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Polls" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Forecast &amp; Aggregators" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Campaign Finance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Venue Comparison" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Notes &amp; Sources" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,13 +479,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -524,7 +524,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="2E5FA3"/>
               </a:solidFill>
@@ -534,7 +534,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -560,7 +560,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="E8802B"/>
               </a:solidFill>
@@ -570,7 +570,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -596,7 +596,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12000">
+            <a:ln w="12000">
               <a:solidFill>
                 <a:srgbClr val="9AA5B1"/>
               </a:solidFill>
@@ -606,7 +606,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -638,7 +638,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -646,8 +646,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -681,7 +681,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -692,8 +692,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -713,7 +713,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -721,8 +721,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -748,8 +748,8 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0">
               <a:solidFill>
@@ -775,13 +775,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -816,10 +816,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2E5FA3"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -852,7 +852,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -860,8 +860,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -891,7 +891,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -902,8 +902,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -923,7 +923,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -931,8 +931,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -960,13 +960,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -1001,10 +1001,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2E5FA3"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1037,7 +1037,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1045,8 +1045,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1076,7 +1076,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -1087,8 +1087,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -1108,7 +1108,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1116,8 +1116,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1145,13 +1145,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -1191,10 +1191,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E8802B"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1224,7 +1224,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1232,8 +1232,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1263,7 +1263,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -1274,8 +1274,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -1295,7 +1295,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1303,8 +1303,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1332,13 +1332,13 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -1372,7 +1372,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="5B8C5A"/>
               </a:solidFill>
@@ -1382,7 +1382,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1413,7 +1413,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1421,8 +1421,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1454,7 +1454,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -1465,8 +1465,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -1486,7 +1486,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1494,8 +1494,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1524,13 +1524,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -1569,7 +1569,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="20000">
+            <a:ln w="20000">
               <a:solidFill>
                 <a:srgbClr val="6B7C93"/>
               </a:solidFill>
@@ -1579,7 +1579,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1611,7 +1611,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1619,8 +1619,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1654,7 +1654,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -1665,8 +1665,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -1686,7 +1686,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1694,8 +1694,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1721,8 +1721,8 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0">
               <a:solidFill>
@@ -1748,13 +1748,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -1793,7 +1793,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="16000">
+            <a:ln w="16000">
               <a:solidFill>
                 <a:srgbClr val="2E5FA3"/>
               </a:solidFill>
@@ -1803,7 +1803,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1829,7 +1829,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="16000">
+            <a:ln w="16000">
               <a:solidFill>
                 <a:srgbClr val="E8802B"/>
               </a:solidFill>
@@ -1839,7 +1839,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1871,7 +1871,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1879,8 +1879,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1914,7 +1914,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -1925,8 +1925,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -1946,7 +1946,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -1954,8 +1954,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -1981,8 +1981,8 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0">
               <a:solidFill>
@@ -2008,13 +2008,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -2053,7 +2053,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="20000">
+            <a:ln w="20000">
               <a:solidFill>
                 <a:srgbClr val="5B8C5A"/>
               </a:solidFill>
@@ -2063,7 +2063,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2095,7 +2095,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2103,8 +2103,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2136,7 +2136,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -2147,8 +2147,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -2168,7 +2168,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2176,8 +2176,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2202,8 +2202,8 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0">
               <a:solidFill>
@@ -2229,13 +2229,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -2274,7 +2274,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
+            <a:ln w="18000">
               <a:solidFill>
                 <a:srgbClr val="8E6FB3"/>
               </a:solidFill>
@@ -2284,7 +2284,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2316,7 +2316,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2324,8 +2324,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2359,7 +2359,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -2370,8 +2370,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -2391,7 +2391,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2399,8 +2399,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2426,8 +2426,8 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0">
               <a:solidFill>
@@ -2453,13 +2453,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -2498,7 +2498,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="2E5FA3"/>
               </a:solidFill>
@@ -2508,7 +2508,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2534,7 +2534,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="C0392B"/>
               </a:solidFill>
@@ -2544,7 +2544,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2576,7 +2576,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2584,8 +2584,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2619,7 +2619,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -2630,8 +2630,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -2651,7 +2651,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2659,8 +2659,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2686,8 +2686,8 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0">
               <a:solidFill>
@@ -2713,13 +2713,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -2758,7 +2758,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="8E6FB3"/>
               </a:solidFill>
@@ -2768,7 +2768,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2794,7 +2794,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="2E5FA3"/>
               </a:solidFill>
@@ -2804,7 +2804,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2835,7 +2835,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2843,8 +2843,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2878,7 +2878,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -2889,8 +2889,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -2910,7 +2910,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -2918,8 +2918,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -2945,8 +2945,8 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0">
               <a:solidFill>
@@ -2972,13 +2972,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -3018,10 +3018,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2E5FA3"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -3051,7 +3051,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -3059,8 +3059,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -3090,7 +3090,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -3101,8 +3101,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -3122,7 +3122,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -3130,8 +3130,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -3159,13 +3159,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1">
                 <a:solidFill>
@@ -3205,10 +3205,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="5B8C5A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -3241,7 +3241,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -3249,8 +3249,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -3280,7 +3280,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:ln w="6350">
               <a:solidFill>
                 <a:srgbClr val="EDEFF3"/>
               </a:solidFill>
@@ -3291,8 +3291,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="950" b="0">
                     <a:solidFill>
@@ -3312,7 +3312,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="44546A"/>
             </a:solidFill>
@@ -3320,8 +3320,8 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
@@ -3619,7 +3619,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -3634,9 +3634,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3656,9 +3656,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3678,9 +3678,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3700,9 +3700,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3722,9 +3722,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3744,9 +3744,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3766,9 +3766,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3778,7 +3778,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -3793,9 +3793,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3815,9 +3815,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3837,9 +3837,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3859,9 +3859,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3881,9 +3881,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3903,9 +3903,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4226,7 +4226,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-14 17:12 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>2026-09-14 17:12 UTC</t>
+          <t>2026-09-14 21:26 UTC</t>
         </is>
       </c>
       <c r="C69" s="66" t="n"/>
@@ -5426,7 +5426,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-14 17:12 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-14 17:12 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-14 17:12 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -27507,7 +27507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-14 17:12 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -28667,7 +28667,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-14 17:12 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -28748,7 +28748,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-14 17:12 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -28932,7 +28932,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 17:12 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -29088,7 +29088,7 @@
         <v>24418.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>5265.509802</v>
+        <v>5265.509802000001</v>
       </c>
     </row>
     <row r="13">
@@ -29098,10 +29098,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1166.8365</v>
+        <v>1200.815</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1745.3141</v>
+        <v>2280.0464</v>
       </c>
     </row>
     <row r="14">
@@ -29124,10 +29124,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-0.045</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="17">
@@ -29197,7 +29197,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0.74</v>
@@ -29211,10 +29211,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>610</v>
+        <v>309</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>219.57</v>
+        <v>51</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29228,10 +29228,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29242,10 +29242,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>98.69</v>
+        <v>300.69</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>518.71</v>
+        <v>166.3</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40345,10 +40345,10 @@
         <v>46279</v>
       </c>
       <c r="B275" s="16" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
       <c r="C275" s="16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="D275" s="17">
         <f>IF(COUNT(B275:C275)=2,B275+C275,"")</f>
@@ -40423,7 +40423,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 17:12 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -40692,7 +40692,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>50051.9</v>
+        <v>50142.06</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40826,7 +40826,7 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>50051.9</v>
+        <v>50142.06</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.26</v>
@@ -40844,7 +40844,7 @@
         <v>0.71</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>52568</v>
+        <v>52248</v>
       </c>
     </row>
     <row r="24">
@@ -40852,16 +40852,16 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>195.68</v>
+        <v>149</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>97.86</v>
+        <v>90.86</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.26</v>
@@ -40881,22 +40881,22 @@
         <v>3</v>
       </c>
       <c r="B25" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>433</v>
+        <v>43.04</v>
       </c>
       <c r="D25" s="16" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="16" t="n">
         <v>0.23</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>0.24</v>
-      </c>
       <c r="G25" s="19" t="n">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>0.68</v>
@@ -40910,22 +40910,22 @@
         <v>4</v>
       </c>
       <c r="B26" s="16" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>5167</v>
+        <v>433</v>
       </c>
       <c r="D26" s="16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="F26" s="16" t="n">
         <v>0.22</v>
       </c>
-      <c r="E26" s="19" t="n">
-        <v>115</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>0.23</v>
-      </c>
       <c r="G26" s="19" t="n">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>0.6</v>
@@ -40939,22 +40939,22 @@
         <v>5</v>
       </c>
       <c r="B27" s="16" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>225</v>
+        <v>5167</v>
       </c>
       <c r="D27" s="16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="F27" s="16" t="n">
         <v>0.21</v>
       </c>
-      <c r="E27" s="19" t="n">
-        <v>50026.14</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>0.22</v>
-      </c>
       <c r="G27" s="19" t="n">
-        <v>103</v>
+        <v>50000</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>0.5600000000000001</v>
@@ -61474,7 +61474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-14 17:12 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -61593,7 +61593,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>53476.92831</v>
+        <v>43347.43772</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61692,10 +61692,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="E16" s="17">
         <f>(C16+D16)/2</f>
@@ -61713,7 +61713,7 @@
         <v>632.130643</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8417.8382</v>
+        <v>403.4139</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61733,7 +61733,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="E17" s="17">
         <f>(C17+D17)/2</f>
@@ -61751,7 +61751,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>9064.36392</v>
+        <v>8410.57555</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61789,7 +61789,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>364.0957</v>
+        <v>185.1006</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61806,7 +61806,7 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>0.15</v>
@@ -61827,7 +61827,7 @@
         <v>101.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8623.377399999999</v>
+        <v>255.6531</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -61844,10 +61844,10 @@
         <v>4.5</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E20" s="17">
         <f>(C20+D20)/2</f>
@@ -61865,7 +61865,7 @@
         <v>229.186665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8672.892400000001</v>
+        <v>8270.0229</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -61882,7 +61882,7 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>0.097</v>
@@ -61903,7 +61903,7 @@
         <v>223.635421</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>8863.29336</v>
+        <v>8265.89251</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -61920,7 +61920,7 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>0.12</v>
@@ -61941,7 +61941,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>382.6018</v>
+        <v>8517.7691</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -61979,7 +61979,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>8422.1122</v>
+        <v>8342.4542</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62017,7 +62017,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>248.77633</v>
+        <v>160.09816</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62055,7 +62055,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>386.87</v>
+        <v>281.3294</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63450,25 +63450,25 @@
         <v>46279</v>
       </c>
       <c r="B76" s="28" t="n">
-        <v>0.12</v>
+        <v>0.145</v>
       </c>
       <c r="C76" s="28" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="D76" s="28" t="n">
         <v>0.09</v>
       </c>
       <c r="E76" s="28" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="F76" s="28" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="G76" s="28" t="n">
-        <v>0.0925</v>
+        <v>0.0905</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="I76" s="28" t="n">
         <v>0.05</v>
@@ -63828,10 +63828,10 @@
         <v>9</v>
       </c>
       <c r="C89" s="16" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="D89" s="16" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="E89" s="17">
         <f>IF(COUNT(C89:D89)=2,(C89+D89)/2,"")</f>
@@ -67029,7 +67029,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-14 17:12 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -68242,7 +68242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-14 17:12 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>
@@ -68561,7 +68561,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>0.8100000000000001</v>
@@ -69576,7 +69576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-14 17:12 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-14 21:26 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -4226,7 +4226,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-14 21:26 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>2026-09-14 21:26 UTC</t>
+          <t>2026-09-14 21:28 UTC</t>
         </is>
       </c>
       <c r="C69" s="66" t="n"/>
@@ -5426,7 +5426,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-14 21:26 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-14 21:26 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-14 21:26 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -27507,7 +27507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-14 21:26 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-14 21:29 UTC.</t>
         </is>
       </c>
     </row>
@@ -28667,7 +28667,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-14 21:26 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-14 21:29 UTC.</t>
         </is>
       </c>
     </row>
@@ -28748,7 +28748,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-14 21:26 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-14 21:29 UTC.</t>
         </is>
       </c>
     </row>
@@ -28932,7 +28932,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:26 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -29098,10 +29098,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1200.815</v>
+        <v>1187.555</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2280.0464</v>
+        <v>2309.2467</v>
       </c>
     </row>
     <row r="14">
@@ -29211,7 +29211,7 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>309</v>
+        <v>577</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>51</v>
@@ -40423,7 +40423,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:26 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -40674,10 +40674,10 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="D17" s="20">
         <f>1-C17</f>
@@ -40692,7 +40692,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>50142.06</v>
+        <v>186</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40823,16 +40823,16 @@
         <v>1</v>
       </c>
       <c r="B23" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>50142.06</v>
+        <v>186</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>619</v>
+        <v>608.86</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0.28</v>
@@ -40844,7 +40844,7 @@
         <v>0.71</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>52248</v>
+        <v>50409</v>
       </c>
     </row>
     <row r="24">
@@ -40852,16 +40852,16 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>149</v>
+        <v>49892.9</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>90.86</v>
+        <v>8</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.26</v>
@@ -40881,22 +40881,22 @@
         <v>3</v>
       </c>
       <c r="B25" s="16" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>43.04</v>
+        <v>133.7</v>
       </c>
       <c r="D25" s="16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="F25" s="16" t="n">
         <v>0.24</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>0.23</v>
-      </c>
       <c r="G25" s="19" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>0.68</v>
@@ -40916,16 +40916,16 @@
         <v>433</v>
       </c>
       <c r="D26" s="16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="F26" s="16" t="n">
         <v>0.23</v>
       </c>
-      <c r="E26" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>0.22</v>
-      </c>
       <c r="G26" s="19" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>0.6</v>
@@ -40945,16 +40945,16 @@
         <v>5167</v>
       </c>
       <c r="D27" s="16" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>50021.2</v>
+      </c>
+      <c r="F27" s="16" t="n">
         <v>0.22</v>
       </c>
-      <c r="E27" s="19" t="n">
-        <v>67</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>0.21</v>
-      </c>
       <c r="G27" s="19" t="n">
-        <v>50000</v>
+        <v>97</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>0.5600000000000001</v>
@@ -61474,7 +61474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-14 21:26 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -61809,7 +61809,7 @@
         <v>0.1</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E19" s="17">
         <f>(C19+D19)/2</f>
@@ -67029,7 +67029,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-14 21:26 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -68242,7 +68242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-14 21:26 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>
@@ -69576,7 +69576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-14 21:26 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-14 21:28 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -4226,7 +4226,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-14 21:28 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>2026-09-14 21:28 UTC</t>
+          <t>2026-09-14 23:24 UTC</t>
         </is>
       </c>
       <c r="C69" s="66" t="n"/>
@@ -5426,7 +5426,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-14 21:28 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-14 21:28 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-14 21:28 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -27507,7 +27507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-14 21:29 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28667,7 +28667,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-14 21:29 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28748,7 +28748,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-14 21:29 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28932,7 +28932,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:28 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -29088,7 +29088,7 @@
         <v>24418.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>5265.509802000001</v>
+        <v>5265.509802</v>
       </c>
     </row>
     <row r="13">
@@ -29098,10 +29098,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1187.555</v>
+        <v>1022.7753</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2309.2467</v>
+        <v>1410.4987</v>
       </c>
     </row>
     <row r="14">
@@ -29124,10 +29124,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-0.05</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="17">
@@ -29197,7 +29197,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0.74</v>
@@ -29211,10 +29211,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>51</v>
+        <v>275.57</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29228,10 +29228,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29242,10 +29242,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>300.69</v>
+        <v>49</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>166.3</v>
+        <v>90.3</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40345,10 +40345,10 @@
         <v>46279</v>
       </c>
       <c r="B275" s="16" t="n">
-        <v>0.73</v>
+        <v>0.725</v>
       </c>
       <c r="C275" s="16" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="D275" s="17">
         <f>IF(COUNT(B275:C275)=2,B275+C275,"")</f>
@@ -40423,7 +40423,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 21:28 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -40674,10 +40674,10 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="D17" s="20">
         <f>1-C17</f>
@@ -40692,7 +40692,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>186</v>
+        <v>50052.9</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40724,7 +40724,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40823,28 +40823,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="16" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>186</v>
+        <v>50052.9</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>608.86</v>
+        <v>1168.87</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0.28</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>0.71</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>50409</v>
+        <v>52568</v>
       </c>
     </row>
     <row r="24">
@@ -40852,28 +40852,28 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>49892.9</v>
+        <v>81</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>8</v>
+        <v>200.86</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>500</v>
+        <v>197</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="25">
@@ -40881,28 +40881,28 @@
         <v>3</v>
       </c>
       <c r="B25" s="16" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>133.7</v>
+        <v>136.23</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>5200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -40916,22 +40916,22 @@
         <v>433</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>81</v>
+        <v>50000</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -40945,22 +40945,22 @@
         <v>5167</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>50021.2</v>
+        <v>94.64</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>97</v>
+        <v>1000</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
@@ -61474,7 +61474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-14 21:28 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -61593,7 +61593,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>43347.43772</v>
+        <v>34518.05687</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61713,7 +61713,7 @@
         <v>632.130643</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>403.4139</v>
+        <v>228.4467</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61751,7 +61751,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8410.57555</v>
+        <v>8638.08252</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61789,7 +61789,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>185.1006</v>
+        <v>199.8755</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61806,10 +61806,10 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="17">
         <f>(C19+D19)/2</f>
@@ -61827,7 +61827,7 @@
         <v>101.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>255.6531</v>
+        <v>179.7184</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -61865,7 +61865,7 @@
         <v>229.186665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8270.0229</v>
+        <v>8212.992399999999</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -61882,10 +61882,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.097</v>
+        <v>0.099</v>
       </c>
       <c r="E21" s="17">
         <f>(C21+D21)/2</f>
@@ -61903,7 +61903,7 @@
         <v>223.635421</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>8265.89251</v>
+        <v>8196.776540000001</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -61920,7 +61920,7 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>0.12</v>
@@ -61941,7 +61941,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>8517.7691</v>
+        <v>225.1231</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -61979,7 +61979,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>8342.4542</v>
+        <v>8269.912200000001</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62017,7 +62017,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>160.09816</v>
+        <v>186.04951</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62034,10 +62034,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E25" s="17">
         <f>(C25+D25)/2</f>
@@ -62055,7 +62055,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>281.3294</v>
+        <v>198.4812</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63459,16 +63459,16 @@
         <v>0.09</v>
       </c>
       <c r="E76" s="28" t="n">
-        <v>0.125</v>
+        <v>0.135</v>
       </c>
       <c r="F76" s="28" t="n">
         <v>0.12</v>
       </c>
       <c r="G76" s="28" t="n">
-        <v>0.0905</v>
+        <v>0.091</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="I76" s="28" t="n">
         <v>0.05</v>
@@ -63477,7 +63477,7 @@
         <v>0.055</v>
       </c>
       <c r="K76" s="28" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="77">
@@ -67029,7 +67029,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-14 21:28 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -68242,7 +68242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-14 21:28 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -68489,7 +68489,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.9</v>
@@ -68600,7 +68600,7 @@
         <v>0.27</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -69576,7 +69576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-14 21:28 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-14 23:24 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -4226,7 +4226,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-15 11:26 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>2026-09-15 11:26 UTC</t>
+          <t>2026-09-15 17:24 UTC</t>
         </is>
       </c>
       <c r="C69" s="66" t="n"/>
@@ -5426,7 +5426,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-15 11:26 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-15 11:26 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-15 11:26 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -27556,7 +27556,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-15 11:26 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28716,7 +28716,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-15 11:26 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28797,7 +28797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-15 11:26 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28981,7 +28981,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 11:26 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -29147,10 +29147,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1293.4272</v>
+        <v>1198.7795</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1665.5711</v>
+        <v>1303.8319</v>
       </c>
     </row>
     <row r="14">
@@ -29173,10 +29173,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.035</v>
+        <v>0.01</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-0.035</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="17">
@@ -29260,10 +29260,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>69.31999999999999</v>
+        <v>135.53</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>80</v>
+        <v>126.21</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29291,10 +29291,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>274.69</v>
+        <v>211.69</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>61.3</v>
+        <v>197.25</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40516,7 +40516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 11:26 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -40767,10 +40767,10 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="D17" s="20">
         <f>1-C17</f>
@@ -40785,7 +40785,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>54.51</v>
+        <v>136.15</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40799,10 +40799,10 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -40817,7 +40817,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40916,28 +40916,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>54.51</v>
+        <v>136.15</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>15</v>
+        <v>0.86</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>273.83</v>
+        <v>238.52</v>
       </c>
     </row>
     <row r="24">
@@ -40945,28 +40945,28 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>146</v>
+        <v>50000</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>500.86</v>
+        <v>641</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>16.9</v>
+        <v>188.44</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>100</v>
+        <v>50122</v>
       </c>
     </row>
     <row r="25">
@@ -40977,25 +40977,25 @@
         <v>0.71</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>76.27</v>
+        <v>42.9</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>82</v>
+        <v>20.32</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26">
@@ -41006,25 +41006,25 @@
         <v>0.7</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>211.57</v>
+        <v>216</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>999.87</v>
+        <v>57</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>1000</v>
+        <v>50000</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>300</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="27">
@@ -41038,22 +41038,22 @@
         <v>421</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>496.44</v>
+        <v>50000</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29">
@@ -61615,7 +61615,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-15 11:26 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -61720,7 +61720,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>2056.361321</v>
+        <v>2081.361321</v>
       </c>
       <c r="C10" s="66" t="n"/>
       <c r="D10" s="66" t="n"/>
@@ -61734,7 +61734,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>50736.95386</v>
+        <v>54652.03404</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61833,10 +61833,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="E16" s="17">
         <f>(C16+D16)/2</f>
@@ -61851,10 +61851,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>632.130643</v>
+        <v>657.130643</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8445.642099999999</v>
+        <v>781.0738</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61871,10 +61871,10 @@
         <v>-4.5</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.14</v>
+        <v>0.132</v>
       </c>
       <c r="E17" s="17">
         <f>(C17+D17)/2</f>
@@ -61892,7 +61892,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8448.07012</v>
+        <v>8904.896699999999</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61909,10 +61909,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="E18" s="17">
         <f>(C18+D18)/2</f>
@@ -61930,7 +61930,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>190.9311</v>
+        <v>8692.718999999999</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61947,10 +61947,10 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="E19" s="17">
         <f>(C19+D19)/2</f>
@@ -61968,7 +61968,7 @@
         <v>101.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8299.162</v>
+        <v>8786.925499999999</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -61985,10 +61985,10 @@
         <v>4.5</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E20" s="17">
         <f>(C20+D20)/2</f>
@@ -62006,7 +62006,7 @@
         <v>229.186665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8203.0738</v>
+        <v>8806.0398</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62023,10 +62023,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="E21" s="17">
         <f>(C21+D21)/2</f>
@@ -62044,7 +62044,7 @@
         <v>223.635421</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>8274.84966</v>
+        <v>8794.74013</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62061,10 +62061,10 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E22" s="17">
         <f>(C22+D22)/2</f>
@@ -62082,7 +62082,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>203.5438</v>
+        <v>8648.223900000001</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62099,7 +62099,7 @@
         <v>13.5</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
@@ -62120,7 +62120,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>8311.811100000001</v>
+        <v>398.5421</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62137,7 +62137,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62158,7 +62158,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>168.69008</v>
+        <v>326.64978</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62175,10 +62175,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E25" s="17">
         <f>(C25+D25)/2</f>
@@ -62196,7 +62196,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>207.0302</v>
+        <v>448.2193</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63626,31 +63626,31 @@
         <v>46280</v>
       </c>
       <c r="B77" s="16" t="n">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>0.1205</v>
+        <v>0.1175</v>
       </c>
       <c r="D77" s="16" t="n">
         <v>0.09</v>
       </c>
       <c r="E77" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F77" s="16" t="n">
         <v>0.125</v>
-      </c>
-      <c r="F77" s="16" t="n">
-        <v>0.12</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>0.091</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="I77" s="16" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="J77" s="16" t="n">
-        <v>0.0525</v>
+        <v>0.052</v>
       </c>
       <c r="K77" s="16" t="n">
         <v>0.095</v>
@@ -67232,7 +67232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-15 11:26 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -68445,7 +68445,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-15 11:26 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -68764,7 +68764,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>0.8</v>
@@ -69802,7 +69802,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-15 11:26 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-15 17:24 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-15 19:20 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:20 UTC</t>
+          <t>2026-09-15 23:24 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-15 19:20 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-15 19:20 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-15 19:20 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -27293,7 +27293,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-15 19:20 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28453,7 +28453,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-15 19:20 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28534,7 +28534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-15 19:20 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28718,7 +28718,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 19:20 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28884,10 +28884,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1233.2716</v>
+        <v>1101.6579</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1941.5703</v>
+        <v>1524.7801</v>
       </c>
     </row>
     <row r="14">
@@ -28910,9 +28910,11 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C15" s="14" t="n"/>
+        <v>0.01</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>-0.01</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -28995,10 +28997,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>115.53</v>
+        <v>74.2</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>126.21</v>
+        <v>60</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29026,10 +29028,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>218.69</v>
+        <v>123.69</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>176.3</v>
+        <v>81.3</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40251,7 +40253,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 19:20 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -40520,7 +40522,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>179.08</v>
+        <v>174.23</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40552,7 +40554,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40654,7 +40656,7 @@
         <v>0.74</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>179.08</v>
+        <v>174.23</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.25</v>
@@ -40666,13 +40668,13 @@
         <v>0.24</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>0.74</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>246.52</v>
+        <v>220.06</v>
       </c>
     </row>
     <row r="24">
@@ -40689,19 +40691,19 @@
         <v>0.24</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>640</v>
+        <v>569</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.23</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>188.44</v>
+        <v>128.7</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>0.73</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>50122</v>
+        <v>50156</v>
       </c>
     </row>
     <row r="25">
@@ -40718,13 +40720,13 @@
         <v>0.23</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>20.31</v>
+        <v>25.97</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>0.6899999999999999</v>
@@ -40747,7 +40749,7 @@
         <v>0.22</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1056.87</v>
+        <v>1061.87</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>0.21</v>
@@ -40776,7 +40778,7 @@
         <v>0.21</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>50000</v>
+        <v>50063.68</v>
       </c>
       <c r="F27" s="16" t="n">
         <v>0.17</v>
@@ -61350,7 +61352,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-15 19:20 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -61469,7 +61471,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>34635.20919</v>
+        <v>53856.52751</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61568,10 +61570,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -61589,7 +61591,7 @@
         <v>657.130643</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8363.9159</v>
+        <v>8845.786700000001</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61606,10 +61608,10 @@
         <v>-4.5</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -61627,7 +61629,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8383.86159</v>
+        <v>8685.63608</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61644,10 +61646,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -61665,7 +61667,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>265.75</v>
+        <v>373.1383</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61685,7 +61687,7 @@
         <v>0.1</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -61703,7 +61705,7 @@
         <v>101.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>371.5574</v>
+        <v>8743.235199999999</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -61720,10 +61722,10 @@
         <v>4.5</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E20" s="17">
         <f>IF(COUNT(C20:D20)=2,(C20+D20)/2,"")</f>
@@ -61741,7 +61743,7 @@
         <v>229.186665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8298.611500000001</v>
+        <v>8677.923500000001</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -61779,7 +61781,7 @@
         <v>223.635421</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>8140.37635</v>
+        <v>8790.79293</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -61796,10 +61798,10 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E22" s="17">
         <f>IF(COUNT(C22:D22)=2,(C22+D22)/2,"")</f>
@@ -61817,7 +61819,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>307.6166</v>
+        <v>8660.9612</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -61833,9 +61835,7 @@
       <c r="B23" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="C23" s="16" t="n"/>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
       </c>
@@ -61855,7 +61855,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>161.2959</v>
+        <v>366.1687</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -61872,7 +61872,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -61893,7 +61893,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>171.16462</v>
+        <v>331.433</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -61910,10 +61910,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -61931,7 +61931,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>126.7835</v>
+        <v>380.2045</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63361,34 +63361,34 @@
         <v>46280</v>
       </c>
       <c r="B77" s="16" t="n">
-        <v>0.225</v>
+        <v>0.19</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="D77" s="16" t="n">
         <v>0.08500000000000001</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>0.091</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>0.065</v>
+        <v>0.075</v>
       </c>
       <c r="I77" s="16" t="n">
         <v>0.04</v>
       </c>
       <c r="J77" s="16" t="n">
-        <v>0.0525</v>
+        <v>0.0515</v>
       </c>
       <c r="K77" s="16" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -63447,7 +63447,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-15 19:20 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-15 19:20 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -65018,7 +65018,7 @@
         <v>0.26</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66017,7 +66017,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-15 19:20 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-15 23:24 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-16 11:27 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-16 17:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-16 11:27 UTC</t>
+          <t>2026-09-16 17:25 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-16 11:27 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-16 11:27 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-16 11:27 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-16 17:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -27342,7 +27342,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-16 11:27 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-16 17:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28502,7 +28502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-16 11:27 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-16 17:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28583,7 +28583,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-16 11:27 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-16 17:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 11:27 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28933,10 +28933,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>809.122</v>
+        <v>1048.1636</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1144.4904</v>
+        <v>1599.2699</v>
       </c>
     </row>
     <row r="14">
@@ -28958,9 +28958,11 @@
           <t>24h price change</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
+      <c r="B15" s="13" t="n">
+        <v>0.005</v>
+      </c>
       <c r="C15" s="14" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="17">
@@ -29044,10 +29046,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29064,7 +29066,7 @@
         <v>0.25</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29075,10 +29077,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>159.99</v>
+        <v>199.99</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>240.82</v>
+        <v>198.74</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40269,7 +40271,7 @@
         <v>0.74</v>
       </c>
       <c r="C277" s="16" t="n">
-        <v>0.26</v>
+        <v>0.255</v>
       </c>
       <c r="D277" s="17">
         <f>IF(COUNT(B277:C277)=2,B277+C277,"")</f>
@@ -40344,7 +40346,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 11:27 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -40613,7 +40615,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>126.37</v>
+        <v>170.6</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40627,7 +40629,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>0.73</v>
@@ -40645,7 +40647,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40747,25 +40749,25 @@
         <v>0.74</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>126.37</v>
+        <v>170.6</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>515.86</v>
+        <v>0.86</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>0.73</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>113</v>
+        <v>50317</v>
       </c>
     </row>
     <row r="24">
@@ -40773,28 +40775,28 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>36</v>
+        <v>50000</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>78.34</v>
+        <v>519</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>75.93000000000001</v>
+        <v>186</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25">
@@ -40805,25 +40807,25 @@
         <v>0.71</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>31.95</v>
+        <v>3.95</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.23</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>193</v>
+        <v>1050</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>0.68</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>700</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="26">
@@ -40834,25 +40836,25 @@
         <v>0.7</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>999.87</v>
+        <v>1042.87</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>1000</v>
+        <v>50100</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27">
@@ -40863,19 +40865,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>440</v>
+        <v>355</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>496.44</v>
+        <v>50000</v>
       </c>
       <c r="F27" s="16" t="n">
         <v>0.17</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>500</v>
+        <v>5500</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>0.5600000000000001</v>
@@ -61491,7 +61493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-16 11:27 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -61596,7 +61598,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>2328.661321</v>
+        <v>2374.474851</v>
       </c>
       <c r="C10" s="66" t="n"/>
       <c r="D10" s="66" t="n"/>
@@ -61610,7 +61612,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>43697.0053</v>
+        <v>51934.37622</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61709,10 +61711,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -61727,10 +61729,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>677.130643</v>
+        <v>692.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>166.4959</v>
+        <v>9101.712</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61750,7 +61752,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.14</v>
+        <v>0.132</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -61768,7 +61770,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8166.21073</v>
+        <v>9105.928959999999</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61788,7 +61790,7 @@
         <v>0.03</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -61806,7 +61808,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>135.2288</v>
+        <v>436.6446</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61823,10 +61825,10 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -61844,7 +61846,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8225.5139</v>
+        <v>8955.134899999999</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -61879,10 +61881,10 @@
         <v/>
       </c>
       <c r="H20" s="19" t="n">
-        <v>319.186665</v>
+        <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8232.1909</v>
+        <v>9167.245800000001</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -61899,10 +61901,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.148</v>
+        <v>0.169</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.186</v>
+        <v>0.204</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -61920,7 +61922,7 @@
         <v>270.935421</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>18169.68666</v>
+        <v>13055.71708</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -61937,7 +61939,7 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>0.1</v>
@@ -61958,7 +61960,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>172.2788</v>
+        <v>612.092</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -61974,7 +61976,9 @@
       <c r="B23" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="C23" s="16" t="n"/>
+      <c r="C23" s="16" t="n">
+        <v>0.01</v>
+      </c>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
       </c>
@@ -61994,7 +61998,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>161.2775</v>
+        <v>459.7187</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62032,7 +62036,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>158.50368</v>
+        <v>506.39888</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62049,10 +62053,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62070,7 +62074,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>180.782</v>
+        <v>495.1833</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63535,34 +63539,34 @@
         <v>46281</v>
       </c>
       <c r="B78" s="28" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="C78" s="28" t="n">
-        <v>0.12</v>
+        <v>0.116</v>
       </c>
       <c r="D78" s="28" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="E78" s="28" t="n">
-        <v>0.135</v>
+        <v>0.15</v>
       </c>
       <c r="F78" s="28" t="n">
         <v>0.135</v>
       </c>
       <c r="G78" s="28" t="n">
-        <v>0.167</v>
+        <v>0.1865</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I78" s="28" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="J78" s="28" t="n">
-        <v>0.0525</v>
+        <v>0.0515</v>
       </c>
       <c r="K78" s="28" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="79">
@@ -63621,7 +63625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-16 11:27 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -64834,7 +64838,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-16 11:27 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -65048,7 +65052,7 @@
         <v>0.04</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="E14" s="20">
         <f>IF(ISNUMBER(D14),1-D14,"")</f>
@@ -65081,7 +65085,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.91</v>
@@ -66215,7 +66219,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-16 11:27 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-16 17:24 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-16 17:25 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-16 17:25 UTC</t>
+          <t>2026-09-16 23:25 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-16 17:24 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-16 17:24 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-16 17:25 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -27342,7 +27342,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-16 17:25 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28502,7 +28502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-16 17:25 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28583,7 +28583,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-16 17:25 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 17:24 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28923,7 +28923,7 @@
         <v>24418.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>5318.209801999999</v>
+        <v>5327.649802</v>
       </c>
     </row>
     <row r="13">
@@ -28933,10 +28933,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1048.1636</v>
+        <v>817.0164</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1599.2699</v>
+        <v>1181.3776</v>
       </c>
     </row>
     <row r="14">
@@ -29046,7 +29046,7 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>160</v>
+        <v>221</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>180</v>
@@ -29077,10 +29077,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>199.99</v>
+        <v>254.99</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>198.74</v>
+        <v>167.74</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40346,7 +40346,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 17:24 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -40597,10 +40597,10 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="D17" s="20">
         <f>1-C17</f>
@@ -40615,7 +40615,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>170.6</v>
+        <v>49.77</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40632,7 +40632,7 @@
         <v>0.24</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -40647,7 +40647,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40746,28 +40746,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="16" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>170.6</v>
+        <v>49.77</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.86</v>
+        <v>719.39</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>50317</v>
+        <v>122.58</v>
       </c>
     </row>
     <row r="24">
@@ -40775,28 +40775,28 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>50000</v>
+        <v>232.91</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>519</v>
+        <v>285.86</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.23</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>186</v>
+        <v>246.68</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="25">
@@ -40804,16 +40804,16 @@
         <v>3</v>
       </c>
       <c r="B25" s="16" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>3.95</v>
+        <v>50000</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>221</v>
+        <v>1042.87</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>0.22</v>
@@ -40822,10 +40822,10 @@
         <v>1050</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>5200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26">
@@ -40833,16 +40833,16 @@
         <v>4</v>
       </c>
       <c r="B26" s="16" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>245</v>
+        <v>3.95</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1042.87</v>
+        <v>50000</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>0.21</v>
@@ -40851,10 +40851,10 @@
         <v>50100</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>300</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="27">
@@ -40862,16 +40862,16 @@
         <v>5</v>
       </c>
       <c r="B27" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>355</v>
+        <v>245</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>50000</v>
+        <v>5496.44</v>
       </c>
       <c r="F27" s="16" t="n">
         <v>0.17</v>
@@ -40880,10 +40880,10 @@
         <v>5500</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
@@ -61493,7 +61493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-16 17:24 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -61612,7 +61612,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>51934.37622</v>
+        <v>46175.59766</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61711,10 +61711,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -61732,7 +61732,7 @@
         <v>692.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>9101.712</v>
+        <v>8419.019</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61752,7 +61752,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.132</v>
+        <v>0.14</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -61770,7 +61770,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>9105.928959999999</v>
+        <v>8161.83122</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61790,7 +61790,7 @@
         <v>0.03</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -61808,7 +61808,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>436.6446</v>
+        <v>158.4</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61825,10 +61825,10 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -61846,7 +61846,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8955.134899999999</v>
+        <v>8229.0131</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -61863,7 +61863,7 @@
         <v>4.5</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>0.14</v>
@@ -61884,7 +61884,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>9167.245800000001</v>
+        <v>8240.3907</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -61901,10 +61901,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.169</v>
+        <v>0.101</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.204</v>
+        <v>0.452</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -61922,7 +61922,7 @@
         <v>270.935421</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>13055.71708</v>
+        <v>12241.05724</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -61960,7 +61960,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>612.092</v>
+        <v>196.4876</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -61998,7 +61998,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>459.7187</v>
+        <v>169.602</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62015,7 +62015,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62036,7 +62036,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>506.39888</v>
+        <v>146.35804</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62053,10 +62053,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62074,7 +62074,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>495.1833</v>
+        <v>169.3139</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63539,22 +63539,22 @@
         <v>46281</v>
       </c>
       <c r="B78" s="28" t="n">
-        <v>0.15</v>
+        <v>0.135</v>
       </c>
       <c r="C78" s="28" t="n">
-        <v>0.116</v>
+        <v>0.12</v>
       </c>
       <c r="D78" s="28" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="E78" s="28" t="n">
-        <v>0.15</v>
+        <v>0.135</v>
       </c>
       <c r="F78" s="28" t="n">
-        <v>0.135</v>
+        <v>0.125</v>
       </c>
       <c r="G78" s="28" t="n">
-        <v>0.1865</v>
+        <v>0.1875</v>
       </c>
       <c r="H78" s="28" t="n">
         <v>0.07000000000000001</v>
@@ -63563,10 +63563,10 @@
         <v>0.045</v>
       </c>
       <c r="J78" s="28" t="n">
-        <v>0.0515</v>
+        <v>0.0525</v>
       </c>
       <c r="K78" s="28" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="79">
@@ -63625,7 +63625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-16 17:24 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-16 17:24 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -65085,7 +65085,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.91</v>
@@ -66219,7 +66219,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-16 17:24 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-16 23:25 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-17 11:26 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-17 11:26 UTC</t>
+          <t>2026-09-17 17:24 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-17 11:26 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-17 11:26 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-17 11:26 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-17 11:26 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-17 11:26 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28632,7 +28632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-17 11:26 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28816,7 +28816,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 11:26 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -28969,10 +28969,10 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>24438.333615</v>
+        <v>24448.33361500001</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>5830.299802</v>
+        <v>6010.959802000001</v>
       </c>
     </row>
     <row r="13">
@@ -28982,10 +28982,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>9760.880800000001</v>
+        <v>9760.9877</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2375.7837</v>
+        <v>1750.9777</v>
       </c>
     </row>
     <row r="14">
@@ -28995,10 +28995,10 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -29008,10 +29008,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.035</v>
+        <v>0.045</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-0.035</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="17">
@@ -29084,7 +29084,7 @@
         <v>0.76</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="D19" s="17">
         <f>(B19+C19)/2</f>
@@ -29095,10 +29095,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>166</v>
+        <v>266</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29112,10 +29112,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29126,10 +29126,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>54.77</v>
+        <v>276</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40361,10 +40361,10 @@
         <v>46282</v>
       </c>
       <c r="B278" s="28" t="n">
-        <v>0.775</v>
+        <v>0.785</v>
       </c>
       <c r="C278" s="28" t="n">
-        <v>0.225</v>
+        <v>0.195</v>
       </c>
       <c r="D278" s="29">
         <f>IF(COUNT(B278:C278)=2,B278+C278,"")</f>
@@ -40439,7 +40439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 11:26 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -40693,7 +40693,7 @@
         <v>0.78</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D17" s="20">
         <f>1-C17</f>
@@ -40708,7 +40708,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>0.01</v>
+        <v>16.28</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40722,7 +40722,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>0.76</v>
@@ -40740,7 +40740,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40842,25 +40842,25 @@
         <v>0.78</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>0.01</v>
+        <v>16.28</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>78</v>
+        <v>50001</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>0.76</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -40871,25 +40871,25 @@
         <v>0.77</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>134.27</v>
+        <v>208.6</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>10049</v>
+        <v>26</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>100</v>
+        <v>50000</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>100</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25">
@@ -40900,25 +40900,25 @@
         <v>0.76</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>331.3</v>
+        <v>349.3</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>496.44</v>
+        <v>10000</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -40926,28 +40926,28 @@
         <v>4</v>
       </c>
       <c r="B26" s="16" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>129.95</v>
+        <v>22.59</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>3.56</v>
+        <v>5496.44</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>0.17</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>500</v>
+        <v>5500</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>200</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="27">
@@ -40955,28 +40955,28 @@
         <v>5</v>
       </c>
       <c r="B27" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>100</v>
+        <v>278</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>13.27</v>
+        <v>3.56</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.011</v>
+        <v>0.09</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>44</v>
+        <v>4084</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
@@ -61634,7 +61634,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-17 11:26 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -61739,7 +61739,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>2390.903035</v>
+        <v>2424.077581</v>
       </c>
       <c r="C10" s="66" t="n"/>
       <c r="D10" s="66" t="n"/>
@@ -61753,7 +61753,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>61588.92255</v>
+        <v>53677.77242</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61852,10 +61852,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -61870,10 +61870,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>697.954173</v>
+        <v>717.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8543.7228</v>
+        <v>9403.056399999999</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61893,7 +61893,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -61911,7 +61911,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8377.782219999999</v>
+        <v>8938.53816</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61928,10 +61928,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -61949,7 +61949,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>266.4377</v>
+        <v>422.6686</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61969,7 +61969,7 @@
         <v>0.13</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -61987,7 +61987,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8413.9231</v>
+        <v>8824.5476</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62004,7 +62004,7 @@
         <v>4.5</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>0.14</v>
@@ -62025,7 +62025,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8448.998600000001</v>
+        <v>8969.751700000001</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62042,10 +62042,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.221</v>
+        <v>0.167</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.222</v>
+        <v>0.194</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62060,10 +62060,10 @@
         <v/>
       </c>
       <c r="H21" s="19" t="n">
-        <v>282.363605</v>
+        <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>18356.34289</v>
+        <v>9137.49156</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62080,7 +62080,7 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>0.1</v>
@@ -62101,7 +62101,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>8525.470499999999</v>
+        <v>695.9318</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62117,7 +62117,9 @@
       <c r="B23" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="C23" s="16" t="n"/>
+      <c r="C23" s="16" t="n">
+        <v>0.01</v>
+      </c>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
       </c>
@@ -62137,7 +62139,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>235.3021</v>
+        <v>462.3706</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62175,7 +62177,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>138.4588</v>
+        <v>403.38434</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62192,10 +62194,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.33</v>
+        <v>0.12</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62213,7 +62215,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>248.6901</v>
+        <v>8898.720499999999</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63713,34 +63715,34 @@
         <v>46282</v>
       </c>
       <c r="B79" s="16" t="n">
-        <v>0.095</v>
+        <v>0.135</v>
       </c>
       <c r="C79" s="16" t="n">
-        <v>0.1165</v>
+        <v>0.116</v>
       </c>
       <c r="D79" s="16" t="n">
         <v>0.08500000000000001</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>0.14</v>
+        <v>0.145</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0.2215</v>
+        <v>0.1805</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I79" s="16" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="J79" s="16" t="n">
         <v>0.0525</v>
       </c>
       <c r="K79" s="16" t="n">
-        <v>0.18</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="80">
@@ -63799,7 +63801,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-17 11:26 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -65032,7 +65034,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-17 11:26 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>
@@ -65246,7 +65248,7 @@
         <v>0.04</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="E14" s="20">
         <f>IF(ISNUMBER(D14),1-D14,"")</f>
@@ -65279,7 +65281,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.91</v>
@@ -65351,7 +65353,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>0.8100000000000001</v>
@@ -65390,7 +65392,7 @@
         <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66436,7 +66438,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-17 11:26 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-17 17:24 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-17 17:24 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-17 17:24 UTC</t>
+          <t>2026-09-17 23:22 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-17 17:24 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-17 17:24 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-17 17:24 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-17 17:24 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-17 17:24 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -28632,7 +28632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-17 17:24 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -28816,7 +28816,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 17:24 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -28969,10 +28969,10 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>24448.33361500001</v>
+        <v>24448.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>6010.959802000001</v>
+        <v>6010.959802</v>
       </c>
     </row>
     <row r="13">
@@ -28982,10 +28982,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>9760.9877</v>
+        <v>12002.9403</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1750.9777</v>
+        <v>12523.9508</v>
       </c>
     </row>
     <row r="14">
@@ -29008,10 +29008,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-0.06</v>
+        <v>-0.055</v>
       </c>
     </row>
     <row r="17">
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0.8</v>
@@ -29095,10 +29095,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>266</v>
+        <v>715.22</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>150</v>
+        <v>1189.44</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29112,10 +29112,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29126,10 +29126,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>20</v>
+        <v>538.1900000000001</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40361,10 +40361,10 @@
         <v>46282</v>
       </c>
       <c r="B278" s="28" t="n">
-        <v>0.785</v>
+        <v>0.79</v>
       </c>
       <c r="C278" s="28" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="D278" s="29">
         <f>IF(COUNT(B278:C278)=2,B278+C278,"")</f>
@@ -40439,7 +40439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 17:24 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -40708,7 +40708,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>16.28</v>
+        <v>20112.82</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40722,10 +40722,10 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -40740,7 +40740,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>29</v>
+        <v>50000</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40842,25 +40842,25 @@
         <v>0.78</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>16.28</v>
+        <v>20112.82</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.21</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>50001</v>
+        <v>50100</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>29</v>
+        <v>50000</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>13</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="24">
@@ -40871,25 +40871,25 @@
         <v>0.77</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>208.6</v>
+        <v>406.38</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.2</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>50000</v>
+        <v>100</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>208</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -40900,7 +40900,7 @@
         <v>0.76</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>349.3</v>
+        <v>831.3</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.19</v>
@@ -40909,16 +40909,16 @@
         <v>10000</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G25" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I25" s="19" t="n">
         <v>100</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -40926,10 +40926,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="16" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>22.59</v>
+        <v>150</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.17</v>
@@ -40955,10 +40955,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="16" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>278</v>
+        <v>50000</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>0.14</v>
@@ -40967,10 +40967,10 @@
         <v>3.56</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>4084</v>
+        <v>5870</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>0.71</v>
@@ -61634,7 +61634,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-17 17:24 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -61739,7 +61739,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>2424.077581</v>
+        <v>2439.077581</v>
       </c>
       <c r="C10" s="66" t="n"/>
       <c r="D10" s="66" t="n"/>
@@ -61753,7 +61753,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>53677.77242</v>
+        <v>35416.22605</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61852,7 +61852,7 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.14</v>
@@ -61870,10 +61870,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>717.954173</v>
+        <v>732.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>9403.056399999999</v>
+        <v>8549.888499999999</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -61893,7 +61893,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.132</v>
+        <v>0.127</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -61911,7 +61911,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8938.53816</v>
+        <v>8479.054260000001</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -61928,10 +61928,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -61949,7 +61949,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>422.6686</v>
+        <v>228.1787</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -61966,10 +61966,10 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -61987,7 +61987,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8824.5476</v>
+        <v>8435.402599999999</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62025,7 +62025,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8969.751700000001</v>
+        <v>8425.918900000001</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62042,10 +62042,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.167</v>
+        <v>0.101</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.194</v>
+        <v>0.3</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62063,7 +62063,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>9137.49156</v>
+        <v>268.39263</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62101,7 +62101,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>695.9318</v>
+        <v>308.2093</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62139,7 +62139,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>462.3706</v>
+        <v>253.6384</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62156,7 +62156,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62177,7 +62177,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>403.38434</v>
+        <v>204.99923</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62194,10 +62194,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62215,7 +62215,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>8898.720499999999</v>
+        <v>299.8491</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63715,22 +63715,22 @@
         <v>46282</v>
       </c>
       <c r="B79" s="16" t="n">
-        <v>0.135</v>
+        <v>0.12</v>
       </c>
       <c r="C79" s="16" t="n">
-        <v>0.116</v>
+        <v>0.1135</v>
       </c>
       <c r="D79" s="16" t="n">
         <v>0.08500000000000001</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="F79" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0.1805</v>
+        <v>0.3025</v>
       </c>
       <c r="H79" s="16" t="n">
         <v>0.07000000000000001</v>
@@ -63739,10 +63739,10 @@
         <v>0.045</v>
       </c>
       <c r="J79" s="16" t="n">
-        <v>0.0525</v>
+        <v>0.0535</v>
       </c>
       <c r="K79" s="16" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="80">
@@ -63801,7 +63801,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-17 17:24 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -65034,7 +65034,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-17 17:24 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>
@@ -65317,7 +65317,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.65</v>
@@ -65353,7 +65353,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>0.8100000000000001</v>
@@ -65392,7 +65392,7 @@
         <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66438,7 +66438,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-17 17:24 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-17 23:22 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-18 11:25 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-18 11:25 UTC</t>
+          <t>2026-09-18 19:35 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-18 11:25 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-18 11:25 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-18 11:25 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -27440,7 +27440,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-18 11:25 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -28600,7 +28600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-18 11:25 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -28681,7 +28681,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-18 11:25 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -28865,7 +28865,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-18 11:25 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -29021,7 +29021,7 @@
         <v>24448.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>6010.959802000002</v>
+        <v>6070.959801999999</v>
       </c>
     </row>
     <row r="13">
@@ -29031,10 +29031,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10197.1573</v>
+        <v>9837.8374</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>11217.4888</v>
+        <v>10586.9709</v>
       </c>
     </row>
     <row r="14">
@@ -29047,7 +29047,7 @@
         <v>0.8</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="15">
@@ -29057,10 +29057,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-0.045</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="17">
@@ -29130,7 +29130,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0.8</v>
@@ -29144,10 +29144,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>102</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29161,10 +29161,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29175,10 +29175,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40454,10 +40454,10 @@
         <v>46283</v>
       </c>
       <c r="B279" s="16" t="n">
-        <v>0.79</v>
+        <v>0.795</v>
       </c>
       <c r="C279" s="16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="D279" s="17">
         <f>IF(COUNT(B279:C279)=2,B279+C279,"")</f>
@@ -40532,7 +40532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-18 11:25 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>281.01</v>
+        <v>29.93</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40815,10 +40815,10 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -40833,7 +40833,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>600</v>
+        <v>1.36</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -40935,25 +40935,25 @@
         <v>0.79</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>281.01</v>
+        <v>29.93</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>10505</v>
+        <v>10518</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>600</v>
+        <v>1.36</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>222</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -40964,25 +40964,25 @@
         <v>0.78</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>20073.92</v>
+        <v>239</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.18</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>88.51000000000001</v>
+        <v>279</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>73</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25">
@@ -40993,25 +40993,25 @@
         <v>0.77</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>726</v>
+        <v>50946.26</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>496.44</v>
+        <v>50496.44</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>637</v>
+        <v>500</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>600</v>
+        <v>50550</v>
       </c>
     </row>
     <row r="26">
@@ -41022,7 +41022,7 @@
         <v>0.76</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>331.3</v>
+        <v>431.3</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.14</v>
@@ -41031,16 +41031,16 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>399</v>
+        <v>50590</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27">
@@ -41048,28 +41048,28 @@
         <v>5</v>
       </c>
       <c r="B27" s="16" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>5870</v>
+        <v>10870</v>
       </c>
       <c r="F27" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>5870</v>
+        <v>10870</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>516</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
@@ -61775,7 +61775,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-18 11:25 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -61894,7 +61894,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>46274.25693</v>
+        <v>70151.11087</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61993,10 +61993,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -62011,10 +62011,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>751.954173</v>
+        <v>751.9541730000001</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8927.5821</v>
+        <v>8825.900100000001</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62034,7 +62034,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62052,7 +62052,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8772.134120000001</v>
+        <v>8646.115659999999</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62069,10 +62069,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -62090,7 +62090,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>513.643</v>
+        <v>228.4396</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62107,10 +62107,10 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -62128,7 +62128,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8731.188399999999</v>
+        <v>8493.142900000001</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62166,7 +62166,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8847.558499999999</v>
+        <v>8505.497499999999</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62183,10 +62183,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.142</v>
+        <v>0.163</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.223</v>
+        <v>0.21</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62204,7 +62204,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>481.38226</v>
+        <v>18686.9989</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62224,7 +62224,7 @@
         <v>0.05</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E22" s="17">
         <f>IF(COUNT(C22:D22)=2,(C22+D22)/2,"")</f>
@@ -62242,7 +62242,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>8558.9776</v>
+        <v>8316.623900000001</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62258,9 +62258,7 @@
       <c r="B23" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="C23" s="16" t="n"/>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
       </c>
@@ -62280,7 +62278,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>447.5847</v>
+        <v>117.4599</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62297,7 +62295,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62318,7 +62316,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>355.56468</v>
+        <v>113.69957</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62335,10 +62333,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62356,7 +62354,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>8668.1844</v>
+        <v>8489.522300000001</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63891,31 +63889,31 @@
         <v>46283</v>
       </c>
       <c r="B80" s="28" t="n">
-        <v>0.155</v>
+        <v>0.11</v>
       </c>
       <c r="C80" s="28" t="n">
-        <v>0.1175</v>
+        <v>0.117</v>
       </c>
       <c r="D80" s="28" t="n">
-        <v>0.065</v>
+        <v>0.055</v>
       </c>
       <c r="E80" s="28" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="F80" s="28" t="n">
         <v>0.135</v>
       </c>
       <c r="G80" s="28" t="n">
-        <v>0.1825</v>
+        <v>0.1865</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="I80" s="28" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="J80" s="28" t="n">
-        <v>0.053</v>
+        <v>0.0515</v>
       </c>
       <c r="K80" s="28" t="n">
         <v>0.105</v>
@@ -63977,7 +63975,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-18 11:25 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -65230,7 +65228,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-18 11:25 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>
@@ -65477,10 +65475,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="E15" s="20">
         <f>IF(ISNUMBER(D15),1-D15,"")</f>
@@ -65549,7 +65547,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>0.8100000000000001</v>
@@ -65588,7 +65586,7 @@
         <v>0.27</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66658,7 +66656,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-18 11:25 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-18 19:35 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -538,12 +538,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$269</f>
+              <f>'Venue Comparison'!$L$15:$L$270</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$B$15:$B$269</f>
+              <f>'Venue Comparison'!$B$15:$B$270</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -574,12 +574,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$269</f>
+              <f>'Venue Comparison'!$L$15:$L$270</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$C$15:$C$269</f>
+              <f>'Venue Comparison'!$C$15:$C$270</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -610,12 +610,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$269</f>
+              <f>'Venue Comparison'!$L$15:$L$270</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$K$15:$K$269</f>
+              <f>'Venue Comparison'!$K$15:$K$270</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1396,12 +1396,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$269</f>
+              <f>'Venue Comparison'!$L$15:$L$270</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$D$15:$D$269</f>
+              <f>'Venue Comparison'!$D$15:$D$270</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2101,12 +2101,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$279</f>
+              <f>'Polymarket'!$K$25:$K$280</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$D$25:$D$279</f>
+              <f>'Polymarket'!$D$25:$D$280</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2325,12 +2325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$279</f>
+              <f>'Polymarket'!$K$25:$K$280</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$B$25:$B$279</f>
+              <f>'Polymarket'!$B$25:$B$280</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2361,12 +2361,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$279</f>
+              <f>'Polymarket'!$K$25:$K$280</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$C$25:$C$279</f>
+              <f>'Polymarket'!$C$25:$C$280</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-18 19:35 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="B48" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-0,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-0,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="D48" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-0,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-0,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="B49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-7,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-7,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
       <c r="C49" s="18">
@@ -4813,7 +4813,7 @@
         <v/>
       </c>
       <c r="D49" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-7,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-7,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="B50" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-30,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-30,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
       <c r="C50" s="18">
@@ -4832,7 +4832,7 @@
         <v/>
       </c>
       <c r="D50" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-30,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-30,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-90,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH(Polymarket!$A$279-90,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
       <c r="C51" s="18">
@@ -4851,7 +4851,7 @@
         <v/>
       </c>
       <c r="D51" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-90,Polymarket!$A$25:$A$279,1))=0,"",INDEX(Polymarket!$A$25:$A$279,MATCH(Polymarket!$A$279-90,Polymarket!$A$25:$A$279,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="B52" s="20">
-        <f>MAX(Polymarket!B25:B279)</f>
+        <f>MAX(Polymarket!B25:B280)</f>
         <v/>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B53" s="20">
-        <f>MIN(Polymarket!B25:B279)</f>
+        <f>MIN(Polymarket!B25:B280)</f>
         <v/>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-18 19:35 UTC</t>
+          <t>2026-09-19 01:10 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="B69" s="59">
-        <f>TEXT(Polymarket!A25,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Polymarket!A279,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Polymarket!A25:A279)&amp;" days)"</f>
+        <f>TEXT(Polymarket!A25,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Polymarket!A280,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Polymarket!A25:A280)&amp;" days)"</f>
         <v/>
       </c>
       <c r="C69" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-18 19:35 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A36,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A36,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H36" s="18">
@@ -5660,7 +5660,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A37,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A37,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H37" s="31">
@@ -5693,7 +5693,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A38,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A38,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H38" s="18">
@@ -5726,7 +5726,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A39,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A39,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H39" s="31">
@@ -5759,7 +5759,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A40,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A40,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H40" s="18">
@@ -5792,7 +5792,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A41,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A41,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H41" s="31">
@@ -5825,7 +5825,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A42,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A42,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H42" s="18">
@@ -5858,7 +5858,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A43,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A43,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H43" s="31">
@@ -5891,7 +5891,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A44,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A44,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H44" s="18">
@@ -5924,7 +5924,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A45,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A45,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H45" s="31">
@@ -5957,7 +5957,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A46,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A46,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H46" s="18">
@@ -5990,7 +5990,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A47,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A47,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H47" s="31">
@@ -6023,7 +6023,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A48,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A48,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H48" s="18">
@@ -6056,7 +6056,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A49,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A49,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H49" s="31">
@@ -6089,7 +6089,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A50,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A50,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H50" s="18">
@@ -6122,7 +6122,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A51,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A51,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H51" s="31">
@@ -6155,7 +6155,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A52,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A52,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H52" s="18">
@@ -6188,7 +6188,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A53,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A53,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H53" s="31">
@@ -6221,7 +6221,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A54,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A54,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H54" s="18">
@@ -6254,7 +6254,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A55,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A55,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H55" s="31">
@@ -6287,7 +6287,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A56,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A56,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H56" s="18">
@@ -6320,7 +6320,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A57,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A57,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H57" s="31">
@@ -6353,7 +6353,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A58,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A58,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H58" s="18">
@@ -6386,7 +6386,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A59,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A59,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H59" s="31">
@@ -6419,7 +6419,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A60,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A60,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H60" s="18">
@@ -6452,7 +6452,7 @@
         <v>0.499</v>
       </c>
       <c r="G61" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A61,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A61,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H61" s="31">
@@ -6485,7 +6485,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A62,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A62,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H62" s="18">
@@ -6518,7 +6518,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A63,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A63,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H63" s="31">
@@ -6551,7 +6551,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A64,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A64,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H64" s="18">
@@ -6584,7 +6584,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A65,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A65,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H65" s="31">
@@ -6617,7 +6617,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A66,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A66,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H66" s="18">
@@ -6650,7 +6650,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A67,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A67,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H67" s="31">
@@ -6683,7 +6683,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A68,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A68,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H68" s="18">
@@ -6716,7 +6716,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A69,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A69,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H69" s="31">
@@ -6749,7 +6749,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A70,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A70,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H70" s="18">
@@ -6782,7 +6782,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A71,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A71,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H71" s="31">
@@ -6815,7 +6815,7 @@
         <v>0.499</v>
       </c>
       <c r="G72" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A72,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A72,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H72" s="18">
@@ -6848,7 +6848,7 @@
         <v>0.499</v>
       </c>
       <c r="G73" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A73,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A73,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H73" s="31">
@@ -6881,7 +6881,7 @@
         <v>0.499</v>
       </c>
       <c r="G74" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A74,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A74,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H74" s="18">
@@ -6914,7 +6914,7 @@
         <v>0.499</v>
       </c>
       <c r="G75" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A75,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A75,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H75" s="31">
@@ -6947,7 +6947,7 @@
         <v>0.499</v>
       </c>
       <c r="G76" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A76,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A76,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H76" s="18">
@@ -6980,7 +6980,7 @@
         <v>0.499</v>
       </c>
       <c r="G77" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A77,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A77,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H77" s="31">
@@ -7013,7 +7013,7 @@
         <v>0.499</v>
       </c>
       <c r="G78" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A78,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A78,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H78" s="18">
@@ -7046,7 +7046,7 @@
         <v>0.499</v>
       </c>
       <c r="G79" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A79,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A79,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H79" s="31">
@@ -7079,7 +7079,7 @@
         <v>0.499</v>
       </c>
       <c r="G80" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A80,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A80,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H80" s="18">
@@ -7112,7 +7112,7 @@
         <v>0.499</v>
       </c>
       <c r="G81" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A81,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A81,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H81" s="31">
@@ -7145,7 +7145,7 @@
         <v>0.499</v>
       </c>
       <c r="G82" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A82,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A82,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H82" s="18">
@@ -7178,7 +7178,7 @@
         <v>0.499</v>
       </c>
       <c r="G83" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A83,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A83,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H83" s="31">
@@ -7211,7 +7211,7 @@
         <v>0.499</v>
       </c>
       <c r="G84" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A84,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A84,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H84" s="18">
@@ -7244,7 +7244,7 @@
         <v>0.499</v>
       </c>
       <c r="G85" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A85,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A85,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H85" s="31">
@@ -7277,7 +7277,7 @@
         <v>0.499</v>
       </c>
       <c r="G86" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A86,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A86,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H86" s="18">
@@ -7310,7 +7310,7 @@
         <v>0.499</v>
       </c>
       <c r="G87" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A87,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A87,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H87" s="31">
@@ -7343,7 +7343,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A88,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A88,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H88" s="18">
@@ -7376,7 +7376,7 @@
         <v>0.499</v>
       </c>
       <c r="G89" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A89,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A89,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H89" s="31">
@@ -7409,7 +7409,7 @@
         <v>0.499</v>
       </c>
       <c r="G90" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A90,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A90,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H90" s="18">
@@ -7442,7 +7442,7 @@
         <v>0.5</v>
       </c>
       <c r="G91" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A91,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A91,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H91" s="31">
@@ -7475,7 +7475,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A92,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A92,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H92" s="18">
@@ -7508,7 +7508,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A93,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A93,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H93" s="31">
@@ -7541,7 +7541,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A94,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A94,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H94" s="18">
@@ -7574,7 +7574,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A95,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A95,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H95" s="31">
@@ -7607,7 +7607,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A96,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A96,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H96" s="18">
@@ -7640,7 +7640,7 @@
         <v>0.499</v>
       </c>
       <c r="G97" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A97,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A97,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H97" s="31">
@@ -7673,7 +7673,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A98,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A98,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H98" s="18">
@@ -7706,7 +7706,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A99,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A99,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H99" s="31">
@@ -7739,7 +7739,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A100,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A100,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H100" s="18">
@@ -7772,7 +7772,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A101,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A101,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H101" s="31">
@@ -7805,7 +7805,7 @@
         <v>0.5</v>
       </c>
       <c r="G102" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A102,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A102,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H102" s="18">
@@ -7838,7 +7838,7 @@
         <v>0.5</v>
       </c>
       <c r="G103" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A103,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A103,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H103" s="31">
@@ -7871,7 +7871,7 @@
         <v>0.5</v>
       </c>
       <c r="G104" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A104,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A104,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H104" s="18">
@@ -7904,7 +7904,7 @@
         <v>0.5</v>
       </c>
       <c r="G105" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A105,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A105,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H105" s="31">
@@ -7937,7 +7937,7 @@
         <v>0.5</v>
       </c>
       <c r="G106" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A106,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A106,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H106" s="18">
@@ -7970,7 +7970,7 @@
         <v>0.5</v>
       </c>
       <c r="G107" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A107,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A107,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H107" s="31">
@@ -8003,7 +8003,7 @@
         <v>0.5</v>
       </c>
       <c r="G108" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A108,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A108,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H108" s="18">
@@ -8036,7 +8036,7 @@
         <v>0.5</v>
       </c>
       <c r="G109" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A109,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A109,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H109" s="31">
@@ -8069,7 +8069,7 @@
         <v>0.5</v>
       </c>
       <c r="G110" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A110,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A110,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H110" s="18">
@@ -8102,7 +8102,7 @@
         <v>0.5</v>
       </c>
       <c r="G111" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A111,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A111,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H111" s="31">
@@ -8135,7 +8135,7 @@
         <v>0.5</v>
       </c>
       <c r="G112" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A112,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A112,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H112" s="18">
@@ -8168,7 +8168,7 @@
         <v>0.5</v>
       </c>
       <c r="G113" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A113,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A113,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H113" s="31">
@@ -8201,7 +8201,7 @@
         <v>0.5</v>
       </c>
       <c r="G114" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A114,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A114,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H114" s="18">
@@ -8234,7 +8234,7 @@
         <v>0.5</v>
       </c>
       <c r="G115" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A115,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A115,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H115" s="31">
@@ -8267,7 +8267,7 @@
         <v>0.5</v>
       </c>
       <c r="G116" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A116,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A116,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H116" s="18">
@@ -8300,7 +8300,7 @@
         <v>0.499</v>
       </c>
       <c r="G117" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A117,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A117,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H117" s="31">
@@ -8333,7 +8333,7 @@
         <v>0.499</v>
       </c>
       <c r="G118" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A118,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A118,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H118" s="18">
@@ -8366,7 +8366,7 @@
         <v>0.499</v>
       </c>
       <c r="G119" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A119,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A119,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H119" s="31">
@@ -8399,7 +8399,7 @@
         <v>0.499</v>
       </c>
       <c r="G120" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A120,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A120,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H120" s="18">
@@ -8432,7 +8432,7 @@
         <v>0.499</v>
       </c>
       <c r="G121" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A121,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A121,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H121" s="31">
@@ -8465,7 +8465,7 @@
         <v>0.499</v>
       </c>
       <c r="G122" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A122,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A122,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H122" s="18">
@@ -8498,7 +8498,7 @@
         <v>0.499</v>
       </c>
       <c r="G123" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A123,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A123,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H123" s="31">
@@ -8531,7 +8531,7 @@
         <v>0.499</v>
       </c>
       <c r="G124" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A124,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A124,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H124" s="18">
@@ -8564,7 +8564,7 @@
         <v>0.499</v>
       </c>
       <c r="G125" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A125,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A125,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H125" s="31">
@@ -8597,7 +8597,7 @@
         <v>0.499</v>
       </c>
       <c r="G126" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A126,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A126,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H126" s="18">
@@ -8630,7 +8630,7 @@
         <v>0.499</v>
       </c>
       <c r="G127" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A127,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A127,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H127" s="31">
@@ -8663,7 +8663,7 @@
         <v>0.499</v>
       </c>
       <c r="G128" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A128,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A128,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H128" s="18">
@@ -8696,7 +8696,7 @@
         <v>0.499</v>
       </c>
       <c r="G129" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A129,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A129,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H129" s="31">
@@ -8729,7 +8729,7 @@
         <v>0.499</v>
       </c>
       <c r="G130" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A130,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A130,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H130" s="18">
@@ -8762,7 +8762,7 @@
         <v>0.499</v>
       </c>
       <c r="G131" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A131,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A131,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H131" s="31">
@@ -8795,7 +8795,7 @@
         <v>0.5</v>
       </c>
       <c r="G132" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A132,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A132,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H132" s="18">
@@ -8828,7 +8828,7 @@
         <v>0.499</v>
       </c>
       <c r="G133" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A133,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A133,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H133" s="31">
@@ -8861,7 +8861,7 @@
         <v>0.5</v>
       </c>
       <c r="G134" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A134,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A134,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H134" s="18">
@@ -8894,7 +8894,7 @@
         <v>0.499</v>
       </c>
       <c r="G135" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A135,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A135,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H135" s="31">
@@ -8927,7 +8927,7 @@
         <v>0.499</v>
       </c>
       <c r="G136" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A136,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A136,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H136" s="18">
@@ -8960,7 +8960,7 @@
         <v>0.5</v>
       </c>
       <c r="G137" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A137,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A137,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H137" s="31">
@@ -8993,7 +8993,7 @@
         <v>0.498</v>
       </c>
       <c r="G138" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A138,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A138,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H138" s="18">
@@ -9026,7 +9026,7 @@
         <v>0.498</v>
       </c>
       <c r="G139" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A139,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A139,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H139" s="31">
@@ -9059,7 +9059,7 @@
         <v>0.498</v>
       </c>
       <c r="G140" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A140,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A140,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H140" s="18">
@@ -9092,7 +9092,7 @@
         <v>0.498</v>
       </c>
       <c r="G141" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A141,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A141,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H141" s="31">
@@ -9125,7 +9125,7 @@
         <v>0.498</v>
       </c>
       <c r="G142" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A142,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A142,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H142" s="18">
@@ -9158,7 +9158,7 @@
         <v>0.498</v>
       </c>
       <c r="G143" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A143,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A143,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H143" s="31">
@@ -9191,7 +9191,7 @@
         <v>0.498</v>
       </c>
       <c r="G144" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A144,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A144,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H144" s="18">
@@ -9224,7 +9224,7 @@
         <v>0.498</v>
       </c>
       <c r="G145" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A145,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A145,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H145" s="31">
@@ -9257,7 +9257,7 @@
         <v>0.498</v>
       </c>
       <c r="G146" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A146,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A146,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H146" s="18">
@@ -9290,7 +9290,7 @@
         <v>0.498</v>
       </c>
       <c r="G147" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A147,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A147,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H147" s="31">
@@ -9323,7 +9323,7 @@
         <v>0.498</v>
       </c>
       <c r="G148" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A148,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A148,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H148" s="18">
@@ -9356,7 +9356,7 @@
         <v>0.498</v>
       </c>
       <c r="G149" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A149,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A149,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H149" s="31">
@@ -9389,7 +9389,7 @@
         <v>0.498</v>
       </c>
       <c r="G150" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A150,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A150,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H150" s="18">
@@ -9422,7 +9422,7 @@
         <v>0.498</v>
       </c>
       <c r="G151" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A151,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A151,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H151" s="31">
@@ -9455,7 +9455,7 @@
         <v>0.498</v>
       </c>
       <c r="G152" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A152,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A152,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H152" s="18">
@@ -9488,7 +9488,7 @@
         <v>0.498</v>
       </c>
       <c r="G153" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A153,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A153,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H153" s="31">
@@ -9521,7 +9521,7 @@
         <v>0.498</v>
       </c>
       <c r="G154" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A154,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A154,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H154" s="18">
@@ -9554,7 +9554,7 @@
         <v>0.498</v>
       </c>
       <c r="G155" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A155,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A155,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H155" s="31">
@@ -9587,7 +9587,7 @@
         <v>0.498</v>
       </c>
       <c r="G156" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A156,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A156,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H156" s="18">
@@ -9620,7 +9620,7 @@
         <v>0.498</v>
       </c>
       <c r="G157" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A157,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A157,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H157" s="31">
@@ -9653,7 +9653,7 @@
         <v>0.498</v>
       </c>
       <c r="G158" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A158,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A158,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H158" s="18">
@@ -9686,7 +9686,7 @@
         <v>0.498</v>
       </c>
       <c r="G159" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A159,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A159,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H159" s="31">
@@ -9719,7 +9719,7 @@
         <v>0.498</v>
       </c>
       <c r="G160" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A160,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A160,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H160" s="18">
@@ -9752,7 +9752,7 @@
         <v>0.498</v>
       </c>
       <c r="G161" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A161,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A161,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H161" s="31">
@@ -9785,7 +9785,7 @@
         <v>0.498</v>
       </c>
       <c r="G162" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A162,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A162,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H162" s="18">
@@ -9818,7 +9818,7 @@
         <v>0.498</v>
       </c>
       <c r="G163" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A163,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A163,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H163" s="31">
@@ -9851,7 +9851,7 @@
         <v>0.498</v>
       </c>
       <c r="G164" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A164,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A164,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H164" s="18">
@@ -9884,7 +9884,7 @@
         <v>0.498</v>
       </c>
       <c r="G165" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A165,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A165,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H165" s="31">
@@ -9917,7 +9917,7 @@
         <v>0.498</v>
       </c>
       <c r="G166" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A166,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A166,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H166" s="18">
@@ -9950,7 +9950,7 @@
         <v>0.498</v>
       </c>
       <c r="G167" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A167,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A167,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H167" s="31">
@@ -9983,7 +9983,7 @@
         <v>0.498</v>
       </c>
       <c r="G168" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A168,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A168,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H168" s="18">
@@ -10016,7 +10016,7 @@
         <v>0.498</v>
       </c>
       <c r="G169" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A169,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A169,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H169" s="31">
@@ -10049,7 +10049,7 @@
         <v>0.498</v>
       </c>
       <c r="G170" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A170,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A170,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H170" s="18">
@@ -10082,7 +10082,7 @@
         <v>0.498</v>
       </c>
       <c r="G171" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A171,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A171,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H171" s="31">
@@ -10115,7 +10115,7 @@
         <v>0.498</v>
       </c>
       <c r="G172" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A172,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A172,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H172" s="18">
@@ -10148,7 +10148,7 @@
         <v>0.498</v>
       </c>
       <c r="G173" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A173,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A173,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H173" s="31">
@@ -10181,7 +10181,7 @@
         <v>0.498</v>
       </c>
       <c r="G174" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A174,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A174,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H174" s="18">
@@ -10214,7 +10214,7 @@
         <v>0.498</v>
       </c>
       <c r="G175" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A175,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A175,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H175" s="31">
@@ -10247,7 +10247,7 @@
         <v>0.498</v>
       </c>
       <c r="G176" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A176,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A176,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H176" s="18">
@@ -10280,7 +10280,7 @@
         <v>0.498</v>
       </c>
       <c r="G177" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A177,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A177,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H177" s="31">
@@ -10313,7 +10313,7 @@
         <v>0.498</v>
       </c>
       <c r="G178" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A178,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A178,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H178" s="18">
@@ -10346,7 +10346,7 @@
         <v>0.498</v>
       </c>
       <c r="G179" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A179,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A179,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H179" s="31">
@@ -10379,7 +10379,7 @@
         <v>0.498</v>
       </c>
       <c r="G180" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A180,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A180,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H180" s="18">
@@ -10412,7 +10412,7 @@
         <v>0.498</v>
       </c>
       <c r="G181" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A181,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A181,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H181" s="31">
@@ -10445,7 +10445,7 @@
         <v>0.498</v>
       </c>
       <c r="G182" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A182,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A182,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H182" s="18">
@@ -10478,7 +10478,7 @@
         <v>0.498</v>
       </c>
       <c r="G183" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A183,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A183,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H183" s="31">
@@ -10511,7 +10511,7 @@
         <v>0.498</v>
       </c>
       <c r="G184" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A184,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A184,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H184" s="18">
@@ -10544,7 +10544,7 @@
         <v>0.498</v>
       </c>
       <c r="G185" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A185,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A185,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H185" s="31">
@@ -10577,7 +10577,7 @@
         <v>0.498</v>
       </c>
       <c r="G186" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A186,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A186,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H186" s="18">
@@ -10610,7 +10610,7 @@
         <v>0.498</v>
       </c>
       <c r="G187" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A187,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A187,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H187" s="31">
@@ -10643,7 +10643,7 @@
         <v>0.498</v>
       </c>
       <c r="G188" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A188,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A188,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H188" s="18">
@@ -10676,7 +10676,7 @@
         <v>0.4970000000000001</v>
       </c>
       <c r="G189" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A189,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A189,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H189" s="31">
@@ -10709,7 +10709,7 @@
         <v>0.498</v>
       </c>
       <c r="G190" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A190,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A190,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H190" s="18">
@@ -10742,7 +10742,7 @@
         <v>0.498</v>
       </c>
       <c r="G191" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A191,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A191,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H191" s="31">
@@ -10775,7 +10775,7 @@
         <v>0.498</v>
       </c>
       <c r="G192" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A192,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A192,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H192" s="18">
@@ -10808,7 +10808,7 @@
         <v>0.498</v>
       </c>
       <c r="G193" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A193,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A193,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H193" s="31">
@@ -10841,7 +10841,7 @@
         <v>0.498</v>
       </c>
       <c r="G194" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A194,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A194,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H194" s="18">
@@ -10874,7 +10874,7 @@
         <v>0.498</v>
       </c>
       <c r="G195" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A195,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A195,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H195" s="31">
@@ -10907,7 +10907,7 @@
         <v>0.498</v>
       </c>
       <c r="G196" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A196,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A196,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H196" s="18">
@@ -10940,7 +10940,7 @@
         <v>0.498</v>
       </c>
       <c r="G197" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A197,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A197,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H197" s="31">
@@ -10973,7 +10973,7 @@
         <v>0.498</v>
       </c>
       <c r="G198" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A198,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A198,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H198" s="18">
@@ -11006,7 +11006,7 @@
         <v>0.498</v>
       </c>
       <c r="G199" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A199,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A199,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H199" s="31">
@@ -11039,7 +11039,7 @@
         <v>0.498</v>
       </c>
       <c r="G200" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A200,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A200,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H200" s="18">
@@ -11072,7 +11072,7 @@
         <v>0.498</v>
       </c>
       <c r="G201" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A201,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A201,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H201" s="31">
@@ -11105,7 +11105,7 @@
         <v>0.498</v>
       </c>
       <c r="G202" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A202,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A202,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H202" s="18">
@@ -11138,7 +11138,7 @@
         <v>0.498</v>
       </c>
       <c r="G203" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A203,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A203,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H203" s="31">
@@ -11171,7 +11171,7 @@
         <v>0.498</v>
       </c>
       <c r="G204" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A204,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A204,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H204" s="18">
@@ -11204,7 +11204,7 @@
         <v>0.498</v>
       </c>
       <c r="G205" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A205,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A205,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H205" s="31">
@@ -11237,7 +11237,7 @@
         <v>0.498</v>
       </c>
       <c r="G206" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A206,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A206,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H206" s="18">
@@ -11270,7 +11270,7 @@
         <v>0.498</v>
       </c>
       <c r="G207" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A207,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A207,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H207" s="31">
@@ -11303,7 +11303,7 @@
         <v>0.498</v>
       </c>
       <c r="G208" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A208,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A208,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H208" s="18">
@@ -11336,7 +11336,7 @@
         <v>0.498</v>
       </c>
       <c r="G209" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A209,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A209,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H209" s="31">
@@ -11369,7 +11369,7 @@
         <v>0.498</v>
       </c>
       <c r="G210" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A210,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A210,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H210" s="18">
@@ -11402,7 +11402,7 @@
         <v>0.498</v>
       </c>
       <c r="G211" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A211,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A211,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H211" s="31">
@@ -11435,7 +11435,7 @@
         <v>0.498</v>
       </c>
       <c r="G212" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A212,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A212,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H212" s="18">
@@ -11468,7 +11468,7 @@
         <v>0.498</v>
       </c>
       <c r="G213" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A213,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A213,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H213" s="31">
@@ -11501,7 +11501,7 @@
         <v>0.498</v>
       </c>
       <c r="G214" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A214,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A214,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H214" s="18">
@@ -11534,7 +11534,7 @@
         <v>0.499</v>
       </c>
       <c r="G215" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A215,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A215,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H215" s="31">
@@ -11567,7 +11567,7 @@
         <v>0.498</v>
       </c>
       <c r="G216" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A216,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A216,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H216" s="18">
@@ -11600,7 +11600,7 @@
         <v>0.498</v>
       </c>
       <c r="G217" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A217,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A217,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H217" s="31">
@@ -11633,7 +11633,7 @@
         <v>0.498</v>
       </c>
       <c r="G218" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A218,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A218,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H218" s="18">
@@ -11666,7 +11666,7 @@
         <v>0.498</v>
       </c>
       <c r="G219" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A219,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A219,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H219" s="31">
@@ -11699,7 +11699,7 @@
         <v>0.498</v>
       </c>
       <c r="G220" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A220,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A220,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H220" s="18">
@@ -11732,7 +11732,7 @@
         <v>0.498</v>
       </c>
       <c r="G221" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A221,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A221,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H221" s="31">
@@ -11765,7 +11765,7 @@
         <v>0.498</v>
       </c>
       <c r="G222" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A222,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A222,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H222" s="18">
@@ -11798,7 +11798,7 @@
         <v>0.499</v>
       </c>
       <c r="G223" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A223,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A223,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H223" s="31">
@@ -11831,7 +11831,7 @@
         <v>0.498</v>
       </c>
       <c r="G224" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A224,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A224,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H224" s="18">
@@ -11864,7 +11864,7 @@
         <v>0.498</v>
       </c>
       <c r="G225" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A225,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A225,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H225" s="31">
@@ -11897,7 +11897,7 @@
         <v>0.498</v>
       </c>
       <c r="G226" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A226,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A226,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H226" s="18">
@@ -11930,7 +11930,7 @@
         <v>0.499</v>
       </c>
       <c r="G227" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A227,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A227,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H227" s="31">
@@ -11963,7 +11963,7 @@
         <v>0.498</v>
       </c>
       <c r="G228" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A228,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A228,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H228" s="18">
@@ -11996,7 +11996,7 @@
         <v>0.498</v>
       </c>
       <c r="G229" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A229,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A229,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H229" s="31">
@@ -12029,7 +12029,7 @@
         <v>0.498</v>
       </c>
       <c r="G230" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A230,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A230,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H230" s="18">
@@ -12062,7 +12062,7 @@
         <v>0.498</v>
       </c>
       <c r="G231" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A231,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A231,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H231" s="31">
@@ -12095,7 +12095,7 @@
         <v>0.498</v>
       </c>
       <c r="G232" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A232,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A232,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H232" s="18">
@@ -12128,7 +12128,7 @@
         <v>0.498</v>
       </c>
       <c r="G233" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A233,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A233,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H233" s="31">
@@ -12161,7 +12161,7 @@
         <v>0.498</v>
       </c>
       <c r="G234" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A234,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A234,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H234" s="18">
@@ -12194,7 +12194,7 @@
         <v>0.499</v>
       </c>
       <c r="G235" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A235,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A235,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H235" s="31">
@@ -12227,7 +12227,7 @@
         <v>0.498</v>
       </c>
       <c r="G236" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A236,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A236,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H236" s="18">
@@ -12260,7 +12260,7 @@
         <v>0.498</v>
       </c>
       <c r="G237" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A237,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A237,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H237" s="31">
@@ -12293,7 +12293,7 @@
         <v>0.498</v>
       </c>
       <c r="G238" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A238,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A238,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H238" s="18">
@@ -12326,7 +12326,7 @@
         <v>0.498</v>
       </c>
       <c r="G239" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A239,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A239,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H239" s="31">
@@ -12359,7 +12359,7 @@
         <v>0.498</v>
       </c>
       <c r="G240" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A240,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A240,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H240" s="18">
@@ -12392,7 +12392,7 @@
         <v>0.498</v>
       </c>
       <c r="G241" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A241,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A241,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H241" s="31">
@@ -12425,7 +12425,7 @@
         <v>0.498</v>
       </c>
       <c r="G242" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A242,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A242,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H242" s="18">
@@ -12458,7 +12458,7 @@
         <v>0.498</v>
       </c>
       <c r="G243" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A243,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A243,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H243" s="31">
@@ -12491,7 +12491,7 @@
         <v>0.498</v>
       </c>
       <c r="G244" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A244,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A244,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H244" s="18">
@@ -12524,7 +12524,7 @@
         <v>0.498</v>
       </c>
       <c r="G245" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A245,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A245,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H245" s="31">
@@ -12557,7 +12557,7 @@
         <v>0.498</v>
       </c>
       <c r="G246" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A246,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A246,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H246" s="18">
@@ -12590,7 +12590,7 @@
         <v>0.498</v>
       </c>
       <c r="G247" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A247,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A247,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H247" s="31">
@@ -12623,7 +12623,7 @@
         <v>0.498</v>
       </c>
       <c r="G248" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A248,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A248,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H248" s="18">
@@ -12656,7 +12656,7 @@
         <v>0.498</v>
       </c>
       <c r="G249" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A249,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A249,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H249" s="31">
@@ -12689,7 +12689,7 @@
         <v>0.498</v>
       </c>
       <c r="G250" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A250,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A250,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H250" s="18">
@@ -12722,7 +12722,7 @@
         <v>0.498</v>
       </c>
       <c r="G251" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A251,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A251,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H251" s="31">
@@ -12755,7 +12755,7 @@
         <v>0.498</v>
       </c>
       <c r="G252" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A252,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A252,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H252" s="18">
@@ -12788,7 +12788,7 @@
         <v>0.498</v>
       </c>
       <c r="G253" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A253,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A253,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H253" s="31">
@@ -12821,7 +12821,7 @@
         <v>0.498</v>
       </c>
       <c r="G254" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A254,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A254,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H254" s="18">
@@ -12854,7 +12854,7 @@
         <v>0.498</v>
       </c>
       <c r="G255" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A255,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A255,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H255" s="31">
@@ -12887,7 +12887,7 @@
         <v>0.498</v>
       </c>
       <c r="G256" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A256,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A256,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H256" s="18">
@@ -12920,7 +12920,7 @@
         <v>0.498</v>
       </c>
       <c r="G257" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A257,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A257,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H257" s="31">
@@ -12953,7 +12953,7 @@
         <v>0.498</v>
       </c>
       <c r="G258" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A258,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A258,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H258" s="18">
@@ -12986,7 +12986,7 @@
         <v>0.498</v>
       </c>
       <c r="G259" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A259,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A259,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H259" s="31">
@@ -13019,7 +13019,7 @@
         <v>0.498</v>
       </c>
       <c r="G260" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A260,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A260,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H260" s="18">
@@ -13052,7 +13052,7 @@
         <v>0.498</v>
       </c>
       <c r="G261" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A261,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A261,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H261" s="31">
@@ -13085,7 +13085,7 @@
         <v>0.498</v>
       </c>
       <c r="G262" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A262,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A262,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H262" s="18">
@@ -13118,7 +13118,7 @@
         <v>0.498</v>
       </c>
       <c r="G263" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A263,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A263,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H263" s="31">
@@ -13151,7 +13151,7 @@
         <v>0.498</v>
       </c>
       <c r="G264" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A264,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A264,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H264" s="18">
@@ -13184,7 +13184,7 @@
         <v>0.498</v>
       </c>
       <c r="G265" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A265,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A265,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H265" s="31">
@@ -13217,7 +13217,7 @@
         <v>0.4970000000000001</v>
       </c>
       <c r="G266" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A266,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A266,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="H266" s="18">
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-18 19:35 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L269"/>
+  <dimension ref="A1:L270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-18 19:35 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>IFERROR(AVERAGE(E15:E269),"")</f>
+        <f>IFERROR(AVERAGE(E15:E270),"")</f>
         <v/>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>IFERROR(MAX(E15:E269),"")</f>
+        <f>IFERROR(MAX(E15:E270),"")</f>
         <v/>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
         </is>
       </c>
       <c r="B10" s="40">
-        <f>COUNT(D15:D269)</f>
+        <f>COUNT(D15:D270)</f>
         <v/>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
         </is>
       </c>
       <c r="B11" s="40">
-        <f>COUNT(A15:A269)-COUNT(D15:D269)</f>
+        <f>COUNT(A15:A270)-COUNT(D15:D270)</f>
         <v/>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         <v>46008</v>
       </c>
       <c r="B15" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A15,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A15,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A15,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A15,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C15" s="100">
@@ -14937,7 +14937,7 @@
         <v/>
       </c>
       <c r="F15" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A15,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A15,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A15,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A15,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G15" s="100">
@@ -14970,7 +14970,7 @@
         <v>46009</v>
       </c>
       <c r="B16" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A16,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A16,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A16,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A16,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C16" s="101">
@@ -14986,7 +14986,7 @@
         <v/>
       </c>
       <c r="F16" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A16,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A16,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A16,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A16,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G16" s="101">
@@ -15019,7 +15019,7 @@
         <v>46010</v>
       </c>
       <c r="B17" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A17,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A17,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A17,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A17,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C17" s="100">
@@ -15035,7 +15035,7 @@
         <v/>
       </c>
       <c r="F17" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A17,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A17,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A17,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A17,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G17" s="100">
@@ -15068,7 +15068,7 @@
         <v>46011</v>
       </c>
       <c r="B18" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A18,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A18,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A18,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A18,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C18" s="101">
@@ -15084,7 +15084,7 @@
         <v/>
       </c>
       <c r="F18" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A18,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A18,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A18,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A18,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G18" s="101">
@@ -15117,7 +15117,7 @@
         <v>46012</v>
       </c>
       <c r="B19" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A19,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A19,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A19,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A19,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C19" s="100">
@@ -15133,7 +15133,7 @@
         <v/>
       </c>
       <c r="F19" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A19,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A19,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A19,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A19,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G19" s="100">
@@ -15166,7 +15166,7 @@
         <v>46013</v>
       </c>
       <c r="B20" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A20,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A20,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A20,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A20,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C20" s="101">
@@ -15182,7 +15182,7 @@
         <v/>
       </c>
       <c r="F20" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A20,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A20,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A20,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A20,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G20" s="101">
@@ -15215,7 +15215,7 @@
         <v>46014</v>
       </c>
       <c r="B21" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A21,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A21,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A21,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A21,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C21" s="100">
@@ -15231,7 +15231,7 @@
         <v/>
       </c>
       <c r="F21" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A21,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A21,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A21,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A21,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G21" s="100">
@@ -15264,7 +15264,7 @@
         <v>46015</v>
       </c>
       <c r="B22" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A22,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A22,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A22,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A22,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C22" s="101">
@@ -15280,7 +15280,7 @@
         <v/>
       </c>
       <c r="F22" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A22,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A22,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A22,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A22,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G22" s="101">
@@ -15313,7 +15313,7 @@
         <v>46016</v>
       </c>
       <c r="B23" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A23,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A23,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A23,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A23,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C23" s="100">
@@ -15329,7 +15329,7 @@
         <v/>
       </c>
       <c r="F23" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A23,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A23,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A23,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A23,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G23" s="100">
@@ -15362,7 +15362,7 @@
         <v>46017</v>
       </c>
       <c r="B24" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A24,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A24,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A24,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A24,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C24" s="101">
@@ -15378,7 +15378,7 @@
         <v/>
       </c>
       <c r="F24" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A24,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A24,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A24,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A24,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G24" s="101">
@@ -15411,7 +15411,7 @@
         <v>46018</v>
       </c>
       <c r="B25" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A25,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A25,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A25,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A25,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C25" s="100">
@@ -15427,7 +15427,7 @@
         <v/>
       </c>
       <c r="F25" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A25,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A25,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A25,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A25,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G25" s="100">
@@ -15460,7 +15460,7 @@
         <v>46019</v>
       </c>
       <c r="B26" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A26,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A26,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A26,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A26,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C26" s="101">
@@ -15476,7 +15476,7 @@
         <v/>
       </c>
       <c r="F26" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A26,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A26,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A26,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A26,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G26" s="101">
@@ -15509,7 +15509,7 @@
         <v>46020</v>
       </c>
       <c r="B27" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A27,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A27,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A27,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A27,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C27" s="100">
@@ -15525,7 +15525,7 @@
         <v/>
       </c>
       <c r="F27" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A27,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A27,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A27,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A27,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G27" s="100">
@@ -15558,7 +15558,7 @@
         <v>46021</v>
       </c>
       <c r="B28" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A28,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A28,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A28,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A28,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C28" s="101">
@@ -15574,7 +15574,7 @@
         <v/>
       </c>
       <c r="F28" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A28,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A28,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A28,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A28,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G28" s="101">
@@ -15607,7 +15607,7 @@
         <v>46022</v>
       </c>
       <c r="B29" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A29,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A29,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A29,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A29,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C29" s="100">
@@ -15623,7 +15623,7 @@
         <v/>
       </c>
       <c r="F29" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A29,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A29,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A29,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A29,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G29" s="100">
@@ -15656,7 +15656,7 @@
         <v>46023</v>
       </c>
       <c r="B30" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A30,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A30,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A30,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A30,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C30" s="101">
@@ -15672,7 +15672,7 @@
         <v/>
       </c>
       <c r="F30" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A30,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A30,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A30,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A30,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G30" s="101">
@@ -15705,7 +15705,7 @@
         <v>46024</v>
       </c>
       <c r="B31" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A31,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A31,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A31,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A31,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C31" s="100">
@@ -15721,7 +15721,7 @@
         <v/>
       </c>
       <c r="F31" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A31,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A31,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A31,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A31,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G31" s="100">
@@ -15754,7 +15754,7 @@
         <v>46025</v>
       </c>
       <c r="B32" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A32,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A32,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A32,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A32,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C32" s="101">
@@ -15770,7 +15770,7 @@
         <v/>
       </c>
       <c r="F32" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A32,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A32,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A32,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A32,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G32" s="101">
@@ -15803,7 +15803,7 @@
         <v>46026</v>
       </c>
       <c r="B33" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A33,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A33,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A33,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A33,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C33" s="100">
@@ -15819,7 +15819,7 @@
         <v/>
       </c>
       <c r="F33" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A33,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A33,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A33,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A33,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G33" s="100">
@@ -15852,7 +15852,7 @@
         <v>46027</v>
       </c>
       <c r="B34" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A34,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A34,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A34,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A34,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C34" s="101">
@@ -15868,7 +15868,7 @@
         <v/>
       </c>
       <c r="F34" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A34,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A34,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A34,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A34,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G34" s="101">
@@ -15901,7 +15901,7 @@
         <v>46028</v>
       </c>
       <c r="B35" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A35,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A35,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A35,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A35,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C35" s="100">
@@ -15917,7 +15917,7 @@
         <v/>
       </c>
       <c r="F35" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A35,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A35,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A35,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A35,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G35" s="100">
@@ -15950,7 +15950,7 @@
         <v>46029</v>
       </c>
       <c r="B36" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A36,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A36,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C36" s="101">
@@ -15966,7 +15966,7 @@
         <v/>
       </c>
       <c r="F36" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A36,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A36,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A36,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A36,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G36" s="101">
@@ -15999,7 +15999,7 @@
         <v>46030</v>
       </c>
       <c r="B37" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A37,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A37,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C37" s="100">
@@ -16015,7 +16015,7 @@
         <v/>
       </c>
       <c r="F37" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A37,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A37,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A37,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A37,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G37" s="100">
@@ -16048,7 +16048,7 @@
         <v>46031</v>
       </c>
       <c r="B38" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A38,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A38,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C38" s="101">
@@ -16064,7 +16064,7 @@
         <v/>
       </c>
       <c r="F38" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A38,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A38,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A38,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A38,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G38" s="101">
@@ -16097,7 +16097,7 @@
         <v>46032</v>
       </c>
       <c r="B39" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A39,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A39,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C39" s="100">
@@ -16113,7 +16113,7 @@
         <v/>
       </c>
       <c r="F39" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A39,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A39,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A39,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A39,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G39" s="100">
@@ -16146,7 +16146,7 @@
         <v>46033</v>
       </c>
       <c r="B40" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A40,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A40,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C40" s="101">
@@ -16162,7 +16162,7 @@
         <v/>
       </c>
       <c r="F40" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A40,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A40,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A40,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A40,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G40" s="101">
@@ -16195,7 +16195,7 @@
         <v>46034</v>
       </c>
       <c r="B41" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A41,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A41,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C41" s="100">
@@ -16211,7 +16211,7 @@
         <v/>
       </c>
       <c r="F41" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A41,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A41,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A41,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A41,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G41" s="100">
@@ -16244,7 +16244,7 @@
         <v>46035</v>
       </c>
       <c r="B42" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A42,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A42,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C42" s="101">
@@ -16260,7 +16260,7 @@
         <v/>
       </c>
       <c r="F42" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A42,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A42,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A42,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A42,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G42" s="101">
@@ -16293,7 +16293,7 @@
         <v>46036</v>
       </c>
       <c r="B43" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A43,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A43,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C43" s="100">
@@ -16309,7 +16309,7 @@
         <v/>
       </c>
       <c r="F43" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A43,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A43,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A43,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A43,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G43" s="100">
@@ -16342,7 +16342,7 @@
         <v>46037</v>
       </c>
       <c r="B44" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A44,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A44,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C44" s="101">
@@ -16358,7 +16358,7 @@
         <v/>
       </c>
       <c r="F44" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A44,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A44,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A44,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A44,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G44" s="101">
@@ -16391,7 +16391,7 @@
         <v>46038</v>
       </c>
       <c r="B45" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A45,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A45,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C45" s="100">
@@ -16407,7 +16407,7 @@
         <v/>
       </c>
       <c r="F45" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A45,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A45,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A45,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A45,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G45" s="100">
@@ -16440,7 +16440,7 @@
         <v>46039</v>
       </c>
       <c r="B46" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A46,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A46,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C46" s="101">
@@ -16456,7 +16456,7 @@
         <v/>
       </c>
       <c r="F46" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A46,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A46,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A46,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A46,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G46" s="101">
@@ -16489,7 +16489,7 @@
         <v>46040</v>
       </c>
       <c r="B47" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A47,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A47,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C47" s="100">
@@ -16505,7 +16505,7 @@
         <v/>
       </c>
       <c r="F47" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A47,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A47,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A47,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A47,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G47" s="100">
@@ -16538,7 +16538,7 @@
         <v>46041</v>
       </c>
       <c r="B48" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A48,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A48,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C48" s="101">
@@ -16554,7 +16554,7 @@
         <v/>
       </c>
       <c r="F48" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A48,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A48,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A48,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A48,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G48" s="101">
@@ -16587,7 +16587,7 @@
         <v>46042</v>
       </c>
       <c r="B49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A49,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A49,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C49" s="100">
@@ -16603,7 +16603,7 @@
         <v/>
       </c>
       <c r="F49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A49,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A49,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A49,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A49,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G49" s="100">
@@ -16636,7 +16636,7 @@
         <v>46043</v>
       </c>
       <c r="B50" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A50,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A50,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C50" s="101">
@@ -16652,7 +16652,7 @@
         <v/>
       </c>
       <c r="F50" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A50,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A50,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A50,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A50,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G50" s="101">
@@ -16685,7 +16685,7 @@
         <v>46044</v>
       </c>
       <c r="B51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A51,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A51,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C51" s="100">
@@ -16701,7 +16701,7 @@
         <v/>
       </c>
       <c r="F51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A51,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A51,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A51,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A51,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G51" s="100">
@@ -16734,7 +16734,7 @@
         <v>46045</v>
       </c>
       <c r="B52" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A52,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A52,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C52" s="101">
@@ -16750,7 +16750,7 @@
         <v/>
       </c>
       <c r="F52" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A52,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A52,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A52,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A52,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G52" s="101">
@@ -16783,7 +16783,7 @@
         <v>46046</v>
       </c>
       <c r="B53" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A53,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A53,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C53" s="100">
@@ -16799,7 +16799,7 @@
         <v/>
       </c>
       <c r="F53" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A53,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A53,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A53,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A53,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G53" s="100">
@@ -16832,7 +16832,7 @@
         <v>46047</v>
       </c>
       <c r="B54" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A54,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A54,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C54" s="101">
@@ -16848,7 +16848,7 @@
         <v/>
       </c>
       <c r="F54" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A54,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A54,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A54,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A54,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G54" s="101">
@@ -16881,7 +16881,7 @@
         <v>46048</v>
       </c>
       <c r="B55" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A55,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A55,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C55" s="100">
@@ -16897,7 +16897,7 @@
         <v/>
       </c>
       <c r="F55" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A55,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A55,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A55,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A55,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G55" s="100">
@@ -16930,7 +16930,7 @@
         <v>46049</v>
       </c>
       <c r="B56" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A56,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A56,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C56" s="101">
@@ -16946,7 +16946,7 @@
         <v/>
       </c>
       <c r="F56" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A56,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A56,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A56,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A56,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G56" s="101">
@@ -16979,7 +16979,7 @@
         <v>46050</v>
       </c>
       <c r="B57" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A57,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A57,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C57" s="100">
@@ -16995,7 +16995,7 @@
         <v/>
       </c>
       <c r="F57" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A57,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A57,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A57,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A57,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G57" s="100">
@@ -17028,7 +17028,7 @@
         <v>46051</v>
       </c>
       <c r="B58" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A58,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A58,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C58" s="101">
@@ -17044,7 +17044,7 @@
         <v/>
       </c>
       <c r="F58" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A58,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A58,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A58,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A58,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G58" s="101">
@@ -17077,7 +17077,7 @@
         <v>46052</v>
       </c>
       <c r="B59" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A59,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A59,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C59" s="100">
@@ -17093,7 +17093,7 @@
         <v/>
       </c>
       <c r="F59" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A59,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A59,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A59,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A59,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G59" s="100">
@@ -17126,7 +17126,7 @@
         <v>46053</v>
       </c>
       <c r="B60" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A60,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A60,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C60" s="101">
@@ -17142,7 +17142,7 @@
         <v/>
       </c>
       <c r="F60" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A60,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A60,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A60,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A60,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G60" s="101">
@@ -17175,7 +17175,7 @@
         <v>46054</v>
       </c>
       <c r="B61" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A61,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A61,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C61" s="100">
@@ -17191,7 +17191,7 @@
         <v/>
       </c>
       <c r="F61" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A61,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A61,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A61,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A61,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G61" s="100">
@@ -17224,7 +17224,7 @@
         <v>46055</v>
       </c>
       <c r="B62" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A62,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A62,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C62" s="101">
@@ -17240,7 +17240,7 @@
         <v/>
       </c>
       <c r="F62" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A62,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A62,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A62,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A62,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G62" s="101">
@@ -17273,7 +17273,7 @@
         <v>46056</v>
       </c>
       <c r="B63" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A63,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A63,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C63" s="100">
@@ -17289,7 +17289,7 @@
         <v/>
       </c>
       <c r="F63" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A63,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A63,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A63,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A63,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G63" s="100">
@@ -17322,7 +17322,7 @@
         <v>46057</v>
       </c>
       <c r="B64" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A64,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A64,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C64" s="101">
@@ -17338,7 +17338,7 @@
         <v/>
       </c>
       <c r="F64" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A64,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A64,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A64,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A64,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G64" s="101">
@@ -17371,7 +17371,7 @@
         <v>46058</v>
       </c>
       <c r="B65" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A65,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A65,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C65" s="100">
@@ -17387,7 +17387,7 @@
         <v/>
       </c>
       <c r="F65" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A65,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A65,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A65,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A65,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G65" s="100">
@@ -17420,7 +17420,7 @@
         <v>46059</v>
       </c>
       <c r="B66" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A66,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A66,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C66" s="101">
@@ -17436,7 +17436,7 @@
         <v/>
       </c>
       <c r="F66" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A66,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A66,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A66,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A66,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G66" s="101">
@@ -17469,7 +17469,7 @@
         <v>46060</v>
       </c>
       <c r="B67" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A67,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A67,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C67" s="100">
@@ -17485,7 +17485,7 @@
         <v/>
       </c>
       <c r="F67" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A67,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A67,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A67,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A67,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G67" s="100">
@@ -17518,7 +17518,7 @@
         <v>46061</v>
       </c>
       <c r="B68" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A68,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A68,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C68" s="101">
@@ -17534,7 +17534,7 @@
         <v/>
       </c>
       <c r="F68" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A68,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A68,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A68,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A68,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G68" s="101">
@@ -17567,7 +17567,7 @@
         <v>46062</v>
       </c>
       <c r="B69" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A69,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A69,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C69" s="100">
@@ -17583,7 +17583,7 @@
         <v/>
       </c>
       <c r="F69" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A69,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A69,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A69,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A69,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G69" s="100">
@@ -17616,7 +17616,7 @@
         <v>46063</v>
       </c>
       <c r="B70" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A70,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A70,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C70" s="101">
@@ -17632,7 +17632,7 @@
         <v/>
       </c>
       <c r="F70" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A70,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A70,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A70,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A70,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G70" s="101">
@@ -17665,7 +17665,7 @@
         <v>46064</v>
       </c>
       <c r="B71" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A71,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A71,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C71" s="100">
@@ -17681,7 +17681,7 @@
         <v/>
       </c>
       <c r="F71" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A71,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A71,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A71,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A71,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G71" s="100">
@@ -17714,7 +17714,7 @@
         <v>46065</v>
       </c>
       <c r="B72" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A72,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A72,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C72" s="101">
@@ -17730,7 +17730,7 @@
         <v/>
       </c>
       <c r="F72" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A72,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A72,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A72,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A72,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G72" s="101">
@@ -17763,7 +17763,7 @@
         <v>46066</v>
       </c>
       <c r="B73" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A73,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A73,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C73" s="100">
@@ -17779,7 +17779,7 @@
         <v/>
       </c>
       <c r="F73" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A73,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A73,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A73,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A73,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G73" s="100">
@@ -17812,7 +17812,7 @@
         <v>46067</v>
       </c>
       <c r="B74" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A74,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A74,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C74" s="101">
@@ -17828,7 +17828,7 @@
         <v/>
       </c>
       <c r="F74" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A74,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A74,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A74,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A74,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G74" s="101">
@@ -17861,7 +17861,7 @@
         <v>46068</v>
       </c>
       <c r="B75" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A75,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A75,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C75" s="100">
@@ -17877,7 +17877,7 @@
         <v/>
       </c>
       <c r="F75" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A75,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A75,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A75,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A75,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G75" s="100">
@@ -17910,7 +17910,7 @@
         <v>46069</v>
       </c>
       <c r="B76" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A76,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A76,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C76" s="101">
@@ -17926,7 +17926,7 @@
         <v/>
       </c>
       <c r="F76" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A76,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A76,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A76,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A76,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G76" s="101">
@@ -17959,7 +17959,7 @@
         <v>46070</v>
       </c>
       <c r="B77" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A77,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A77,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C77" s="100">
@@ -17975,7 +17975,7 @@
         <v/>
       </c>
       <c r="F77" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A77,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A77,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A77,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A77,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G77" s="100">
@@ -18008,7 +18008,7 @@
         <v>46071</v>
       </c>
       <c r="B78" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A78,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A78,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C78" s="101">
@@ -18024,7 +18024,7 @@
         <v/>
       </c>
       <c r="F78" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A78,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A78,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A78,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A78,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G78" s="101">
@@ -18057,7 +18057,7 @@
         <v>46072</v>
       </c>
       <c r="B79" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A79,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A79,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C79" s="100">
@@ -18073,7 +18073,7 @@
         <v/>
       </c>
       <c r="F79" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A79,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A79,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A79,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A79,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G79" s="100">
@@ -18106,7 +18106,7 @@
         <v>46073</v>
       </c>
       <c r="B80" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A80,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A80,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C80" s="101">
@@ -18122,7 +18122,7 @@
         <v/>
       </c>
       <c r="F80" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A80,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A80,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A80,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A80,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G80" s="101">
@@ -18155,7 +18155,7 @@
         <v>46074</v>
       </c>
       <c r="B81" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A81,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A81,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C81" s="100">
@@ -18171,7 +18171,7 @@
         <v/>
       </c>
       <c r="F81" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A81,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A81,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A81,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A81,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G81" s="100">
@@ -18204,7 +18204,7 @@
         <v>46075</v>
       </c>
       <c r="B82" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A82,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A82,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C82" s="101">
@@ -18220,7 +18220,7 @@
         <v/>
       </c>
       <c r="F82" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A82,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A82,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A82,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A82,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G82" s="101">
@@ -18253,7 +18253,7 @@
         <v>46076</v>
       </c>
       <c r="B83" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A83,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A83,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C83" s="100">
@@ -18269,7 +18269,7 @@
         <v/>
       </c>
       <c r="F83" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A83,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A83,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A83,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A83,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G83" s="100">
@@ -18302,7 +18302,7 @@
         <v>46077</v>
       </c>
       <c r="B84" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A84,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A84,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C84" s="101">
@@ -18318,7 +18318,7 @@
         <v/>
       </c>
       <c r="F84" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A84,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A84,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A84,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A84,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G84" s="101">
@@ -18351,7 +18351,7 @@
         <v>46078</v>
       </c>
       <c r="B85" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A85,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A85,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C85" s="100">
@@ -18367,7 +18367,7 @@
         <v/>
       </c>
       <c r="F85" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A85,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A85,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A85,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A85,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G85" s="100">
@@ -18400,7 +18400,7 @@
         <v>46079</v>
       </c>
       <c r="B86" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A86,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A86,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C86" s="101">
@@ -18416,7 +18416,7 @@
         <v/>
       </c>
       <c r="F86" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A86,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A86,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A86,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A86,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G86" s="101">
@@ -18449,7 +18449,7 @@
         <v>46080</v>
       </c>
       <c r="B87" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A87,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A87,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C87" s="100">
@@ -18465,7 +18465,7 @@
         <v/>
       </c>
       <c r="F87" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A87,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A87,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A87,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A87,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G87" s="100">
@@ -18498,7 +18498,7 @@
         <v>46081</v>
       </c>
       <c r="B88" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A88,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A88,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C88" s="101">
@@ -18514,7 +18514,7 @@
         <v/>
       </c>
       <c r="F88" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A88,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A88,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A88,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A88,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G88" s="101">
@@ -18547,7 +18547,7 @@
         <v>46082</v>
       </c>
       <c r="B89" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A89,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A89,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C89" s="100">
@@ -18563,7 +18563,7 @@
         <v/>
       </c>
       <c r="F89" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A89,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A89,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A89,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A89,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G89" s="100">
@@ -18596,7 +18596,7 @@
         <v>46083</v>
       </c>
       <c r="B90" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A90,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A90,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C90" s="101">
@@ -18612,7 +18612,7 @@
         <v/>
       </c>
       <c r="F90" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A90,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A90,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A90,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A90,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G90" s="101">
@@ -18645,7 +18645,7 @@
         <v>46084</v>
       </c>
       <c r="B91" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A91,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A91,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C91" s="100">
@@ -18661,7 +18661,7 @@
         <v/>
       </c>
       <c r="F91" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A91,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A91,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A91,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A91,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G91" s="100">
@@ -18694,7 +18694,7 @@
         <v>46085</v>
       </c>
       <c r="B92" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A92,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A92,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C92" s="101">
@@ -18710,7 +18710,7 @@
         <v/>
       </c>
       <c r="F92" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A92,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A92,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A92,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A92,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G92" s="101">
@@ -18743,7 +18743,7 @@
         <v>46086</v>
       </c>
       <c r="B93" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A93,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A93,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C93" s="100">
@@ -18759,7 +18759,7 @@
         <v/>
       </c>
       <c r="F93" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A93,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A93,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A93,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A93,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G93" s="100">
@@ -18792,7 +18792,7 @@
         <v>46087</v>
       </c>
       <c r="B94" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A94,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A94,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C94" s="101">
@@ -18808,7 +18808,7 @@
         <v/>
       </c>
       <c r="F94" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A94,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A94,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A94,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A94,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G94" s="101">
@@ -18841,7 +18841,7 @@
         <v>46088</v>
       </c>
       <c r="B95" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A95,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A95,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C95" s="100">
@@ -18857,7 +18857,7 @@
         <v/>
       </c>
       <c r="F95" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A95,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A95,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A95,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A95,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G95" s="100">
@@ -18890,7 +18890,7 @@
         <v>46089</v>
       </c>
       <c r="B96" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A96,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A96,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C96" s="101">
@@ -18906,7 +18906,7 @@
         <v/>
       </c>
       <c r="F96" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A96,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A96,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A96,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A96,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G96" s="101">
@@ -18939,7 +18939,7 @@
         <v>46090</v>
       </c>
       <c r="B97" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A97,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A97,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C97" s="100">
@@ -18955,7 +18955,7 @@
         <v/>
       </c>
       <c r="F97" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A97,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A97,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A97,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A97,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G97" s="100">
@@ -18988,7 +18988,7 @@
         <v>46091</v>
       </c>
       <c r="B98" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A98,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A98,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C98" s="101">
@@ -19004,7 +19004,7 @@
         <v/>
       </c>
       <c r="F98" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A98,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A98,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A98,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A98,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G98" s="101">
@@ -19037,7 +19037,7 @@
         <v>46092</v>
       </c>
       <c r="B99" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A99,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A99,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C99" s="100">
@@ -19053,7 +19053,7 @@
         <v/>
       </c>
       <c r="F99" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A99,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A99,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A99,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A99,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G99" s="100">
@@ -19086,7 +19086,7 @@
         <v>46093</v>
       </c>
       <c r="B100" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A100,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A100,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C100" s="101">
@@ -19102,7 +19102,7 @@
         <v/>
       </c>
       <c r="F100" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A100,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A100,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A100,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A100,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G100" s="101">
@@ -19135,7 +19135,7 @@
         <v>46094</v>
       </c>
       <c r="B101" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A101,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A101,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C101" s="100">
@@ -19151,7 +19151,7 @@
         <v/>
       </c>
       <c r="F101" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A101,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A101,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A101,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A101,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G101" s="100">
@@ -19184,7 +19184,7 @@
         <v>46095</v>
       </c>
       <c r="B102" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A102,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A102,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C102" s="101">
@@ -19200,7 +19200,7 @@
         <v/>
       </c>
       <c r="F102" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A102,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A102,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A102,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A102,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G102" s="101">
@@ -19233,7 +19233,7 @@
         <v>46096</v>
       </c>
       <c r="B103" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A103,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A103,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C103" s="100">
@@ -19249,7 +19249,7 @@
         <v/>
       </c>
       <c r="F103" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A103,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A103,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A103,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A103,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G103" s="100">
@@ -19282,7 +19282,7 @@
         <v>46097</v>
       </c>
       <c r="B104" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A104,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A104,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C104" s="101">
@@ -19298,7 +19298,7 @@
         <v/>
       </c>
       <c r="F104" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A104,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A104,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A104,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A104,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G104" s="101">
@@ -19331,7 +19331,7 @@
         <v>46098</v>
       </c>
       <c r="B105" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A105,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A105,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C105" s="100">
@@ -19347,7 +19347,7 @@
         <v/>
       </c>
       <c r="F105" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A105,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A105,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A105,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A105,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G105" s="100">
@@ -19380,7 +19380,7 @@
         <v>46099</v>
       </c>
       <c r="B106" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A106,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A106,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C106" s="101">
@@ -19396,7 +19396,7 @@
         <v/>
       </c>
       <c r="F106" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A106,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A106,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A106,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A106,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G106" s="101">
@@ -19429,7 +19429,7 @@
         <v>46100</v>
       </c>
       <c r="B107" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A107,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A107,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C107" s="100">
@@ -19445,7 +19445,7 @@
         <v/>
       </c>
       <c r="F107" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A107,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A107,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A107,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A107,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G107" s="100">
@@ -19478,7 +19478,7 @@
         <v>46101</v>
       </c>
       <c r="B108" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A108,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A108,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C108" s="101">
@@ -19494,7 +19494,7 @@
         <v/>
       </c>
       <c r="F108" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A108,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A108,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A108,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A108,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G108" s="101">
@@ -19527,7 +19527,7 @@
         <v>46102</v>
       </c>
       <c r="B109" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A109,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A109,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C109" s="100">
@@ -19543,7 +19543,7 @@
         <v/>
       </c>
       <c r="F109" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A109,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A109,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A109,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A109,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G109" s="100">
@@ -19576,7 +19576,7 @@
         <v>46103</v>
       </c>
       <c r="B110" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A110,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A110,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C110" s="101">
@@ -19592,7 +19592,7 @@
         <v/>
       </c>
       <c r="F110" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A110,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A110,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A110,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A110,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G110" s="101">
@@ -19625,7 +19625,7 @@
         <v>46104</v>
       </c>
       <c r="B111" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A111,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A111,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C111" s="100">
@@ -19641,7 +19641,7 @@
         <v/>
       </c>
       <c r="F111" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A111,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A111,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A111,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A111,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G111" s="100">
@@ -19674,7 +19674,7 @@
         <v>46105</v>
       </c>
       <c r="B112" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A112,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A112,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C112" s="101">
@@ -19690,7 +19690,7 @@
         <v/>
       </c>
       <c r="F112" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A112,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A112,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A112,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A112,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G112" s="101">
@@ -19723,7 +19723,7 @@
         <v>46106</v>
       </c>
       <c r="B113" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A113,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A113,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C113" s="100">
@@ -19739,7 +19739,7 @@
         <v/>
       </c>
       <c r="F113" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A113,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A113,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A113,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A113,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G113" s="100">
@@ -19772,7 +19772,7 @@
         <v>46107</v>
       </c>
       <c r="B114" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A114,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A114,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C114" s="101">
@@ -19788,7 +19788,7 @@
         <v/>
       </c>
       <c r="F114" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A114,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A114,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A114,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A114,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G114" s="101">
@@ -19821,7 +19821,7 @@
         <v>46108</v>
       </c>
       <c r="B115" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A115,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A115,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C115" s="100">
@@ -19837,7 +19837,7 @@
         <v/>
       </c>
       <c r="F115" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A115,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A115,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A115,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A115,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G115" s="100">
@@ -19870,7 +19870,7 @@
         <v>46109</v>
       </c>
       <c r="B116" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A116,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A116,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C116" s="101">
@@ -19886,7 +19886,7 @@
         <v/>
       </c>
       <c r="F116" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A116,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A116,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A116,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A116,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G116" s="101">
@@ -19919,7 +19919,7 @@
         <v>46110</v>
       </c>
       <c r="B117" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A117,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A117,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C117" s="100">
@@ -19935,7 +19935,7 @@
         <v/>
       </c>
       <c r="F117" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A117,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A117,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A117,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A117,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G117" s="100">
@@ -19968,7 +19968,7 @@
         <v>46121</v>
       </c>
       <c r="B118" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A118,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A118,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C118" s="101">
@@ -19984,7 +19984,7 @@
         <v/>
       </c>
       <c r="F118" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A118,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A118,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A118,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A118,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G118" s="101">
@@ -20017,7 +20017,7 @@
         <v>46130</v>
       </c>
       <c r="B119" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A119,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A119,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C119" s="100">
@@ -20033,7 +20033,7 @@
         <v/>
       </c>
       <c r="F119" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A119,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A119,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A119,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A119,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G119" s="100">
@@ -20066,7 +20066,7 @@
         <v>46134</v>
       </c>
       <c r="B120" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A120,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A120,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C120" s="101">
@@ -20082,7 +20082,7 @@
         <v/>
       </c>
       <c r="F120" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A120,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A120,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A120,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A120,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G120" s="101">
@@ -20115,7 +20115,7 @@
         <v>46135</v>
       </c>
       <c r="B121" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A121,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A121,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C121" s="100">
@@ -20131,7 +20131,7 @@
         <v/>
       </c>
       <c r="F121" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A121,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A121,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A121,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A121,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G121" s="100">
@@ -20164,7 +20164,7 @@
         <v>46136</v>
       </c>
       <c r="B122" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A122,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A122,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C122" s="101">
@@ -20180,7 +20180,7 @@
         <v/>
       </c>
       <c r="F122" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A122,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A122,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A122,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A122,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G122" s="101">
@@ -20213,7 +20213,7 @@
         <v>46137</v>
       </c>
       <c r="B123" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A123,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A123,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C123" s="100">
@@ -20229,7 +20229,7 @@
         <v/>
       </c>
       <c r="F123" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A123,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A123,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A123,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A123,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G123" s="100">
@@ -20262,7 +20262,7 @@
         <v>46138</v>
       </c>
       <c r="B124" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A124,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A124,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C124" s="101">
@@ -20278,7 +20278,7 @@
         <v/>
       </c>
       <c r="F124" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A124,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A124,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A124,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A124,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G124" s="101">
@@ -20311,7 +20311,7 @@
         <v>46139</v>
       </c>
       <c r="B125" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A125,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A125,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C125" s="100">
@@ -20327,7 +20327,7 @@
         <v/>
       </c>
       <c r="F125" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A125,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A125,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A125,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A125,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G125" s="100">
@@ -20360,7 +20360,7 @@
         <v>46140</v>
       </c>
       <c r="B126" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A126,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A126,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C126" s="101">
@@ -20376,7 +20376,7 @@
         <v/>
       </c>
       <c r="F126" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A126,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A126,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A126,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A126,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G126" s="101">
@@ -20409,7 +20409,7 @@
         <v>46141</v>
       </c>
       <c r="B127" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A127,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A127,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C127" s="100">
@@ -20425,7 +20425,7 @@
         <v/>
       </c>
       <c r="F127" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A127,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A127,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A127,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A127,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G127" s="100">
@@ -20458,7 +20458,7 @@
         <v>46142</v>
       </c>
       <c r="B128" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A128,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A128,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C128" s="101">
@@ -20474,7 +20474,7 @@
         <v/>
       </c>
       <c r="F128" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A128,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A128,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A128,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A128,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G128" s="101">
@@ -20507,7 +20507,7 @@
         <v>46143</v>
       </c>
       <c r="B129" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A129,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A129,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C129" s="100">
@@ -20523,7 +20523,7 @@
         <v/>
       </c>
       <c r="F129" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A129,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A129,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A129,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A129,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G129" s="100">
@@ -20556,7 +20556,7 @@
         <v>46144</v>
       </c>
       <c r="B130" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A130,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A130,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C130" s="101">
@@ -20572,7 +20572,7 @@
         <v/>
       </c>
       <c r="F130" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A130,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A130,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A130,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A130,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G130" s="101">
@@ -20605,7 +20605,7 @@
         <v>46145</v>
       </c>
       <c r="B131" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A131,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A131,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C131" s="100">
@@ -20621,7 +20621,7 @@
         <v/>
       </c>
       <c r="F131" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A131,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A131,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A131,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A131,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G131" s="100">
@@ -20654,7 +20654,7 @@
         <v>46146</v>
       </c>
       <c r="B132" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A132,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A132,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C132" s="101">
@@ -20670,7 +20670,7 @@
         <v/>
       </c>
       <c r="F132" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A132,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A132,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A132,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A132,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G132" s="101">
@@ -20703,7 +20703,7 @@
         <v>46147</v>
       </c>
       <c r="B133" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A133,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A133,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C133" s="100">
@@ -20719,7 +20719,7 @@
         <v/>
       </c>
       <c r="F133" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A133,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A133,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A133,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A133,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G133" s="100">
@@ -20752,7 +20752,7 @@
         <v>46148</v>
       </c>
       <c r="B134" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A134,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A134,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C134" s="101">
@@ -20768,7 +20768,7 @@
         <v/>
       </c>
       <c r="F134" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A134,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A134,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A134,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A134,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G134" s="101">
@@ -20801,7 +20801,7 @@
         <v>46149</v>
       </c>
       <c r="B135" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A135,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A135,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C135" s="100">
@@ -20817,7 +20817,7 @@
         <v/>
       </c>
       <c r="F135" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A135,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A135,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A135,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A135,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G135" s="100">
@@ -20850,7 +20850,7 @@
         <v>46150</v>
       </c>
       <c r="B136" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A136,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A136,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C136" s="101">
@@ -20866,7 +20866,7 @@
         <v/>
       </c>
       <c r="F136" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A136,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A136,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A136,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A136,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G136" s="101">
@@ -20899,7 +20899,7 @@
         <v>46151</v>
       </c>
       <c r="B137" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A137,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A137,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C137" s="100">
@@ -20915,7 +20915,7 @@
         <v/>
       </c>
       <c r="F137" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A137,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A137,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A137,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A137,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G137" s="100">
@@ -20948,7 +20948,7 @@
         <v>46152</v>
       </c>
       <c r="B138" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A138,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A138,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C138" s="101">
@@ -20964,7 +20964,7 @@
         <v/>
       </c>
       <c r="F138" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A138,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A138,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A138,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A138,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G138" s="101">
@@ -20997,7 +20997,7 @@
         <v>46153</v>
       </c>
       <c r="B139" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A139,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A139,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C139" s="100">
@@ -21013,7 +21013,7 @@
         <v/>
       </c>
       <c r="F139" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A139,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A139,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A139,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A139,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G139" s="100">
@@ -21046,7 +21046,7 @@
         <v>46154</v>
       </c>
       <c r="B140" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A140,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A140,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C140" s="101">
@@ -21062,7 +21062,7 @@
         <v/>
       </c>
       <c r="F140" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A140,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A140,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A140,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A140,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G140" s="101">
@@ -21095,7 +21095,7 @@
         <v>46155</v>
       </c>
       <c r="B141" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A141,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A141,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C141" s="100">
@@ -21111,7 +21111,7 @@
         <v/>
       </c>
       <c r="F141" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A141,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A141,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A141,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A141,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G141" s="100">
@@ -21144,7 +21144,7 @@
         <v>46156</v>
       </c>
       <c r="B142" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A142,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A142,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C142" s="101">
@@ -21160,7 +21160,7 @@
         <v/>
       </c>
       <c r="F142" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A142,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A142,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A142,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A142,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G142" s="101">
@@ -21193,7 +21193,7 @@
         <v>46157</v>
       </c>
       <c r="B143" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A143,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A143,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C143" s="100">
@@ -21209,7 +21209,7 @@
         <v/>
       </c>
       <c r="F143" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A143,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A143,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A143,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A143,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G143" s="100">
@@ -21242,7 +21242,7 @@
         <v>46158</v>
       </c>
       <c r="B144" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A144,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A144,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C144" s="101">
@@ -21258,7 +21258,7 @@
         <v/>
       </c>
       <c r="F144" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A144,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A144,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A144,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A144,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G144" s="101">
@@ -21291,7 +21291,7 @@
         <v>46159</v>
       </c>
       <c r="B145" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A145,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A145,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C145" s="100">
@@ -21307,7 +21307,7 @@
         <v/>
       </c>
       <c r="F145" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A145,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A145,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A145,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A145,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G145" s="100">
@@ -21340,7 +21340,7 @@
         <v>46160</v>
       </c>
       <c r="B146" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A146,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A146,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C146" s="101">
@@ -21356,7 +21356,7 @@
         <v/>
       </c>
       <c r="F146" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A146,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A146,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A146,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A146,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G146" s="101">
@@ -21389,7 +21389,7 @@
         <v>46161</v>
       </c>
       <c r="B147" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A147,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A147,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C147" s="100">
@@ -21405,7 +21405,7 @@
         <v/>
       </c>
       <c r="F147" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A147,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A147,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A147,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A147,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G147" s="100">
@@ -21438,7 +21438,7 @@
         <v>46162</v>
       </c>
       <c r="B148" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A148,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A148,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C148" s="101">
@@ -21454,7 +21454,7 @@
         <v/>
       </c>
       <c r="F148" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A148,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A148,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A148,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A148,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G148" s="101">
@@ -21487,7 +21487,7 @@
         <v>46163</v>
       </c>
       <c r="B149" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A149,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A149,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C149" s="100">
@@ -21503,7 +21503,7 @@
         <v/>
       </c>
       <c r="F149" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A149,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A149,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A149,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A149,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G149" s="100">
@@ -21536,7 +21536,7 @@
         <v>46164</v>
       </c>
       <c r="B150" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A150,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A150,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C150" s="101">
@@ -21552,7 +21552,7 @@
         <v/>
       </c>
       <c r="F150" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A150,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A150,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A150,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A150,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G150" s="101">
@@ -21585,7 +21585,7 @@
         <v>46165</v>
       </c>
       <c r="B151" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A151,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A151,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C151" s="100">
@@ -21601,7 +21601,7 @@
         <v/>
       </c>
       <c r="F151" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A151,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A151,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A151,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A151,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G151" s="100">
@@ -21634,7 +21634,7 @@
         <v>46166</v>
       </c>
       <c r="B152" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A152,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A152,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C152" s="101">
@@ -21650,7 +21650,7 @@
         <v/>
       </c>
       <c r="F152" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A152,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A152,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A152,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A152,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G152" s="101">
@@ -21683,7 +21683,7 @@
         <v>46167</v>
       </c>
       <c r="B153" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A153,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A153,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C153" s="100">
@@ -21699,7 +21699,7 @@
         <v/>
       </c>
       <c r="F153" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A153,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A153,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A153,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A153,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G153" s="100">
@@ -21732,7 +21732,7 @@
         <v>46168</v>
       </c>
       <c r="B154" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A154,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A154,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C154" s="101">
@@ -21748,7 +21748,7 @@
         <v/>
       </c>
       <c r="F154" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A154,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A154,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A154,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A154,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G154" s="101">
@@ -21781,7 +21781,7 @@
         <v>46169</v>
       </c>
       <c r="B155" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A155,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A155,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C155" s="100">
@@ -21797,7 +21797,7 @@
         <v/>
       </c>
       <c r="F155" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A155,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A155,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A155,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A155,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G155" s="100">
@@ -21830,7 +21830,7 @@
         <v>46170</v>
       </c>
       <c r="B156" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A156,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A156,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C156" s="101">
@@ -21846,7 +21846,7 @@
         <v/>
       </c>
       <c r="F156" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A156,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A156,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A156,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A156,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G156" s="101">
@@ -21879,7 +21879,7 @@
         <v>46171</v>
       </c>
       <c r="B157" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A157,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A157,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C157" s="100">
@@ -21895,7 +21895,7 @@
         <v/>
       </c>
       <c r="F157" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A157,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A157,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A157,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A157,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G157" s="100">
@@ -21928,7 +21928,7 @@
         <v>46172</v>
       </c>
       <c r="B158" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A158,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A158,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C158" s="101">
@@ -21944,7 +21944,7 @@
         <v/>
       </c>
       <c r="F158" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A158,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A158,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A158,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A158,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G158" s="101">
@@ -21977,7 +21977,7 @@
         <v>46173</v>
       </c>
       <c r="B159" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A159,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A159,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C159" s="100">
@@ -21993,7 +21993,7 @@
         <v/>
       </c>
       <c r="F159" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A159,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A159,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A159,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A159,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G159" s="100">
@@ -22026,7 +22026,7 @@
         <v>46174</v>
       </c>
       <c r="B160" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A160,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A160,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C160" s="101">
@@ -22042,7 +22042,7 @@
         <v/>
       </c>
       <c r="F160" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A160,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A160,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A160,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A160,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G160" s="101">
@@ -22075,7 +22075,7 @@
         <v>46175</v>
       </c>
       <c r="B161" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A161,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A161,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C161" s="100">
@@ -22091,7 +22091,7 @@
         <v/>
       </c>
       <c r="F161" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A161,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A161,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A161,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A161,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G161" s="100">
@@ -22124,7 +22124,7 @@
         <v>46176</v>
       </c>
       <c r="B162" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A162,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A162,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C162" s="101">
@@ -22140,7 +22140,7 @@
         <v/>
       </c>
       <c r="F162" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A162,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A162,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A162,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A162,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G162" s="101">
@@ -22173,7 +22173,7 @@
         <v>46177</v>
       </c>
       <c r="B163" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A163,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A163,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C163" s="100">
@@ -22189,7 +22189,7 @@
         <v/>
       </c>
       <c r="F163" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A163,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A163,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A163,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A163,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G163" s="100">
@@ -22222,7 +22222,7 @@
         <v>46178</v>
       </c>
       <c r="B164" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A164,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A164,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C164" s="101">
@@ -22238,7 +22238,7 @@
         <v/>
       </c>
       <c r="F164" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A164,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A164,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A164,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A164,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G164" s="101">
@@ -22271,7 +22271,7 @@
         <v>46179</v>
       </c>
       <c r="B165" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A165,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A165,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C165" s="100">
@@ -22287,7 +22287,7 @@
         <v/>
       </c>
       <c r="F165" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A165,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A165,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A165,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A165,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G165" s="100">
@@ -22320,7 +22320,7 @@
         <v>46180</v>
       </c>
       <c r="B166" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A166,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A166,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C166" s="101">
@@ -22336,7 +22336,7 @@
         <v/>
       </c>
       <c r="F166" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A166,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A166,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A166,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A166,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G166" s="101">
@@ -22369,7 +22369,7 @@
         <v>46181</v>
       </c>
       <c r="B167" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A167,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A167,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C167" s="100">
@@ -22385,7 +22385,7 @@
         <v/>
       </c>
       <c r="F167" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A167,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A167,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A167,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A167,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G167" s="100">
@@ -22418,7 +22418,7 @@
         <v>46182</v>
       </c>
       <c r="B168" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A168,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A168,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C168" s="101">
@@ -22434,7 +22434,7 @@
         <v/>
       </c>
       <c r="F168" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A168,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A168,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A168,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A168,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G168" s="101">
@@ -22467,7 +22467,7 @@
         <v>46183</v>
       </c>
       <c r="B169" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A169,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A169,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C169" s="100">
@@ -22483,7 +22483,7 @@
         <v/>
       </c>
       <c r="F169" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A169,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A169,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A169,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A169,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G169" s="100">
@@ -22516,7 +22516,7 @@
         <v>46184</v>
       </c>
       <c r="B170" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A170,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A170,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C170" s="101">
@@ -22532,7 +22532,7 @@
         <v/>
       </c>
       <c r="F170" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A170,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A170,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A170,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A170,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G170" s="101">
@@ -22565,7 +22565,7 @@
         <v>46185</v>
       </c>
       <c r="B171" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A171,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A171,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C171" s="100">
@@ -22581,7 +22581,7 @@
         <v/>
       </c>
       <c r="F171" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A171,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A171,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A171,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A171,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G171" s="100">
@@ -22614,7 +22614,7 @@
         <v>46186</v>
       </c>
       <c r="B172" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A172,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A172,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C172" s="101">
@@ -22630,7 +22630,7 @@
         <v/>
       </c>
       <c r="F172" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A172,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A172,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A172,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A172,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G172" s="101">
@@ -22663,7 +22663,7 @@
         <v>46187</v>
       </c>
       <c r="B173" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A173,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A173,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C173" s="100">
@@ -22679,7 +22679,7 @@
         <v/>
       </c>
       <c r="F173" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A173,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A173,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A173,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A173,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G173" s="100">
@@ -22712,7 +22712,7 @@
         <v>46188</v>
       </c>
       <c r="B174" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A174,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A174,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C174" s="101">
@@ -22728,7 +22728,7 @@
         <v/>
       </c>
       <c r="F174" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A174,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A174,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A174,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A174,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G174" s="101">
@@ -22761,7 +22761,7 @@
         <v>46189</v>
       </c>
       <c r="B175" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A175,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A175,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C175" s="100">
@@ -22777,7 +22777,7 @@
         <v/>
       </c>
       <c r="F175" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A175,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A175,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A175,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A175,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G175" s="100">
@@ -22810,7 +22810,7 @@
         <v>46190</v>
       </c>
       <c r="B176" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A176,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A176,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C176" s="101">
@@ -22826,7 +22826,7 @@
         <v/>
       </c>
       <c r="F176" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A176,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A176,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A176,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A176,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G176" s="101">
@@ -22859,7 +22859,7 @@
         <v>46191</v>
       </c>
       <c r="B177" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A177,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A177,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C177" s="100">
@@ -22875,7 +22875,7 @@
         <v/>
       </c>
       <c r="F177" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A177,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A177,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A177,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A177,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G177" s="100">
@@ -22908,7 +22908,7 @@
         <v>46192</v>
       </c>
       <c r="B178" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A178,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A178,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C178" s="101">
@@ -22924,7 +22924,7 @@
         <v/>
       </c>
       <c r="F178" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A178,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A178,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A178,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A178,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G178" s="101">
@@ -22957,7 +22957,7 @@
         <v>46193</v>
       </c>
       <c r="B179" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A179,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A179,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C179" s="100">
@@ -22973,7 +22973,7 @@
         <v/>
       </c>
       <c r="F179" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A179,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A179,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A179,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A179,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G179" s="100">
@@ -23006,7 +23006,7 @@
         <v>46194</v>
       </c>
       <c r="B180" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A180,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A180,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C180" s="101">
@@ -23022,7 +23022,7 @@
         <v/>
       </c>
       <c r="F180" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A180,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A180,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A180,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A180,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G180" s="101">
@@ -23055,7 +23055,7 @@
         <v>46195</v>
       </c>
       <c r="B181" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A181,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A181,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C181" s="100">
@@ -23071,7 +23071,7 @@
         <v/>
       </c>
       <c r="F181" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A181,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A181,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A181,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A181,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G181" s="100">
@@ -23104,7 +23104,7 @@
         <v>46196</v>
       </c>
       <c r="B182" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A182,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A182,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C182" s="101">
@@ -23120,7 +23120,7 @@
         <v/>
       </c>
       <c r="F182" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A182,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A182,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A182,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A182,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G182" s="101">
@@ -23153,7 +23153,7 @@
         <v>46197</v>
       </c>
       <c r="B183" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A183,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A183,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C183" s="100">
@@ -23169,7 +23169,7 @@
         <v/>
       </c>
       <c r="F183" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A183,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A183,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A183,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A183,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G183" s="100">
@@ -23202,7 +23202,7 @@
         <v>46198</v>
       </c>
       <c r="B184" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A184,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A184,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C184" s="101">
@@ -23218,7 +23218,7 @@
         <v/>
       </c>
       <c r="F184" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A184,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A184,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A184,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A184,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G184" s="101">
@@ -23251,7 +23251,7 @@
         <v>46199</v>
       </c>
       <c r="B185" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A185,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A185,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C185" s="100">
@@ -23267,7 +23267,7 @@
         <v/>
       </c>
       <c r="F185" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A185,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A185,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A185,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A185,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G185" s="100">
@@ -23300,7 +23300,7 @@
         <v>46200</v>
       </c>
       <c r="B186" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A186,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A186,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C186" s="101">
@@ -23316,7 +23316,7 @@
         <v/>
       </c>
       <c r="F186" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A186,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A186,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A186,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A186,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G186" s="101">
@@ -23349,7 +23349,7 @@
         <v>46201</v>
       </c>
       <c r="B187" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A187,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A187,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C187" s="100">
@@ -23365,7 +23365,7 @@
         <v/>
       </c>
       <c r="F187" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A187,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A187,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A187,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A187,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G187" s="100">
@@ -23398,7 +23398,7 @@
         <v>46202</v>
       </c>
       <c r="B188" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A188,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A188,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C188" s="101">
@@ -23414,7 +23414,7 @@
         <v/>
       </c>
       <c r="F188" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A188,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A188,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A188,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A188,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G188" s="101">
@@ -23447,7 +23447,7 @@
         <v>46203</v>
       </c>
       <c r="B189" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A189,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A189,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C189" s="100">
@@ -23463,7 +23463,7 @@
         <v/>
       </c>
       <c r="F189" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A189,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A189,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A189,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A189,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G189" s="100">
@@ -23496,7 +23496,7 @@
         <v>46204</v>
       </c>
       <c r="B190" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A190,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A190,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C190" s="101">
@@ -23512,7 +23512,7 @@
         <v/>
       </c>
       <c r="F190" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A190,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A190,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A190,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A190,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G190" s="101">
@@ -23545,7 +23545,7 @@
         <v>46205</v>
       </c>
       <c r="B191" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A191,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A191,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C191" s="100">
@@ -23561,7 +23561,7 @@
         <v/>
       </c>
       <c r="F191" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A191,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A191,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A191,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A191,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G191" s="100">
@@ -23594,7 +23594,7 @@
         <v>46206</v>
       </c>
       <c r="B192" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A192,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A192,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C192" s="101">
@@ -23610,7 +23610,7 @@
         <v/>
       </c>
       <c r="F192" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A192,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A192,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A192,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A192,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G192" s="101">
@@ -23643,7 +23643,7 @@
         <v>46207</v>
       </c>
       <c r="B193" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A193,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A193,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C193" s="100">
@@ -23659,7 +23659,7 @@
         <v/>
       </c>
       <c r="F193" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A193,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A193,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A193,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A193,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G193" s="100">
@@ -23692,7 +23692,7 @@
         <v>46208</v>
       </c>
       <c r="B194" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A194,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A194,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C194" s="101">
@@ -23708,7 +23708,7 @@
         <v/>
       </c>
       <c r="F194" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A194,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A194,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A194,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A194,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G194" s="101">
@@ -23741,7 +23741,7 @@
         <v>46209</v>
       </c>
       <c r="B195" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A195,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A195,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C195" s="100">
@@ -23757,7 +23757,7 @@
         <v/>
       </c>
       <c r="F195" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A195,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A195,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A195,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A195,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G195" s="100">
@@ -23790,7 +23790,7 @@
         <v>46210</v>
       </c>
       <c r="B196" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A196,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A196,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C196" s="101">
@@ -23806,7 +23806,7 @@
         <v/>
       </c>
       <c r="F196" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A196,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A196,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A196,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A196,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G196" s="101">
@@ -23839,7 +23839,7 @@
         <v>46211</v>
       </c>
       <c r="B197" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A197,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A197,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C197" s="100">
@@ -23855,7 +23855,7 @@
         <v/>
       </c>
       <c r="F197" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A197,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A197,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A197,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A197,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G197" s="100">
@@ -23888,7 +23888,7 @@
         <v>46212</v>
       </c>
       <c r="B198" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A198,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A198,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C198" s="101">
@@ -23904,7 +23904,7 @@
         <v/>
       </c>
       <c r="F198" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A198,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A198,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A198,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A198,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G198" s="101">
@@ -23937,7 +23937,7 @@
         <v>46213</v>
       </c>
       <c r="B199" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A199,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A199,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C199" s="100">
@@ -23953,7 +23953,7 @@
         <v/>
       </c>
       <c r="F199" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A199,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A199,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A199,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A199,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G199" s="100">
@@ -23986,7 +23986,7 @@
         <v>46214</v>
       </c>
       <c r="B200" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A200,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A200,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C200" s="101">
@@ -24002,7 +24002,7 @@
         <v/>
       </c>
       <c r="F200" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A200,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A200,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A200,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A200,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G200" s="101">
@@ -24035,7 +24035,7 @@
         <v>46215</v>
       </c>
       <c r="B201" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A201,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A201,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C201" s="100">
@@ -24051,7 +24051,7 @@
         <v/>
       </c>
       <c r="F201" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A201,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A201,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A201,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A201,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G201" s="100">
@@ -24084,7 +24084,7 @@
         <v>46216</v>
       </c>
       <c r="B202" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A202,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A202,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C202" s="101">
@@ -24100,7 +24100,7 @@
         <v/>
       </c>
       <c r="F202" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A202,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A202,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A202,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A202,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G202" s="101">
@@ -24133,7 +24133,7 @@
         <v>46217</v>
       </c>
       <c r="B203" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A203,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A203,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C203" s="100">
@@ -24149,7 +24149,7 @@
         <v/>
       </c>
       <c r="F203" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A203,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A203,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A203,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A203,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G203" s="100">
@@ -24182,7 +24182,7 @@
         <v>46218</v>
       </c>
       <c r="B204" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A204,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A204,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C204" s="101">
@@ -24198,7 +24198,7 @@
         <v/>
       </c>
       <c r="F204" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A204,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A204,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A204,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A204,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G204" s="101">
@@ -24231,7 +24231,7 @@
         <v>46219</v>
       </c>
       <c r="B205" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A205,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A205,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C205" s="100">
@@ -24247,7 +24247,7 @@
         <v/>
       </c>
       <c r="F205" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A205,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A205,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A205,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A205,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G205" s="100">
@@ -24280,7 +24280,7 @@
         <v>46220</v>
       </c>
       <c r="B206" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A206,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A206,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C206" s="101">
@@ -24296,7 +24296,7 @@
         <v/>
       </c>
       <c r="F206" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A206,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A206,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A206,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A206,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G206" s="101">
@@ -24329,7 +24329,7 @@
         <v>46221</v>
       </c>
       <c r="B207" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A207,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A207,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C207" s="100">
@@ -24345,7 +24345,7 @@
         <v/>
       </c>
       <c r="F207" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A207,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A207,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A207,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A207,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G207" s="100">
@@ -24378,7 +24378,7 @@
         <v>46222</v>
       </c>
       <c r="B208" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A208,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A208,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C208" s="101">
@@ -24394,7 +24394,7 @@
         <v/>
       </c>
       <c r="F208" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A208,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A208,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A208,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A208,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G208" s="101">
@@ -24427,7 +24427,7 @@
         <v>46223</v>
       </c>
       <c r="B209" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A209,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A209,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C209" s="100">
@@ -24443,7 +24443,7 @@
         <v/>
       </c>
       <c r="F209" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A209,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A209,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A209,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A209,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G209" s="100">
@@ -24476,7 +24476,7 @@
         <v>46224</v>
       </c>
       <c r="B210" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A210,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A210,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C210" s="101">
@@ -24492,7 +24492,7 @@
         <v/>
       </c>
       <c r="F210" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A210,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A210,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A210,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A210,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G210" s="101">
@@ -24525,7 +24525,7 @@
         <v>46225</v>
       </c>
       <c r="B211" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A211,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A211,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C211" s="100">
@@ -24541,7 +24541,7 @@
         <v/>
       </c>
       <c r="F211" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A211,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A211,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A211,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A211,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G211" s="100">
@@ -24574,7 +24574,7 @@
         <v>46226</v>
       </c>
       <c r="B212" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A212,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A212,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C212" s="101">
@@ -24590,7 +24590,7 @@
         <v/>
       </c>
       <c r="F212" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A212,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A212,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A212,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A212,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G212" s="101">
@@ -24623,7 +24623,7 @@
         <v>46227</v>
       </c>
       <c r="B213" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A213,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A213,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C213" s="100">
@@ -24639,7 +24639,7 @@
         <v/>
       </c>
       <c r="F213" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A213,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A213,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A213,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A213,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G213" s="100">
@@ -24672,7 +24672,7 @@
         <v>46228</v>
       </c>
       <c r="B214" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A214,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A214,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C214" s="101">
@@ -24688,7 +24688,7 @@
         <v/>
       </c>
       <c r="F214" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A214,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A214,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A214,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A214,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G214" s="101">
@@ -24721,7 +24721,7 @@
         <v>46229</v>
       </c>
       <c r="B215" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A215,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A215,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C215" s="100">
@@ -24737,7 +24737,7 @@
         <v/>
       </c>
       <c r="F215" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A215,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A215,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A215,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A215,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G215" s="100">
@@ -24770,7 +24770,7 @@
         <v>46230</v>
       </c>
       <c r="B216" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A216,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A216,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C216" s="101">
@@ -24786,7 +24786,7 @@
         <v/>
       </c>
       <c r="F216" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A216,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A216,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A216,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A216,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G216" s="101">
@@ -24819,7 +24819,7 @@
         <v>46231</v>
       </c>
       <c r="B217" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A217,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A217,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C217" s="100">
@@ -24835,7 +24835,7 @@
         <v/>
       </c>
       <c r="F217" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A217,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A217,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A217,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A217,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G217" s="100">
@@ -24868,7 +24868,7 @@
         <v>46232</v>
       </c>
       <c r="B218" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A218,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A218,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C218" s="101">
@@ -24884,7 +24884,7 @@
         <v/>
       </c>
       <c r="F218" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A218,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A218,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A218,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A218,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G218" s="101">
@@ -24917,7 +24917,7 @@
         <v>46233</v>
       </c>
       <c r="B219" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A219,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A219,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C219" s="100">
@@ -24933,7 +24933,7 @@
         <v/>
       </c>
       <c r="F219" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A219,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A219,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A219,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A219,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G219" s="100">
@@ -24966,7 +24966,7 @@
         <v>46234</v>
       </c>
       <c r="B220" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A220,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A220,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C220" s="101">
@@ -24982,7 +24982,7 @@
         <v/>
       </c>
       <c r="F220" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A220,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A220,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A220,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A220,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G220" s="101">
@@ -25015,7 +25015,7 @@
         <v>46235</v>
       </c>
       <c r="B221" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A221,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A221,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C221" s="100">
@@ -25031,7 +25031,7 @@
         <v/>
       </c>
       <c r="F221" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A221,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A221,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A221,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A221,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G221" s="100">
@@ -25064,7 +25064,7 @@
         <v>46236</v>
       </c>
       <c r="B222" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A222,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A222,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C222" s="101">
@@ -25080,7 +25080,7 @@
         <v/>
       </c>
       <c r="F222" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A222,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A222,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A222,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A222,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G222" s="101">
@@ -25113,7 +25113,7 @@
         <v>46237</v>
       </c>
       <c r="B223" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A223,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A223,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C223" s="100">
@@ -25129,7 +25129,7 @@
         <v/>
       </c>
       <c r="F223" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A223,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A223,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A223,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A223,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G223" s="100">
@@ -25162,7 +25162,7 @@
         <v>46238</v>
       </c>
       <c r="B224" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A224,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A224,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C224" s="101">
@@ -25178,7 +25178,7 @@
         <v/>
       </c>
       <c r="F224" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A224,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A224,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A224,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A224,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G224" s="101">
@@ -25211,7 +25211,7 @@
         <v>46239</v>
       </c>
       <c r="B225" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A225,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A225,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C225" s="100">
@@ -25227,7 +25227,7 @@
         <v/>
       </c>
       <c r="F225" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A225,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A225,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A225,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A225,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G225" s="100">
@@ -25260,7 +25260,7 @@
         <v>46240</v>
       </c>
       <c r="B226" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A226,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A226,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C226" s="101">
@@ -25276,7 +25276,7 @@
         <v/>
       </c>
       <c r="F226" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A226,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A226,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A226,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A226,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G226" s="101">
@@ -25309,7 +25309,7 @@
         <v>46241</v>
       </c>
       <c r="B227" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A227,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A227,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C227" s="100">
@@ -25325,7 +25325,7 @@
         <v/>
       </c>
       <c r="F227" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A227,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A227,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A227,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A227,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G227" s="100">
@@ -25358,7 +25358,7 @@
         <v>46242</v>
       </c>
       <c r="B228" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A228,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A228,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C228" s="101">
@@ -25374,7 +25374,7 @@
         <v/>
       </c>
       <c r="F228" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A228,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A228,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A228,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A228,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G228" s="101">
@@ -25407,7 +25407,7 @@
         <v>46243</v>
       </c>
       <c r="B229" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A229,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A229,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C229" s="100">
@@ -25423,7 +25423,7 @@
         <v/>
       </c>
       <c r="F229" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A229,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A229,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A229,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A229,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G229" s="100">
@@ -25456,7 +25456,7 @@
         <v>46244</v>
       </c>
       <c r="B230" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A230,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A230,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C230" s="101">
@@ -25472,7 +25472,7 @@
         <v/>
       </c>
       <c r="F230" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A230,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A230,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A230,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A230,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G230" s="101">
@@ -25505,7 +25505,7 @@
         <v>46245</v>
       </c>
       <c r="B231" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A231,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A231,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C231" s="100">
@@ -25521,7 +25521,7 @@
         <v/>
       </c>
       <c r="F231" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A231,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A231,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A231,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A231,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G231" s="100">
@@ -25554,7 +25554,7 @@
         <v>46246</v>
       </c>
       <c r="B232" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A232,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A232,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C232" s="101">
@@ -25570,7 +25570,7 @@
         <v/>
       </c>
       <c r="F232" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A232,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A232,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A232,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A232,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G232" s="101">
@@ -25603,7 +25603,7 @@
         <v>46247</v>
       </c>
       <c r="B233" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A233,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A233,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C233" s="100">
@@ -25619,7 +25619,7 @@
         <v/>
       </c>
       <c r="F233" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A233,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A233,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A233,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A233,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G233" s="100">
@@ -25652,7 +25652,7 @@
         <v>46248</v>
       </c>
       <c r="B234" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A234,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A234,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C234" s="101">
@@ -25668,7 +25668,7 @@
         <v/>
       </c>
       <c r="F234" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A234,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A234,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A234,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A234,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G234" s="101">
@@ -25701,7 +25701,7 @@
         <v>46249</v>
       </c>
       <c r="B235" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A235,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A235,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C235" s="100">
@@ -25717,7 +25717,7 @@
         <v/>
       </c>
       <c r="F235" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A235,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A235,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A235,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A235,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G235" s="100">
@@ -25750,7 +25750,7 @@
         <v>46250</v>
       </c>
       <c r="B236" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A236,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A236,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C236" s="101">
@@ -25766,7 +25766,7 @@
         <v/>
       </c>
       <c r="F236" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A236,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A236,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A236,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A236,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G236" s="101">
@@ -25799,7 +25799,7 @@
         <v>46251</v>
       </c>
       <c r="B237" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A237,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A237,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C237" s="100">
@@ -25815,7 +25815,7 @@
         <v/>
       </c>
       <c r="F237" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A237,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A237,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A237,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A237,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G237" s="100">
@@ -25848,7 +25848,7 @@
         <v>46252</v>
       </c>
       <c r="B238" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A238,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A238,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C238" s="101">
@@ -25864,7 +25864,7 @@
         <v/>
       </c>
       <c r="F238" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A238,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A238,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A238,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A238,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G238" s="101">
@@ -25897,7 +25897,7 @@
         <v>46253</v>
       </c>
       <c r="B239" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A239,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A239,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C239" s="100">
@@ -25913,7 +25913,7 @@
         <v/>
       </c>
       <c r="F239" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A239,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A239,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A239,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A239,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G239" s="100">
@@ -25946,7 +25946,7 @@
         <v>46254</v>
       </c>
       <c r="B240" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A240,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A240,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C240" s="101">
@@ -25962,7 +25962,7 @@
         <v/>
       </c>
       <c r="F240" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A240,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A240,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A240,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A240,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G240" s="101">
@@ -25995,7 +25995,7 @@
         <v>46255</v>
       </c>
       <c r="B241" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A241,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A241,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C241" s="100">
@@ -26011,7 +26011,7 @@
         <v/>
       </c>
       <c r="F241" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A241,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A241,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A241,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A241,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G241" s="100">
@@ -26044,7 +26044,7 @@
         <v>46256</v>
       </c>
       <c r="B242" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A242,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A242,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C242" s="101">
@@ -26060,7 +26060,7 @@
         <v/>
       </c>
       <c r="F242" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A242,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A242,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A242,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A242,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G242" s="101">
@@ -26093,7 +26093,7 @@
         <v>46257</v>
       </c>
       <c r="B243" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A243,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A243,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C243" s="100">
@@ -26109,7 +26109,7 @@
         <v/>
       </c>
       <c r="F243" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A243,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A243,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A243,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A243,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G243" s="100">
@@ -26142,7 +26142,7 @@
         <v>46258</v>
       </c>
       <c r="B244" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A244,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A244,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C244" s="101">
@@ -26158,7 +26158,7 @@
         <v/>
       </c>
       <c r="F244" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A244,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A244,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A244,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A244,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G244" s="101">
@@ -26191,7 +26191,7 @@
         <v>46259</v>
       </c>
       <c r="B245" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A245,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A245,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C245" s="100">
@@ -26207,7 +26207,7 @@
         <v/>
       </c>
       <c r="F245" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A245,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A245,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A245,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A245,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G245" s="100">
@@ -26240,7 +26240,7 @@
         <v>46260</v>
       </c>
       <c r="B246" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A246,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A246,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C246" s="101">
@@ -26256,7 +26256,7 @@
         <v/>
       </c>
       <c r="F246" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A246,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A246,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A246,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A246,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G246" s="101">
@@ -26289,7 +26289,7 @@
         <v>46261</v>
       </c>
       <c r="B247" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A247,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A247,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C247" s="100">
@@ -26305,7 +26305,7 @@
         <v/>
       </c>
       <c r="F247" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A247,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A247,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A247,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A247,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G247" s="100">
@@ -26338,7 +26338,7 @@
         <v>46262</v>
       </c>
       <c r="B248" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A248,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A248,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C248" s="101">
@@ -26354,7 +26354,7 @@
         <v/>
       </c>
       <c r="F248" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A248,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A248,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A248,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A248,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G248" s="101">
@@ -26387,7 +26387,7 @@
         <v>46263</v>
       </c>
       <c r="B249" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A249,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A249,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C249" s="100">
@@ -26403,7 +26403,7 @@
         <v/>
       </c>
       <c r="F249" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A249,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A249,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A249,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A249,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G249" s="100">
@@ -26436,7 +26436,7 @@
         <v>46264</v>
       </c>
       <c r="B250" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A250,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A250,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C250" s="101">
@@ -26452,7 +26452,7 @@
         <v/>
       </c>
       <c r="F250" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A250,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A250,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A250,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A250,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G250" s="101">
@@ -26485,7 +26485,7 @@
         <v>46265</v>
       </c>
       <c r="B251" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A251,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A251,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C251" s="100">
@@ -26501,7 +26501,7 @@
         <v/>
       </c>
       <c r="F251" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A251,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A251,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A251,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A251,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G251" s="100">
@@ -26534,7 +26534,7 @@
         <v>46266</v>
       </c>
       <c r="B252" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A252,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A252,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C252" s="101">
@@ -26550,7 +26550,7 @@
         <v/>
       </c>
       <c r="F252" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A252,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A252,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A252,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A252,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G252" s="101">
@@ -26583,7 +26583,7 @@
         <v>46267</v>
       </c>
       <c r="B253" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A253,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A253,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C253" s="100">
@@ -26599,7 +26599,7 @@
         <v/>
       </c>
       <c r="F253" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A253,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A253,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A253,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A253,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G253" s="100">
@@ -26632,7 +26632,7 @@
         <v>46268</v>
       </c>
       <c r="B254" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A254,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A254,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C254" s="101">
@@ -26648,7 +26648,7 @@
         <v/>
       </c>
       <c r="F254" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A254,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A254,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A254,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A254,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G254" s="101">
@@ -26681,7 +26681,7 @@
         <v>46269</v>
       </c>
       <c r="B255" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A255,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A255,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C255" s="100">
@@ -26697,7 +26697,7 @@
         <v/>
       </c>
       <c r="F255" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A255,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A255,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A255,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A255,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G255" s="100">
@@ -26730,7 +26730,7 @@
         <v>46270</v>
       </c>
       <c r="B256" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A256,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A256,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C256" s="101">
@@ -26746,7 +26746,7 @@
         <v/>
       </c>
       <c r="F256" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A256,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A256,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A256,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A256,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G256" s="101">
@@ -26779,7 +26779,7 @@
         <v>46271</v>
       </c>
       <c r="B257" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A257,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A257,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C257" s="100">
@@ -26795,7 +26795,7 @@
         <v/>
       </c>
       <c r="F257" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A257,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A257,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A257,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A257,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G257" s="100">
@@ -26828,7 +26828,7 @@
         <v>46272</v>
       </c>
       <c r="B258" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A258,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A258,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C258" s="101">
@@ -26844,7 +26844,7 @@
         <v/>
       </c>
       <c r="F258" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A258,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A258,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A258,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A258,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G258" s="101">
@@ -26877,7 +26877,7 @@
         <v>46273</v>
       </c>
       <c r="B259" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A259,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A259,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C259" s="100">
@@ -26893,7 +26893,7 @@
         <v/>
       </c>
       <c r="F259" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A259,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A259,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A259,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A259,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G259" s="100">
@@ -26926,7 +26926,7 @@
         <v>46274</v>
       </c>
       <c r="B260" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A260,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A260,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C260" s="101">
@@ -26942,7 +26942,7 @@
         <v/>
       </c>
       <c r="F260" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A260,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A260,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A260,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A260,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G260" s="101">
@@ -26975,7 +26975,7 @@
         <v>46275</v>
       </c>
       <c r="B261" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A261,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A261,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C261" s="100">
@@ -26991,7 +26991,7 @@
         <v/>
       </c>
       <c r="F261" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A261,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A261,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A261,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A261,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G261" s="100">
@@ -27024,7 +27024,7 @@
         <v>46276</v>
       </c>
       <c r="B262" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A262,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A262,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C262" s="101">
@@ -27040,7 +27040,7 @@
         <v/>
       </c>
       <c r="F262" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A262,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A262,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A262,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A262,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G262" s="101">
@@ -27073,7 +27073,7 @@
         <v>46277</v>
       </c>
       <c r="B263" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A263,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A263,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C263" s="100">
@@ -27089,7 +27089,7 @@
         <v/>
       </c>
       <c r="F263" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A263,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A263,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A263,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A263,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G263" s="100">
@@ -27122,7 +27122,7 @@
         <v>46278</v>
       </c>
       <c r="B264" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A264,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A264,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C264" s="101">
@@ -27138,7 +27138,7 @@
         <v/>
       </c>
       <c r="F264" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A264,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A264,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A264,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A264,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G264" s="101">
@@ -27171,7 +27171,7 @@
         <v>46279</v>
       </c>
       <c r="B265" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A265,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A265,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C265" s="100">
@@ -27187,7 +27187,7 @@
         <v/>
       </c>
       <c r="F265" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A265,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A265,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A265,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A265,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G265" s="100">
@@ -27220,7 +27220,7 @@
         <v>46280</v>
       </c>
       <c r="B266" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A266,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A266,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C266" s="101">
@@ -27236,7 +27236,7 @@
         <v/>
       </c>
       <c r="F266" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A266,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A266,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A266,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A266,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G266" s="101">
@@ -27269,7 +27269,7 @@
         <v>46281</v>
       </c>
       <c r="B267" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A267,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A267,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A267,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A267,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C267" s="100">
@@ -27285,7 +27285,7 @@
         <v/>
       </c>
       <c r="F267" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A267,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A267,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A267,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A267,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G267" s="100">
@@ -27318,7 +27318,7 @@
         <v>46282</v>
       </c>
       <c r="B268" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A268,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A268,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A268,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A268,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C268" s="101">
@@ -27334,7 +27334,7 @@
         <v/>
       </c>
       <c r="F268" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A268,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A268,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A268,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A268,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G268" s="101">
@@ -27367,7 +27367,7 @@
         <v>46283</v>
       </c>
       <c r="B269" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$279,MATCH($A269,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$B$25:$B$279,MATCH($A269,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A269,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A269,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="C269" s="100">
@@ -27383,7 +27383,7 @@
         <v/>
       </c>
       <c r="F269" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$279,MATCH($A269,Polymarket!$A$25:$A$279,0))=0,"",INDEX(Polymarket!$C$25:$C$279,MATCH($A269,Polymarket!$A$25:$A$279,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A269,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A269,Polymarket!$A$25:$A$280,0))),"")</f>
         <v/>
       </c>
       <c r="G269" s="100">
@@ -27408,6 +27408,55 @@
       <c r="L269" s="26" t="inlineStr">
         <is>
           <t>18 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="41" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B270" s="101">
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A270,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A270,Polymarket!$A$25:$A$280,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C270" s="101">
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A270,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A270,Kalshi!$A$31:$A$462,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D270" s="31">
+        <f>IF(AND(ISNUMBER(B270),ISNUMBER(C270)),B270-C270,"")</f>
+        <v/>
+      </c>
+      <c r="E270" s="29">
+        <f>IF(ISNUMBER(D270),ABS(D270),"")</f>
+        <v/>
+      </c>
+      <c r="F270" s="101">
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A270,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A270,Polymarket!$A$25:$A$280,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G270" s="101">
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A270,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A270,Kalshi!$A$31:$A$462,0))),"")</f>
+        <v/>
+      </c>
+      <c r="H270" s="30">
+        <f>IF(AND(ISNUMBER(B270),ISNUMBER(C270)),MIN(B270,C270),"")</f>
+        <v/>
+      </c>
+      <c r="I270" s="30">
+        <f>IF(AND(ISNUMBER(F270),ISNUMBER(G270)),MIN(F270,G270),"")</f>
+        <v/>
+      </c>
+      <c r="J270" s="29">
+        <f>IF(AND(ISNUMBER(H270),ISNUMBER(I270)),H270+I270,"")</f>
+        <v/>
+      </c>
+      <c r="K270" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L270" s="38" t="inlineStr">
+        <is>
+          <t>19 Sep</t>
         </is>
       </c>
     </row>
@@ -27440,7 +27489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-18 19:35 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -28600,7 +28649,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-18 19:35 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -28681,7 +28730,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-18 19:35 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -28840,7 +28889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K279"/>
+  <dimension ref="A1:K280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28865,7 +28914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-18 19:35 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -29021,7 +29070,7 @@
         <v>24448.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>6070.959801999999</v>
+        <v>6070.959802000001</v>
       </c>
     </row>
     <row r="13">
@@ -29031,10 +29080,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>9837.8374</v>
+        <v>10262.9195</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>10586.9709</v>
+        <v>12448.2311</v>
       </c>
     </row>
     <row r="14">
@@ -29057,10 +29106,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="17">
@@ -29130,7 +29179,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0.8</v>
@@ -29144,10 +29193,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>79.98999999999999</v>
+        <v>225</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29161,10 +29210,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29175,10 +29224,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>200</v>
+        <v>6934</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40454,10 +40503,10 @@
         <v>46283</v>
       </c>
       <c r="B279" s="16" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="C279" s="16" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="D279" s="17">
         <f>IF(COUNT(B279:C279)=2,B279+C279,"")</f>
@@ -40490,6 +40539,50 @@
       <c r="K279" s="26" t="inlineStr">
         <is>
           <t>18 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="41" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B280" s="28" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="C280" s="28" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D280" s="29">
+        <f>IF(COUNT(B280:C280)=2,B280+C280,"")</f>
+        <v/>
+      </c>
+      <c r="E280" s="30">
+        <f>IF(ISNUMBER(B280),IFERROR(B280/$D280,""),"")</f>
+        <v/>
+      </c>
+      <c r="F280" s="30">
+        <f>IF(ISNUMBER(C280),IFERROR(C280/$D280,""),"")</f>
+        <v/>
+      </c>
+      <c r="G280" s="31">
+        <f>IF(COUNT(B280:C280)=2,B280-C280,"")</f>
+        <v/>
+      </c>
+      <c r="H280" s="31">
+        <f>IFERROR(IF(AND(ISNUMBER(B280),INDEX($B$25:$B280,MATCH($A280-7,$A$25:$A280,1))&lt;&gt;0,INDEX($A$25:$A280,MATCH($A280-7,$A$25:$A280,1))&lt;&gt;0,$A280-INDEX($A$25:$A280,MATCH($A280-7,$A$25:$A280,1))&lt;=10),B280-INDEX($B$25:$B280,MATCH($A280-7,$A$25:$A280,1)),""),"")</f>
+        <v/>
+      </c>
+      <c r="I280" s="31">
+        <f>IFERROR(IF(AND(ISNUMBER(B280),INDEX($B$25:$B280,MATCH($A280-30,$A$25:$A280,1))&lt;&gt;0,INDEX($A$25:$A280,MATCH($A280-30,$A$25:$A280,1))&lt;&gt;0,$A280-INDEX($A$25:$A280,MATCH($A280-30,$A$25:$A280,1))&lt;=33),B280-INDEX($B$25:$B280,MATCH($A280-30,$A$25:$A280,1)),""),"")</f>
+        <v/>
+      </c>
+      <c r="J280" s="42">
+        <f>DATE(2026,11,3)-A280</f>
+        <v/>
+      </c>
+      <c r="K280" s="26" t="inlineStr">
+        <is>
+          <t>19 Sep</t>
         </is>
       </c>
     </row>
@@ -40532,7 +40625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-18 19:35 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40894,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>29.93</v>
+        <v>82.22</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40935,13 +41028,13 @@
         <v>0.79</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>29.93</v>
+        <v>82.22</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>10518</v>
+        <v>10796.48</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0.2</v>
@@ -40953,7 +41046,7 @@
         <v>0.79</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>28</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="24">
@@ -40964,25 +41057,25 @@
         <v>0.78</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>239</v>
+        <v>207.34</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.18</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>279</v>
+        <v>718</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>0.78</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>167</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25">
@@ -40993,7 +41086,7 @@
         <v>0.77</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>50946.26</v>
+        <v>50958.92</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
@@ -41005,7 +41098,7 @@
         <v>0.18</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>500</v>
+        <v>411</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>0.77</v>
@@ -41034,7 +41127,7 @@
         <v>0.17</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>50590</v>
+        <v>50500</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>0.76</v>
@@ -61749,7 +61842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -61775,7 +61868,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-18 19:35 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -61894,7 +61987,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>70151.11087</v>
+        <v>26543.24248</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -61993,10 +62086,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -62014,7 +62107,7 @@
         <v>751.9541730000001</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8825.900100000001</v>
+        <v>250.8313</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62034,7 +62127,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.134</v>
+        <v>0.14</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62052,7 +62145,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8646.115659999999</v>
+        <v>8318.6726</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62068,11 +62161,9 @@
       <c r="B18" s="78" t="n">
         <v>-1.5</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="C18" s="16" t="n"/>
       <c r="D18" s="16" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -62090,7 +62181,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>228.4396</v>
+        <v>191.5515</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62107,10 +62198,10 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -62128,7 +62219,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8493.142900000001</v>
+        <v>8315.9421</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62166,7 +62257,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8505.497499999999</v>
+        <v>8469.404200000001</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62183,10 +62274,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.163</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.21</v>
+        <v>0.398</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62204,7 +62295,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>18686.9989</v>
+        <v>140.30802</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62221,10 +62312,10 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="E22" s="17">
         <f>IF(COUNT(C22:D22)=2,(C22+D22)/2,"")</f>
@@ -62242,7 +62333,7 @@
         <v>122.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>8316.623900000001</v>
+        <v>175.8884</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62278,7 +62369,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>117.4599</v>
+        <v>183.4474</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62295,7 +62386,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62316,7 +62407,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>113.69957</v>
+        <v>213.37916</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62333,10 +62424,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62354,7 +62445,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>8489.522300000001</v>
+        <v>154.3533</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -63889,40 +63980,75 @@
         <v>46283</v>
       </c>
       <c r="B80" s="28" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="C80" s="28" t="n">
-        <v>0.117</v>
+        <v>0.1125</v>
       </c>
       <c r="D80" s="28" t="n">
-        <v>0.055</v>
+        <v>0.08</v>
       </c>
       <c r="E80" s="28" t="n">
         <v>0.14</v>
       </c>
       <c r="F80" s="28" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G80" s="28" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="H80" s="28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I80" s="28" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J80" s="28" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="K80" s="28" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="39" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B81" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F81" s="16" t="n">
         <v>0.135</v>
       </c>
-      <c r="G80" s="28" t="n">
-        <v>0.1865</v>
-      </c>
-      <c r="H80" s="28" t="n">
+      <c r="G81" s="16" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H81" s="16" t="n">
         <v>0.065</v>
       </c>
-      <c r="I80" s="28" t="n">
+      <c r="I81" s="16" t="n">
         <v>0.04</v>
       </c>
-      <c r="J80" s="28" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="K80" s="28" t="n">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>All ten brackets, daily closes from CLOB /prices-history at fidelity=1440. The market opened 11 Aug 2026, so the series is only 38 days long and the brackets are thin — read it as a sanity check on the ladder above, not as a trend.</t>
+      <c r="J81" s="16" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="K81" s="16" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>All ten brackets, daily closes from CLOB /prices-history at fidelity=1440. The market opened 11 Aug 2026, so the series is only 39 days long and the brackets are thin — read it as a sanity check on the ladder above, not as a trend.</t>
         </is>
       </c>
     </row>
@@ -63933,7 +64059,7 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A82:K82"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="B8:F8"/>
@@ -63975,7 +64101,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-18 19:35 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -65228,7 +65354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-18 19:35 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -65475,7 +65601,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.89</v>
@@ -65511,10 +65637,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="E16" s="20">
         <f>IF(ISNUMBER(D16),1-D16,"")</f>
@@ -65547,10 +65673,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="E17" s="20">
         <f>IF(ISNUMBER(D17),1-D17,"")</f>
@@ -65586,7 +65712,7 @@
         <v>0.27</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66656,7 +66782,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-18 19:35 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-19 01:10 UTC.</t>
         </is>
       </c>
     </row>
@@ -67231,7 +67357,7 @@
         </is>
       </c>
       <c r="B28" s="50" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="29">

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -1620,12 +1620,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$462</f>
+              <f>'Kalshi'!$M$31:$M$463</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$B$31:$B$462</f>
+              <f>'Kalshi'!$B$31:$B$463</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1656,12 +1656,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$462</f>
+              <f>'Kalshi'!$M$31:$M$463</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$C$31:$C$462</f>
+              <f>'Kalshi'!$C$31:$C$463</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1880,12 +1880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$462</f>
+              <f>'Kalshi'!$M$31:$M$463</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$L$31:$L$462</f>
+              <f>'Kalshi'!$L$31:$L$463</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-19 01:10 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-19 01:10 UTC</t>
+          <t>2026-09-19 14:25 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="B70" s="59">
-        <f>TEXT(Kalshi!A31,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Kalshi!A462,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Kalshi!A31:A462)&amp;" days)"</f>
+        <f>TEXT(Kalshi!A31,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Kalshi!A463,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Kalshi!A31:A463)&amp;" days)"</f>
         <v/>
       </c>
       <c r="C70" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-19 01:10 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-19 01:10 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-19 01:10 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v/>
       </c>
       <c r="C15" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A15,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A15,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A15,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A15,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D15" s="18">
@@ -14941,7 +14941,7 @@
         <v/>
       </c>
       <c r="G15" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A15,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A15,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A15,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A15,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H15" s="20">
@@ -14974,7 +14974,7 @@
         <v/>
       </c>
       <c r="C16" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A16,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A16,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A16,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A16,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D16" s="31">
@@ -14990,7 +14990,7 @@
         <v/>
       </c>
       <c r="G16" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A16,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A16,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A16,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A16,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H16" s="30">
@@ -15023,7 +15023,7 @@
         <v/>
       </c>
       <c r="C17" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A17,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A17,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A17,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A17,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D17" s="18">
@@ -15039,7 +15039,7 @@
         <v/>
       </c>
       <c r="G17" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A17,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A17,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A17,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A17,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H17" s="20">
@@ -15072,7 +15072,7 @@
         <v/>
       </c>
       <c r="C18" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A18,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A18,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A18,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A18,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D18" s="31">
@@ -15088,7 +15088,7 @@
         <v/>
       </c>
       <c r="G18" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A18,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A18,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A18,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A18,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H18" s="30">
@@ -15121,7 +15121,7 @@
         <v/>
       </c>
       <c r="C19" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A19,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A19,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A19,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A19,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D19" s="18">
@@ -15137,7 +15137,7 @@
         <v/>
       </c>
       <c r="G19" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A19,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A19,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A19,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A19,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H19" s="20">
@@ -15170,7 +15170,7 @@
         <v/>
       </c>
       <c r="C20" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A20,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A20,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A20,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A20,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D20" s="31">
@@ -15186,7 +15186,7 @@
         <v/>
       </c>
       <c r="G20" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A20,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A20,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A20,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A20,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H20" s="30">
@@ -15219,7 +15219,7 @@
         <v/>
       </c>
       <c r="C21" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A21,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A21,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A21,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A21,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D21" s="18">
@@ -15235,7 +15235,7 @@
         <v/>
       </c>
       <c r="G21" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A21,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A21,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A21,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A21,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
@@ -15268,7 +15268,7 @@
         <v/>
       </c>
       <c r="C22" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A22,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A22,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A22,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A22,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D22" s="31">
@@ -15284,7 +15284,7 @@
         <v/>
       </c>
       <c r="G22" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A22,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A22,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A22,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A22,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H22" s="30">
@@ -15317,7 +15317,7 @@
         <v/>
       </c>
       <c r="C23" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A23,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A23,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A23,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A23,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D23" s="18">
@@ -15333,7 +15333,7 @@
         <v/>
       </c>
       <c r="G23" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A23,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A23,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A23,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A23,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
@@ -15366,7 +15366,7 @@
         <v/>
       </c>
       <c r="C24" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A24,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A24,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A24,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A24,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D24" s="31">
@@ -15382,7 +15382,7 @@
         <v/>
       </c>
       <c r="G24" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A24,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A24,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A24,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A24,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H24" s="30">
@@ -15415,7 +15415,7 @@
         <v/>
       </c>
       <c r="C25" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A25,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A25,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A25,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A25,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D25" s="18">
@@ -15431,7 +15431,7 @@
         <v/>
       </c>
       <c r="G25" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A25,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A25,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A25,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A25,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
@@ -15464,7 +15464,7 @@
         <v/>
       </c>
       <c r="C26" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A26,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A26,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A26,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A26,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D26" s="31">
@@ -15480,7 +15480,7 @@
         <v/>
       </c>
       <c r="G26" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A26,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A26,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A26,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A26,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H26" s="30">
@@ -15513,7 +15513,7 @@
         <v/>
       </c>
       <c r="C27" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A27,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A27,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A27,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A27,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D27" s="18">
@@ -15529,7 +15529,7 @@
         <v/>
       </c>
       <c r="G27" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A27,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A27,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A27,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A27,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H27" s="20">
@@ -15562,7 +15562,7 @@
         <v/>
       </c>
       <c r="C28" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A28,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A28,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A28,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A28,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D28" s="31">
@@ -15578,7 +15578,7 @@
         <v/>
       </c>
       <c r="G28" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A28,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A28,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A28,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A28,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H28" s="30">
@@ -15611,7 +15611,7 @@
         <v/>
       </c>
       <c r="C29" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A29,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A29,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A29,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A29,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D29" s="18">
@@ -15627,7 +15627,7 @@
         <v/>
       </c>
       <c r="G29" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A29,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A29,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A29,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A29,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H29" s="20">
@@ -15660,7 +15660,7 @@
         <v/>
       </c>
       <c r="C30" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A30,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A30,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A30,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A30,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D30" s="31">
@@ -15676,7 +15676,7 @@
         <v/>
       </c>
       <c r="G30" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A30,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A30,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A30,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A30,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H30" s="30">
@@ -15709,7 +15709,7 @@
         <v/>
       </c>
       <c r="C31" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A31,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A31,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A31,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A31,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D31" s="18">
@@ -15725,7 +15725,7 @@
         <v/>
       </c>
       <c r="G31" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A31,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A31,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A31,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A31,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H31" s="20">
@@ -15758,7 +15758,7 @@
         <v/>
       </c>
       <c r="C32" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A32,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A32,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A32,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A32,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D32" s="31">
@@ -15774,7 +15774,7 @@
         <v/>
       </c>
       <c r="G32" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A32,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A32,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A32,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A32,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H32" s="30">
@@ -15807,7 +15807,7 @@
         <v/>
       </c>
       <c r="C33" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A33,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A33,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A33,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A33,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D33" s="18">
@@ -15823,7 +15823,7 @@
         <v/>
       </c>
       <c r="G33" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A33,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A33,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A33,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A33,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H33" s="20">
@@ -15856,7 +15856,7 @@
         <v/>
       </c>
       <c r="C34" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A34,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A34,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A34,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A34,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D34" s="31">
@@ -15872,7 +15872,7 @@
         <v/>
       </c>
       <c r="G34" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A34,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A34,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A34,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A34,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H34" s="30">
@@ -15905,7 +15905,7 @@
         <v/>
       </c>
       <c r="C35" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A35,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A35,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A35,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A35,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D35" s="18">
@@ -15921,7 +15921,7 @@
         <v/>
       </c>
       <c r="G35" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A35,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A35,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A35,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A35,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H35" s="20">
@@ -15954,7 +15954,7 @@
         <v/>
       </c>
       <c r="C36" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A36,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A36,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A36,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A36,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D36" s="31">
@@ -15970,7 +15970,7 @@
         <v/>
       </c>
       <c r="G36" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A36,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A36,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A36,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A36,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H36" s="30">
@@ -16003,7 +16003,7 @@
         <v/>
       </c>
       <c r="C37" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A37,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A37,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A37,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A37,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D37" s="18">
@@ -16019,7 +16019,7 @@
         <v/>
       </c>
       <c r="G37" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A37,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A37,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A37,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A37,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H37" s="20">
@@ -16052,7 +16052,7 @@
         <v/>
       </c>
       <c r="C38" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A38,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A38,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A38,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A38,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D38" s="31">
@@ -16068,7 +16068,7 @@
         <v/>
       </c>
       <c r="G38" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A38,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A38,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A38,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A38,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H38" s="30">
@@ -16101,7 +16101,7 @@
         <v/>
       </c>
       <c r="C39" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A39,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A39,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A39,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A39,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D39" s="18">
@@ -16117,7 +16117,7 @@
         <v/>
       </c>
       <c r="G39" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A39,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A39,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A39,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A39,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H39" s="20">
@@ -16150,7 +16150,7 @@
         <v/>
       </c>
       <c r="C40" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A40,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A40,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A40,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A40,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D40" s="31">
@@ -16166,7 +16166,7 @@
         <v/>
       </c>
       <c r="G40" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A40,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A40,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A40,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A40,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H40" s="30">
@@ -16199,7 +16199,7 @@
         <v/>
       </c>
       <c r="C41" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A41,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A41,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A41,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A41,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D41" s="18">
@@ -16215,7 +16215,7 @@
         <v/>
       </c>
       <c r="G41" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A41,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A41,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A41,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A41,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H41" s="20">
@@ -16248,7 +16248,7 @@
         <v/>
       </c>
       <c r="C42" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A42,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A42,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A42,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A42,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D42" s="31">
@@ -16264,7 +16264,7 @@
         <v/>
       </c>
       <c r="G42" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A42,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A42,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A42,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A42,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H42" s="30">
@@ -16297,7 +16297,7 @@
         <v/>
       </c>
       <c r="C43" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A43,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A43,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A43,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A43,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D43" s="18">
@@ -16313,7 +16313,7 @@
         <v/>
       </c>
       <c r="G43" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A43,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A43,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A43,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A43,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H43" s="20">
@@ -16346,7 +16346,7 @@
         <v/>
       </c>
       <c r="C44" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A44,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A44,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A44,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A44,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D44" s="31">
@@ -16362,7 +16362,7 @@
         <v/>
       </c>
       <c r="G44" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A44,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A44,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A44,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A44,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H44" s="30">
@@ -16395,7 +16395,7 @@
         <v/>
       </c>
       <c r="C45" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A45,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A45,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A45,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A45,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D45" s="18">
@@ -16411,7 +16411,7 @@
         <v/>
       </c>
       <c r="G45" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A45,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A45,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A45,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A45,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H45" s="20">
@@ -16444,7 +16444,7 @@
         <v/>
       </c>
       <c r="C46" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A46,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A46,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A46,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A46,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D46" s="31">
@@ -16460,7 +16460,7 @@
         <v/>
       </c>
       <c r="G46" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A46,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A46,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A46,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A46,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H46" s="30">
@@ -16493,7 +16493,7 @@
         <v/>
       </c>
       <c r="C47" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A47,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A47,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A47,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A47,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D47" s="18">
@@ -16509,7 +16509,7 @@
         <v/>
       </c>
       <c r="G47" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A47,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A47,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A47,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A47,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H47" s="20">
@@ -16542,7 +16542,7 @@
         <v/>
       </c>
       <c r="C48" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A48,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A48,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A48,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A48,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D48" s="31">
@@ -16558,7 +16558,7 @@
         <v/>
       </c>
       <c r="G48" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A48,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A48,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A48,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A48,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H48" s="30">
@@ -16591,7 +16591,7 @@
         <v/>
       </c>
       <c r="C49" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A49,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A49,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A49,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A49,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D49" s="18">
@@ -16607,7 +16607,7 @@
         <v/>
       </c>
       <c r="G49" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A49,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A49,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A49,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A49,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H49" s="20">
@@ -16640,7 +16640,7 @@
         <v/>
       </c>
       <c r="C50" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A50,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A50,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A50,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A50,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D50" s="31">
@@ -16656,7 +16656,7 @@
         <v/>
       </c>
       <c r="G50" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A50,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A50,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A50,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A50,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H50" s="30">
@@ -16689,7 +16689,7 @@
         <v/>
       </c>
       <c r="C51" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A51,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A51,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A51,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A51,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D51" s="18">
@@ -16705,7 +16705,7 @@
         <v/>
       </c>
       <c r="G51" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A51,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A51,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A51,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A51,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H51" s="20">
@@ -16738,7 +16738,7 @@
         <v/>
       </c>
       <c r="C52" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A52,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A52,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A52,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A52,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D52" s="31">
@@ -16754,7 +16754,7 @@
         <v/>
       </c>
       <c r="G52" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A52,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A52,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A52,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A52,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H52" s="30">
@@ -16787,7 +16787,7 @@
         <v/>
       </c>
       <c r="C53" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A53,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A53,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A53,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A53,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D53" s="18">
@@ -16803,7 +16803,7 @@
         <v/>
       </c>
       <c r="G53" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A53,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A53,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A53,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A53,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H53" s="20">
@@ -16836,7 +16836,7 @@
         <v/>
       </c>
       <c r="C54" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A54,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A54,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A54,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A54,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D54" s="31">
@@ -16852,7 +16852,7 @@
         <v/>
       </c>
       <c r="G54" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A54,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A54,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A54,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A54,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H54" s="30">
@@ -16885,7 +16885,7 @@
         <v/>
       </c>
       <c r="C55" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A55,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A55,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A55,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A55,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D55" s="18">
@@ -16901,7 +16901,7 @@
         <v/>
       </c>
       <c r="G55" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A55,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A55,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A55,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A55,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H55" s="20">
@@ -16934,7 +16934,7 @@
         <v/>
       </c>
       <c r="C56" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A56,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A56,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A56,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A56,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D56" s="31">
@@ -16950,7 +16950,7 @@
         <v/>
       </c>
       <c r="G56" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A56,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A56,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A56,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A56,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H56" s="30">
@@ -16983,7 +16983,7 @@
         <v/>
       </c>
       <c r="C57" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A57,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A57,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A57,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A57,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D57" s="18">
@@ -16999,7 +16999,7 @@
         <v/>
       </c>
       <c r="G57" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A57,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A57,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A57,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A57,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H57" s="20">
@@ -17032,7 +17032,7 @@
         <v/>
       </c>
       <c r="C58" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A58,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A58,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A58,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A58,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D58" s="31">
@@ -17048,7 +17048,7 @@
         <v/>
       </c>
       <c r="G58" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A58,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A58,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A58,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A58,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H58" s="30">
@@ -17081,7 +17081,7 @@
         <v/>
       </c>
       <c r="C59" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A59,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A59,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A59,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A59,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D59" s="18">
@@ -17097,7 +17097,7 @@
         <v/>
       </c>
       <c r="G59" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A59,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A59,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A59,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A59,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H59" s="20">
@@ -17130,7 +17130,7 @@
         <v/>
       </c>
       <c r="C60" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A60,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A60,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A60,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A60,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D60" s="31">
@@ -17146,7 +17146,7 @@
         <v/>
       </c>
       <c r="G60" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A60,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A60,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A60,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A60,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H60" s="30">
@@ -17179,7 +17179,7 @@
         <v/>
       </c>
       <c r="C61" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A61,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A61,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A61,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A61,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D61" s="18">
@@ -17195,7 +17195,7 @@
         <v/>
       </c>
       <c r="G61" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A61,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A61,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A61,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A61,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H61" s="20">
@@ -17228,7 +17228,7 @@
         <v/>
       </c>
       <c r="C62" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A62,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A62,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A62,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A62,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D62" s="31">
@@ -17244,7 +17244,7 @@
         <v/>
       </c>
       <c r="G62" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A62,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A62,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A62,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A62,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H62" s="30">
@@ -17277,7 +17277,7 @@
         <v/>
       </c>
       <c r="C63" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A63,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A63,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A63,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A63,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D63" s="18">
@@ -17293,7 +17293,7 @@
         <v/>
       </c>
       <c r="G63" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A63,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A63,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A63,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A63,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H63" s="20">
@@ -17326,7 +17326,7 @@
         <v/>
       </c>
       <c r="C64" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A64,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A64,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A64,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A64,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D64" s="31">
@@ -17342,7 +17342,7 @@
         <v/>
       </c>
       <c r="G64" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A64,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A64,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A64,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A64,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H64" s="30">
@@ -17375,7 +17375,7 @@
         <v/>
       </c>
       <c r="C65" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A65,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A65,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A65,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A65,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D65" s="18">
@@ -17391,7 +17391,7 @@
         <v/>
       </c>
       <c r="G65" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A65,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A65,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A65,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A65,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H65" s="20">
@@ -17424,7 +17424,7 @@
         <v/>
       </c>
       <c r="C66" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A66,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A66,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A66,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A66,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D66" s="31">
@@ -17440,7 +17440,7 @@
         <v/>
       </c>
       <c r="G66" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A66,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A66,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A66,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A66,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H66" s="30">
@@ -17473,7 +17473,7 @@
         <v/>
       </c>
       <c r="C67" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A67,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A67,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A67,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A67,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D67" s="18">
@@ -17489,7 +17489,7 @@
         <v/>
       </c>
       <c r="G67" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A67,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A67,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A67,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A67,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H67" s="20">
@@ -17522,7 +17522,7 @@
         <v/>
       </c>
       <c r="C68" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A68,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A68,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A68,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A68,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D68" s="31">
@@ -17538,7 +17538,7 @@
         <v/>
       </c>
       <c r="G68" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A68,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A68,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A68,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A68,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H68" s="30">
@@ -17571,7 +17571,7 @@
         <v/>
       </c>
       <c r="C69" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A69,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A69,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A69,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A69,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D69" s="18">
@@ -17587,7 +17587,7 @@
         <v/>
       </c>
       <c r="G69" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A69,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A69,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A69,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A69,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H69" s="20">
@@ -17620,7 +17620,7 @@
         <v/>
       </c>
       <c r="C70" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A70,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A70,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A70,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A70,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D70" s="31">
@@ -17636,7 +17636,7 @@
         <v/>
       </c>
       <c r="G70" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A70,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A70,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A70,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A70,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H70" s="30">
@@ -17669,7 +17669,7 @@
         <v/>
       </c>
       <c r="C71" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A71,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A71,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A71,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A71,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D71" s="18">
@@ -17685,7 +17685,7 @@
         <v/>
       </c>
       <c r="G71" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A71,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A71,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A71,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A71,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H71" s="20">
@@ -17718,7 +17718,7 @@
         <v/>
       </c>
       <c r="C72" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A72,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A72,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A72,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A72,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D72" s="31">
@@ -17734,7 +17734,7 @@
         <v/>
       </c>
       <c r="G72" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A72,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A72,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A72,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A72,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H72" s="30">
@@ -17767,7 +17767,7 @@
         <v/>
       </c>
       <c r="C73" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A73,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A73,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A73,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A73,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D73" s="18">
@@ -17783,7 +17783,7 @@
         <v/>
       </c>
       <c r="G73" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A73,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A73,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A73,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A73,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H73" s="20">
@@ -17816,7 +17816,7 @@
         <v/>
       </c>
       <c r="C74" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A74,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A74,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A74,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A74,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D74" s="31">
@@ -17832,7 +17832,7 @@
         <v/>
       </c>
       <c r="G74" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A74,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A74,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A74,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A74,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H74" s="30">
@@ -17865,7 +17865,7 @@
         <v/>
       </c>
       <c r="C75" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A75,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A75,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A75,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A75,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D75" s="18">
@@ -17881,7 +17881,7 @@
         <v/>
       </c>
       <c r="G75" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A75,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A75,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A75,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A75,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H75" s="20">
@@ -17914,7 +17914,7 @@
         <v/>
       </c>
       <c r="C76" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A76,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A76,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A76,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A76,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D76" s="31">
@@ -17930,7 +17930,7 @@
         <v/>
       </c>
       <c r="G76" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A76,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A76,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A76,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A76,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H76" s="30">
@@ -17963,7 +17963,7 @@
         <v/>
       </c>
       <c r="C77" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A77,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A77,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A77,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A77,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D77" s="18">
@@ -17979,7 +17979,7 @@
         <v/>
       </c>
       <c r="G77" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A77,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A77,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A77,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A77,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H77" s="20">
@@ -18012,7 +18012,7 @@
         <v/>
       </c>
       <c r="C78" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A78,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A78,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A78,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A78,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D78" s="31">
@@ -18028,7 +18028,7 @@
         <v/>
       </c>
       <c r="G78" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A78,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A78,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A78,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A78,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H78" s="30">
@@ -18061,7 +18061,7 @@
         <v/>
       </c>
       <c r="C79" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A79,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A79,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A79,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A79,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D79" s="18">
@@ -18077,7 +18077,7 @@
         <v/>
       </c>
       <c r="G79" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A79,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A79,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A79,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A79,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H79" s="20">
@@ -18110,7 +18110,7 @@
         <v/>
       </c>
       <c r="C80" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A80,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A80,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A80,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A80,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D80" s="31">
@@ -18126,7 +18126,7 @@
         <v/>
       </c>
       <c r="G80" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A80,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A80,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A80,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A80,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H80" s="30">
@@ -18159,7 +18159,7 @@
         <v/>
       </c>
       <c r="C81" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A81,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A81,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A81,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A81,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D81" s="18">
@@ -18175,7 +18175,7 @@
         <v/>
       </c>
       <c r="G81" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A81,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A81,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A81,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A81,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H81" s="20">
@@ -18208,7 +18208,7 @@
         <v/>
       </c>
       <c r="C82" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A82,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A82,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A82,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A82,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D82" s="31">
@@ -18224,7 +18224,7 @@
         <v/>
       </c>
       <c r="G82" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A82,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A82,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A82,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A82,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H82" s="30">
@@ -18257,7 +18257,7 @@
         <v/>
       </c>
       <c r="C83" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A83,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A83,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A83,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A83,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D83" s="18">
@@ -18273,7 +18273,7 @@
         <v/>
       </c>
       <c r="G83" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A83,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A83,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A83,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A83,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H83" s="20">
@@ -18306,7 +18306,7 @@
         <v/>
       </c>
       <c r="C84" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A84,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A84,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A84,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A84,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D84" s="31">
@@ -18322,7 +18322,7 @@
         <v/>
       </c>
       <c r="G84" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A84,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A84,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A84,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A84,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H84" s="30">
@@ -18355,7 +18355,7 @@
         <v/>
       </c>
       <c r="C85" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A85,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A85,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A85,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A85,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D85" s="18">
@@ -18371,7 +18371,7 @@
         <v/>
       </c>
       <c r="G85" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A85,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A85,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A85,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A85,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H85" s="20">
@@ -18404,7 +18404,7 @@
         <v/>
       </c>
       <c r="C86" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A86,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A86,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A86,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A86,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D86" s="31">
@@ -18420,7 +18420,7 @@
         <v/>
       </c>
       <c r="G86" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A86,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A86,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A86,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A86,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H86" s="30">
@@ -18453,7 +18453,7 @@
         <v/>
       </c>
       <c r="C87" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A87,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A87,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A87,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A87,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D87" s="18">
@@ -18469,7 +18469,7 @@
         <v/>
       </c>
       <c r="G87" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A87,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A87,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A87,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A87,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H87" s="20">
@@ -18502,7 +18502,7 @@
         <v/>
       </c>
       <c r="C88" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A88,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A88,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A88,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A88,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D88" s="31">
@@ -18518,7 +18518,7 @@
         <v/>
       </c>
       <c r="G88" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A88,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A88,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A88,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A88,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H88" s="30">
@@ -18551,7 +18551,7 @@
         <v/>
       </c>
       <c r="C89" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A89,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A89,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A89,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A89,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D89" s="18">
@@ -18567,7 +18567,7 @@
         <v/>
       </c>
       <c r="G89" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A89,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A89,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A89,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A89,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H89" s="20">
@@ -18600,7 +18600,7 @@
         <v/>
       </c>
       <c r="C90" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A90,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A90,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A90,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A90,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D90" s="31">
@@ -18616,7 +18616,7 @@
         <v/>
       </c>
       <c r="G90" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A90,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A90,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A90,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A90,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H90" s="30">
@@ -18649,7 +18649,7 @@
         <v/>
       </c>
       <c r="C91" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A91,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A91,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A91,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A91,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D91" s="18">
@@ -18665,7 +18665,7 @@
         <v/>
       </c>
       <c r="G91" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A91,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A91,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A91,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A91,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H91" s="20">
@@ -18698,7 +18698,7 @@
         <v/>
       </c>
       <c r="C92" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A92,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A92,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A92,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A92,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D92" s="31">
@@ -18714,7 +18714,7 @@
         <v/>
       </c>
       <c r="G92" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A92,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A92,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A92,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A92,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H92" s="30">
@@ -18747,7 +18747,7 @@
         <v/>
       </c>
       <c r="C93" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A93,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A93,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A93,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A93,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D93" s="18">
@@ -18763,7 +18763,7 @@
         <v/>
       </c>
       <c r="G93" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A93,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A93,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A93,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A93,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H93" s="20">
@@ -18796,7 +18796,7 @@
         <v/>
       </c>
       <c r="C94" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A94,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A94,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A94,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A94,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D94" s="31">
@@ -18812,7 +18812,7 @@
         <v/>
       </c>
       <c r="G94" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A94,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A94,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A94,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A94,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H94" s="30">
@@ -18845,7 +18845,7 @@
         <v/>
       </c>
       <c r="C95" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A95,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A95,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A95,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A95,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D95" s="18">
@@ -18861,7 +18861,7 @@
         <v/>
       </c>
       <c r="G95" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A95,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A95,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A95,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A95,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H95" s="20">
@@ -18894,7 +18894,7 @@
         <v/>
       </c>
       <c r="C96" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A96,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A96,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A96,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A96,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D96" s="31">
@@ -18910,7 +18910,7 @@
         <v/>
       </c>
       <c r="G96" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A96,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A96,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A96,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A96,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H96" s="30">
@@ -18943,7 +18943,7 @@
         <v/>
       </c>
       <c r="C97" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A97,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A97,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A97,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A97,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D97" s="18">
@@ -18959,7 +18959,7 @@
         <v/>
       </c>
       <c r="G97" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A97,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A97,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A97,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A97,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H97" s="20">
@@ -18992,7 +18992,7 @@
         <v/>
       </c>
       <c r="C98" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A98,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A98,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A98,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A98,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D98" s="31">
@@ -19008,7 +19008,7 @@
         <v/>
       </c>
       <c r="G98" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A98,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A98,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A98,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A98,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H98" s="30">
@@ -19041,7 +19041,7 @@
         <v/>
       </c>
       <c r="C99" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A99,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A99,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A99,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A99,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D99" s="18">
@@ -19057,7 +19057,7 @@
         <v/>
       </c>
       <c r="G99" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A99,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A99,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A99,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A99,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H99" s="20">
@@ -19090,7 +19090,7 @@
         <v/>
       </c>
       <c r="C100" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A100,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A100,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A100,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A100,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D100" s="31">
@@ -19106,7 +19106,7 @@
         <v/>
       </c>
       <c r="G100" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A100,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A100,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A100,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A100,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H100" s="30">
@@ -19139,7 +19139,7 @@
         <v/>
       </c>
       <c r="C101" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A101,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A101,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A101,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A101,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D101" s="18">
@@ -19155,7 +19155,7 @@
         <v/>
       </c>
       <c r="G101" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A101,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A101,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A101,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A101,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H101" s="20">
@@ -19188,7 +19188,7 @@
         <v/>
       </c>
       <c r="C102" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A102,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A102,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A102,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A102,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D102" s="31">
@@ -19204,7 +19204,7 @@
         <v/>
       </c>
       <c r="G102" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A102,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A102,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A102,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A102,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H102" s="30">
@@ -19237,7 +19237,7 @@
         <v/>
       </c>
       <c r="C103" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A103,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A103,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A103,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A103,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D103" s="18">
@@ -19253,7 +19253,7 @@
         <v/>
       </c>
       <c r="G103" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A103,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A103,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A103,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A103,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H103" s="20">
@@ -19286,7 +19286,7 @@
         <v/>
       </c>
       <c r="C104" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A104,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A104,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A104,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A104,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D104" s="31">
@@ -19302,7 +19302,7 @@
         <v/>
       </c>
       <c r="G104" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A104,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A104,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A104,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A104,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H104" s="30">
@@ -19335,7 +19335,7 @@
         <v/>
       </c>
       <c r="C105" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A105,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A105,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A105,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A105,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D105" s="18">
@@ -19351,7 +19351,7 @@
         <v/>
       </c>
       <c r="G105" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A105,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A105,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A105,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A105,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H105" s="20">
@@ -19384,7 +19384,7 @@
         <v/>
       </c>
       <c r="C106" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A106,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A106,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A106,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A106,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D106" s="31">
@@ -19400,7 +19400,7 @@
         <v/>
       </c>
       <c r="G106" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A106,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A106,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A106,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A106,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H106" s="30">
@@ -19433,7 +19433,7 @@
         <v/>
       </c>
       <c r="C107" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A107,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A107,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A107,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A107,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D107" s="18">
@@ -19449,7 +19449,7 @@
         <v/>
       </c>
       <c r="G107" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A107,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A107,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A107,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A107,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H107" s="20">
@@ -19482,7 +19482,7 @@
         <v/>
       </c>
       <c r="C108" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A108,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A108,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A108,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A108,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D108" s="31">
@@ -19498,7 +19498,7 @@
         <v/>
       </c>
       <c r="G108" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A108,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A108,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A108,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A108,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H108" s="30">
@@ -19531,7 +19531,7 @@
         <v/>
       </c>
       <c r="C109" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A109,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A109,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A109,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A109,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D109" s="18">
@@ -19547,7 +19547,7 @@
         <v/>
       </c>
       <c r="G109" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A109,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A109,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A109,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A109,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H109" s="20">
@@ -19580,7 +19580,7 @@
         <v/>
       </c>
       <c r="C110" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A110,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A110,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A110,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A110,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D110" s="31">
@@ -19596,7 +19596,7 @@
         <v/>
       </c>
       <c r="G110" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A110,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A110,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A110,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A110,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H110" s="30">
@@ -19629,7 +19629,7 @@
         <v/>
       </c>
       <c r="C111" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A111,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A111,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A111,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A111,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D111" s="18">
@@ -19645,7 +19645,7 @@
         <v/>
       </c>
       <c r="G111" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A111,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A111,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A111,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A111,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H111" s="20">
@@ -19678,7 +19678,7 @@
         <v/>
       </c>
       <c r="C112" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A112,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A112,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A112,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A112,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D112" s="31">
@@ -19694,7 +19694,7 @@
         <v/>
       </c>
       <c r="G112" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A112,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A112,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A112,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A112,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H112" s="30">
@@ -19727,7 +19727,7 @@
         <v/>
       </c>
       <c r="C113" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A113,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A113,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A113,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A113,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D113" s="18">
@@ -19743,7 +19743,7 @@
         <v/>
       </c>
       <c r="G113" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A113,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A113,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A113,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A113,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H113" s="20">
@@ -19776,7 +19776,7 @@
         <v/>
       </c>
       <c r="C114" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A114,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A114,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A114,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A114,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D114" s="31">
@@ -19792,7 +19792,7 @@
         <v/>
       </c>
       <c r="G114" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A114,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A114,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A114,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A114,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H114" s="30">
@@ -19825,7 +19825,7 @@
         <v/>
       </c>
       <c r="C115" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A115,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A115,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A115,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A115,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D115" s="18">
@@ -19841,7 +19841,7 @@
         <v/>
       </c>
       <c r="G115" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A115,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A115,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A115,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A115,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H115" s="20">
@@ -19874,7 +19874,7 @@
         <v/>
       </c>
       <c r="C116" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A116,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A116,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A116,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A116,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D116" s="31">
@@ -19890,7 +19890,7 @@
         <v/>
       </c>
       <c r="G116" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A116,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A116,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A116,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A116,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H116" s="30">
@@ -19923,7 +19923,7 @@
         <v/>
       </c>
       <c r="C117" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A117,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A117,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A117,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A117,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D117" s="18">
@@ -19939,7 +19939,7 @@
         <v/>
       </c>
       <c r="G117" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A117,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A117,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A117,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A117,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H117" s="20">
@@ -19972,7 +19972,7 @@
         <v/>
       </c>
       <c r="C118" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A118,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A118,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A118,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A118,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D118" s="31">
@@ -19988,7 +19988,7 @@
         <v/>
       </c>
       <c r="G118" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A118,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A118,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A118,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A118,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H118" s="30">
@@ -20021,7 +20021,7 @@
         <v/>
       </c>
       <c r="C119" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A119,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A119,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A119,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A119,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D119" s="18">
@@ -20037,7 +20037,7 @@
         <v/>
       </c>
       <c r="G119" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A119,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A119,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A119,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A119,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H119" s="20">
@@ -20070,7 +20070,7 @@
         <v/>
       </c>
       <c r="C120" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A120,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A120,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A120,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A120,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D120" s="31">
@@ -20086,7 +20086,7 @@
         <v/>
       </c>
       <c r="G120" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A120,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A120,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A120,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A120,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H120" s="30">
@@ -20119,7 +20119,7 @@
         <v/>
       </c>
       <c r="C121" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A121,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A121,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A121,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A121,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D121" s="18">
@@ -20135,7 +20135,7 @@
         <v/>
       </c>
       <c r="G121" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A121,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A121,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A121,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A121,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H121" s="20">
@@ -20168,7 +20168,7 @@
         <v/>
       </c>
       <c r="C122" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A122,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A122,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A122,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A122,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D122" s="31">
@@ -20184,7 +20184,7 @@
         <v/>
       </c>
       <c r="G122" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A122,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A122,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A122,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A122,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H122" s="30">
@@ -20217,7 +20217,7 @@
         <v/>
       </c>
       <c r="C123" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A123,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A123,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A123,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A123,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D123" s="18">
@@ -20233,7 +20233,7 @@
         <v/>
       </c>
       <c r="G123" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A123,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A123,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A123,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A123,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H123" s="20">
@@ -20266,7 +20266,7 @@
         <v/>
       </c>
       <c r="C124" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A124,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A124,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A124,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A124,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D124" s="31">
@@ -20282,7 +20282,7 @@
         <v/>
       </c>
       <c r="G124" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A124,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A124,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A124,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A124,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H124" s="30">
@@ -20315,7 +20315,7 @@
         <v/>
       </c>
       <c r="C125" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A125,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A125,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A125,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A125,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D125" s="18">
@@ -20331,7 +20331,7 @@
         <v/>
       </c>
       <c r="G125" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A125,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A125,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A125,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A125,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H125" s="20">
@@ -20364,7 +20364,7 @@
         <v/>
       </c>
       <c r="C126" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A126,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A126,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A126,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A126,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D126" s="31">
@@ -20380,7 +20380,7 @@
         <v/>
       </c>
       <c r="G126" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A126,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A126,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A126,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A126,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H126" s="30">
@@ -20413,7 +20413,7 @@
         <v/>
       </c>
       <c r="C127" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A127,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A127,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A127,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A127,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D127" s="18">
@@ -20429,7 +20429,7 @@
         <v/>
       </c>
       <c r="G127" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A127,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A127,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A127,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A127,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H127" s="20">
@@ -20462,7 +20462,7 @@
         <v/>
       </c>
       <c r="C128" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A128,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A128,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A128,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A128,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D128" s="31">
@@ -20478,7 +20478,7 @@
         <v/>
       </c>
       <c r="G128" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A128,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A128,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A128,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A128,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H128" s="30">
@@ -20511,7 +20511,7 @@
         <v/>
       </c>
       <c r="C129" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A129,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A129,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A129,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A129,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D129" s="18">
@@ -20527,7 +20527,7 @@
         <v/>
       </c>
       <c r="G129" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A129,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A129,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A129,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A129,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H129" s="20">
@@ -20560,7 +20560,7 @@
         <v/>
       </c>
       <c r="C130" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A130,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A130,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A130,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A130,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D130" s="31">
@@ -20576,7 +20576,7 @@
         <v/>
       </c>
       <c r="G130" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A130,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A130,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A130,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A130,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H130" s="30">
@@ -20609,7 +20609,7 @@
         <v/>
       </c>
       <c r="C131" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A131,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A131,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A131,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A131,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D131" s="18">
@@ -20625,7 +20625,7 @@
         <v/>
       </c>
       <c r="G131" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A131,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A131,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A131,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A131,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H131" s="20">
@@ -20658,7 +20658,7 @@
         <v/>
       </c>
       <c r="C132" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A132,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A132,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A132,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A132,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D132" s="31">
@@ -20674,7 +20674,7 @@
         <v/>
       </c>
       <c r="G132" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A132,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A132,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A132,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A132,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H132" s="30">
@@ -20707,7 +20707,7 @@
         <v/>
       </c>
       <c r="C133" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A133,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A133,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A133,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A133,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D133" s="18">
@@ -20723,7 +20723,7 @@
         <v/>
       </c>
       <c r="G133" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A133,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A133,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A133,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A133,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H133" s="20">
@@ -20756,7 +20756,7 @@
         <v/>
       </c>
       <c r="C134" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A134,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A134,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A134,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A134,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D134" s="31">
@@ -20772,7 +20772,7 @@
         <v/>
       </c>
       <c r="G134" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A134,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A134,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A134,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A134,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H134" s="30">
@@ -20805,7 +20805,7 @@
         <v/>
       </c>
       <c r="C135" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A135,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A135,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A135,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A135,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D135" s="18">
@@ -20821,7 +20821,7 @@
         <v/>
       </c>
       <c r="G135" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A135,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A135,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A135,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A135,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H135" s="20">
@@ -20854,7 +20854,7 @@
         <v/>
       </c>
       <c r="C136" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A136,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A136,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A136,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A136,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D136" s="31">
@@ -20870,7 +20870,7 @@
         <v/>
       </c>
       <c r="G136" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A136,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A136,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A136,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A136,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H136" s="30">
@@ -20903,7 +20903,7 @@
         <v/>
       </c>
       <c r="C137" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A137,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A137,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A137,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A137,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D137" s="18">
@@ -20919,7 +20919,7 @@
         <v/>
       </c>
       <c r="G137" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A137,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A137,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A137,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A137,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H137" s="20">
@@ -20952,7 +20952,7 @@
         <v/>
       </c>
       <c r="C138" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A138,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A138,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A138,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A138,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D138" s="31">
@@ -20968,7 +20968,7 @@
         <v/>
       </c>
       <c r="G138" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A138,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A138,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A138,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A138,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H138" s="30">
@@ -21001,7 +21001,7 @@
         <v/>
       </c>
       <c r="C139" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A139,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A139,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A139,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A139,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D139" s="18">
@@ -21017,7 +21017,7 @@
         <v/>
       </c>
       <c r="G139" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A139,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A139,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A139,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A139,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H139" s="20">
@@ -21050,7 +21050,7 @@
         <v/>
       </c>
       <c r="C140" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A140,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A140,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A140,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A140,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D140" s="31">
@@ -21066,7 +21066,7 @@
         <v/>
       </c>
       <c r="G140" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A140,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A140,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A140,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A140,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H140" s="30">
@@ -21099,7 +21099,7 @@
         <v/>
       </c>
       <c r="C141" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A141,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A141,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A141,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A141,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D141" s="18">
@@ -21115,7 +21115,7 @@
         <v/>
       </c>
       <c r="G141" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A141,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A141,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A141,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A141,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H141" s="20">
@@ -21148,7 +21148,7 @@
         <v/>
       </c>
       <c r="C142" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A142,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A142,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A142,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A142,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D142" s="31">
@@ -21164,7 +21164,7 @@
         <v/>
       </c>
       <c r="G142" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A142,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A142,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A142,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A142,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H142" s="30">
@@ -21197,7 +21197,7 @@
         <v/>
       </c>
       <c r="C143" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A143,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A143,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A143,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A143,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D143" s="18">
@@ -21213,7 +21213,7 @@
         <v/>
       </c>
       <c r="G143" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A143,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A143,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A143,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A143,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H143" s="20">
@@ -21246,7 +21246,7 @@
         <v/>
       </c>
       <c r="C144" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A144,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A144,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A144,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A144,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D144" s="31">
@@ -21262,7 +21262,7 @@
         <v/>
       </c>
       <c r="G144" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A144,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A144,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A144,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A144,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H144" s="30">
@@ -21295,7 +21295,7 @@
         <v/>
       </c>
       <c r="C145" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A145,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A145,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A145,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A145,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D145" s="18">
@@ -21311,7 +21311,7 @@
         <v/>
       </c>
       <c r="G145" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A145,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A145,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A145,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A145,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H145" s="20">
@@ -21344,7 +21344,7 @@
         <v/>
       </c>
       <c r="C146" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A146,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A146,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A146,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A146,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D146" s="31">
@@ -21360,7 +21360,7 @@
         <v/>
       </c>
       <c r="G146" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A146,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A146,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A146,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A146,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H146" s="30">
@@ -21393,7 +21393,7 @@
         <v/>
       </c>
       <c r="C147" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A147,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A147,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A147,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A147,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D147" s="18">
@@ -21409,7 +21409,7 @@
         <v/>
       </c>
       <c r="G147" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A147,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A147,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A147,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A147,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H147" s="20">
@@ -21442,7 +21442,7 @@
         <v/>
       </c>
       <c r="C148" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A148,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A148,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A148,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A148,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D148" s="31">
@@ -21458,7 +21458,7 @@
         <v/>
       </c>
       <c r="G148" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A148,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A148,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A148,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A148,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H148" s="30">
@@ -21491,7 +21491,7 @@
         <v/>
       </c>
       <c r="C149" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A149,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A149,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A149,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A149,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D149" s="18">
@@ -21507,7 +21507,7 @@
         <v/>
       </c>
       <c r="G149" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A149,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A149,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A149,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A149,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H149" s="20">
@@ -21540,7 +21540,7 @@
         <v/>
       </c>
       <c r="C150" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A150,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A150,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A150,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A150,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D150" s="31">
@@ -21556,7 +21556,7 @@
         <v/>
       </c>
       <c r="G150" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A150,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A150,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A150,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A150,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H150" s="30">
@@ -21589,7 +21589,7 @@
         <v/>
       </c>
       <c r="C151" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A151,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A151,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A151,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A151,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D151" s="18">
@@ -21605,7 +21605,7 @@
         <v/>
       </c>
       <c r="G151" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A151,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A151,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A151,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A151,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H151" s="20">
@@ -21638,7 +21638,7 @@
         <v/>
       </c>
       <c r="C152" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A152,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A152,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A152,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A152,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D152" s="31">
@@ -21654,7 +21654,7 @@
         <v/>
       </c>
       <c r="G152" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A152,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A152,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A152,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A152,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H152" s="30">
@@ -21687,7 +21687,7 @@
         <v/>
       </c>
       <c r="C153" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A153,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A153,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A153,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A153,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D153" s="18">
@@ -21703,7 +21703,7 @@
         <v/>
       </c>
       <c r="G153" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A153,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A153,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A153,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A153,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H153" s="20">
@@ -21736,7 +21736,7 @@
         <v/>
       </c>
       <c r="C154" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A154,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A154,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A154,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A154,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D154" s="31">
@@ -21752,7 +21752,7 @@
         <v/>
       </c>
       <c r="G154" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A154,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A154,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A154,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A154,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H154" s="30">
@@ -21785,7 +21785,7 @@
         <v/>
       </c>
       <c r="C155" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A155,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A155,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A155,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A155,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D155" s="18">
@@ -21801,7 +21801,7 @@
         <v/>
       </c>
       <c r="G155" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A155,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A155,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A155,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A155,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H155" s="20">
@@ -21834,7 +21834,7 @@
         <v/>
       </c>
       <c r="C156" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A156,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A156,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A156,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A156,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D156" s="31">
@@ -21850,7 +21850,7 @@
         <v/>
       </c>
       <c r="G156" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A156,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A156,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A156,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A156,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H156" s="30">
@@ -21883,7 +21883,7 @@
         <v/>
       </c>
       <c r="C157" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A157,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A157,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A157,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A157,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D157" s="18">
@@ -21899,7 +21899,7 @@
         <v/>
       </c>
       <c r="G157" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A157,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A157,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A157,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A157,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H157" s="20">
@@ -21932,7 +21932,7 @@
         <v/>
       </c>
       <c r="C158" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A158,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A158,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A158,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A158,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D158" s="31">
@@ -21948,7 +21948,7 @@
         <v/>
       </c>
       <c r="G158" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A158,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A158,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A158,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A158,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H158" s="30">
@@ -21981,7 +21981,7 @@
         <v/>
       </c>
       <c r="C159" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A159,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A159,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A159,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A159,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D159" s="18">
@@ -21997,7 +21997,7 @@
         <v/>
       </c>
       <c r="G159" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A159,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A159,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A159,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A159,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H159" s="20">
@@ -22030,7 +22030,7 @@
         <v/>
       </c>
       <c r="C160" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A160,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A160,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A160,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A160,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D160" s="31">
@@ -22046,7 +22046,7 @@
         <v/>
       </c>
       <c r="G160" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A160,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A160,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A160,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A160,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H160" s="30">
@@ -22079,7 +22079,7 @@
         <v/>
       </c>
       <c r="C161" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A161,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A161,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A161,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A161,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D161" s="18">
@@ -22095,7 +22095,7 @@
         <v/>
       </c>
       <c r="G161" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A161,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A161,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A161,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A161,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H161" s="20">
@@ -22128,7 +22128,7 @@
         <v/>
       </c>
       <c r="C162" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A162,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A162,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A162,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A162,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D162" s="31">
@@ -22144,7 +22144,7 @@
         <v/>
       </c>
       <c r="G162" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A162,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A162,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A162,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A162,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H162" s="30">
@@ -22177,7 +22177,7 @@
         <v/>
       </c>
       <c r="C163" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A163,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A163,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A163,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A163,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D163" s="18">
@@ -22193,7 +22193,7 @@
         <v/>
       </c>
       <c r="G163" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A163,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A163,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A163,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A163,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H163" s="20">
@@ -22226,7 +22226,7 @@
         <v/>
       </c>
       <c r="C164" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A164,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A164,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A164,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A164,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D164" s="31">
@@ -22242,7 +22242,7 @@
         <v/>
       </c>
       <c r="G164" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A164,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A164,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A164,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A164,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H164" s="30">
@@ -22275,7 +22275,7 @@
         <v/>
       </c>
       <c r="C165" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A165,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A165,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A165,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A165,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D165" s="18">
@@ -22291,7 +22291,7 @@
         <v/>
       </c>
       <c r="G165" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A165,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A165,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A165,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A165,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H165" s="20">
@@ -22324,7 +22324,7 @@
         <v/>
       </c>
       <c r="C166" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A166,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A166,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A166,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A166,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D166" s="31">
@@ -22340,7 +22340,7 @@
         <v/>
       </c>
       <c r="G166" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A166,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A166,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A166,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A166,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H166" s="30">
@@ -22373,7 +22373,7 @@
         <v/>
       </c>
       <c r="C167" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A167,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A167,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A167,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A167,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D167" s="18">
@@ -22389,7 +22389,7 @@
         <v/>
       </c>
       <c r="G167" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A167,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A167,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A167,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A167,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H167" s="20">
@@ -22422,7 +22422,7 @@
         <v/>
       </c>
       <c r="C168" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A168,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A168,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A168,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A168,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D168" s="31">
@@ -22438,7 +22438,7 @@
         <v/>
       </c>
       <c r="G168" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A168,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A168,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A168,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A168,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H168" s="30">
@@ -22471,7 +22471,7 @@
         <v/>
       </c>
       <c r="C169" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A169,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A169,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A169,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A169,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D169" s="18">
@@ -22487,7 +22487,7 @@
         <v/>
       </c>
       <c r="G169" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A169,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A169,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A169,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A169,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H169" s="20">
@@ -22520,7 +22520,7 @@
         <v/>
       </c>
       <c r="C170" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A170,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A170,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A170,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A170,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D170" s="31">
@@ -22536,7 +22536,7 @@
         <v/>
       </c>
       <c r="G170" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A170,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A170,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A170,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A170,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H170" s="30">
@@ -22569,7 +22569,7 @@
         <v/>
       </c>
       <c r="C171" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A171,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A171,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A171,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A171,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D171" s="18">
@@ -22585,7 +22585,7 @@
         <v/>
       </c>
       <c r="G171" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A171,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A171,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A171,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A171,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H171" s="20">
@@ -22618,7 +22618,7 @@
         <v/>
       </c>
       <c r="C172" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A172,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A172,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A172,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A172,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D172" s="31">
@@ -22634,7 +22634,7 @@
         <v/>
       </c>
       <c r="G172" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A172,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A172,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A172,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A172,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H172" s="30">
@@ -22667,7 +22667,7 @@
         <v/>
       </c>
       <c r="C173" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A173,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A173,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A173,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A173,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D173" s="18">
@@ -22683,7 +22683,7 @@
         <v/>
       </c>
       <c r="G173" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A173,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A173,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A173,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A173,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H173" s="20">
@@ -22716,7 +22716,7 @@
         <v/>
       </c>
       <c r="C174" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A174,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A174,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A174,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A174,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D174" s="31">
@@ -22732,7 +22732,7 @@
         <v/>
       </c>
       <c r="G174" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A174,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A174,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A174,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A174,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H174" s="30">
@@ -22765,7 +22765,7 @@
         <v/>
       </c>
       <c r="C175" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A175,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A175,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A175,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A175,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D175" s="18">
@@ -22781,7 +22781,7 @@
         <v/>
       </c>
       <c r="G175" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A175,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A175,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A175,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A175,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H175" s="20">
@@ -22814,7 +22814,7 @@
         <v/>
       </c>
       <c r="C176" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A176,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A176,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A176,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A176,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D176" s="31">
@@ -22830,7 +22830,7 @@
         <v/>
       </c>
       <c r="G176" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A176,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A176,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A176,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A176,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H176" s="30">
@@ -22863,7 +22863,7 @@
         <v/>
       </c>
       <c r="C177" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A177,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A177,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A177,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A177,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D177" s="18">
@@ -22879,7 +22879,7 @@
         <v/>
       </c>
       <c r="G177" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A177,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A177,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A177,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A177,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H177" s="20">
@@ -22912,7 +22912,7 @@
         <v/>
       </c>
       <c r="C178" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A178,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A178,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A178,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A178,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D178" s="31">
@@ -22928,7 +22928,7 @@
         <v/>
       </c>
       <c r="G178" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A178,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A178,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A178,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A178,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H178" s="30">
@@ -22961,7 +22961,7 @@
         <v/>
       </c>
       <c r="C179" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A179,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A179,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A179,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A179,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D179" s="18">
@@ -22977,7 +22977,7 @@
         <v/>
       </c>
       <c r="G179" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A179,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A179,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A179,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A179,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H179" s="20">
@@ -23010,7 +23010,7 @@
         <v/>
       </c>
       <c r="C180" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A180,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A180,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A180,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A180,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D180" s="31">
@@ -23026,7 +23026,7 @@
         <v/>
       </c>
       <c r="G180" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A180,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A180,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A180,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A180,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H180" s="30">
@@ -23059,7 +23059,7 @@
         <v/>
       </c>
       <c r="C181" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A181,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A181,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A181,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A181,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D181" s="18">
@@ -23075,7 +23075,7 @@
         <v/>
       </c>
       <c r="G181" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A181,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A181,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A181,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A181,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H181" s="20">
@@ -23108,7 +23108,7 @@
         <v/>
       </c>
       <c r="C182" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A182,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A182,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A182,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A182,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D182" s="31">
@@ -23124,7 +23124,7 @@
         <v/>
       </c>
       <c r="G182" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A182,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A182,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A182,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A182,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H182" s="30">
@@ -23157,7 +23157,7 @@
         <v/>
       </c>
       <c r="C183" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A183,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A183,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A183,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A183,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D183" s="18">
@@ -23173,7 +23173,7 @@
         <v/>
       </c>
       <c r="G183" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A183,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A183,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A183,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A183,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H183" s="20">
@@ -23206,7 +23206,7 @@
         <v/>
       </c>
       <c r="C184" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A184,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A184,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A184,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A184,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D184" s="31">
@@ -23222,7 +23222,7 @@
         <v/>
       </c>
       <c r="G184" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A184,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A184,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A184,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A184,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H184" s="30">
@@ -23255,7 +23255,7 @@
         <v/>
       </c>
       <c r="C185" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A185,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A185,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A185,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A185,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D185" s="18">
@@ -23271,7 +23271,7 @@
         <v/>
       </c>
       <c r="G185" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A185,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A185,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A185,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A185,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H185" s="20">
@@ -23304,7 +23304,7 @@
         <v/>
       </c>
       <c r="C186" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A186,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A186,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A186,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A186,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D186" s="31">
@@ -23320,7 +23320,7 @@
         <v/>
       </c>
       <c r="G186" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A186,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A186,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A186,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A186,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H186" s="30">
@@ -23353,7 +23353,7 @@
         <v/>
       </c>
       <c r="C187" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A187,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A187,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A187,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A187,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D187" s="18">
@@ -23369,7 +23369,7 @@
         <v/>
       </c>
       <c r="G187" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A187,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A187,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A187,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A187,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H187" s="20">
@@ -23402,7 +23402,7 @@
         <v/>
       </c>
       <c r="C188" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A188,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A188,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A188,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A188,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D188" s="31">
@@ -23418,7 +23418,7 @@
         <v/>
       </c>
       <c r="G188" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A188,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A188,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A188,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A188,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H188" s="30">
@@ -23451,7 +23451,7 @@
         <v/>
       </c>
       <c r="C189" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A189,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A189,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A189,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A189,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D189" s="18">
@@ -23467,7 +23467,7 @@
         <v/>
       </c>
       <c r="G189" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A189,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A189,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A189,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A189,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H189" s="20">
@@ -23500,7 +23500,7 @@
         <v/>
       </c>
       <c r="C190" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A190,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A190,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A190,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A190,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D190" s="31">
@@ -23516,7 +23516,7 @@
         <v/>
       </c>
       <c r="G190" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A190,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A190,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A190,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A190,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H190" s="30">
@@ -23549,7 +23549,7 @@
         <v/>
       </c>
       <c r="C191" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A191,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A191,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A191,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A191,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D191" s="18">
@@ -23565,7 +23565,7 @@
         <v/>
       </c>
       <c r="G191" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A191,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A191,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A191,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A191,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H191" s="20">
@@ -23598,7 +23598,7 @@
         <v/>
       </c>
       <c r="C192" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A192,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A192,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A192,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A192,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D192" s="31">
@@ -23614,7 +23614,7 @@
         <v/>
       </c>
       <c r="G192" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A192,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A192,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A192,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A192,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H192" s="30">
@@ -23647,7 +23647,7 @@
         <v/>
       </c>
       <c r="C193" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A193,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A193,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A193,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A193,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D193" s="18">
@@ -23663,7 +23663,7 @@
         <v/>
       </c>
       <c r="G193" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A193,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A193,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A193,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A193,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H193" s="20">
@@ -23696,7 +23696,7 @@
         <v/>
       </c>
       <c r="C194" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A194,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A194,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A194,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A194,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D194" s="31">
@@ -23712,7 +23712,7 @@
         <v/>
       </c>
       <c r="G194" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A194,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A194,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A194,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A194,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H194" s="30">
@@ -23745,7 +23745,7 @@
         <v/>
       </c>
       <c r="C195" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A195,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A195,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A195,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A195,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D195" s="18">
@@ -23761,7 +23761,7 @@
         <v/>
       </c>
       <c r="G195" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A195,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A195,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A195,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A195,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H195" s="20">
@@ -23794,7 +23794,7 @@
         <v/>
       </c>
       <c r="C196" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A196,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A196,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A196,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A196,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D196" s="31">
@@ -23810,7 +23810,7 @@
         <v/>
       </c>
       <c r="G196" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A196,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A196,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A196,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A196,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H196" s="30">
@@ -23843,7 +23843,7 @@
         <v/>
       </c>
       <c r="C197" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A197,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A197,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A197,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A197,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D197" s="18">
@@ -23859,7 +23859,7 @@
         <v/>
       </c>
       <c r="G197" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A197,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A197,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A197,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A197,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H197" s="20">
@@ -23892,7 +23892,7 @@
         <v/>
       </c>
       <c r="C198" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A198,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A198,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A198,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A198,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D198" s="31">
@@ -23908,7 +23908,7 @@
         <v/>
       </c>
       <c r="G198" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A198,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A198,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A198,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A198,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H198" s="30">
@@ -23941,7 +23941,7 @@
         <v/>
       </c>
       <c r="C199" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A199,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A199,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A199,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A199,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D199" s="18">
@@ -23957,7 +23957,7 @@
         <v/>
       </c>
       <c r="G199" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A199,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A199,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A199,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A199,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H199" s="20">
@@ -23990,7 +23990,7 @@
         <v/>
       </c>
       <c r="C200" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A200,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A200,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A200,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A200,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D200" s="31">
@@ -24006,7 +24006,7 @@
         <v/>
       </c>
       <c r="G200" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A200,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A200,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A200,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A200,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H200" s="30">
@@ -24039,7 +24039,7 @@
         <v/>
       </c>
       <c r="C201" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A201,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A201,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A201,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A201,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D201" s="18">
@@ -24055,7 +24055,7 @@
         <v/>
       </c>
       <c r="G201" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A201,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A201,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A201,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A201,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H201" s="20">
@@ -24088,7 +24088,7 @@
         <v/>
       </c>
       <c r="C202" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A202,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A202,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A202,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A202,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D202" s="31">
@@ -24104,7 +24104,7 @@
         <v/>
       </c>
       <c r="G202" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A202,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A202,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A202,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A202,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H202" s="30">
@@ -24137,7 +24137,7 @@
         <v/>
       </c>
       <c r="C203" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A203,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A203,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A203,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A203,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D203" s="18">
@@ -24153,7 +24153,7 @@
         <v/>
       </c>
       <c r="G203" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A203,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A203,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A203,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A203,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H203" s="20">
@@ -24186,7 +24186,7 @@
         <v/>
       </c>
       <c r="C204" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A204,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A204,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A204,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A204,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D204" s="31">
@@ -24202,7 +24202,7 @@
         <v/>
       </c>
       <c r="G204" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A204,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A204,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A204,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A204,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H204" s="30">
@@ -24235,7 +24235,7 @@
         <v/>
       </c>
       <c r="C205" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A205,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A205,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A205,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A205,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D205" s="18">
@@ -24251,7 +24251,7 @@
         <v/>
       </c>
       <c r="G205" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A205,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A205,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A205,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A205,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H205" s="20">
@@ -24284,7 +24284,7 @@
         <v/>
       </c>
       <c r="C206" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A206,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A206,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A206,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A206,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D206" s="31">
@@ -24300,7 +24300,7 @@
         <v/>
       </c>
       <c r="G206" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A206,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A206,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A206,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A206,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H206" s="30">
@@ -24333,7 +24333,7 @@
         <v/>
       </c>
       <c r="C207" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A207,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A207,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A207,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A207,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D207" s="18">
@@ -24349,7 +24349,7 @@
         <v/>
       </c>
       <c r="G207" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A207,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A207,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A207,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A207,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H207" s="20">
@@ -24382,7 +24382,7 @@
         <v/>
       </c>
       <c r="C208" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A208,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A208,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A208,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A208,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D208" s="31">
@@ -24398,7 +24398,7 @@
         <v/>
       </c>
       <c r="G208" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A208,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A208,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A208,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A208,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H208" s="30">
@@ -24431,7 +24431,7 @@
         <v/>
       </c>
       <c r="C209" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A209,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A209,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A209,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A209,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D209" s="18">
@@ -24447,7 +24447,7 @@
         <v/>
       </c>
       <c r="G209" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A209,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A209,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A209,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A209,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H209" s="20">
@@ -24480,7 +24480,7 @@
         <v/>
       </c>
       <c r="C210" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A210,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A210,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A210,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A210,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D210" s="31">
@@ -24496,7 +24496,7 @@
         <v/>
       </c>
       <c r="G210" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A210,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A210,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A210,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A210,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H210" s="30">
@@ -24529,7 +24529,7 @@
         <v/>
       </c>
       <c r="C211" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A211,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A211,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A211,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A211,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D211" s="18">
@@ -24545,7 +24545,7 @@
         <v/>
       </c>
       <c r="G211" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A211,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A211,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A211,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A211,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H211" s="20">
@@ -24578,7 +24578,7 @@
         <v/>
       </c>
       <c r="C212" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A212,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A212,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A212,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A212,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D212" s="31">
@@ -24594,7 +24594,7 @@
         <v/>
       </c>
       <c r="G212" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A212,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A212,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A212,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A212,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H212" s="30">
@@ -24627,7 +24627,7 @@
         <v/>
       </c>
       <c r="C213" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A213,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A213,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A213,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A213,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D213" s="18">
@@ -24643,7 +24643,7 @@
         <v/>
       </c>
       <c r="G213" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A213,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A213,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A213,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A213,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H213" s="20">
@@ -24676,7 +24676,7 @@
         <v/>
       </c>
       <c r="C214" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A214,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A214,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A214,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A214,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D214" s="31">
@@ -24692,7 +24692,7 @@
         <v/>
       </c>
       <c r="G214" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A214,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A214,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A214,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A214,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H214" s="30">
@@ -24725,7 +24725,7 @@
         <v/>
       </c>
       <c r="C215" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A215,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A215,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A215,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A215,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D215" s="18">
@@ -24741,7 +24741,7 @@
         <v/>
       </c>
       <c r="G215" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A215,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A215,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A215,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A215,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H215" s="20">
@@ -24774,7 +24774,7 @@
         <v/>
       </c>
       <c r="C216" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A216,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A216,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A216,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A216,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D216" s="31">
@@ -24790,7 +24790,7 @@
         <v/>
       </c>
       <c r="G216" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A216,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A216,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A216,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A216,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H216" s="30">
@@ -24823,7 +24823,7 @@
         <v/>
       </c>
       <c r="C217" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A217,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A217,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A217,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A217,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D217" s="18">
@@ -24839,7 +24839,7 @@
         <v/>
       </c>
       <c r="G217" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A217,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A217,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A217,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A217,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H217" s="20">
@@ -24872,7 +24872,7 @@
         <v/>
       </c>
       <c r="C218" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A218,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A218,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A218,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A218,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D218" s="31">
@@ -24888,7 +24888,7 @@
         <v/>
       </c>
       <c r="G218" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A218,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A218,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A218,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A218,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H218" s="30">
@@ -24921,7 +24921,7 @@
         <v/>
       </c>
       <c r="C219" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A219,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A219,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A219,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A219,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D219" s="18">
@@ -24937,7 +24937,7 @@
         <v/>
       </c>
       <c r="G219" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A219,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A219,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A219,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A219,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H219" s="20">
@@ -24970,7 +24970,7 @@
         <v/>
       </c>
       <c r="C220" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A220,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A220,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A220,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A220,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D220" s="31">
@@ -24986,7 +24986,7 @@
         <v/>
       </c>
       <c r="G220" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A220,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A220,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A220,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A220,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H220" s="30">
@@ -25019,7 +25019,7 @@
         <v/>
       </c>
       <c r="C221" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A221,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A221,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A221,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A221,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D221" s="18">
@@ -25035,7 +25035,7 @@
         <v/>
       </c>
       <c r="G221" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A221,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A221,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A221,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A221,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H221" s="20">
@@ -25068,7 +25068,7 @@
         <v/>
       </c>
       <c r="C222" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A222,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A222,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A222,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A222,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D222" s="31">
@@ -25084,7 +25084,7 @@
         <v/>
       </c>
       <c r="G222" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A222,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A222,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A222,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A222,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H222" s="30">
@@ -25117,7 +25117,7 @@
         <v/>
       </c>
       <c r="C223" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A223,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A223,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A223,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A223,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D223" s="18">
@@ -25133,7 +25133,7 @@
         <v/>
       </c>
       <c r="G223" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A223,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A223,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A223,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A223,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H223" s="20">
@@ -25166,7 +25166,7 @@
         <v/>
       </c>
       <c r="C224" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A224,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A224,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A224,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A224,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D224" s="31">
@@ -25182,7 +25182,7 @@
         <v/>
       </c>
       <c r="G224" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A224,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A224,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A224,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A224,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H224" s="30">
@@ -25215,7 +25215,7 @@
         <v/>
       </c>
       <c r="C225" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A225,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A225,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A225,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A225,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D225" s="18">
@@ -25231,7 +25231,7 @@
         <v/>
       </c>
       <c r="G225" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A225,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A225,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A225,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A225,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H225" s="20">
@@ -25264,7 +25264,7 @@
         <v/>
       </c>
       <c r="C226" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A226,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A226,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A226,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A226,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D226" s="31">
@@ -25280,7 +25280,7 @@
         <v/>
       </c>
       <c r="G226" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A226,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A226,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A226,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A226,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H226" s="30">
@@ -25313,7 +25313,7 @@
         <v/>
       </c>
       <c r="C227" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A227,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A227,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A227,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A227,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D227" s="18">
@@ -25329,7 +25329,7 @@
         <v/>
       </c>
       <c r="G227" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A227,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A227,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A227,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A227,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H227" s="20">
@@ -25362,7 +25362,7 @@
         <v/>
       </c>
       <c r="C228" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A228,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A228,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A228,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A228,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D228" s="31">
@@ -25378,7 +25378,7 @@
         <v/>
       </c>
       <c r="G228" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A228,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A228,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A228,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A228,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H228" s="30">
@@ -25411,7 +25411,7 @@
         <v/>
       </c>
       <c r="C229" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A229,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A229,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A229,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A229,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D229" s="18">
@@ -25427,7 +25427,7 @@
         <v/>
       </c>
       <c r="G229" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A229,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A229,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A229,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A229,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H229" s="20">
@@ -25460,7 +25460,7 @@
         <v/>
       </c>
       <c r="C230" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A230,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A230,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A230,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A230,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D230" s="31">
@@ -25476,7 +25476,7 @@
         <v/>
       </c>
       <c r="G230" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A230,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A230,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A230,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A230,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H230" s="30">
@@ -25509,7 +25509,7 @@
         <v/>
       </c>
       <c r="C231" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A231,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A231,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A231,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A231,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D231" s="18">
@@ -25525,7 +25525,7 @@
         <v/>
       </c>
       <c r="G231" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A231,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A231,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A231,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A231,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H231" s="20">
@@ -25558,7 +25558,7 @@
         <v/>
       </c>
       <c r="C232" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A232,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A232,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A232,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A232,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D232" s="31">
@@ -25574,7 +25574,7 @@
         <v/>
       </c>
       <c r="G232" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A232,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A232,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A232,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A232,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H232" s="30">
@@ -25607,7 +25607,7 @@
         <v/>
       </c>
       <c r="C233" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A233,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A233,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A233,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A233,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D233" s="18">
@@ -25623,7 +25623,7 @@
         <v/>
       </c>
       <c r="G233" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A233,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A233,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A233,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A233,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H233" s="20">
@@ -25656,7 +25656,7 @@
         <v/>
       </c>
       <c r="C234" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A234,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A234,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A234,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A234,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D234" s="31">
@@ -25672,7 +25672,7 @@
         <v/>
       </c>
       <c r="G234" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A234,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A234,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A234,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A234,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H234" s="30">
@@ -25705,7 +25705,7 @@
         <v/>
       </c>
       <c r="C235" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A235,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A235,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A235,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A235,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D235" s="18">
@@ -25721,7 +25721,7 @@
         <v/>
       </c>
       <c r="G235" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A235,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A235,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A235,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A235,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H235" s="20">
@@ -25754,7 +25754,7 @@
         <v/>
       </c>
       <c r="C236" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A236,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A236,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A236,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A236,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D236" s="31">
@@ -25770,7 +25770,7 @@
         <v/>
       </c>
       <c r="G236" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A236,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A236,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A236,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A236,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H236" s="30">
@@ -25803,7 +25803,7 @@
         <v/>
       </c>
       <c r="C237" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A237,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A237,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A237,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A237,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D237" s="18">
@@ -25819,7 +25819,7 @@
         <v/>
       </c>
       <c r="G237" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A237,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A237,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A237,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A237,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H237" s="20">
@@ -25852,7 +25852,7 @@
         <v/>
       </c>
       <c r="C238" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A238,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A238,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A238,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A238,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D238" s="31">
@@ -25868,7 +25868,7 @@
         <v/>
       </c>
       <c r="G238" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A238,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A238,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A238,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A238,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H238" s="30">
@@ -25901,7 +25901,7 @@
         <v/>
       </c>
       <c r="C239" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A239,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A239,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A239,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A239,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D239" s="18">
@@ -25917,7 +25917,7 @@
         <v/>
       </c>
       <c r="G239" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A239,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A239,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A239,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A239,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H239" s="20">
@@ -25950,7 +25950,7 @@
         <v/>
       </c>
       <c r="C240" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A240,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A240,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A240,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A240,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D240" s="31">
@@ -25966,7 +25966,7 @@
         <v/>
       </c>
       <c r="G240" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A240,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A240,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A240,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A240,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H240" s="30">
@@ -25999,7 +25999,7 @@
         <v/>
       </c>
       <c r="C241" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A241,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A241,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A241,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A241,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D241" s="18">
@@ -26015,7 +26015,7 @@
         <v/>
       </c>
       <c r="G241" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A241,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A241,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A241,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A241,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H241" s="20">
@@ -26048,7 +26048,7 @@
         <v/>
       </c>
       <c r="C242" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A242,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A242,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A242,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A242,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D242" s="31">
@@ -26064,7 +26064,7 @@
         <v/>
       </c>
       <c r="G242" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A242,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A242,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A242,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A242,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H242" s="30">
@@ -26097,7 +26097,7 @@
         <v/>
       </c>
       <c r="C243" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A243,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A243,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A243,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A243,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D243" s="18">
@@ -26113,7 +26113,7 @@
         <v/>
       </c>
       <c r="G243" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A243,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A243,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A243,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A243,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H243" s="20">
@@ -26146,7 +26146,7 @@
         <v/>
       </c>
       <c r="C244" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A244,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A244,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A244,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A244,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D244" s="31">
@@ -26162,7 +26162,7 @@
         <v/>
       </c>
       <c r="G244" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A244,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A244,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A244,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A244,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H244" s="30">
@@ -26195,7 +26195,7 @@
         <v/>
       </c>
       <c r="C245" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A245,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A245,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A245,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A245,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D245" s="18">
@@ -26211,7 +26211,7 @@
         <v/>
       </c>
       <c r="G245" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A245,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A245,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A245,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A245,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H245" s="20">
@@ -26244,7 +26244,7 @@
         <v/>
       </c>
       <c r="C246" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A246,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A246,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A246,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A246,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D246" s="31">
@@ -26260,7 +26260,7 @@
         <v/>
       </c>
       <c r="G246" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A246,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A246,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A246,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A246,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H246" s="30">
@@ -26293,7 +26293,7 @@
         <v/>
       </c>
       <c r="C247" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A247,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A247,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A247,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A247,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D247" s="18">
@@ -26309,7 +26309,7 @@
         <v/>
       </c>
       <c r="G247" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A247,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A247,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A247,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A247,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H247" s="20">
@@ -26342,7 +26342,7 @@
         <v/>
       </c>
       <c r="C248" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A248,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A248,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A248,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A248,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D248" s="31">
@@ -26358,7 +26358,7 @@
         <v/>
       </c>
       <c r="G248" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A248,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A248,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A248,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A248,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H248" s="30">
@@ -26391,7 +26391,7 @@
         <v/>
       </c>
       <c r="C249" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A249,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A249,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A249,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A249,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D249" s="18">
@@ -26407,7 +26407,7 @@
         <v/>
       </c>
       <c r="G249" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A249,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A249,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A249,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A249,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H249" s="20">
@@ -26440,7 +26440,7 @@
         <v/>
       </c>
       <c r="C250" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A250,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A250,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A250,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A250,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D250" s="31">
@@ -26456,7 +26456,7 @@
         <v/>
       </c>
       <c r="G250" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A250,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A250,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A250,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A250,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H250" s="30">
@@ -26489,7 +26489,7 @@
         <v/>
       </c>
       <c r="C251" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A251,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A251,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A251,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A251,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D251" s="18">
@@ -26505,7 +26505,7 @@
         <v/>
       </c>
       <c r="G251" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A251,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A251,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A251,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A251,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H251" s="20">
@@ -26538,7 +26538,7 @@
         <v/>
       </c>
       <c r="C252" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A252,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A252,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A252,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A252,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D252" s="31">
@@ -26554,7 +26554,7 @@
         <v/>
       </c>
       <c r="G252" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A252,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A252,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A252,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A252,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H252" s="30">
@@ -26587,7 +26587,7 @@
         <v/>
       </c>
       <c r="C253" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A253,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A253,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A253,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A253,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D253" s="18">
@@ -26603,7 +26603,7 @@
         <v/>
       </c>
       <c r="G253" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A253,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A253,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A253,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A253,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H253" s="20">
@@ -26636,7 +26636,7 @@
         <v/>
       </c>
       <c r="C254" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A254,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A254,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A254,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A254,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D254" s="31">
@@ -26652,7 +26652,7 @@
         <v/>
       </c>
       <c r="G254" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A254,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A254,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A254,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A254,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H254" s="30">
@@ -26685,7 +26685,7 @@
         <v/>
       </c>
       <c r="C255" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A255,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A255,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A255,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A255,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D255" s="18">
@@ -26701,7 +26701,7 @@
         <v/>
       </c>
       <c r="G255" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A255,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A255,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A255,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A255,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H255" s="20">
@@ -26734,7 +26734,7 @@
         <v/>
       </c>
       <c r="C256" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A256,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A256,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A256,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A256,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D256" s="31">
@@ -26750,7 +26750,7 @@
         <v/>
       </c>
       <c r="G256" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A256,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A256,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A256,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A256,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H256" s="30">
@@ -26783,7 +26783,7 @@
         <v/>
       </c>
       <c r="C257" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A257,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A257,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A257,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A257,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D257" s="18">
@@ -26799,7 +26799,7 @@
         <v/>
       </c>
       <c r="G257" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A257,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A257,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A257,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A257,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H257" s="20">
@@ -26832,7 +26832,7 @@
         <v/>
       </c>
       <c r="C258" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A258,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A258,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A258,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A258,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D258" s="31">
@@ -26848,7 +26848,7 @@
         <v/>
       </c>
       <c r="G258" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A258,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A258,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A258,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A258,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H258" s="30">
@@ -26881,7 +26881,7 @@
         <v/>
       </c>
       <c r="C259" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A259,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A259,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A259,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A259,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D259" s="18">
@@ -26897,7 +26897,7 @@
         <v/>
       </c>
       <c r="G259" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A259,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A259,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A259,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A259,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H259" s="20">
@@ -26930,7 +26930,7 @@
         <v/>
       </c>
       <c r="C260" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A260,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A260,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A260,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A260,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D260" s="31">
@@ -26946,7 +26946,7 @@
         <v/>
       </c>
       <c r="G260" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A260,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A260,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A260,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A260,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H260" s="30">
@@ -26979,7 +26979,7 @@
         <v/>
       </c>
       <c r="C261" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A261,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A261,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A261,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A261,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D261" s="18">
@@ -26995,7 +26995,7 @@
         <v/>
       </c>
       <c r="G261" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A261,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A261,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A261,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A261,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H261" s="20">
@@ -27028,7 +27028,7 @@
         <v/>
       </c>
       <c r="C262" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A262,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A262,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A262,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A262,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D262" s="31">
@@ -27044,7 +27044,7 @@
         <v/>
       </c>
       <c r="G262" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A262,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A262,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A262,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A262,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H262" s="30">
@@ -27077,7 +27077,7 @@
         <v/>
       </c>
       <c r="C263" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A263,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A263,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A263,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A263,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D263" s="18">
@@ -27093,7 +27093,7 @@
         <v/>
       </c>
       <c r="G263" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A263,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A263,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A263,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A263,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H263" s="20">
@@ -27126,7 +27126,7 @@
         <v/>
       </c>
       <c r="C264" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A264,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A264,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A264,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A264,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D264" s="31">
@@ -27142,7 +27142,7 @@
         <v/>
       </c>
       <c r="G264" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A264,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A264,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A264,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A264,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H264" s="30">
@@ -27175,7 +27175,7 @@
         <v/>
       </c>
       <c r="C265" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A265,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A265,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A265,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A265,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D265" s="18">
@@ -27191,7 +27191,7 @@
         <v/>
       </c>
       <c r="G265" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A265,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A265,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A265,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A265,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H265" s="20">
@@ -27224,7 +27224,7 @@
         <v/>
       </c>
       <c r="C266" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A266,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A266,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A266,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A266,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D266" s="31">
@@ -27240,7 +27240,7 @@
         <v/>
       </c>
       <c r="G266" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A266,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A266,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A266,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A266,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H266" s="30">
@@ -27273,7 +27273,7 @@
         <v/>
       </c>
       <c r="C267" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A267,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A267,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A267,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A267,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D267" s="18">
@@ -27289,7 +27289,7 @@
         <v/>
       </c>
       <c r="G267" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A267,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A267,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A267,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A267,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H267" s="20">
@@ -27322,7 +27322,7 @@
         <v/>
       </c>
       <c r="C268" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A268,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A268,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A268,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A268,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D268" s="31">
@@ -27338,7 +27338,7 @@
         <v/>
       </c>
       <c r="G268" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A268,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A268,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A268,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A268,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H268" s="30">
@@ -27371,7 +27371,7 @@
         <v/>
       </c>
       <c r="C269" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A269,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A269,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A269,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A269,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D269" s="18">
@@ -27387,7 +27387,7 @@
         <v/>
       </c>
       <c r="G269" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A269,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A269,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A269,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A269,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H269" s="20">
@@ -27420,7 +27420,7 @@
         <v/>
       </c>
       <c r="C270" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$462,MATCH($A270,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$D$31:$D$462,MATCH($A270,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A270,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A270,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="D270" s="31">
@@ -27436,7 +27436,7 @@
         <v/>
       </c>
       <c r="G270" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$462,MATCH($A270,Kalshi!$A$31:$A$462,0))=0,"",INDEX(Kalshi!$G$31:$G$462,MATCH($A270,Kalshi!$A$31:$A$462,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A270,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A270,Kalshi!$A$31:$A$463,0))),"")</f>
         <v/>
       </c>
       <c r="H270" s="30">
@@ -27489,7 +27489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-19 01:10 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28649,7 +28649,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-19 01:10 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28730,7 +28730,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-19 01:10 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 01:10 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>24448.333615</v>
+        <v>24454.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>6070.959802000001</v>
+        <v>6070.959802</v>
       </c>
     </row>
     <row r="13">
@@ -29080,10 +29080,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10262.9195</v>
+        <v>10759.28</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>12448.2311</v>
+        <v>13207.2516</v>
       </c>
     </row>
     <row r="14">
@@ -29106,10 +29106,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="17">
@@ -29179,10 +29179,10 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D19" s="17">
         <f>(B19+C19)/2</f>
@@ -29193,10 +29193,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>169</v>
+        <v>3795</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29224,10 +29224,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>6934</v>
+        <v>6914</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>246</v>
+        <v>805.88</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40547,7 +40547,7 @@
         <v>46284</v>
       </c>
       <c r="B280" s="28" t="n">
-        <v>0.785</v>
+        <v>0.8</v>
       </c>
       <c r="C280" s="28" t="n">
         <v>0.21</v>
@@ -40598,7 +40598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M462"/>
+  <dimension ref="A1:M463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40625,7 +40625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 01:10 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -40799,10 +40799,10 @@
         </is>
       </c>
       <c r="B13" s="43" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C13" s="44" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15">
@@ -40879,7 +40879,7 @@
         <v>0.79</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="D17" s="20">
         <f>1-C17</f>
@@ -40894,7 +40894,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>82.22</v>
+        <v>12.52</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40908,10 +40908,10 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -40926,7 +40926,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>1.36</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -41028,25 +41028,25 @@
         <v>0.79</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>82.22</v>
+        <v>12.52</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>10796.48</v>
+        <v>433</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>1.36</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>21.08</v>
+        <v>77.18000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -41057,25 +41057,25 @@
         <v>0.78</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>207.34</v>
+        <v>329.34</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>200</v>
+        <v>10209.49</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>718</v>
+        <v>283.7</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>212</v>
+        <v>50050</v>
       </c>
     </row>
     <row r="25">
@@ -41086,7 +41086,7 @@
         <v>0.77</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>50958.92</v>
+        <v>50276</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
@@ -41095,16 +41095,16 @@
         <v>50496.44</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>411</v>
+        <v>527</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>50550</v>
+        <v>650</v>
       </c>
     </row>
     <row r="26">
@@ -41115,7 +41115,7 @@
         <v>0.76</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>431.3</v>
+        <v>931.3</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.14</v>
@@ -41124,16 +41124,16 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>50500</v>
+        <v>80</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27">
@@ -41147,22 +41147,22 @@
         <v>100</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>10870</v>
+        <v>5000</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>10870</v>
+        <v>50500</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -61827,6 +61827,54 @@
       <c r="M462" s="38" t="inlineStr">
         <is>
           <t>18 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="39" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B463" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C463" s="16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D463" s="17">
+        <f>IF(COUNT(B463:C463)=2,(B463+C463)/2,"")</f>
+        <v/>
+      </c>
+      <c r="E463" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F463" s="16" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G463" s="17">
+        <f>IF(COUNT(E463:F463)=2,(E463+F463)/2,"")</f>
+        <v/>
+      </c>
+      <c r="H463" s="17">
+        <f>IF(AND(ISNUMBER(D463),ISNUMBER(G463)),D463+G463,"")</f>
+        <v/>
+      </c>
+      <c r="I463" s="20">
+        <f>IFERROR(D463/H463,"")</f>
+        <v/>
+      </c>
+      <c r="J463" s="18">
+        <f>IF(AND(ISNUMBER(D463),ISNUMBER(G463)),D463-G463,"")</f>
+        <v/>
+      </c>
+      <c r="K463" s="45" t="n">
+        <v>20011.85</v>
+      </c>
+      <c r="L463" s="45" t="n">
+        <v>70312.10000000001</v>
+      </c>
+      <c r="M463" s="26" t="inlineStr">
+        <is>
+          <t>19 Sep</t>
         </is>
       </c>
     </row>
@@ -61868,7 +61916,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-19 01:10 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -61973,7 +62021,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>2458.077581</v>
+        <v>2503.077581</v>
       </c>
       <c r="C10" s="66" t="n"/>
       <c r="D10" s="66" t="n"/>
@@ -61987,7 +62035,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>26543.24248</v>
+        <v>44185.74066</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -62086,7 +62134,7 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.16</v>
@@ -62104,10 +62152,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>751.9541730000001</v>
+        <v>756.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>250.8313</v>
+        <v>8550.3256</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62127,7 +62175,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62145,7 +62193,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8318.6726</v>
+        <v>8783.42368</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62161,9 +62209,11 @@
       <c r="B18" s="78" t="n">
         <v>-1.5</v>
       </c>
-      <c r="C18" s="16" t="n"/>
+      <c r="C18" s="16" t="n">
+        <v>0.01</v>
+      </c>
       <c r="D18" s="16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -62181,7 +62231,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>191.5515</v>
+        <v>310.7984</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62201,7 +62251,7 @@
         <v>0.13</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="E19" s="17">
         <f>IF(COUNT(C19:D19)=2,(C19+D19)/2,"")</f>
@@ -62219,7 +62269,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8315.9421</v>
+        <v>8621.8665</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62257,7 +62307,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8469.404200000001</v>
+        <v>8645.790199999999</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62274,10 +62324,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.398</v>
+        <v>0.698</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62295,7 +62345,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>140.30802</v>
+        <v>299.61265</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62312,10 +62362,10 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.12</v>
+        <v>0.105</v>
       </c>
       <c r="E22" s="17">
         <f>IF(COUNT(C22:D22)=2,(C22+D22)/2,"")</f>
@@ -62330,10 +62380,10 @@
         <v/>
       </c>
       <c r="H22" s="19" t="n">
-        <v>122.03</v>
+        <v>162.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>175.8884</v>
+        <v>305.46013</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62349,7 +62399,9 @@
       <c r="B23" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="C23" s="16" t="n"/>
+      <c r="C23" s="16" t="n">
+        <v>0.01</v>
+      </c>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
       </c>
@@ -62369,7 +62421,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>183.4474</v>
+        <v>320.5605</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62386,7 +62438,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62407,7 +62459,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>213.37916</v>
+        <v>241.61581</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62424,10 +62476,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62445,7 +62497,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>154.3533</v>
+        <v>8445.709199999999</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -64015,34 +64067,34 @@
         <v>46284</v>
       </c>
       <c r="B81" s="16" t="n">
-        <v>0.12</v>
+        <v>0.145</v>
       </c>
       <c r="C81" s="16" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="D81" s="16" t="n">
         <v>0.08</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.145</v>
+        <v>0.15</v>
       </c>
       <c r="F81" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G81" s="16" t="n">
-        <v>0.242</v>
+        <v>0.4005</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>0.065</v>
+        <v>0.09</v>
       </c>
       <c r="I81" s="16" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="J81" s="16" t="n">
-        <v>0.051</v>
+        <v>0.0525</v>
       </c>
       <c r="K81" s="16" t="n">
-        <v>0.345</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="82">
@@ -64076,7 +64128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -64101,7 +64153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-19 01:10 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -64300,12 +64352,8 @@
       <c r="B14" s="91" t="n">
         <v>310000</v>
       </c>
-      <c r="C14" s="16" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>0.79</v>
-      </c>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
       <c r="E14" s="17">
         <f>IF(COUNT(C14:D14)=2,(C14+D14)/2,"")</f>
         <v/>
@@ -64336,12 +64384,8 @@
       <c r="B15" s="91" t="n">
         <v>320000</v>
       </c>
-      <c r="C15" s="16" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>0.66</v>
-      </c>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
       <c r="E15" s="17">
         <f>IF(COUNT(C15:D15)=2,(C15+D15)/2,"")</f>
         <v/>
@@ -64372,11 +64416,9 @@
       <c r="B16" s="91" t="n">
         <v>340000</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>0.47</v>
-      </c>
+      <c r="C16" s="16" t="n"/>
       <c r="D16" s="16" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -64408,12 +64450,8 @@
       <c r="B17" s="91" t="n">
         <v>360000</v>
       </c>
-      <c r="C17" s="16" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>0.41</v>
-      </c>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
         <v/>
@@ -64444,12 +64482,8 @@
       <c r="B18" s="91" t="n">
         <v>370000</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>0.29</v>
-      </c>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
         <v/>
@@ -65302,7 +65336,27 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="41" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B68" s="28" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="C68" s="28" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D68" s="28" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E68" s="28" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F68" s="28" t="n">
+        <v>0.255</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Columns are nested, not exclusive: each is P(turnout ≥ that threshold), so within a row they must fall from left to right. Kalshi began quoting this ladder on 2026-05-08.</t>
         </is>
@@ -65314,8 +65368,8 @@
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A69:J69"/>
     <mergeCell ref="B7:G7"/>
-    <mergeCell ref="A68:J68"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -65329,7 +65383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -65354,7 +65408,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-19 01:10 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>
@@ -65568,7 +65622,7 @@
         <v>0.04</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E14" s="20">
         <f>IF(ISNUMBER(D14),1-D14,"")</f>
@@ -65601,10 +65655,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="E15" s="20">
         <f>IF(ISNUMBER(D15),1-D15,"")</f>
@@ -65637,10 +65691,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="E16" s="20">
         <f>IF(ISNUMBER(D16),1-D16,"")</f>
@@ -65673,7 +65727,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>0.73</v>
@@ -65709,10 +65763,10 @@
         <v>11</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -65782,7 +65836,7 @@
       </c>
       <c r="C20" s="16" t="n"/>
       <c r="D20" s="16" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="E20" s="20">
         <f>IF(ISNUMBER(D20),1-D20,"")</f>
@@ -66725,9 +66779,34 @@
       <c r="J62" s="88" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Kalshi began quoting this ladder on 20 Aug 2026, so the history is only 30 days long. Values are the mid of the daily closing YES bid and the ask derived from the closing NO bid; where only one side closed, the same fallback as the live ladder applies.</t>
+      <c r="A63" s="39" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B63" s="16" t="n"/>
+      <c r="C63" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H63" s="16" t="n"/>
+      <c r="I63" s="16" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Kalshi began quoting this ladder on 20 Aug 2026, so the history is only 31 days long. Values are the mid of the daily closing YES bid and the ask derived from the closing NO bid; where only one side closed, the same fallback as the live ladder applies.</t>
         </is>
       </c>
     </row>
@@ -66737,7 +66816,7 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A64:J64"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
@@ -66782,7 +66861,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-19 01:10 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-19 14:25 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-19 14:25 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-19 14:25 UTC</t>
+          <t>2026-09-19 19:19 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-19 14:25 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-19 14:25 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-19 14:25 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -27489,7 +27489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-19 14:25 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -28649,7 +28649,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-19 14:25 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -28730,7 +28730,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-19 14:25 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 14:25 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -29070,7 +29070,7 @@
         <v>24454.333615</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>6070.959802</v>
+        <v>6070.959802000001</v>
       </c>
     </row>
     <row r="13">
@@ -29080,10 +29080,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10759.28</v>
+        <v>10683.4667</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>13207.2516</v>
+        <v>11928.2861</v>
       </c>
     </row>
     <row r="14">
@@ -29105,11 +29105,9 @@
           <t>24h price change</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="B15" s="13" t="n"/>
       <c r="C15" s="14" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="17">
@@ -29182,7 +29180,7 @@
         <v>0.79</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="D19" s="17">
         <f>(B19+C19)/2</f>
@@ -29196,7 +29194,7 @@
         <v>246</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>3795</v>
+        <v>5</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29213,7 +29211,7 @@
         <v>0.2</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="D20" s="17">
         <f>(B20+C20)/2</f>
@@ -29224,10 +29222,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>6914</v>
+        <v>6899</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>805.88</v>
+        <v>5</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40547,10 +40545,10 @@
         <v>46284</v>
       </c>
       <c r="B280" s="28" t="n">
-        <v>0.8</v>
+        <v>0.795</v>
       </c>
       <c r="C280" s="28" t="n">
-        <v>0.21</v>
+        <v>0.205</v>
       </c>
       <c r="D280" s="29">
         <f>IF(COUNT(B280:C280)=2,B280+C280,"")</f>
@@ -40625,7 +40623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 14:25 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -40879,7 +40877,7 @@
         <v>0.79</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="D17" s="20">
         <f>1-C17</f>
@@ -40894,7 +40892,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>12.52</v>
+        <v>9.99</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40908,10 +40906,10 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -40926,7 +40924,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>9.460000000000001</v>
+        <v>200</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -41028,25 +41026,25 @@
         <v>0.79</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>12.52</v>
+        <v>9.99</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>433</v>
+        <v>10272.7</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>9.460000000000001</v>
+        <v>200</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>77.18000000000001</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="24">
@@ -41057,25 +41055,25 @@
         <v>0.78</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>329.34</v>
+        <v>12.01</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>10209.49</v>
+        <v>200</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>283.7</v>
+        <v>322.02</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>50050</v>
+        <v>275.59</v>
       </c>
     </row>
     <row r="25">
@@ -41086,25 +41084,25 @@
         <v>0.77</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>50276</v>
+        <v>276</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>50496.44</v>
+        <v>496.44</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>650</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="26">
@@ -41115,7 +41113,7 @@
         <v>0.76</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>931.3</v>
+        <v>431.3</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.14</v>
@@ -41124,16 +41122,16 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -41144,25 +41142,25 @@
         <v>0.75</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>100</v>
+        <v>335.15</v>
       </c>
       <c r="D27" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>5870</v>
+      </c>
+      <c r="F27" s="16" t="n">
         <v>0.13</v>
       </c>
-      <c r="E27" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>0.17</v>
-      </c>
       <c r="G27" s="19" t="n">
-        <v>50500</v>
+        <v>350</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29">
@@ -61916,7 +61914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-19 14:25 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -62035,7 +62033,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>44185.74066</v>
+        <v>50948.27326</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -62152,10 +62150,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>756.954173</v>
+        <v>756.9541730000001</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8550.3256</v>
+        <v>8240.18</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62175,7 +62173,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62193,7 +62191,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8783.42368</v>
+        <v>8356.796469999999</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62231,7 +62229,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>310.7984</v>
+        <v>120.1168</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62248,7 +62246,7 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>0.17</v>
@@ -62269,7 +62267,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8621.8665</v>
+        <v>8521.8091</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62307,7 +62305,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8645.790199999999</v>
+        <v>8552.1288</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62324,10 +62322,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.101</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.698</v>
+        <v>0.398</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62345,7 +62343,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>299.61265</v>
+        <v>202.66707</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62362,10 +62360,10 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.105</v>
+        <v>0.119</v>
       </c>
       <c r="E22" s="17">
         <f>IF(COUNT(C22:D22)=2,(C22+D22)/2,"")</f>
@@ -62383,7 +62381,7 @@
         <v>162.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>305.46013</v>
+        <v>107.97379</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62421,7 +62419,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>320.5605</v>
+        <v>8198.950800000001</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62438,7 +62436,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62459,7 +62457,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>241.61581</v>
+        <v>163.72466</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62497,7 +62495,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>8445.709199999999</v>
+        <v>8412.117099999999</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -64070,31 +64068,31 @@
         <v>0.145</v>
       </c>
       <c r="C81" s="16" t="n">
-        <v>0.119</v>
+        <v>0.1185</v>
       </c>
       <c r="D81" s="16" t="n">
         <v>0.08</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.15</v>
+        <v>0.155</v>
       </c>
       <c r="F81" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G81" s="16" t="n">
-        <v>0.4005</v>
+        <v>0.243</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>0.09</v>
+        <v>0.0675</v>
       </c>
       <c r="I81" s="16" t="n">
         <v>0.045</v>
       </c>
       <c r="J81" s="16" t="n">
-        <v>0.0525</v>
+        <v>0.051</v>
       </c>
       <c r="K81" s="16" t="n">
-        <v>0.27</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="82">
@@ -64153,7 +64151,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-19 14:25 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -65408,7 +65406,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-19 14:25 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -65622,7 +65620,7 @@
         <v>0.04</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="E14" s="20">
         <f>IF(ISNUMBER(D14),1-D14,"")</f>
@@ -65655,7 +65653,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.9</v>
@@ -65691,7 +65689,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.67</v>
@@ -65730,7 +65728,7 @@
         <v>0.22</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="E17" s="20">
         <f>IF(ISNUMBER(D17),1-D17,"")</f>
@@ -65766,7 +65764,7 @@
         <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66861,7 +66859,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-19 14:25 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-19 19:19 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -538,12 +538,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$270</f>
+              <f>'Venue Comparison'!$L$15:$L$271</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$B$15:$B$270</f>
+              <f>'Venue Comparison'!$B$15:$B$271</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -574,12 +574,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$270</f>
+              <f>'Venue Comparison'!$L$15:$L$271</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$C$15:$C$270</f>
+              <f>'Venue Comparison'!$C$15:$C$271</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -610,12 +610,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$270</f>
+              <f>'Venue Comparison'!$L$15:$L$271</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$K$15:$K$270</f>
+              <f>'Venue Comparison'!$K$15:$K$271</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1396,12 +1396,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$270</f>
+              <f>'Venue Comparison'!$L$15:$L$271</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$D$15:$D$270</f>
+              <f>'Venue Comparison'!$D$15:$D$271</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2101,12 +2101,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$280</f>
+              <f>'Polymarket'!$K$25:$K$281</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$D$25:$D$280</f>
+              <f>'Polymarket'!$D$25:$D$281</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2325,12 +2325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$280</f>
+              <f>'Polymarket'!$K$25:$K$281</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$B$25:$B$280</f>
+              <f>'Polymarket'!$B$25:$B$281</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2361,12 +2361,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$280</f>
+              <f>'Polymarket'!$K$25:$K$281</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$C$25:$C$280</f>
+              <f>'Polymarket'!$C$25:$C$281</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-19 19:19 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="B48" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="D48" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-0,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="B49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
       <c r="C49" s="18">
@@ -4813,7 +4813,7 @@
         <v/>
       </c>
       <c r="D49" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-7,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="B50" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
       <c r="C50" s="18">
@@ -4832,7 +4832,7 @@
         <v/>
       </c>
       <c r="D50" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-30,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
       <c r="C51" s="18">
@@ -4851,7 +4851,7 @@
         <v/>
       </c>
       <c r="D51" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))=0,"",INDEX(Polymarket!$A$25:$A$280,MATCH(Polymarket!$A$280-90,Polymarket!$A$25:$A$280,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="B52" s="20">
-        <f>MAX(Polymarket!B25:B280)</f>
+        <f>MAX(Polymarket!B25:B281)</f>
         <v/>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B53" s="20">
-        <f>MIN(Polymarket!B25:B280)</f>
+        <f>MIN(Polymarket!B25:B281)</f>
         <v/>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-19 19:19 UTC</t>
+          <t>2026-09-20 01:08 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="B69" s="59">
-        <f>TEXT(Polymarket!A25,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Polymarket!A280,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Polymarket!A25:A280)&amp;" days)"</f>
+        <f>TEXT(Polymarket!A25,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Polymarket!A281,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Polymarket!A25:A281)&amp;" days)"</f>
         <v/>
       </c>
       <c r="C69" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-19 19:19 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H36" s="18">
@@ -5660,7 +5660,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H37" s="31">
@@ -5693,7 +5693,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H38" s="18">
@@ -5726,7 +5726,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H39" s="31">
@@ -5759,7 +5759,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H40" s="18">
@@ -5792,7 +5792,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H41" s="31">
@@ -5825,7 +5825,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H42" s="18">
@@ -5858,7 +5858,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H43" s="31">
@@ -5891,7 +5891,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H44" s="18">
@@ -5924,7 +5924,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H45" s="31">
@@ -5957,7 +5957,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H46" s="18">
@@ -5990,7 +5990,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H47" s="31">
@@ -6023,7 +6023,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H48" s="18">
@@ -6056,7 +6056,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H49" s="31">
@@ -6089,7 +6089,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H50" s="18">
@@ -6122,7 +6122,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H51" s="31">
@@ -6155,7 +6155,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H52" s="18">
@@ -6188,7 +6188,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H53" s="31">
@@ -6221,7 +6221,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H54" s="18">
@@ -6254,7 +6254,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H55" s="31">
@@ -6287,7 +6287,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H56" s="18">
@@ -6320,7 +6320,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H57" s="31">
@@ -6353,7 +6353,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H58" s="18">
@@ -6386,7 +6386,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H59" s="31">
@@ -6419,7 +6419,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H60" s="18">
@@ -6452,7 +6452,7 @@
         <v>0.499</v>
       </c>
       <c r="G61" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H61" s="31">
@@ -6485,7 +6485,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H62" s="18">
@@ -6518,7 +6518,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H63" s="31">
@@ -6551,7 +6551,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H64" s="18">
@@ -6584,7 +6584,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H65" s="31">
@@ -6617,7 +6617,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H66" s="18">
@@ -6650,7 +6650,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H67" s="31">
@@ -6683,7 +6683,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H68" s="18">
@@ -6716,7 +6716,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H69" s="31">
@@ -6749,7 +6749,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H70" s="18">
@@ -6782,7 +6782,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H71" s="31">
@@ -6815,7 +6815,7 @@
         <v>0.499</v>
       </c>
       <c r="G72" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H72" s="18">
@@ -6848,7 +6848,7 @@
         <v>0.499</v>
       </c>
       <c r="G73" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H73" s="31">
@@ -6881,7 +6881,7 @@
         <v>0.499</v>
       </c>
       <c r="G74" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H74" s="18">
@@ -6914,7 +6914,7 @@
         <v>0.499</v>
       </c>
       <c r="G75" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H75" s="31">
@@ -6947,7 +6947,7 @@
         <v>0.499</v>
       </c>
       <c r="G76" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H76" s="18">
@@ -6980,7 +6980,7 @@
         <v>0.499</v>
       </c>
       <c r="G77" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H77" s="31">
@@ -7013,7 +7013,7 @@
         <v>0.499</v>
       </c>
       <c r="G78" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H78" s="18">
@@ -7046,7 +7046,7 @@
         <v>0.499</v>
       </c>
       <c r="G79" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H79" s="31">
@@ -7079,7 +7079,7 @@
         <v>0.499</v>
       </c>
       <c r="G80" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H80" s="18">
@@ -7112,7 +7112,7 @@
         <v>0.499</v>
       </c>
       <c r="G81" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H81" s="31">
@@ -7145,7 +7145,7 @@
         <v>0.499</v>
       </c>
       <c r="G82" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H82" s="18">
@@ -7178,7 +7178,7 @@
         <v>0.499</v>
       </c>
       <c r="G83" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H83" s="31">
@@ -7211,7 +7211,7 @@
         <v>0.499</v>
       </c>
       <c r="G84" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H84" s="18">
@@ -7244,7 +7244,7 @@
         <v>0.499</v>
       </c>
       <c r="G85" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H85" s="31">
@@ -7277,7 +7277,7 @@
         <v>0.499</v>
       </c>
       <c r="G86" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H86" s="18">
@@ -7310,7 +7310,7 @@
         <v>0.499</v>
       </c>
       <c r="G87" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H87" s="31">
@@ -7343,7 +7343,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H88" s="18">
@@ -7376,7 +7376,7 @@
         <v>0.499</v>
       </c>
       <c r="G89" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H89" s="31">
@@ -7409,7 +7409,7 @@
         <v>0.499</v>
       </c>
       <c r="G90" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H90" s="18">
@@ -7442,7 +7442,7 @@
         <v>0.5</v>
       </c>
       <c r="G91" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H91" s="31">
@@ -7475,7 +7475,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H92" s="18">
@@ -7508,7 +7508,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H93" s="31">
@@ -7541,7 +7541,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H94" s="18">
@@ -7574,7 +7574,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H95" s="31">
@@ -7607,7 +7607,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H96" s="18">
@@ -7640,7 +7640,7 @@
         <v>0.499</v>
       </c>
       <c r="G97" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H97" s="31">
@@ -7673,7 +7673,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H98" s="18">
@@ -7706,7 +7706,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H99" s="31">
@@ -7739,7 +7739,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H100" s="18">
@@ -7772,7 +7772,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H101" s="31">
@@ -7805,7 +7805,7 @@
         <v>0.5</v>
       </c>
       <c r="G102" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H102" s="18">
@@ -7838,7 +7838,7 @@
         <v>0.5</v>
       </c>
       <c r="G103" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H103" s="31">
@@ -7871,7 +7871,7 @@
         <v>0.5</v>
       </c>
       <c r="G104" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H104" s="18">
@@ -7904,7 +7904,7 @@
         <v>0.5</v>
       </c>
       <c r="G105" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H105" s="31">
@@ -7937,7 +7937,7 @@
         <v>0.5</v>
       </c>
       <c r="G106" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H106" s="18">
@@ -7970,7 +7970,7 @@
         <v>0.5</v>
       </c>
       <c r="G107" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H107" s="31">
@@ -8003,7 +8003,7 @@
         <v>0.5</v>
       </c>
       <c r="G108" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H108" s="18">
@@ -8036,7 +8036,7 @@
         <v>0.5</v>
       </c>
       <c r="G109" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H109" s="31">
@@ -8069,7 +8069,7 @@
         <v>0.5</v>
       </c>
       <c r="G110" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H110" s="18">
@@ -8102,7 +8102,7 @@
         <v>0.5</v>
       </c>
       <c r="G111" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H111" s="31">
@@ -8135,7 +8135,7 @@
         <v>0.5</v>
       </c>
       <c r="G112" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H112" s="18">
@@ -8168,7 +8168,7 @@
         <v>0.5</v>
       </c>
       <c r="G113" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H113" s="31">
@@ -8201,7 +8201,7 @@
         <v>0.5</v>
       </c>
       <c r="G114" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H114" s="18">
@@ -8234,7 +8234,7 @@
         <v>0.5</v>
       </c>
       <c r="G115" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H115" s="31">
@@ -8267,7 +8267,7 @@
         <v>0.5</v>
       </c>
       <c r="G116" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H116" s="18">
@@ -8300,7 +8300,7 @@
         <v>0.499</v>
       </c>
       <c r="G117" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H117" s="31">
@@ -8333,7 +8333,7 @@
         <v>0.499</v>
       </c>
       <c r="G118" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H118" s="18">
@@ -8366,7 +8366,7 @@
         <v>0.499</v>
       </c>
       <c r="G119" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H119" s="31">
@@ -8399,7 +8399,7 @@
         <v>0.499</v>
       </c>
       <c r="G120" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H120" s="18">
@@ -8432,7 +8432,7 @@
         <v>0.499</v>
       </c>
       <c r="G121" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H121" s="31">
@@ -8465,7 +8465,7 @@
         <v>0.499</v>
       </c>
       <c r="G122" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H122" s="18">
@@ -8498,7 +8498,7 @@
         <v>0.499</v>
       </c>
       <c r="G123" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H123" s="31">
@@ -8531,7 +8531,7 @@
         <v>0.499</v>
       </c>
       <c r="G124" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H124" s="18">
@@ -8564,7 +8564,7 @@
         <v>0.499</v>
       </c>
       <c r="G125" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H125" s="31">
@@ -8597,7 +8597,7 @@
         <v>0.499</v>
       </c>
       <c r="G126" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H126" s="18">
@@ -8630,7 +8630,7 @@
         <v>0.499</v>
       </c>
       <c r="G127" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H127" s="31">
@@ -8663,7 +8663,7 @@
         <v>0.499</v>
       </c>
       <c r="G128" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H128" s="18">
@@ -8696,7 +8696,7 @@
         <v>0.499</v>
       </c>
       <c r="G129" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H129" s="31">
@@ -8729,7 +8729,7 @@
         <v>0.499</v>
       </c>
       <c r="G130" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H130" s="18">
@@ -8762,7 +8762,7 @@
         <v>0.499</v>
       </c>
       <c r="G131" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H131" s="31">
@@ -8795,7 +8795,7 @@
         <v>0.5</v>
       </c>
       <c r="G132" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H132" s="18">
@@ -8828,7 +8828,7 @@
         <v>0.499</v>
       </c>
       <c r="G133" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H133" s="31">
@@ -8861,7 +8861,7 @@
         <v>0.5</v>
       </c>
       <c r="G134" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H134" s="18">
@@ -8894,7 +8894,7 @@
         <v>0.499</v>
       </c>
       <c r="G135" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H135" s="31">
@@ -8927,7 +8927,7 @@
         <v>0.499</v>
       </c>
       <c r="G136" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H136" s="18">
@@ -8960,7 +8960,7 @@
         <v>0.5</v>
       </c>
       <c r="G137" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H137" s="31">
@@ -8993,7 +8993,7 @@
         <v>0.498</v>
       </c>
       <c r="G138" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H138" s="18">
@@ -9026,7 +9026,7 @@
         <v>0.498</v>
       </c>
       <c r="G139" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H139" s="31">
@@ -9059,7 +9059,7 @@
         <v>0.498</v>
       </c>
       <c r="G140" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H140" s="18">
@@ -9092,7 +9092,7 @@
         <v>0.498</v>
       </c>
       <c r="G141" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H141" s="31">
@@ -9125,7 +9125,7 @@
         <v>0.498</v>
       </c>
       <c r="G142" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H142" s="18">
@@ -9158,7 +9158,7 @@
         <v>0.498</v>
       </c>
       <c r="G143" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H143" s="31">
@@ -9191,7 +9191,7 @@
         <v>0.498</v>
       </c>
       <c r="G144" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H144" s="18">
@@ -9224,7 +9224,7 @@
         <v>0.498</v>
       </c>
       <c r="G145" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H145" s="31">
@@ -9257,7 +9257,7 @@
         <v>0.498</v>
       </c>
       <c r="G146" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H146" s="18">
@@ -9290,7 +9290,7 @@
         <v>0.498</v>
       </c>
       <c r="G147" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H147" s="31">
@@ -9323,7 +9323,7 @@
         <v>0.498</v>
       </c>
       <c r="G148" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H148" s="18">
@@ -9356,7 +9356,7 @@
         <v>0.498</v>
       </c>
       <c r="G149" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H149" s="31">
@@ -9389,7 +9389,7 @@
         <v>0.498</v>
       </c>
       <c r="G150" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H150" s="18">
@@ -9422,7 +9422,7 @@
         <v>0.498</v>
       </c>
       <c r="G151" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H151" s="31">
@@ -9455,7 +9455,7 @@
         <v>0.498</v>
       </c>
       <c r="G152" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H152" s="18">
@@ -9488,7 +9488,7 @@
         <v>0.498</v>
       </c>
       <c r="G153" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H153" s="31">
@@ -9521,7 +9521,7 @@
         <v>0.498</v>
       </c>
       <c r="G154" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H154" s="18">
@@ -9554,7 +9554,7 @@
         <v>0.498</v>
       </c>
       <c r="G155" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H155" s="31">
@@ -9587,7 +9587,7 @@
         <v>0.498</v>
       </c>
       <c r="G156" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H156" s="18">
@@ -9620,7 +9620,7 @@
         <v>0.498</v>
       </c>
       <c r="G157" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H157" s="31">
@@ -9653,7 +9653,7 @@
         <v>0.498</v>
       </c>
       <c r="G158" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H158" s="18">
@@ -9686,7 +9686,7 @@
         <v>0.498</v>
       </c>
       <c r="G159" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H159" s="31">
@@ -9719,7 +9719,7 @@
         <v>0.498</v>
       </c>
       <c r="G160" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H160" s="18">
@@ -9752,7 +9752,7 @@
         <v>0.498</v>
       </c>
       <c r="G161" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H161" s="31">
@@ -9785,7 +9785,7 @@
         <v>0.498</v>
       </c>
       <c r="G162" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H162" s="18">
@@ -9818,7 +9818,7 @@
         <v>0.498</v>
       </c>
       <c r="G163" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H163" s="31">
@@ -9851,7 +9851,7 @@
         <v>0.498</v>
       </c>
       <c r="G164" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H164" s="18">
@@ -9884,7 +9884,7 @@
         <v>0.498</v>
       </c>
       <c r="G165" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H165" s="31">
@@ -9917,7 +9917,7 @@
         <v>0.498</v>
       </c>
       <c r="G166" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H166" s="18">
@@ -9950,7 +9950,7 @@
         <v>0.498</v>
       </c>
       <c r="G167" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H167" s="31">
@@ -9983,7 +9983,7 @@
         <v>0.498</v>
       </c>
       <c r="G168" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H168" s="18">
@@ -10016,7 +10016,7 @@
         <v>0.498</v>
       </c>
       <c r="G169" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H169" s="31">
@@ -10049,7 +10049,7 @@
         <v>0.498</v>
       </c>
       <c r="G170" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H170" s="18">
@@ -10082,7 +10082,7 @@
         <v>0.498</v>
       </c>
       <c r="G171" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H171" s="31">
@@ -10115,7 +10115,7 @@
         <v>0.498</v>
       </c>
       <c r="G172" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H172" s="18">
@@ -10148,7 +10148,7 @@
         <v>0.498</v>
       </c>
       <c r="G173" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H173" s="31">
@@ -10181,7 +10181,7 @@
         <v>0.498</v>
       </c>
       <c r="G174" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H174" s="18">
@@ -10214,7 +10214,7 @@
         <v>0.498</v>
       </c>
       <c r="G175" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H175" s="31">
@@ -10247,7 +10247,7 @@
         <v>0.498</v>
       </c>
       <c r="G176" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H176" s="18">
@@ -10280,7 +10280,7 @@
         <v>0.498</v>
       </c>
       <c r="G177" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H177" s="31">
@@ -10313,7 +10313,7 @@
         <v>0.498</v>
       </c>
       <c r="G178" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H178" s="18">
@@ -10346,7 +10346,7 @@
         <v>0.498</v>
       </c>
       <c r="G179" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H179" s="31">
@@ -10379,7 +10379,7 @@
         <v>0.498</v>
       </c>
       <c r="G180" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H180" s="18">
@@ -10412,7 +10412,7 @@
         <v>0.498</v>
       </c>
       <c r="G181" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H181" s="31">
@@ -10445,7 +10445,7 @@
         <v>0.498</v>
       </c>
       <c r="G182" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H182" s="18">
@@ -10478,7 +10478,7 @@
         <v>0.498</v>
       </c>
       <c r="G183" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H183" s="31">
@@ -10511,7 +10511,7 @@
         <v>0.498</v>
       </c>
       <c r="G184" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H184" s="18">
@@ -10544,7 +10544,7 @@
         <v>0.498</v>
       </c>
       <c r="G185" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H185" s="31">
@@ -10577,7 +10577,7 @@
         <v>0.498</v>
       </c>
       <c r="G186" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H186" s="18">
@@ -10610,7 +10610,7 @@
         <v>0.498</v>
       </c>
       <c r="G187" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H187" s="31">
@@ -10643,7 +10643,7 @@
         <v>0.498</v>
       </c>
       <c r="G188" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H188" s="18">
@@ -10676,7 +10676,7 @@
         <v>0.4970000000000001</v>
       </c>
       <c r="G189" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H189" s="31">
@@ -10709,7 +10709,7 @@
         <v>0.498</v>
       </c>
       <c r="G190" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H190" s="18">
@@ -10742,7 +10742,7 @@
         <v>0.498</v>
       </c>
       <c r="G191" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H191" s="31">
@@ -10775,7 +10775,7 @@
         <v>0.498</v>
       </c>
       <c r="G192" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H192" s="18">
@@ -10808,7 +10808,7 @@
         <v>0.498</v>
       </c>
       <c r="G193" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H193" s="31">
@@ -10841,7 +10841,7 @@
         <v>0.498</v>
       </c>
       <c r="G194" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H194" s="18">
@@ -10874,7 +10874,7 @@
         <v>0.498</v>
       </c>
       <c r="G195" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H195" s="31">
@@ -10907,7 +10907,7 @@
         <v>0.498</v>
       </c>
       <c r="G196" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H196" s="18">
@@ -10940,7 +10940,7 @@
         <v>0.498</v>
       </c>
       <c r="G197" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H197" s="31">
@@ -10973,7 +10973,7 @@
         <v>0.498</v>
       </c>
       <c r="G198" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H198" s="18">
@@ -11006,7 +11006,7 @@
         <v>0.498</v>
       </c>
       <c r="G199" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H199" s="31">
@@ -11039,7 +11039,7 @@
         <v>0.498</v>
       </c>
       <c r="G200" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H200" s="18">
@@ -11072,7 +11072,7 @@
         <v>0.498</v>
       </c>
       <c r="G201" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H201" s="31">
@@ -11105,7 +11105,7 @@
         <v>0.498</v>
       </c>
       <c r="G202" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H202" s="18">
@@ -11138,7 +11138,7 @@
         <v>0.498</v>
       </c>
       <c r="G203" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H203" s="31">
@@ -11171,7 +11171,7 @@
         <v>0.498</v>
       </c>
       <c r="G204" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H204" s="18">
@@ -11204,7 +11204,7 @@
         <v>0.498</v>
       </c>
       <c r="G205" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H205" s="31">
@@ -11237,7 +11237,7 @@
         <v>0.498</v>
       </c>
       <c r="G206" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H206" s="18">
@@ -11270,7 +11270,7 @@
         <v>0.498</v>
       </c>
       <c r="G207" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H207" s="31">
@@ -11303,7 +11303,7 @@
         <v>0.498</v>
       </c>
       <c r="G208" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H208" s="18">
@@ -11336,7 +11336,7 @@
         <v>0.498</v>
       </c>
       <c r="G209" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H209" s="31">
@@ -11369,7 +11369,7 @@
         <v>0.498</v>
       </c>
       <c r="G210" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H210" s="18">
@@ -11402,7 +11402,7 @@
         <v>0.498</v>
       </c>
       <c r="G211" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H211" s="31">
@@ -11435,7 +11435,7 @@
         <v>0.498</v>
       </c>
       <c r="G212" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H212" s="18">
@@ -11468,7 +11468,7 @@
         <v>0.498</v>
       </c>
       <c r="G213" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H213" s="31">
@@ -11501,7 +11501,7 @@
         <v>0.498</v>
       </c>
       <c r="G214" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H214" s="18">
@@ -11534,7 +11534,7 @@
         <v>0.499</v>
       </c>
       <c r="G215" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H215" s="31">
@@ -11567,7 +11567,7 @@
         <v>0.498</v>
       </c>
       <c r="G216" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H216" s="18">
@@ -11600,7 +11600,7 @@
         <v>0.498</v>
       </c>
       <c r="G217" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H217" s="31">
@@ -11633,7 +11633,7 @@
         <v>0.498</v>
       </c>
       <c r="G218" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H218" s="18">
@@ -11666,7 +11666,7 @@
         <v>0.498</v>
       </c>
       <c r="G219" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H219" s="31">
@@ -11699,7 +11699,7 @@
         <v>0.498</v>
       </c>
       <c r="G220" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H220" s="18">
@@ -11732,7 +11732,7 @@
         <v>0.498</v>
       </c>
       <c r="G221" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H221" s="31">
@@ -11765,7 +11765,7 @@
         <v>0.498</v>
       </c>
       <c r="G222" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H222" s="18">
@@ -11798,7 +11798,7 @@
         <v>0.499</v>
       </c>
       <c r="G223" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H223" s="31">
@@ -11831,7 +11831,7 @@
         <v>0.498</v>
       </c>
       <c r="G224" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H224" s="18">
@@ -11864,7 +11864,7 @@
         <v>0.498</v>
       </c>
       <c r="G225" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H225" s="31">
@@ -11897,7 +11897,7 @@
         <v>0.498</v>
       </c>
       <c r="G226" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H226" s="18">
@@ -11930,7 +11930,7 @@
         <v>0.499</v>
       </c>
       <c r="G227" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H227" s="31">
@@ -11963,7 +11963,7 @@
         <v>0.498</v>
       </c>
       <c r="G228" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H228" s="18">
@@ -11996,7 +11996,7 @@
         <v>0.498</v>
       </c>
       <c r="G229" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H229" s="31">
@@ -12029,7 +12029,7 @@
         <v>0.498</v>
       </c>
       <c r="G230" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H230" s="18">
@@ -12062,7 +12062,7 @@
         <v>0.498</v>
       </c>
       <c r="G231" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H231" s="31">
@@ -12095,7 +12095,7 @@
         <v>0.498</v>
       </c>
       <c r="G232" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H232" s="18">
@@ -12128,7 +12128,7 @@
         <v>0.498</v>
       </c>
       <c r="G233" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H233" s="31">
@@ -12161,7 +12161,7 @@
         <v>0.498</v>
       </c>
       <c r="G234" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H234" s="18">
@@ -12194,7 +12194,7 @@
         <v>0.499</v>
       </c>
       <c r="G235" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H235" s="31">
@@ -12227,7 +12227,7 @@
         <v>0.498</v>
       </c>
       <c r="G236" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H236" s="18">
@@ -12260,7 +12260,7 @@
         <v>0.498</v>
       </c>
       <c r="G237" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H237" s="31">
@@ -12293,7 +12293,7 @@
         <v>0.498</v>
       </c>
       <c r="G238" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H238" s="18">
@@ -12326,7 +12326,7 @@
         <v>0.498</v>
       </c>
       <c r="G239" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H239" s="31">
@@ -12359,7 +12359,7 @@
         <v>0.498</v>
       </c>
       <c r="G240" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H240" s="18">
@@ -12392,7 +12392,7 @@
         <v>0.498</v>
       </c>
       <c r="G241" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H241" s="31">
@@ -12425,7 +12425,7 @@
         <v>0.498</v>
       </c>
       <c r="G242" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H242" s="18">
@@ -12458,7 +12458,7 @@
         <v>0.498</v>
       </c>
       <c r="G243" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H243" s="31">
@@ -12491,7 +12491,7 @@
         <v>0.498</v>
       </c>
       <c r="G244" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H244" s="18">
@@ -12524,7 +12524,7 @@
         <v>0.498</v>
       </c>
       <c r="G245" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H245" s="31">
@@ -12557,7 +12557,7 @@
         <v>0.498</v>
       </c>
       <c r="G246" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H246" s="18">
@@ -12590,7 +12590,7 @@
         <v>0.498</v>
       </c>
       <c r="G247" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H247" s="31">
@@ -12623,7 +12623,7 @@
         <v>0.498</v>
       </c>
       <c r="G248" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H248" s="18">
@@ -12656,7 +12656,7 @@
         <v>0.498</v>
       </c>
       <c r="G249" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H249" s="31">
@@ -12689,7 +12689,7 @@
         <v>0.498</v>
       </c>
       <c r="G250" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H250" s="18">
@@ -12722,7 +12722,7 @@
         <v>0.498</v>
       </c>
       <c r="G251" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H251" s="31">
@@ -12755,7 +12755,7 @@
         <v>0.498</v>
       </c>
       <c r="G252" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H252" s="18">
@@ -12788,7 +12788,7 @@
         <v>0.498</v>
       </c>
       <c r="G253" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H253" s="31">
@@ -12821,7 +12821,7 @@
         <v>0.498</v>
       </c>
       <c r="G254" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H254" s="18">
@@ -12854,7 +12854,7 @@
         <v>0.498</v>
       </c>
       <c r="G255" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H255" s="31">
@@ -12887,7 +12887,7 @@
         <v>0.498</v>
       </c>
       <c r="G256" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H256" s="18">
@@ -12920,7 +12920,7 @@
         <v>0.498</v>
       </c>
       <c r="G257" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H257" s="31">
@@ -12953,7 +12953,7 @@
         <v>0.498</v>
       </c>
       <c r="G258" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H258" s="18">
@@ -12986,7 +12986,7 @@
         <v>0.498</v>
       </c>
       <c r="G259" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H259" s="31">
@@ -13019,7 +13019,7 @@
         <v>0.498</v>
       </c>
       <c r="G260" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H260" s="18">
@@ -13052,7 +13052,7 @@
         <v>0.498</v>
       </c>
       <c r="G261" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H261" s="31">
@@ -13085,7 +13085,7 @@
         <v>0.498</v>
       </c>
       <c r="G262" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H262" s="18">
@@ -13118,7 +13118,7 @@
         <v>0.498</v>
       </c>
       <c r="G263" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H263" s="31">
@@ -13151,7 +13151,7 @@
         <v>0.498</v>
       </c>
       <c r="G264" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H264" s="18">
@@ -13184,7 +13184,7 @@
         <v>0.498</v>
       </c>
       <c r="G265" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H265" s="31">
@@ -13217,7 +13217,7 @@
         <v>0.4970000000000001</v>
       </c>
       <c r="G266" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="H266" s="18">
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-19 19:19 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L270"/>
+  <dimension ref="A1:L271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-19 19:19 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>IFERROR(AVERAGE(E15:E270),"")</f>
+        <f>IFERROR(AVERAGE(E15:E271),"")</f>
         <v/>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>IFERROR(MAX(E15:E270),"")</f>
+        <f>IFERROR(MAX(E15:E271),"")</f>
         <v/>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
         </is>
       </c>
       <c r="B10" s="40">
-        <f>COUNT(D15:D270)</f>
+        <f>COUNT(D15:D271)</f>
         <v/>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
         </is>
       </c>
       <c r="B11" s="40">
-        <f>COUNT(A15:A270)-COUNT(D15:D270)</f>
+        <f>COUNT(A15:A271)-COUNT(D15:D271)</f>
         <v/>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         <v>46008</v>
       </c>
       <c r="B15" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A15,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A15,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A15,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A15,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C15" s="100">
@@ -14937,7 +14937,7 @@
         <v/>
       </c>
       <c r="F15" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A15,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A15,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A15,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A15,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G15" s="100">
@@ -14970,7 +14970,7 @@
         <v>46009</v>
       </c>
       <c r="B16" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A16,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A16,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A16,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A16,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C16" s="101">
@@ -14986,7 +14986,7 @@
         <v/>
       </c>
       <c r="F16" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A16,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A16,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A16,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A16,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G16" s="101">
@@ -15019,7 +15019,7 @@
         <v>46010</v>
       </c>
       <c r="B17" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A17,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A17,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A17,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A17,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C17" s="100">
@@ -15035,7 +15035,7 @@
         <v/>
       </c>
       <c r="F17" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A17,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A17,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A17,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A17,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G17" s="100">
@@ -15068,7 +15068,7 @@
         <v>46011</v>
       </c>
       <c r="B18" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A18,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A18,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A18,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A18,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C18" s="101">
@@ -15084,7 +15084,7 @@
         <v/>
       </c>
       <c r="F18" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A18,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A18,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A18,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A18,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G18" s="101">
@@ -15117,7 +15117,7 @@
         <v>46012</v>
       </c>
       <c r="B19" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A19,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A19,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A19,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A19,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C19" s="100">
@@ -15133,7 +15133,7 @@
         <v/>
       </c>
       <c r="F19" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A19,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A19,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A19,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A19,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G19" s="100">
@@ -15166,7 +15166,7 @@
         <v>46013</v>
       </c>
       <c r="B20" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A20,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A20,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A20,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A20,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C20" s="101">
@@ -15182,7 +15182,7 @@
         <v/>
       </c>
       <c r="F20" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A20,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A20,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A20,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A20,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G20" s="101">
@@ -15215,7 +15215,7 @@
         <v>46014</v>
       </c>
       <c r="B21" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A21,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A21,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A21,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A21,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C21" s="100">
@@ -15231,7 +15231,7 @@
         <v/>
       </c>
       <c r="F21" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A21,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A21,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A21,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A21,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G21" s="100">
@@ -15264,7 +15264,7 @@
         <v>46015</v>
       </c>
       <c r="B22" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A22,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A22,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A22,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A22,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C22" s="101">
@@ -15280,7 +15280,7 @@
         <v/>
       </c>
       <c r="F22" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A22,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A22,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A22,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A22,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G22" s="101">
@@ -15313,7 +15313,7 @@
         <v>46016</v>
       </c>
       <c r="B23" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A23,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A23,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A23,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A23,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C23" s="100">
@@ -15329,7 +15329,7 @@
         <v/>
       </c>
       <c r="F23" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A23,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A23,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A23,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A23,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G23" s="100">
@@ -15362,7 +15362,7 @@
         <v>46017</v>
       </c>
       <c r="B24" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A24,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A24,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A24,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A24,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C24" s="101">
@@ -15378,7 +15378,7 @@
         <v/>
       </c>
       <c r="F24" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A24,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A24,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A24,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A24,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G24" s="101">
@@ -15411,7 +15411,7 @@
         <v>46018</v>
       </c>
       <c r="B25" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A25,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A25,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A25,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A25,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C25" s="100">
@@ -15427,7 +15427,7 @@
         <v/>
       </c>
       <c r="F25" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A25,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A25,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A25,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A25,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G25" s="100">
@@ -15460,7 +15460,7 @@
         <v>46019</v>
       </c>
       <c r="B26" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A26,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A26,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A26,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A26,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C26" s="101">
@@ -15476,7 +15476,7 @@
         <v/>
       </c>
       <c r="F26" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A26,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A26,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A26,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A26,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G26" s="101">
@@ -15509,7 +15509,7 @@
         <v>46020</v>
       </c>
       <c r="B27" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A27,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A27,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A27,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A27,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C27" s="100">
@@ -15525,7 +15525,7 @@
         <v/>
       </c>
       <c r="F27" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A27,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A27,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A27,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A27,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G27" s="100">
@@ -15558,7 +15558,7 @@
         <v>46021</v>
       </c>
       <c r="B28" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A28,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A28,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A28,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A28,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C28" s="101">
@@ -15574,7 +15574,7 @@
         <v/>
       </c>
       <c r="F28" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A28,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A28,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A28,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A28,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G28" s="101">
@@ -15607,7 +15607,7 @@
         <v>46022</v>
       </c>
       <c r="B29" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A29,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A29,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A29,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A29,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C29" s="100">
@@ -15623,7 +15623,7 @@
         <v/>
       </c>
       <c r="F29" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A29,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A29,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A29,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A29,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G29" s="100">
@@ -15656,7 +15656,7 @@
         <v>46023</v>
       </c>
       <c r="B30" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A30,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A30,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A30,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A30,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C30" s="101">
@@ -15672,7 +15672,7 @@
         <v/>
       </c>
       <c r="F30" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A30,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A30,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A30,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A30,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G30" s="101">
@@ -15705,7 +15705,7 @@
         <v>46024</v>
       </c>
       <c r="B31" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A31,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A31,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A31,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A31,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C31" s="100">
@@ -15721,7 +15721,7 @@
         <v/>
       </c>
       <c r="F31" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A31,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A31,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A31,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A31,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G31" s="100">
@@ -15754,7 +15754,7 @@
         <v>46025</v>
       </c>
       <c r="B32" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A32,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A32,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A32,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A32,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C32" s="101">
@@ -15770,7 +15770,7 @@
         <v/>
       </c>
       <c r="F32" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A32,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A32,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A32,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A32,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G32" s="101">
@@ -15803,7 +15803,7 @@
         <v>46026</v>
       </c>
       <c r="B33" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A33,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A33,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A33,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A33,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C33" s="100">
@@ -15819,7 +15819,7 @@
         <v/>
       </c>
       <c r="F33" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A33,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A33,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A33,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A33,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G33" s="100">
@@ -15852,7 +15852,7 @@
         <v>46027</v>
       </c>
       <c r="B34" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A34,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A34,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A34,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A34,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C34" s="101">
@@ -15868,7 +15868,7 @@
         <v/>
       </c>
       <c r="F34" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A34,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A34,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A34,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A34,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G34" s="101">
@@ -15901,7 +15901,7 @@
         <v>46028</v>
       </c>
       <c r="B35" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A35,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A35,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A35,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A35,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C35" s="100">
@@ -15917,7 +15917,7 @@
         <v/>
       </c>
       <c r="F35" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A35,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A35,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A35,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A35,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G35" s="100">
@@ -15950,7 +15950,7 @@
         <v>46029</v>
       </c>
       <c r="B36" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A36,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C36" s="101">
@@ -15966,7 +15966,7 @@
         <v/>
       </c>
       <c r="F36" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A36,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A36,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A36,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A36,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G36" s="101">
@@ -15999,7 +15999,7 @@
         <v>46030</v>
       </c>
       <c r="B37" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A37,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C37" s="100">
@@ -16015,7 +16015,7 @@
         <v/>
       </c>
       <c r="F37" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A37,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A37,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A37,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A37,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G37" s="100">
@@ -16048,7 +16048,7 @@
         <v>46031</v>
       </c>
       <c r="B38" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A38,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C38" s="101">
@@ -16064,7 +16064,7 @@
         <v/>
       </c>
       <c r="F38" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A38,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A38,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A38,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A38,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G38" s="101">
@@ -16097,7 +16097,7 @@
         <v>46032</v>
       </c>
       <c r="B39" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A39,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C39" s="100">
@@ -16113,7 +16113,7 @@
         <v/>
       </c>
       <c r="F39" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A39,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A39,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A39,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A39,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G39" s="100">
@@ -16146,7 +16146,7 @@
         <v>46033</v>
       </c>
       <c r="B40" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A40,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C40" s="101">
@@ -16162,7 +16162,7 @@
         <v/>
       </c>
       <c r="F40" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A40,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A40,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A40,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A40,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G40" s="101">
@@ -16195,7 +16195,7 @@
         <v>46034</v>
       </c>
       <c r="B41" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A41,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C41" s="100">
@@ -16211,7 +16211,7 @@
         <v/>
       </c>
       <c r="F41" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A41,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A41,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A41,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A41,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G41" s="100">
@@ -16244,7 +16244,7 @@
         <v>46035</v>
       </c>
       <c r="B42" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A42,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C42" s="101">
@@ -16260,7 +16260,7 @@
         <v/>
       </c>
       <c r="F42" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A42,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A42,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A42,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A42,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G42" s="101">
@@ -16293,7 +16293,7 @@
         <v>46036</v>
       </c>
       <c r="B43" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A43,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C43" s="100">
@@ -16309,7 +16309,7 @@
         <v/>
       </c>
       <c r="F43" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A43,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A43,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A43,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A43,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G43" s="100">
@@ -16342,7 +16342,7 @@
         <v>46037</v>
       </c>
       <c r="B44" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A44,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C44" s="101">
@@ -16358,7 +16358,7 @@
         <v/>
       </c>
       <c r="F44" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A44,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A44,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A44,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A44,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G44" s="101">
@@ -16391,7 +16391,7 @@
         <v>46038</v>
       </c>
       <c r="B45" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A45,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C45" s="100">
@@ -16407,7 +16407,7 @@
         <v/>
       </c>
       <c r="F45" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A45,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A45,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A45,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A45,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G45" s="100">
@@ -16440,7 +16440,7 @@
         <v>46039</v>
       </c>
       <c r="B46" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A46,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C46" s="101">
@@ -16456,7 +16456,7 @@
         <v/>
       </c>
       <c r="F46" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A46,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A46,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A46,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A46,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G46" s="101">
@@ -16489,7 +16489,7 @@
         <v>46040</v>
       </c>
       <c r="B47" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A47,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C47" s="100">
@@ -16505,7 +16505,7 @@
         <v/>
       </c>
       <c r="F47" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A47,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A47,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A47,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A47,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G47" s="100">
@@ -16538,7 +16538,7 @@
         <v>46041</v>
       </c>
       <c r="B48" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A48,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C48" s="101">
@@ -16554,7 +16554,7 @@
         <v/>
       </c>
       <c r="F48" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A48,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A48,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A48,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A48,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G48" s="101">
@@ -16587,7 +16587,7 @@
         <v>46042</v>
       </c>
       <c r="B49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A49,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C49" s="100">
@@ -16603,7 +16603,7 @@
         <v/>
       </c>
       <c r="F49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A49,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A49,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A49,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A49,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G49" s="100">
@@ -16636,7 +16636,7 @@
         <v>46043</v>
       </c>
       <c r="B50" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A50,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C50" s="101">
@@ -16652,7 +16652,7 @@
         <v/>
       </c>
       <c r="F50" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A50,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A50,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A50,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A50,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G50" s="101">
@@ -16685,7 +16685,7 @@
         <v>46044</v>
       </c>
       <c r="B51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A51,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C51" s="100">
@@ -16701,7 +16701,7 @@
         <v/>
       </c>
       <c r="F51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A51,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A51,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A51,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A51,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G51" s="100">
@@ -16734,7 +16734,7 @@
         <v>46045</v>
       </c>
       <c r="B52" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A52,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C52" s="101">
@@ -16750,7 +16750,7 @@
         <v/>
       </c>
       <c r="F52" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A52,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A52,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A52,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A52,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G52" s="101">
@@ -16783,7 +16783,7 @@
         <v>46046</v>
       </c>
       <c r="B53" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A53,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C53" s="100">
@@ -16799,7 +16799,7 @@
         <v/>
       </c>
       <c r="F53" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A53,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A53,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A53,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A53,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G53" s="100">
@@ -16832,7 +16832,7 @@
         <v>46047</v>
       </c>
       <c r="B54" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A54,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C54" s="101">
@@ -16848,7 +16848,7 @@
         <v/>
       </c>
       <c r="F54" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A54,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A54,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A54,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A54,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G54" s="101">
@@ -16881,7 +16881,7 @@
         <v>46048</v>
       </c>
       <c r="B55" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A55,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C55" s="100">
@@ -16897,7 +16897,7 @@
         <v/>
       </c>
       <c r="F55" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A55,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A55,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A55,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A55,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G55" s="100">
@@ -16930,7 +16930,7 @@
         <v>46049</v>
       </c>
       <c r="B56" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A56,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C56" s="101">
@@ -16946,7 +16946,7 @@
         <v/>
       </c>
       <c r="F56" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A56,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A56,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A56,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A56,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G56" s="101">
@@ -16979,7 +16979,7 @@
         <v>46050</v>
       </c>
       <c r="B57" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A57,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C57" s="100">
@@ -16995,7 +16995,7 @@
         <v/>
       </c>
       <c r="F57" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A57,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A57,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A57,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A57,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G57" s="100">
@@ -17028,7 +17028,7 @@
         <v>46051</v>
       </c>
       <c r="B58" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A58,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C58" s="101">
@@ -17044,7 +17044,7 @@
         <v/>
       </c>
       <c r="F58" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A58,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A58,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A58,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A58,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G58" s="101">
@@ -17077,7 +17077,7 @@
         <v>46052</v>
       </c>
       <c r="B59" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A59,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C59" s="100">
@@ -17093,7 +17093,7 @@
         <v/>
       </c>
       <c r="F59" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A59,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A59,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A59,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A59,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G59" s="100">
@@ -17126,7 +17126,7 @@
         <v>46053</v>
       </c>
       <c r="B60" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A60,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C60" s="101">
@@ -17142,7 +17142,7 @@
         <v/>
       </c>
       <c r="F60" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A60,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A60,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A60,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A60,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G60" s="101">
@@ -17175,7 +17175,7 @@
         <v>46054</v>
       </c>
       <c r="B61" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A61,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C61" s="100">
@@ -17191,7 +17191,7 @@
         <v/>
       </c>
       <c r="F61" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A61,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A61,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A61,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A61,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G61" s="100">
@@ -17224,7 +17224,7 @@
         <v>46055</v>
       </c>
       <c r="B62" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A62,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C62" s="101">
@@ -17240,7 +17240,7 @@
         <v/>
       </c>
       <c r="F62" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A62,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A62,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A62,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A62,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G62" s="101">
@@ -17273,7 +17273,7 @@
         <v>46056</v>
       </c>
       <c r="B63" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A63,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C63" s="100">
@@ -17289,7 +17289,7 @@
         <v/>
       </c>
       <c r="F63" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A63,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A63,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A63,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A63,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G63" s="100">
@@ -17322,7 +17322,7 @@
         <v>46057</v>
       </c>
       <c r="B64" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A64,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C64" s="101">
@@ -17338,7 +17338,7 @@
         <v/>
       </c>
       <c r="F64" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A64,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A64,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A64,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A64,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G64" s="101">
@@ -17371,7 +17371,7 @@
         <v>46058</v>
       </c>
       <c r="B65" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A65,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C65" s="100">
@@ -17387,7 +17387,7 @@
         <v/>
       </c>
       <c r="F65" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A65,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A65,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A65,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A65,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G65" s="100">
@@ -17420,7 +17420,7 @@
         <v>46059</v>
       </c>
       <c r="B66" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A66,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C66" s="101">
@@ -17436,7 +17436,7 @@
         <v/>
       </c>
       <c r="F66" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A66,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A66,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A66,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A66,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G66" s="101">
@@ -17469,7 +17469,7 @@
         <v>46060</v>
       </c>
       <c r="B67" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A67,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C67" s="100">
@@ -17485,7 +17485,7 @@
         <v/>
       </c>
       <c r="F67" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A67,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A67,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A67,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A67,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G67" s="100">
@@ -17518,7 +17518,7 @@
         <v>46061</v>
       </c>
       <c r="B68" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A68,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C68" s="101">
@@ -17534,7 +17534,7 @@
         <v/>
       </c>
       <c r="F68" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A68,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A68,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A68,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A68,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G68" s="101">
@@ -17567,7 +17567,7 @@
         <v>46062</v>
       </c>
       <c r="B69" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A69,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C69" s="100">
@@ -17583,7 +17583,7 @@
         <v/>
       </c>
       <c r="F69" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A69,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A69,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A69,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A69,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G69" s="100">
@@ -17616,7 +17616,7 @@
         <v>46063</v>
       </c>
       <c r="B70" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A70,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C70" s="101">
@@ -17632,7 +17632,7 @@
         <v/>
       </c>
       <c r="F70" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A70,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A70,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A70,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A70,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G70" s="101">
@@ -17665,7 +17665,7 @@
         <v>46064</v>
       </c>
       <c r="B71" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A71,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C71" s="100">
@@ -17681,7 +17681,7 @@
         <v/>
       </c>
       <c r="F71" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A71,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A71,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A71,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A71,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G71" s="100">
@@ -17714,7 +17714,7 @@
         <v>46065</v>
       </c>
       <c r="B72" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A72,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C72" s="101">
@@ -17730,7 +17730,7 @@
         <v/>
       </c>
       <c r="F72" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A72,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A72,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A72,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A72,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G72" s="101">
@@ -17763,7 +17763,7 @@
         <v>46066</v>
       </c>
       <c r="B73" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A73,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C73" s="100">
@@ -17779,7 +17779,7 @@
         <v/>
       </c>
       <c r="F73" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A73,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A73,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A73,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A73,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G73" s="100">
@@ -17812,7 +17812,7 @@
         <v>46067</v>
       </c>
       <c r="B74" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A74,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C74" s="101">
@@ -17828,7 +17828,7 @@
         <v/>
       </c>
       <c r="F74" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A74,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A74,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A74,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A74,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G74" s="101">
@@ -17861,7 +17861,7 @@
         <v>46068</v>
       </c>
       <c r="B75" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A75,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C75" s="100">
@@ -17877,7 +17877,7 @@
         <v/>
       </c>
       <c r="F75" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A75,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A75,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A75,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A75,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G75" s="100">
@@ -17910,7 +17910,7 @@
         <v>46069</v>
       </c>
       <c r="B76" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A76,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C76" s="101">
@@ -17926,7 +17926,7 @@
         <v/>
       </c>
       <c r="F76" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A76,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A76,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A76,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A76,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G76" s="101">
@@ -17959,7 +17959,7 @@
         <v>46070</v>
       </c>
       <c r="B77" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A77,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C77" s="100">
@@ -17975,7 +17975,7 @@
         <v/>
       </c>
       <c r="F77" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A77,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A77,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A77,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A77,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G77" s="100">
@@ -18008,7 +18008,7 @@
         <v>46071</v>
       </c>
       <c r="B78" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A78,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C78" s="101">
@@ -18024,7 +18024,7 @@
         <v/>
       </c>
       <c r="F78" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A78,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A78,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A78,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A78,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G78" s="101">
@@ -18057,7 +18057,7 @@
         <v>46072</v>
       </c>
       <c r="B79" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A79,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C79" s="100">
@@ -18073,7 +18073,7 @@
         <v/>
       </c>
       <c r="F79" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A79,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A79,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A79,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A79,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G79" s="100">
@@ -18106,7 +18106,7 @@
         <v>46073</v>
       </c>
       <c r="B80" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A80,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C80" s="101">
@@ -18122,7 +18122,7 @@
         <v/>
       </c>
       <c r="F80" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A80,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A80,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A80,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A80,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G80" s="101">
@@ -18155,7 +18155,7 @@
         <v>46074</v>
       </c>
       <c r="B81" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A81,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C81" s="100">
@@ -18171,7 +18171,7 @@
         <v/>
       </c>
       <c r="F81" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A81,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A81,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A81,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A81,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G81" s="100">
@@ -18204,7 +18204,7 @@
         <v>46075</v>
       </c>
       <c r="B82" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A82,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C82" s="101">
@@ -18220,7 +18220,7 @@
         <v/>
       </c>
       <c r="F82" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A82,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A82,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A82,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A82,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G82" s="101">
@@ -18253,7 +18253,7 @@
         <v>46076</v>
       </c>
       <c r="B83" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A83,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C83" s="100">
@@ -18269,7 +18269,7 @@
         <v/>
       </c>
       <c r="F83" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A83,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A83,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A83,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A83,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G83" s="100">
@@ -18302,7 +18302,7 @@
         <v>46077</v>
       </c>
       <c r="B84" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A84,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C84" s="101">
@@ -18318,7 +18318,7 @@
         <v/>
       </c>
       <c r="F84" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A84,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A84,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A84,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A84,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G84" s="101">
@@ -18351,7 +18351,7 @@
         <v>46078</v>
       </c>
       <c r="B85" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A85,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C85" s="100">
@@ -18367,7 +18367,7 @@
         <v/>
       </c>
       <c r="F85" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A85,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A85,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A85,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A85,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G85" s="100">
@@ -18400,7 +18400,7 @@
         <v>46079</v>
       </c>
       <c r="B86" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A86,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C86" s="101">
@@ -18416,7 +18416,7 @@
         <v/>
       </c>
       <c r="F86" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A86,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A86,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A86,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A86,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G86" s="101">
@@ -18449,7 +18449,7 @@
         <v>46080</v>
       </c>
       <c r="B87" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A87,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C87" s="100">
@@ -18465,7 +18465,7 @@
         <v/>
       </c>
       <c r="F87" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A87,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A87,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A87,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A87,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G87" s="100">
@@ -18498,7 +18498,7 @@
         <v>46081</v>
       </c>
       <c r="B88" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A88,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C88" s="101">
@@ -18514,7 +18514,7 @@
         <v/>
       </c>
       <c r="F88" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A88,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A88,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A88,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A88,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G88" s="101">
@@ -18547,7 +18547,7 @@
         <v>46082</v>
       </c>
       <c r="B89" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A89,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C89" s="100">
@@ -18563,7 +18563,7 @@
         <v/>
       </c>
       <c r="F89" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A89,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A89,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A89,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A89,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G89" s="100">
@@ -18596,7 +18596,7 @@
         <v>46083</v>
       </c>
       <c r="B90" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A90,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C90" s="101">
@@ -18612,7 +18612,7 @@
         <v/>
       </c>
       <c r="F90" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A90,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A90,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A90,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A90,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G90" s="101">
@@ -18645,7 +18645,7 @@
         <v>46084</v>
       </c>
       <c r="B91" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A91,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C91" s="100">
@@ -18661,7 +18661,7 @@
         <v/>
       </c>
       <c r="F91" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A91,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A91,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A91,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A91,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G91" s="100">
@@ -18694,7 +18694,7 @@
         <v>46085</v>
       </c>
       <c r="B92" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A92,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C92" s="101">
@@ -18710,7 +18710,7 @@
         <v/>
       </c>
       <c r="F92" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A92,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A92,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A92,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A92,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G92" s="101">
@@ -18743,7 +18743,7 @@
         <v>46086</v>
       </c>
       <c r="B93" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A93,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C93" s="100">
@@ -18759,7 +18759,7 @@
         <v/>
       </c>
       <c r="F93" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A93,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A93,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A93,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A93,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G93" s="100">
@@ -18792,7 +18792,7 @@
         <v>46087</v>
       </c>
       <c r="B94" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A94,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C94" s="101">
@@ -18808,7 +18808,7 @@
         <v/>
       </c>
       <c r="F94" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A94,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A94,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A94,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A94,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G94" s="101">
@@ -18841,7 +18841,7 @@
         <v>46088</v>
       </c>
       <c r="B95" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A95,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C95" s="100">
@@ -18857,7 +18857,7 @@
         <v/>
       </c>
       <c r="F95" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A95,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A95,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A95,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A95,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G95" s="100">
@@ -18890,7 +18890,7 @@
         <v>46089</v>
       </c>
       <c r="B96" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A96,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C96" s="101">
@@ -18906,7 +18906,7 @@
         <v/>
       </c>
       <c r="F96" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A96,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A96,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A96,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A96,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G96" s="101">
@@ -18939,7 +18939,7 @@
         <v>46090</v>
       </c>
       <c r="B97" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A97,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C97" s="100">
@@ -18955,7 +18955,7 @@
         <v/>
       </c>
       <c r="F97" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A97,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A97,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A97,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A97,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G97" s="100">
@@ -18988,7 +18988,7 @@
         <v>46091</v>
       </c>
       <c r="B98" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A98,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C98" s="101">
@@ -19004,7 +19004,7 @@
         <v/>
       </c>
       <c r="F98" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A98,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A98,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A98,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A98,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G98" s="101">
@@ -19037,7 +19037,7 @@
         <v>46092</v>
       </c>
       <c r="B99" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A99,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C99" s="100">
@@ -19053,7 +19053,7 @@
         <v/>
       </c>
       <c r="F99" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A99,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A99,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A99,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A99,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G99" s="100">
@@ -19086,7 +19086,7 @@
         <v>46093</v>
       </c>
       <c r="B100" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A100,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C100" s="101">
@@ -19102,7 +19102,7 @@
         <v/>
       </c>
       <c r="F100" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A100,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A100,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A100,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A100,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G100" s="101">
@@ -19135,7 +19135,7 @@
         <v>46094</v>
       </c>
       <c r="B101" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A101,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C101" s="100">
@@ -19151,7 +19151,7 @@
         <v/>
       </c>
       <c r="F101" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A101,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A101,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A101,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A101,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G101" s="100">
@@ -19184,7 +19184,7 @@
         <v>46095</v>
       </c>
       <c r="B102" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A102,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C102" s="101">
@@ -19200,7 +19200,7 @@
         <v/>
       </c>
       <c r="F102" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A102,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A102,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A102,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A102,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G102" s="101">
@@ -19233,7 +19233,7 @@
         <v>46096</v>
       </c>
       <c r="B103" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A103,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C103" s="100">
@@ -19249,7 +19249,7 @@
         <v/>
       </c>
       <c r="F103" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A103,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A103,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A103,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A103,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G103" s="100">
@@ -19282,7 +19282,7 @@
         <v>46097</v>
       </c>
       <c r="B104" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A104,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C104" s="101">
@@ -19298,7 +19298,7 @@
         <v/>
       </c>
       <c r="F104" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A104,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A104,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A104,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A104,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G104" s="101">
@@ -19331,7 +19331,7 @@
         <v>46098</v>
       </c>
       <c r="B105" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A105,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C105" s="100">
@@ -19347,7 +19347,7 @@
         <v/>
       </c>
       <c r="F105" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A105,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A105,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A105,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A105,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G105" s="100">
@@ -19380,7 +19380,7 @@
         <v>46099</v>
       </c>
       <c r="B106" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A106,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C106" s="101">
@@ -19396,7 +19396,7 @@
         <v/>
       </c>
       <c r="F106" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A106,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A106,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A106,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A106,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G106" s="101">
@@ -19429,7 +19429,7 @@
         <v>46100</v>
       </c>
       <c r="B107" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A107,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C107" s="100">
@@ -19445,7 +19445,7 @@
         <v/>
       </c>
       <c r="F107" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A107,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A107,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A107,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A107,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G107" s="100">
@@ -19478,7 +19478,7 @@
         <v>46101</v>
       </c>
       <c r="B108" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A108,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C108" s="101">
@@ -19494,7 +19494,7 @@
         <v/>
       </c>
       <c r="F108" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A108,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A108,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A108,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A108,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G108" s="101">
@@ -19527,7 +19527,7 @@
         <v>46102</v>
       </c>
       <c r="B109" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A109,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C109" s="100">
@@ -19543,7 +19543,7 @@
         <v/>
       </c>
       <c r="F109" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A109,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A109,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A109,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A109,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G109" s="100">
@@ -19576,7 +19576,7 @@
         <v>46103</v>
       </c>
       <c r="B110" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A110,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C110" s="101">
@@ -19592,7 +19592,7 @@
         <v/>
       </c>
       <c r="F110" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A110,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A110,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A110,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A110,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G110" s="101">
@@ -19625,7 +19625,7 @@
         <v>46104</v>
       </c>
       <c r="B111" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A111,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C111" s="100">
@@ -19641,7 +19641,7 @@
         <v/>
       </c>
       <c r="F111" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A111,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A111,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A111,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A111,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G111" s="100">
@@ -19674,7 +19674,7 @@
         <v>46105</v>
       </c>
       <c r="B112" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A112,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C112" s="101">
@@ -19690,7 +19690,7 @@
         <v/>
       </c>
       <c r="F112" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A112,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A112,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A112,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A112,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G112" s="101">
@@ -19723,7 +19723,7 @@
         <v>46106</v>
       </c>
       <c r="B113" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A113,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C113" s="100">
@@ -19739,7 +19739,7 @@
         <v/>
       </c>
       <c r="F113" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A113,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A113,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A113,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A113,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G113" s="100">
@@ -19772,7 +19772,7 @@
         <v>46107</v>
       </c>
       <c r="B114" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A114,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C114" s="101">
@@ -19788,7 +19788,7 @@
         <v/>
       </c>
       <c r="F114" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A114,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A114,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A114,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A114,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G114" s="101">
@@ -19821,7 +19821,7 @@
         <v>46108</v>
       </c>
       <c r="B115" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A115,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C115" s="100">
@@ -19837,7 +19837,7 @@
         <v/>
       </c>
       <c r="F115" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A115,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A115,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A115,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A115,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G115" s="100">
@@ -19870,7 +19870,7 @@
         <v>46109</v>
       </c>
       <c r="B116" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A116,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C116" s="101">
@@ -19886,7 +19886,7 @@
         <v/>
       </c>
       <c r="F116" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A116,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A116,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A116,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A116,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G116" s="101">
@@ -19919,7 +19919,7 @@
         <v>46110</v>
       </c>
       <c r="B117" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A117,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C117" s="100">
@@ -19935,7 +19935,7 @@
         <v/>
       </c>
       <c r="F117" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A117,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A117,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A117,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A117,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G117" s="100">
@@ -19968,7 +19968,7 @@
         <v>46121</v>
       </c>
       <c r="B118" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A118,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C118" s="101">
@@ -19984,7 +19984,7 @@
         <v/>
       </c>
       <c r="F118" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A118,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A118,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A118,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A118,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G118" s="101">
@@ -20017,7 +20017,7 @@
         <v>46130</v>
       </c>
       <c r="B119" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A119,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C119" s="100">
@@ -20033,7 +20033,7 @@
         <v/>
       </c>
       <c r="F119" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A119,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A119,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A119,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A119,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G119" s="100">
@@ -20066,7 +20066,7 @@
         <v>46134</v>
       </c>
       <c r="B120" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A120,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C120" s="101">
@@ -20082,7 +20082,7 @@
         <v/>
       </c>
       <c r="F120" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A120,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A120,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A120,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A120,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G120" s="101">
@@ -20115,7 +20115,7 @@
         <v>46135</v>
       </c>
       <c r="B121" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A121,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C121" s="100">
@@ -20131,7 +20131,7 @@
         <v/>
       </c>
       <c r="F121" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A121,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A121,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A121,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A121,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G121" s="100">
@@ -20164,7 +20164,7 @@
         <v>46136</v>
       </c>
       <c r="B122" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A122,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C122" s="101">
@@ -20180,7 +20180,7 @@
         <v/>
       </c>
       <c r="F122" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A122,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A122,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A122,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A122,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G122" s="101">
@@ -20213,7 +20213,7 @@
         <v>46137</v>
       </c>
       <c r="B123" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A123,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C123" s="100">
@@ -20229,7 +20229,7 @@
         <v/>
       </c>
       <c r="F123" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A123,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A123,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A123,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A123,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G123" s="100">
@@ -20262,7 +20262,7 @@
         <v>46138</v>
       </c>
       <c r="B124" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A124,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C124" s="101">
@@ -20278,7 +20278,7 @@
         <v/>
       </c>
       <c r="F124" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A124,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A124,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A124,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A124,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G124" s="101">
@@ -20311,7 +20311,7 @@
         <v>46139</v>
       </c>
       <c r="B125" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A125,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C125" s="100">
@@ -20327,7 +20327,7 @@
         <v/>
       </c>
       <c r="F125" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A125,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A125,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A125,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A125,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G125" s="100">
@@ -20360,7 +20360,7 @@
         <v>46140</v>
       </c>
       <c r="B126" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A126,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C126" s="101">
@@ -20376,7 +20376,7 @@
         <v/>
       </c>
       <c r="F126" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A126,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A126,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A126,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A126,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G126" s="101">
@@ -20409,7 +20409,7 @@
         <v>46141</v>
       </c>
       <c r="B127" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A127,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C127" s="100">
@@ -20425,7 +20425,7 @@
         <v/>
       </c>
       <c r="F127" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A127,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A127,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A127,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A127,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G127" s="100">
@@ -20458,7 +20458,7 @@
         <v>46142</v>
       </c>
       <c r="B128" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A128,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C128" s="101">
@@ -20474,7 +20474,7 @@
         <v/>
       </c>
       <c r="F128" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A128,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A128,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A128,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A128,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G128" s="101">
@@ -20507,7 +20507,7 @@
         <v>46143</v>
       </c>
       <c r="B129" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A129,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C129" s="100">
@@ -20523,7 +20523,7 @@
         <v/>
       </c>
       <c r="F129" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A129,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A129,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A129,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A129,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G129" s="100">
@@ -20556,7 +20556,7 @@
         <v>46144</v>
       </c>
       <c r="B130" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A130,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C130" s="101">
@@ -20572,7 +20572,7 @@
         <v/>
       </c>
       <c r="F130" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A130,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A130,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A130,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A130,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G130" s="101">
@@ -20605,7 +20605,7 @@
         <v>46145</v>
       </c>
       <c r="B131" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A131,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C131" s="100">
@@ -20621,7 +20621,7 @@
         <v/>
       </c>
       <c r="F131" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A131,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A131,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A131,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A131,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G131" s="100">
@@ -20654,7 +20654,7 @@
         <v>46146</v>
       </c>
       <c r="B132" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A132,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C132" s="101">
@@ -20670,7 +20670,7 @@
         <v/>
       </c>
       <c r="F132" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A132,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A132,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A132,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A132,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G132" s="101">
@@ -20703,7 +20703,7 @@
         <v>46147</v>
       </c>
       <c r="B133" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A133,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C133" s="100">
@@ -20719,7 +20719,7 @@
         <v/>
       </c>
       <c r="F133" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A133,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A133,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A133,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A133,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G133" s="100">
@@ -20752,7 +20752,7 @@
         <v>46148</v>
       </c>
       <c r="B134" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A134,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C134" s="101">
@@ -20768,7 +20768,7 @@
         <v/>
       </c>
       <c r="F134" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A134,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A134,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A134,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A134,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G134" s="101">
@@ -20801,7 +20801,7 @@
         <v>46149</v>
       </c>
       <c r="B135" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A135,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C135" s="100">
@@ -20817,7 +20817,7 @@
         <v/>
       </c>
       <c r="F135" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A135,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A135,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A135,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A135,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G135" s="100">
@@ -20850,7 +20850,7 @@
         <v>46150</v>
       </c>
       <c r="B136" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A136,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C136" s="101">
@@ -20866,7 +20866,7 @@
         <v/>
       </c>
       <c r="F136" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A136,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A136,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A136,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A136,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G136" s="101">
@@ -20899,7 +20899,7 @@
         <v>46151</v>
       </c>
       <c r="B137" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A137,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C137" s="100">
@@ -20915,7 +20915,7 @@
         <v/>
       </c>
       <c r="F137" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A137,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A137,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A137,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A137,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G137" s="100">
@@ -20948,7 +20948,7 @@
         <v>46152</v>
       </c>
       <c r="B138" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A138,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C138" s="101">
@@ -20964,7 +20964,7 @@
         <v/>
       </c>
       <c r="F138" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A138,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A138,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A138,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A138,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G138" s="101">
@@ -20997,7 +20997,7 @@
         <v>46153</v>
       </c>
       <c r="B139" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A139,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C139" s="100">
@@ -21013,7 +21013,7 @@
         <v/>
       </c>
       <c r="F139" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A139,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A139,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A139,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A139,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G139" s="100">
@@ -21046,7 +21046,7 @@
         <v>46154</v>
       </c>
       <c r="B140" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A140,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C140" s="101">
@@ -21062,7 +21062,7 @@
         <v/>
       </c>
       <c r="F140" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A140,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A140,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A140,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A140,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G140" s="101">
@@ -21095,7 +21095,7 @@
         <v>46155</v>
       </c>
       <c r="B141" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A141,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C141" s="100">
@@ -21111,7 +21111,7 @@
         <v/>
       </c>
       <c r="F141" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A141,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A141,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A141,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A141,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G141" s="100">
@@ -21144,7 +21144,7 @@
         <v>46156</v>
       </c>
       <c r="B142" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A142,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C142" s="101">
@@ -21160,7 +21160,7 @@
         <v/>
       </c>
       <c r="F142" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A142,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A142,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A142,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A142,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G142" s="101">
@@ -21193,7 +21193,7 @@
         <v>46157</v>
       </c>
       <c r="B143" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A143,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C143" s="100">
@@ -21209,7 +21209,7 @@
         <v/>
       </c>
       <c r="F143" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A143,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A143,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A143,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A143,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G143" s="100">
@@ -21242,7 +21242,7 @@
         <v>46158</v>
       </c>
       <c r="B144" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A144,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C144" s="101">
@@ -21258,7 +21258,7 @@
         <v/>
       </c>
       <c r="F144" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A144,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A144,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A144,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A144,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G144" s="101">
@@ -21291,7 +21291,7 @@
         <v>46159</v>
       </c>
       <c r="B145" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A145,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C145" s="100">
@@ -21307,7 +21307,7 @@
         <v/>
       </c>
       <c r="F145" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A145,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A145,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A145,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A145,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G145" s="100">
@@ -21340,7 +21340,7 @@
         <v>46160</v>
       </c>
       <c r="B146" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A146,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C146" s="101">
@@ -21356,7 +21356,7 @@
         <v/>
       </c>
       <c r="F146" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A146,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A146,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A146,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A146,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G146" s="101">
@@ -21389,7 +21389,7 @@
         <v>46161</v>
       </c>
       <c r="B147" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A147,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C147" s="100">
@@ -21405,7 +21405,7 @@
         <v/>
       </c>
       <c r="F147" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A147,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A147,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A147,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A147,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G147" s="100">
@@ -21438,7 +21438,7 @@
         <v>46162</v>
       </c>
       <c r="B148" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A148,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C148" s="101">
@@ -21454,7 +21454,7 @@
         <v/>
       </c>
       <c r="F148" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A148,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A148,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A148,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A148,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G148" s="101">
@@ -21487,7 +21487,7 @@
         <v>46163</v>
       </c>
       <c r="B149" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A149,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C149" s="100">
@@ -21503,7 +21503,7 @@
         <v/>
       </c>
       <c r="F149" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A149,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A149,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A149,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A149,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G149" s="100">
@@ -21536,7 +21536,7 @@
         <v>46164</v>
       </c>
       <c r="B150" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A150,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C150" s="101">
@@ -21552,7 +21552,7 @@
         <v/>
       </c>
       <c r="F150" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A150,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A150,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A150,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A150,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G150" s="101">
@@ -21585,7 +21585,7 @@
         <v>46165</v>
       </c>
       <c r="B151" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A151,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C151" s="100">
@@ -21601,7 +21601,7 @@
         <v/>
       </c>
       <c r="F151" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A151,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A151,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A151,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A151,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G151" s="100">
@@ -21634,7 +21634,7 @@
         <v>46166</v>
       </c>
       <c r="B152" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A152,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C152" s="101">
@@ -21650,7 +21650,7 @@
         <v/>
       </c>
       <c r="F152" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A152,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A152,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A152,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A152,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G152" s="101">
@@ -21683,7 +21683,7 @@
         <v>46167</v>
       </c>
       <c r="B153" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A153,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C153" s="100">
@@ -21699,7 +21699,7 @@
         <v/>
       </c>
       <c r="F153" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A153,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A153,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A153,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A153,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G153" s="100">
@@ -21732,7 +21732,7 @@
         <v>46168</v>
       </c>
       <c r="B154" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A154,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C154" s="101">
@@ -21748,7 +21748,7 @@
         <v/>
       </c>
       <c r="F154" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A154,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A154,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A154,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A154,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G154" s="101">
@@ -21781,7 +21781,7 @@
         <v>46169</v>
       </c>
       <c r="B155" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A155,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C155" s="100">
@@ -21797,7 +21797,7 @@
         <v/>
       </c>
       <c r="F155" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A155,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A155,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A155,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A155,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G155" s="100">
@@ -21830,7 +21830,7 @@
         <v>46170</v>
       </c>
       <c r="B156" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A156,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C156" s="101">
@@ -21846,7 +21846,7 @@
         <v/>
       </c>
       <c r="F156" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A156,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A156,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A156,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A156,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G156" s="101">
@@ -21879,7 +21879,7 @@
         <v>46171</v>
       </c>
       <c r="B157" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A157,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C157" s="100">
@@ -21895,7 +21895,7 @@
         <v/>
       </c>
       <c r="F157" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A157,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A157,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A157,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A157,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G157" s="100">
@@ -21928,7 +21928,7 @@
         <v>46172</v>
       </c>
       <c r="B158" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A158,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C158" s="101">
@@ -21944,7 +21944,7 @@
         <v/>
       </c>
       <c r="F158" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A158,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A158,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A158,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A158,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G158" s="101">
@@ -21977,7 +21977,7 @@
         <v>46173</v>
       </c>
       <c r="B159" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A159,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C159" s="100">
@@ -21993,7 +21993,7 @@
         <v/>
       </c>
       <c r="F159" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A159,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A159,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A159,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A159,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G159" s="100">
@@ -22026,7 +22026,7 @@
         <v>46174</v>
       </c>
       <c r="B160" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A160,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C160" s="101">
@@ -22042,7 +22042,7 @@
         <v/>
       </c>
       <c r="F160" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A160,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A160,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A160,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A160,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G160" s="101">
@@ -22075,7 +22075,7 @@
         <v>46175</v>
       </c>
       <c r="B161" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A161,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C161" s="100">
@@ -22091,7 +22091,7 @@
         <v/>
       </c>
       <c r="F161" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A161,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A161,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A161,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A161,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G161" s="100">
@@ -22124,7 +22124,7 @@
         <v>46176</v>
       </c>
       <c r="B162" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A162,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C162" s="101">
@@ -22140,7 +22140,7 @@
         <v/>
       </c>
       <c r="F162" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A162,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A162,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A162,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A162,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G162" s="101">
@@ -22173,7 +22173,7 @@
         <v>46177</v>
       </c>
       <c r="B163" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A163,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C163" s="100">
@@ -22189,7 +22189,7 @@
         <v/>
       </c>
       <c r="F163" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A163,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A163,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A163,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A163,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G163" s="100">
@@ -22222,7 +22222,7 @@
         <v>46178</v>
       </c>
       <c r="B164" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A164,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C164" s="101">
@@ -22238,7 +22238,7 @@
         <v/>
       </c>
       <c r="F164" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A164,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A164,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A164,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A164,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G164" s="101">
@@ -22271,7 +22271,7 @@
         <v>46179</v>
       </c>
       <c r="B165" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A165,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C165" s="100">
@@ -22287,7 +22287,7 @@
         <v/>
       </c>
       <c r="F165" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A165,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A165,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A165,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A165,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G165" s="100">
@@ -22320,7 +22320,7 @@
         <v>46180</v>
       </c>
       <c r="B166" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A166,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C166" s="101">
@@ -22336,7 +22336,7 @@
         <v/>
       </c>
       <c r="F166" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A166,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A166,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A166,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A166,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G166" s="101">
@@ -22369,7 +22369,7 @@
         <v>46181</v>
       </c>
       <c r="B167" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A167,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C167" s="100">
@@ -22385,7 +22385,7 @@
         <v/>
       </c>
       <c r="F167" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A167,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A167,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A167,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A167,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G167" s="100">
@@ -22418,7 +22418,7 @@
         <v>46182</v>
       </c>
       <c r="B168" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A168,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C168" s="101">
@@ -22434,7 +22434,7 @@
         <v/>
       </c>
       <c r="F168" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A168,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A168,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A168,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A168,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G168" s="101">
@@ -22467,7 +22467,7 @@
         <v>46183</v>
       </c>
       <c r="B169" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A169,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C169" s="100">
@@ -22483,7 +22483,7 @@
         <v/>
       </c>
       <c r="F169" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A169,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A169,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A169,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A169,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G169" s="100">
@@ -22516,7 +22516,7 @@
         <v>46184</v>
       </c>
       <c r="B170" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A170,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C170" s="101">
@@ -22532,7 +22532,7 @@
         <v/>
       </c>
       <c r="F170" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A170,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A170,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A170,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A170,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G170" s="101">
@@ -22565,7 +22565,7 @@
         <v>46185</v>
       </c>
       <c r="B171" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A171,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C171" s="100">
@@ -22581,7 +22581,7 @@
         <v/>
       </c>
       <c r="F171" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A171,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A171,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A171,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A171,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G171" s="100">
@@ -22614,7 +22614,7 @@
         <v>46186</v>
       </c>
       <c r="B172" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A172,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C172" s="101">
@@ -22630,7 +22630,7 @@
         <v/>
       </c>
       <c r="F172" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A172,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A172,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A172,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A172,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G172" s="101">
@@ -22663,7 +22663,7 @@
         <v>46187</v>
       </c>
       <c r="B173" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A173,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C173" s="100">
@@ -22679,7 +22679,7 @@
         <v/>
       </c>
       <c r="F173" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A173,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A173,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A173,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A173,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G173" s="100">
@@ -22712,7 +22712,7 @@
         <v>46188</v>
       </c>
       <c r="B174" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A174,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C174" s="101">
@@ -22728,7 +22728,7 @@
         <v/>
       </c>
       <c r="F174" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A174,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A174,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A174,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A174,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G174" s="101">
@@ -22761,7 +22761,7 @@
         <v>46189</v>
       </c>
       <c r="B175" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A175,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C175" s="100">
@@ -22777,7 +22777,7 @@
         <v/>
       </c>
       <c r="F175" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A175,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A175,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A175,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A175,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G175" s="100">
@@ -22810,7 +22810,7 @@
         <v>46190</v>
       </c>
       <c r="B176" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A176,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C176" s="101">
@@ -22826,7 +22826,7 @@
         <v/>
       </c>
       <c r="F176" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A176,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A176,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A176,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A176,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G176" s="101">
@@ -22859,7 +22859,7 @@
         <v>46191</v>
       </c>
       <c r="B177" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A177,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C177" s="100">
@@ -22875,7 +22875,7 @@
         <v/>
       </c>
       <c r="F177" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A177,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A177,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A177,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A177,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G177" s="100">
@@ -22908,7 +22908,7 @@
         <v>46192</v>
       </c>
       <c r="B178" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A178,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C178" s="101">
@@ -22924,7 +22924,7 @@
         <v/>
       </c>
       <c r="F178" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A178,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A178,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A178,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A178,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G178" s="101">
@@ -22957,7 +22957,7 @@
         <v>46193</v>
       </c>
       <c r="B179" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A179,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C179" s="100">
@@ -22973,7 +22973,7 @@
         <v/>
       </c>
       <c r="F179" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A179,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A179,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A179,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A179,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G179" s="100">
@@ -23006,7 +23006,7 @@
         <v>46194</v>
       </c>
       <c r="B180" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A180,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C180" s="101">
@@ -23022,7 +23022,7 @@
         <v/>
       </c>
       <c r="F180" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A180,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A180,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A180,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A180,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G180" s="101">
@@ -23055,7 +23055,7 @@
         <v>46195</v>
       </c>
       <c r="B181" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A181,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C181" s="100">
@@ -23071,7 +23071,7 @@
         <v/>
       </c>
       <c r="F181" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A181,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A181,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A181,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A181,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G181" s="100">
@@ -23104,7 +23104,7 @@
         <v>46196</v>
       </c>
       <c r="B182" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A182,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C182" s="101">
@@ -23120,7 +23120,7 @@
         <v/>
       </c>
       <c r="F182" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A182,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A182,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A182,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A182,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G182" s="101">
@@ -23153,7 +23153,7 @@
         <v>46197</v>
       </c>
       <c r="B183" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A183,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C183" s="100">
@@ -23169,7 +23169,7 @@
         <v/>
       </c>
       <c r="F183" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A183,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A183,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A183,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A183,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G183" s="100">
@@ -23202,7 +23202,7 @@
         <v>46198</v>
       </c>
       <c r="B184" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A184,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C184" s="101">
@@ -23218,7 +23218,7 @@
         <v/>
       </c>
       <c r="F184" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A184,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A184,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A184,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A184,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G184" s="101">
@@ -23251,7 +23251,7 @@
         <v>46199</v>
       </c>
       <c r="B185" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A185,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C185" s="100">
@@ -23267,7 +23267,7 @@
         <v/>
       </c>
       <c r="F185" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A185,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A185,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A185,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A185,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G185" s="100">
@@ -23300,7 +23300,7 @@
         <v>46200</v>
       </c>
       <c r="B186" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A186,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C186" s="101">
@@ -23316,7 +23316,7 @@
         <v/>
       </c>
       <c r="F186" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A186,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A186,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A186,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A186,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G186" s="101">
@@ -23349,7 +23349,7 @@
         <v>46201</v>
       </c>
       <c r="B187" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A187,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C187" s="100">
@@ -23365,7 +23365,7 @@
         <v/>
       </c>
       <c r="F187" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A187,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A187,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A187,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A187,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G187" s="100">
@@ -23398,7 +23398,7 @@
         <v>46202</v>
       </c>
       <c r="B188" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A188,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C188" s="101">
@@ -23414,7 +23414,7 @@
         <v/>
       </c>
       <c r="F188" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A188,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A188,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A188,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A188,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G188" s="101">
@@ -23447,7 +23447,7 @@
         <v>46203</v>
       </c>
       <c r="B189" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A189,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C189" s="100">
@@ -23463,7 +23463,7 @@
         <v/>
       </c>
       <c r="F189" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A189,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A189,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A189,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A189,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G189" s="100">
@@ -23496,7 +23496,7 @@
         <v>46204</v>
       </c>
       <c r="B190" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A190,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C190" s="101">
@@ -23512,7 +23512,7 @@
         <v/>
       </c>
       <c r="F190" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A190,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A190,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A190,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A190,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G190" s="101">
@@ -23545,7 +23545,7 @@
         <v>46205</v>
       </c>
       <c r="B191" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A191,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C191" s="100">
@@ -23561,7 +23561,7 @@
         <v/>
       </c>
       <c r="F191" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A191,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A191,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A191,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A191,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G191" s="100">
@@ -23594,7 +23594,7 @@
         <v>46206</v>
       </c>
       <c r="B192" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A192,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C192" s="101">
@@ -23610,7 +23610,7 @@
         <v/>
       </c>
       <c r="F192" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A192,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A192,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A192,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A192,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G192" s="101">
@@ -23643,7 +23643,7 @@
         <v>46207</v>
       </c>
       <c r="B193" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A193,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C193" s="100">
@@ -23659,7 +23659,7 @@
         <v/>
       </c>
       <c r="F193" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A193,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A193,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A193,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A193,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G193" s="100">
@@ -23692,7 +23692,7 @@
         <v>46208</v>
       </c>
       <c r="B194" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A194,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C194" s="101">
@@ -23708,7 +23708,7 @@
         <v/>
       </c>
       <c r="F194" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A194,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A194,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A194,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A194,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G194" s="101">
@@ -23741,7 +23741,7 @@
         <v>46209</v>
       </c>
       <c r="B195" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A195,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C195" s="100">
@@ -23757,7 +23757,7 @@
         <v/>
       </c>
       <c r="F195" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A195,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A195,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A195,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A195,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G195" s="100">
@@ -23790,7 +23790,7 @@
         <v>46210</v>
       </c>
       <c r="B196" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A196,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C196" s="101">
@@ -23806,7 +23806,7 @@
         <v/>
       </c>
       <c r="F196" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A196,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A196,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A196,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A196,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G196" s="101">
@@ -23839,7 +23839,7 @@
         <v>46211</v>
       </c>
       <c r="B197" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A197,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C197" s="100">
@@ -23855,7 +23855,7 @@
         <v/>
       </c>
       <c r="F197" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A197,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A197,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A197,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A197,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G197" s="100">
@@ -23888,7 +23888,7 @@
         <v>46212</v>
       </c>
       <c r="B198" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A198,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C198" s="101">
@@ -23904,7 +23904,7 @@
         <v/>
       </c>
       <c r="F198" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A198,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A198,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A198,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A198,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G198" s="101">
@@ -23937,7 +23937,7 @@
         <v>46213</v>
       </c>
       <c r="B199" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A199,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C199" s="100">
@@ -23953,7 +23953,7 @@
         <v/>
       </c>
       <c r="F199" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A199,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A199,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A199,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A199,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G199" s="100">
@@ -23986,7 +23986,7 @@
         <v>46214</v>
       </c>
       <c r="B200" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A200,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C200" s="101">
@@ -24002,7 +24002,7 @@
         <v/>
       </c>
       <c r="F200" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A200,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A200,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A200,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A200,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G200" s="101">
@@ -24035,7 +24035,7 @@
         <v>46215</v>
       </c>
       <c r="B201" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A201,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C201" s="100">
@@ -24051,7 +24051,7 @@
         <v/>
       </c>
       <c r="F201" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A201,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A201,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A201,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A201,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G201" s="100">
@@ -24084,7 +24084,7 @@
         <v>46216</v>
       </c>
       <c r="B202" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A202,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C202" s="101">
@@ -24100,7 +24100,7 @@
         <v/>
       </c>
       <c r="F202" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A202,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A202,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A202,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A202,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G202" s="101">
@@ -24133,7 +24133,7 @@
         <v>46217</v>
       </c>
       <c r="B203" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A203,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C203" s="100">
@@ -24149,7 +24149,7 @@
         <v/>
       </c>
       <c r="F203" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A203,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A203,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A203,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A203,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G203" s="100">
@@ -24182,7 +24182,7 @@
         <v>46218</v>
       </c>
       <c r="B204" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A204,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C204" s="101">
@@ -24198,7 +24198,7 @@
         <v/>
       </c>
       <c r="F204" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A204,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A204,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A204,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A204,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G204" s="101">
@@ -24231,7 +24231,7 @@
         <v>46219</v>
       </c>
       <c r="B205" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A205,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C205" s="100">
@@ -24247,7 +24247,7 @@
         <v/>
       </c>
       <c r="F205" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A205,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A205,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A205,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A205,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G205" s="100">
@@ -24280,7 +24280,7 @@
         <v>46220</v>
       </c>
       <c r="B206" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A206,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C206" s="101">
@@ -24296,7 +24296,7 @@
         <v/>
       </c>
       <c r="F206" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A206,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A206,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A206,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A206,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G206" s="101">
@@ -24329,7 +24329,7 @@
         <v>46221</v>
       </c>
       <c r="B207" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A207,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C207" s="100">
@@ -24345,7 +24345,7 @@
         <v/>
       </c>
       <c r="F207" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A207,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A207,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A207,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A207,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G207" s="100">
@@ -24378,7 +24378,7 @@
         <v>46222</v>
       </c>
       <c r="B208" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A208,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C208" s="101">
@@ -24394,7 +24394,7 @@
         <v/>
       </c>
       <c r="F208" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A208,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A208,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A208,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A208,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G208" s="101">
@@ -24427,7 +24427,7 @@
         <v>46223</v>
       </c>
       <c r="B209" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A209,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C209" s="100">
@@ -24443,7 +24443,7 @@
         <v/>
       </c>
       <c r="F209" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A209,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A209,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A209,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A209,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G209" s="100">
@@ -24476,7 +24476,7 @@
         <v>46224</v>
       </c>
       <c r="B210" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A210,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C210" s="101">
@@ -24492,7 +24492,7 @@
         <v/>
       </c>
       <c r="F210" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A210,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A210,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A210,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A210,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G210" s="101">
@@ -24525,7 +24525,7 @@
         <v>46225</v>
       </c>
       <c r="B211" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A211,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C211" s="100">
@@ -24541,7 +24541,7 @@
         <v/>
       </c>
       <c r="F211" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A211,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A211,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A211,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A211,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G211" s="100">
@@ -24574,7 +24574,7 @@
         <v>46226</v>
       </c>
       <c r="B212" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A212,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C212" s="101">
@@ -24590,7 +24590,7 @@
         <v/>
       </c>
       <c r="F212" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A212,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A212,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A212,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A212,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G212" s="101">
@@ -24623,7 +24623,7 @@
         <v>46227</v>
       </c>
       <c r="B213" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A213,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C213" s="100">
@@ -24639,7 +24639,7 @@
         <v/>
       </c>
       <c r="F213" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A213,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A213,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A213,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A213,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G213" s="100">
@@ -24672,7 +24672,7 @@
         <v>46228</v>
       </c>
       <c r="B214" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A214,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C214" s="101">
@@ -24688,7 +24688,7 @@
         <v/>
       </c>
       <c r="F214" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A214,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A214,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A214,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A214,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G214" s="101">
@@ -24721,7 +24721,7 @@
         <v>46229</v>
       </c>
       <c r="B215" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A215,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C215" s="100">
@@ -24737,7 +24737,7 @@
         <v/>
       </c>
       <c r="F215" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A215,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A215,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A215,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A215,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G215" s="100">
@@ -24770,7 +24770,7 @@
         <v>46230</v>
       </c>
       <c r="B216" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A216,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C216" s="101">
@@ -24786,7 +24786,7 @@
         <v/>
       </c>
       <c r="F216" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A216,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A216,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A216,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A216,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G216" s="101">
@@ -24819,7 +24819,7 @@
         <v>46231</v>
       </c>
       <c r="B217" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A217,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C217" s="100">
@@ -24835,7 +24835,7 @@
         <v/>
       </c>
       <c r="F217" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A217,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A217,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A217,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A217,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G217" s="100">
@@ -24868,7 +24868,7 @@
         <v>46232</v>
       </c>
       <c r="B218" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A218,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C218" s="101">
@@ -24884,7 +24884,7 @@
         <v/>
       </c>
       <c r="F218" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A218,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A218,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A218,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A218,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G218" s="101">
@@ -24917,7 +24917,7 @@
         <v>46233</v>
       </c>
       <c r="B219" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A219,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C219" s="100">
@@ -24933,7 +24933,7 @@
         <v/>
       </c>
       <c r="F219" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A219,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A219,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A219,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A219,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G219" s="100">
@@ -24966,7 +24966,7 @@
         <v>46234</v>
       </c>
       <c r="B220" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A220,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C220" s="101">
@@ -24982,7 +24982,7 @@
         <v/>
       </c>
       <c r="F220" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A220,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A220,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A220,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A220,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G220" s="101">
@@ -25015,7 +25015,7 @@
         <v>46235</v>
       </c>
       <c r="B221" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A221,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C221" s="100">
@@ -25031,7 +25031,7 @@
         <v/>
       </c>
       <c r="F221" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A221,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A221,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A221,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A221,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G221" s="100">
@@ -25064,7 +25064,7 @@
         <v>46236</v>
       </c>
       <c r="B222" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A222,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C222" s="101">
@@ -25080,7 +25080,7 @@
         <v/>
       </c>
       <c r="F222" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A222,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A222,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A222,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A222,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G222" s="101">
@@ -25113,7 +25113,7 @@
         <v>46237</v>
       </c>
       <c r="B223" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A223,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C223" s="100">
@@ -25129,7 +25129,7 @@
         <v/>
       </c>
       <c r="F223" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A223,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A223,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A223,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A223,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G223" s="100">
@@ -25162,7 +25162,7 @@
         <v>46238</v>
       </c>
       <c r="B224" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A224,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C224" s="101">
@@ -25178,7 +25178,7 @@
         <v/>
       </c>
       <c r="F224" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A224,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A224,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A224,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A224,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G224" s="101">
@@ -25211,7 +25211,7 @@
         <v>46239</v>
       </c>
       <c r="B225" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A225,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C225" s="100">
@@ -25227,7 +25227,7 @@
         <v/>
       </c>
       <c r="F225" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A225,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A225,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A225,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A225,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G225" s="100">
@@ -25260,7 +25260,7 @@
         <v>46240</v>
       </c>
       <c r="B226" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A226,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C226" s="101">
@@ -25276,7 +25276,7 @@
         <v/>
       </c>
       <c r="F226" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A226,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A226,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A226,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A226,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G226" s="101">
@@ -25309,7 +25309,7 @@
         <v>46241</v>
       </c>
       <c r="B227" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A227,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C227" s="100">
@@ -25325,7 +25325,7 @@
         <v/>
       </c>
       <c r="F227" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A227,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A227,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A227,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A227,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G227" s="100">
@@ -25358,7 +25358,7 @@
         <v>46242</v>
       </c>
       <c r="B228" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A228,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C228" s="101">
@@ -25374,7 +25374,7 @@
         <v/>
       </c>
       <c r="F228" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A228,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A228,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A228,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A228,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G228" s="101">
@@ -25407,7 +25407,7 @@
         <v>46243</v>
       </c>
       <c r="B229" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A229,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C229" s="100">
@@ -25423,7 +25423,7 @@
         <v/>
       </c>
       <c r="F229" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A229,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A229,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A229,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A229,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G229" s="100">
@@ -25456,7 +25456,7 @@
         <v>46244</v>
       </c>
       <c r="B230" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A230,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C230" s="101">
@@ -25472,7 +25472,7 @@
         <v/>
       </c>
       <c r="F230" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A230,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A230,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A230,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A230,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G230" s="101">
@@ -25505,7 +25505,7 @@
         <v>46245</v>
       </c>
       <c r="B231" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A231,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C231" s="100">
@@ -25521,7 +25521,7 @@
         <v/>
       </c>
       <c r="F231" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A231,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A231,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A231,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A231,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G231" s="100">
@@ -25554,7 +25554,7 @@
         <v>46246</v>
       </c>
       <c r="B232" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A232,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C232" s="101">
@@ -25570,7 +25570,7 @@
         <v/>
       </c>
       <c r="F232" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A232,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A232,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A232,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A232,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G232" s="101">
@@ -25603,7 +25603,7 @@
         <v>46247</v>
       </c>
       <c r="B233" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A233,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C233" s="100">
@@ -25619,7 +25619,7 @@
         <v/>
       </c>
       <c r="F233" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A233,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A233,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A233,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A233,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G233" s="100">
@@ -25652,7 +25652,7 @@
         <v>46248</v>
       </c>
       <c r="B234" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A234,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C234" s="101">
@@ -25668,7 +25668,7 @@
         <v/>
       </c>
       <c r="F234" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A234,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A234,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A234,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A234,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G234" s="101">
@@ -25701,7 +25701,7 @@
         <v>46249</v>
       </c>
       <c r="B235" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A235,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C235" s="100">
@@ -25717,7 +25717,7 @@
         <v/>
       </c>
       <c r="F235" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A235,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A235,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A235,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A235,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G235" s="100">
@@ -25750,7 +25750,7 @@
         <v>46250</v>
       </c>
       <c r="B236" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A236,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C236" s="101">
@@ -25766,7 +25766,7 @@
         <v/>
       </c>
       <c r="F236" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A236,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A236,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A236,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A236,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G236" s="101">
@@ -25799,7 +25799,7 @@
         <v>46251</v>
       </c>
       <c r="B237" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A237,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C237" s="100">
@@ -25815,7 +25815,7 @@
         <v/>
       </c>
       <c r="F237" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A237,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A237,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A237,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A237,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G237" s="100">
@@ -25848,7 +25848,7 @@
         <v>46252</v>
       </c>
       <c r="B238" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A238,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C238" s="101">
@@ -25864,7 +25864,7 @@
         <v/>
       </c>
       <c r="F238" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A238,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A238,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A238,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A238,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G238" s="101">
@@ -25897,7 +25897,7 @@
         <v>46253</v>
       </c>
       <c r="B239" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A239,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C239" s="100">
@@ -25913,7 +25913,7 @@
         <v/>
       </c>
       <c r="F239" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A239,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A239,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A239,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A239,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G239" s="100">
@@ -25946,7 +25946,7 @@
         <v>46254</v>
       </c>
       <c r="B240" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A240,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C240" s="101">
@@ -25962,7 +25962,7 @@
         <v/>
       </c>
       <c r="F240" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A240,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A240,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A240,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A240,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G240" s="101">
@@ -25995,7 +25995,7 @@
         <v>46255</v>
       </c>
       <c r="B241" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A241,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C241" s="100">
@@ -26011,7 +26011,7 @@
         <v/>
       </c>
       <c r="F241" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A241,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A241,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A241,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A241,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G241" s="100">
@@ -26044,7 +26044,7 @@
         <v>46256</v>
       </c>
       <c r="B242" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A242,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C242" s="101">
@@ -26060,7 +26060,7 @@
         <v/>
       </c>
       <c r="F242" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A242,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A242,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A242,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A242,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G242" s="101">
@@ -26093,7 +26093,7 @@
         <v>46257</v>
       </c>
       <c r="B243" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A243,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C243" s="100">
@@ -26109,7 +26109,7 @@
         <v/>
       </c>
       <c r="F243" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A243,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A243,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A243,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A243,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G243" s="100">
@@ -26142,7 +26142,7 @@
         <v>46258</v>
       </c>
       <c r="B244" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A244,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C244" s="101">
@@ -26158,7 +26158,7 @@
         <v/>
       </c>
       <c r="F244" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A244,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A244,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A244,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A244,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G244" s="101">
@@ -26191,7 +26191,7 @@
         <v>46259</v>
       </c>
       <c r="B245" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A245,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C245" s="100">
@@ -26207,7 +26207,7 @@
         <v/>
       </c>
       <c r="F245" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A245,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A245,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A245,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A245,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G245" s="100">
@@ -26240,7 +26240,7 @@
         <v>46260</v>
       </c>
       <c r="B246" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A246,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C246" s="101">
@@ -26256,7 +26256,7 @@
         <v/>
       </c>
       <c r="F246" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A246,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A246,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A246,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A246,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G246" s="101">
@@ -26289,7 +26289,7 @@
         <v>46261</v>
       </c>
       <c r="B247" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A247,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C247" s="100">
@@ -26305,7 +26305,7 @@
         <v/>
       </c>
       <c r="F247" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A247,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A247,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A247,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A247,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G247" s="100">
@@ -26338,7 +26338,7 @@
         <v>46262</v>
       </c>
       <c r="B248" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A248,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C248" s="101">
@@ -26354,7 +26354,7 @@
         <v/>
       </c>
       <c r="F248" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A248,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A248,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A248,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A248,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G248" s="101">
@@ -26387,7 +26387,7 @@
         <v>46263</v>
       </c>
       <c r="B249" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A249,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C249" s="100">
@@ -26403,7 +26403,7 @@
         <v/>
       </c>
       <c r="F249" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A249,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A249,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A249,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A249,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G249" s="100">
@@ -26436,7 +26436,7 @@
         <v>46264</v>
       </c>
       <c r="B250" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A250,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C250" s="101">
@@ -26452,7 +26452,7 @@
         <v/>
       </c>
       <c r="F250" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A250,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A250,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A250,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A250,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G250" s="101">
@@ -26485,7 +26485,7 @@
         <v>46265</v>
       </c>
       <c r="B251" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A251,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C251" s="100">
@@ -26501,7 +26501,7 @@
         <v/>
       </c>
       <c r="F251" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A251,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A251,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A251,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A251,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G251" s="100">
@@ -26534,7 +26534,7 @@
         <v>46266</v>
       </c>
       <c r="B252" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A252,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C252" s="101">
@@ -26550,7 +26550,7 @@
         <v/>
       </c>
       <c r="F252" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A252,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A252,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A252,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A252,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G252" s="101">
@@ -26583,7 +26583,7 @@
         <v>46267</v>
       </c>
       <c r="B253" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A253,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C253" s="100">
@@ -26599,7 +26599,7 @@
         <v/>
       </c>
       <c r="F253" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A253,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A253,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A253,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A253,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G253" s="100">
@@ -26632,7 +26632,7 @@
         <v>46268</v>
       </c>
       <c r="B254" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A254,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C254" s="101">
@@ -26648,7 +26648,7 @@
         <v/>
       </c>
       <c r="F254" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A254,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A254,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A254,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A254,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G254" s="101">
@@ -26681,7 +26681,7 @@
         <v>46269</v>
       </c>
       <c r="B255" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A255,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C255" s="100">
@@ -26697,7 +26697,7 @@
         <v/>
       </c>
       <c r="F255" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A255,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A255,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A255,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A255,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G255" s="100">
@@ -26730,7 +26730,7 @@
         <v>46270</v>
       </c>
       <c r="B256" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A256,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C256" s="101">
@@ -26746,7 +26746,7 @@
         <v/>
       </c>
       <c r="F256" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A256,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A256,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A256,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A256,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G256" s="101">
@@ -26779,7 +26779,7 @@
         <v>46271</v>
       </c>
       <c r="B257" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A257,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C257" s="100">
@@ -26795,7 +26795,7 @@
         <v/>
       </c>
       <c r="F257" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A257,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A257,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A257,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A257,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G257" s="100">
@@ -26828,7 +26828,7 @@
         <v>46272</v>
       </c>
       <c r="B258" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A258,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C258" s="101">
@@ -26844,7 +26844,7 @@
         <v/>
       </c>
       <c r="F258" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A258,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A258,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A258,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A258,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G258" s="101">
@@ -26877,7 +26877,7 @@
         <v>46273</v>
       </c>
       <c r="B259" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A259,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C259" s="100">
@@ -26893,7 +26893,7 @@
         <v/>
       </c>
       <c r="F259" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A259,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A259,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A259,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A259,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G259" s="100">
@@ -26926,7 +26926,7 @@
         <v>46274</v>
       </c>
       <c r="B260" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A260,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C260" s="101">
@@ -26942,7 +26942,7 @@
         <v/>
       </c>
       <c r="F260" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A260,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A260,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A260,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A260,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G260" s="101">
@@ -26975,7 +26975,7 @@
         <v>46275</v>
       </c>
       <c r="B261" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A261,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C261" s="100">
@@ -26991,7 +26991,7 @@
         <v/>
       </c>
       <c r="F261" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A261,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A261,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A261,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A261,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G261" s="100">
@@ -27024,7 +27024,7 @@
         <v>46276</v>
       </c>
       <c r="B262" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A262,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C262" s="101">
@@ -27040,7 +27040,7 @@
         <v/>
       </c>
       <c r="F262" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A262,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A262,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A262,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A262,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G262" s="101">
@@ -27073,7 +27073,7 @@
         <v>46277</v>
       </c>
       <c r="B263" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A263,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C263" s="100">
@@ -27089,7 +27089,7 @@
         <v/>
       </c>
       <c r="F263" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A263,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A263,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A263,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A263,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G263" s="100">
@@ -27122,7 +27122,7 @@
         <v>46278</v>
       </c>
       <c r="B264" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A264,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C264" s="101">
@@ -27138,7 +27138,7 @@
         <v/>
       </c>
       <c r="F264" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A264,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A264,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A264,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A264,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G264" s="101">
@@ -27171,7 +27171,7 @@
         <v>46279</v>
       </c>
       <c r="B265" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A265,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C265" s="100">
@@ -27187,7 +27187,7 @@
         <v/>
       </c>
       <c r="F265" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A265,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A265,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A265,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A265,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G265" s="100">
@@ -27220,7 +27220,7 @@
         <v>46280</v>
       </c>
       <c r="B266" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A266,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C266" s="101">
@@ -27236,7 +27236,7 @@
         <v/>
       </c>
       <c r="F266" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A266,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A266,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A266,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A266,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G266" s="101">
@@ -27269,7 +27269,7 @@
         <v>46281</v>
       </c>
       <c r="B267" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A267,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A267,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A267,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A267,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C267" s="100">
@@ -27285,7 +27285,7 @@
         <v/>
       </c>
       <c r="F267" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A267,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A267,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A267,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A267,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G267" s="100">
@@ -27318,7 +27318,7 @@
         <v>46282</v>
       </c>
       <c r="B268" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A268,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A268,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A268,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A268,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C268" s="101">
@@ -27334,7 +27334,7 @@
         <v/>
       </c>
       <c r="F268" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A268,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A268,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A268,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A268,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G268" s="101">
@@ -27367,7 +27367,7 @@
         <v>46283</v>
       </c>
       <c r="B269" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A269,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A269,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A269,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A269,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C269" s="100">
@@ -27383,7 +27383,7 @@
         <v/>
       </c>
       <c r="F269" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A269,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A269,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A269,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A269,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G269" s="100">
@@ -27416,7 +27416,7 @@
         <v>46284</v>
       </c>
       <c r="B270" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$280,MATCH($A270,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$B$25:$B$280,MATCH($A270,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A270,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A270,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="C270" s="101">
@@ -27432,7 +27432,7 @@
         <v/>
       </c>
       <c r="F270" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$280,MATCH($A270,Polymarket!$A$25:$A$280,0))=0,"",INDEX(Polymarket!$C$25:$C$280,MATCH($A270,Polymarket!$A$25:$A$280,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A270,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A270,Polymarket!$A$25:$A$281,0))),"")</f>
         <v/>
       </c>
       <c r="G270" s="101">
@@ -27457,6 +27457,55 @@
       <c r="L270" s="38" t="inlineStr">
         <is>
           <t>19 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="39" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B271" s="100">
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A271,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A271,Polymarket!$A$25:$A$281,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C271" s="100">
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A271,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A271,Kalshi!$A$31:$A$463,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D271" s="18">
+        <f>IF(AND(ISNUMBER(B271),ISNUMBER(C271)),B271-C271,"")</f>
+        <v/>
+      </c>
+      <c r="E271" s="17">
+        <f>IF(ISNUMBER(D271),ABS(D271),"")</f>
+        <v/>
+      </c>
+      <c r="F271" s="100">
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A271,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A271,Polymarket!$A$25:$A$281,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G271" s="100">
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A271,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A271,Kalshi!$A$31:$A$463,0))),"")</f>
+        <v/>
+      </c>
+      <c r="H271" s="20">
+        <f>IF(AND(ISNUMBER(B271),ISNUMBER(C271)),MIN(B271,C271),"")</f>
+        <v/>
+      </c>
+      <c r="I271" s="20">
+        <f>IF(AND(ISNUMBER(F271),ISNUMBER(G271)),MIN(F271,G271),"")</f>
+        <v/>
+      </c>
+      <c r="J271" s="17">
+        <f>IF(AND(ISNUMBER(H271),ISNUMBER(I271)),H271+I271,"")</f>
+        <v/>
+      </c>
+      <c r="K271" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L271" s="26" t="inlineStr">
+        <is>
+          <t>20 Sep</t>
         </is>
       </c>
     </row>
@@ -27489,7 +27538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-19 19:19 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -28649,7 +28698,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-19 19:19 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -28730,7 +28779,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-19 19:19 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K280"/>
+  <dimension ref="A1:K281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28914,7 +28963,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 19:19 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -29080,10 +29129,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10683.4667</v>
+        <v>11037.3545</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>11928.2861</v>
+        <v>14243.5465</v>
       </c>
     </row>
     <row r="14">
@@ -29105,9 +29154,11 @@
           <t>24h price change</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
+      <c r="B15" s="13" t="n">
+        <v>0.01</v>
+      </c>
       <c r="C15" s="14" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="17">
@@ -29222,10 +29273,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>6899</v>
+        <v>7299</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>5</v>
+        <v>320</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40545,10 +40596,10 @@
         <v>46284</v>
       </c>
       <c r="B280" s="28" t="n">
-        <v>0.795</v>
+        <v>0.785</v>
       </c>
       <c r="C280" s="28" t="n">
-        <v>0.205</v>
+        <v>0.21</v>
       </c>
       <c r="D280" s="29">
         <f>IF(COUNT(B280:C280)=2,B280+C280,"")</f>
@@ -40581,6 +40632,50 @@
       <c r="K280" s="26" t="inlineStr">
         <is>
           <t>19 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="39" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B281" s="16" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="C281" s="16" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="D281" s="17">
+        <f>IF(COUNT(B281:C281)=2,B281+C281,"")</f>
+        <v/>
+      </c>
+      <c r="E281" s="20">
+        <f>IF(ISNUMBER(B281),IFERROR(B281/$D281,""),"")</f>
+        <v/>
+      </c>
+      <c r="F281" s="20">
+        <f>IF(ISNUMBER(C281),IFERROR(C281/$D281,""),"")</f>
+        <v/>
+      </c>
+      <c r="G281" s="18">
+        <f>IF(COUNT(B281:C281)=2,B281-C281,"")</f>
+        <v/>
+      </c>
+      <c r="H281" s="18">
+        <f>IFERROR(IF(AND(ISNUMBER(B281),INDEX($B$25:$B281,MATCH($A281-7,$A$25:$A281,1))&lt;&gt;0,INDEX($A$25:$A281,MATCH($A281-7,$A$25:$A281,1))&lt;&gt;0,$A281-INDEX($A$25:$A281,MATCH($A281-7,$A$25:$A281,1))&lt;=10),B281-INDEX($B$25:$B281,MATCH($A281-7,$A$25:$A281,1)),""),"")</f>
+        <v/>
+      </c>
+      <c r="I281" s="18">
+        <f>IFERROR(IF(AND(ISNUMBER(B281),INDEX($B$25:$B281,MATCH($A281-30,$A$25:$A281,1))&lt;&gt;0,INDEX($A$25:$A281,MATCH($A281-30,$A$25:$A281,1))&lt;&gt;0,$A281-INDEX($A$25:$A281,MATCH($A281-30,$A$25:$A281,1))&lt;=33),B281-INDEX($B$25:$B281,MATCH($A281-30,$A$25:$A281,1)),""),"")</f>
+        <v/>
+      </c>
+      <c r="J281" s="40">
+        <f>DATE(2026,11,3)-A281</f>
+        <v/>
+      </c>
+      <c r="K281" s="26" t="inlineStr">
+        <is>
+          <t>20 Sep</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40718,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-19 19:19 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -40892,7 +40987,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>9.99</v>
+        <v>6.9</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -40909,7 +41004,7 @@
         <v>0.19</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -40924,7 +41019,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>200</v>
+        <v>1154.86</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -41026,25 +41121,25 @@
         <v>0.79</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>9.99</v>
+        <v>6.9</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>10272.7</v>
+        <v>10772.7</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>200</v>
+        <v>1154.86</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>7.23</v>
+        <v>170.41</v>
       </c>
     </row>
     <row r="24">
@@ -41055,7 +41150,7 @@
         <v>0.78</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>12.01</v>
+        <v>200</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.18</v>
@@ -41064,16 +41159,16 @@
         <v>200</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>322.02</v>
+        <v>500</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>275.59</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="25">
@@ -41084,7 +41179,7 @@
         <v>0.77</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>276</v>
+        <v>538</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
@@ -41093,16 +41188,16 @@
         <v>496.44</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>500</v>
+        <v>207</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>55.33</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26">
@@ -41113,7 +41208,7 @@
         <v>0.76</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>431.3</v>
+        <v>669.3</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.14</v>
@@ -41122,16 +41217,16 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>1000</v>
+        <v>5870</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>50</v>
+        <v>629.4</v>
       </c>
     </row>
     <row r="27">
@@ -41142,7 +41237,7 @@
         <v>0.75</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>335.15</v>
+        <v>100</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>0.12</v>
@@ -41151,16 +41246,16 @@
         <v>5870</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.13</v>
+        <v>0.028</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>350</v>
+        <v>1.08</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
@@ -61888,7 +61983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -61914,7 +62009,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-19 19:19 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -62033,7 +62128,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>50948.27326</v>
+        <v>54244.4535</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -62132,7 +62227,7 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.16</v>
@@ -62153,7 +62248,7 @@
         <v>756.9541730000001</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>8240.18</v>
+        <v>536.8973</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62173,7 +62268,7 @@
         <v>0.1</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.137</v>
+        <v>0.131</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62191,7 +62286,7 @@
         <v>179.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8356.796469999999</v>
+        <v>8813.09101</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62208,10 +62303,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -62229,7 +62324,7 @@
         <v>156.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>120.1168</v>
+        <v>8682.998</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62267,7 +62362,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8521.8091</v>
+        <v>8767.0573</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62305,7 +62400,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8552.1288</v>
+        <v>8768.0798</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62322,10 +62417,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.398</v>
+        <v>0.209</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62343,7 +62438,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>202.66707</v>
+        <v>534.01116</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62360,10 +62455,10 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.119</v>
+        <v>0.095</v>
       </c>
       <c r="E22" s="17">
         <f>IF(COUNT(C22:D22)=2,(C22+D22)/2,"")</f>
@@ -62381,7 +62476,7 @@
         <v>162.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>107.97379</v>
+        <v>732.8140100000001</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62419,7 +62514,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>8198.950800000001</v>
+        <v>8582.8621</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62436,7 +62531,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62457,7 +62552,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>163.72466</v>
+        <v>374.69576</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62495,7 +62590,7 @@
         <v>115.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>8412.117099999999</v>
+        <v>8836.7649</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -64065,51 +64160,86 @@
         <v>46284</v>
       </c>
       <c r="B81" s="16" t="n">
-        <v>0.145</v>
+        <v>0.21</v>
       </c>
       <c r="C81" s="16" t="n">
-        <v>0.1185</v>
+        <v>0.12</v>
       </c>
       <c r="D81" s="16" t="n">
         <v>0.08</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.155</v>
+        <v>0.145</v>
       </c>
       <c r="F81" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G81" s="16" t="n">
-        <v>0.243</v>
+        <v>0.251</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>0.0675</v>
+        <v>0.09</v>
       </c>
       <c r="I81" s="16" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="J81" s="16" t="n">
         <v>0.051</v>
       </c>
       <c r="K81" s="16" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="41" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B82" s="28" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="C82" s="28" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="D82" s="28" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E82" s="28" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="F82" s="28" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G82" s="28" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="H82" s="28" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="I82" s="28" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J82" s="28" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="K82" s="28" t="n">
         <v>0.105</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>All ten brackets, daily closes from CLOB /prices-history at fidelity=1440. The market opened 11 Aug 2026, so the series is only 39 days long and the brackets are thin — read it as a sanity check on the ladder above, not as a trend.</t>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>All ten brackets, daily closes from CLOB /prices-history at fidelity=1440. The market opened 11 Aug 2026, so the series is only 40 days long and the brackets are thin — read it as a sanity check on the ladder above, not as a trend.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="B7:F7"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B7:F7"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A82:K82"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="B8:F8"/>
@@ -64151,7 +64281,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-19 19:19 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -64350,8 +64480,12 @@
       <c r="B14" s="91" t="n">
         <v>310000</v>
       </c>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
+      <c r="C14" s="16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0.79</v>
+      </c>
       <c r="E14" s="17">
         <f>IF(COUNT(C14:D14)=2,(C14+D14)/2,"")</f>
         <v/>
@@ -64382,8 +64516,12 @@
       <c r="B15" s="91" t="n">
         <v>320000</v>
       </c>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
+      <c r="C15" s="16" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0.66</v>
+      </c>
       <c r="E15" s="17">
         <f>IF(COUNT(C15:D15)=2,(C15+D15)/2,"")</f>
         <v/>
@@ -64414,9 +64552,11 @@
       <c r="B16" s="91" t="n">
         <v>340000</v>
       </c>
-      <c r="C16" s="16" t="n"/>
+      <c r="C16" s="16" t="n">
+        <v>0.47</v>
+      </c>
       <c r="D16" s="16" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -64448,8 +64588,12 @@
       <c r="B17" s="91" t="n">
         <v>360000</v>
       </c>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
+      <c r="C17" s="16" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>0.41</v>
+      </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
         <v/>
@@ -64480,8 +64624,12 @@
       <c r="B18" s="91" t="n">
         <v>370000</v>
       </c>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
+      <c r="C18" s="16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>0.29</v>
+      </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
         <v/>
@@ -65406,7 +65554,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-19 19:19 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -65620,7 +65768,7 @@
         <v>0.04</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E14" s="20">
         <f>IF(ISNUMBER(D14),1-D14,"")</f>
@@ -65653,7 +65801,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.9</v>
@@ -65689,7 +65837,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.67</v>
@@ -65728,7 +65876,7 @@
         <v>0.22</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="E17" s="20">
         <f>IF(ISNUMBER(D17),1-D17,"")</f>
@@ -65764,7 +65912,7 @@
         <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66859,7 +67007,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-19 19:19 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-20 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -67434,7 +67582,7 @@
         </is>
       </c>
       <c r="B28" s="50" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="29">

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -1620,12 +1620,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$463</f>
+              <f>'Kalshi'!$M$31:$M$464</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$B$31:$B$463</f>
+              <f>'Kalshi'!$B$31:$B$464</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1656,12 +1656,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$463</f>
+              <f>'Kalshi'!$M$31:$M$464</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$C$31:$C$463</f>
+              <f>'Kalshi'!$C$31:$C$464</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1880,12 +1880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$463</f>
+              <f>'Kalshi'!$M$31:$M$464</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$L$31:$L$463</f>
+              <f>'Kalshi'!$L$31:$L$464</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-20 01:08 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-20 01:08 UTC</t>
+          <t>2026-09-20 14:41 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="B70" s="59">
-        <f>TEXT(Kalshi!A31,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Kalshi!A463,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Kalshi!A31:A463)&amp;" days)"</f>
+        <f>TEXT(Kalshi!A31,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Kalshi!A464,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Kalshi!A31:A464)&amp;" days)"</f>
         <v/>
       </c>
       <c r="C70" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-20 01:08 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-20 01:08 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-20 01:08 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v/>
       </c>
       <c r="C15" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A15,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A15,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A15,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A15,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D15" s="18">
@@ -14941,7 +14941,7 @@
         <v/>
       </c>
       <c r="G15" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A15,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A15,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A15,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A15,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H15" s="20">
@@ -14974,7 +14974,7 @@
         <v/>
       </c>
       <c r="C16" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A16,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A16,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A16,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A16,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D16" s="31">
@@ -14990,7 +14990,7 @@
         <v/>
       </c>
       <c r="G16" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A16,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A16,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A16,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A16,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H16" s="30">
@@ -15023,7 +15023,7 @@
         <v/>
       </c>
       <c r="C17" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A17,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A17,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A17,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A17,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D17" s="18">
@@ -15039,7 +15039,7 @@
         <v/>
       </c>
       <c r="G17" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A17,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A17,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A17,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A17,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H17" s="20">
@@ -15072,7 +15072,7 @@
         <v/>
       </c>
       <c r="C18" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A18,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A18,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A18,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A18,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D18" s="31">
@@ -15088,7 +15088,7 @@
         <v/>
       </c>
       <c r="G18" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A18,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A18,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A18,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A18,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H18" s="30">
@@ -15121,7 +15121,7 @@
         <v/>
       </c>
       <c r="C19" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A19,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A19,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A19,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A19,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D19" s="18">
@@ -15137,7 +15137,7 @@
         <v/>
       </c>
       <c r="G19" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A19,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A19,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A19,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A19,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H19" s="20">
@@ -15170,7 +15170,7 @@
         <v/>
       </c>
       <c r="C20" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A20,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A20,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A20,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A20,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D20" s="31">
@@ -15186,7 +15186,7 @@
         <v/>
       </c>
       <c r="G20" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A20,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A20,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A20,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A20,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H20" s="30">
@@ -15219,7 +15219,7 @@
         <v/>
       </c>
       <c r="C21" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A21,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A21,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A21,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A21,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D21" s="18">
@@ -15235,7 +15235,7 @@
         <v/>
       </c>
       <c r="G21" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A21,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A21,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A21,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A21,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
@@ -15268,7 +15268,7 @@
         <v/>
       </c>
       <c r="C22" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A22,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A22,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A22,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A22,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D22" s="31">
@@ -15284,7 +15284,7 @@
         <v/>
       </c>
       <c r="G22" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A22,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A22,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A22,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A22,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H22" s="30">
@@ -15317,7 +15317,7 @@
         <v/>
       </c>
       <c r="C23" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A23,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A23,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A23,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A23,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D23" s="18">
@@ -15333,7 +15333,7 @@
         <v/>
       </c>
       <c r="G23" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A23,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A23,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A23,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A23,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
@@ -15366,7 +15366,7 @@
         <v/>
       </c>
       <c r="C24" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A24,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A24,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A24,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A24,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D24" s="31">
@@ -15382,7 +15382,7 @@
         <v/>
       </c>
       <c r="G24" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A24,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A24,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A24,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A24,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H24" s="30">
@@ -15415,7 +15415,7 @@
         <v/>
       </c>
       <c r="C25" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A25,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A25,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A25,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A25,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D25" s="18">
@@ -15431,7 +15431,7 @@
         <v/>
       </c>
       <c r="G25" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A25,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A25,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A25,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A25,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
@@ -15464,7 +15464,7 @@
         <v/>
       </c>
       <c r="C26" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A26,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A26,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A26,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A26,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D26" s="31">
@@ -15480,7 +15480,7 @@
         <v/>
       </c>
       <c r="G26" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A26,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A26,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A26,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A26,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H26" s="30">
@@ -15513,7 +15513,7 @@
         <v/>
       </c>
       <c r="C27" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A27,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A27,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A27,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A27,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D27" s="18">
@@ -15529,7 +15529,7 @@
         <v/>
       </c>
       <c r="G27" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A27,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A27,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A27,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A27,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H27" s="20">
@@ -15562,7 +15562,7 @@
         <v/>
       </c>
       <c r="C28" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A28,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A28,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A28,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A28,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D28" s="31">
@@ -15578,7 +15578,7 @@
         <v/>
       </c>
       <c r="G28" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A28,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A28,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A28,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A28,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H28" s="30">
@@ -15611,7 +15611,7 @@
         <v/>
       </c>
       <c r="C29" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A29,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A29,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A29,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A29,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D29" s="18">
@@ -15627,7 +15627,7 @@
         <v/>
       </c>
       <c r="G29" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A29,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A29,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A29,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A29,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H29" s="20">
@@ -15660,7 +15660,7 @@
         <v/>
       </c>
       <c r="C30" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A30,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A30,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A30,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A30,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D30" s="31">
@@ -15676,7 +15676,7 @@
         <v/>
       </c>
       <c r="G30" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A30,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A30,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A30,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A30,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H30" s="30">
@@ -15709,7 +15709,7 @@
         <v/>
       </c>
       <c r="C31" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A31,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A31,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A31,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A31,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D31" s="18">
@@ -15725,7 +15725,7 @@
         <v/>
       </c>
       <c r="G31" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A31,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A31,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A31,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A31,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H31" s="20">
@@ -15758,7 +15758,7 @@
         <v/>
       </c>
       <c r="C32" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A32,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A32,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A32,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A32,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D32" s="31">
@@ -15774,7 +15774,7 @@
         <v/>
       </c>
       <c r="G32" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A32,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A32,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A32,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A32,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H32" s="30">
@@ -15807,7 +15807,7 @@
         <v/>
       </c>
       <c r="C33" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A33,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A33,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A33,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A33,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D33" s="18">
@@ -15823,7 +15823,7 @@
         <v/>
       </c>
       <c r="G33" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A33,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A33,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A33,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A33,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H33" s="20">
@@ -15856,7 +15856,7 @@
         <v/>
       </c>
       <c r="C34" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A34,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A34,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A34,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A34,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D34" s="31">
@@ -15872,7 +15872,7 @@
         <v/>
       </c>
       <c r="G34" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A34,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A34,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A34,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A34,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H34" s="30">
@@ -15905,7 +15905,7 @@
         <v/>
       </c>
       <c r="C35" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A35,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A35,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A35,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A35,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D35" s="18">
@@ -15921,7 +15921,7 @@
         <v/>
       </c>
       <c r="G35" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A35,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A35,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A35,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A35,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H35" s="20">
@@ -15954,7 +15954,7 @@
         <v/>
       </c>
       <c r="C36" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A36,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A36,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A36,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A36,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D36" s="31">
@@ -15970,7 +15970,7 @@
         <v/>
       </c>
       <c r="G36" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A36,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A36,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A36,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A36,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H36" s="30">
@@ -16003,7 +16003,7 @@
         <v/>
       </c>
       <c r="C37" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A37,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A37,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A37,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A37,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D37" s="18">
@@ -16019,7 +16019,7 @@
         <v/>
       </c>
       <c r="G37" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A37,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A37,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A37,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A37,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H37" s="20">
@@ -16052,7 +16052,7 @@
         <v/>
       </c>
       <c r="C38" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A38,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A38,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A38,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A38,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D38" s="31">
@@ -16068,7 +16068,7 @@
         <v/>
       </c>
       <c r="G38" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A38,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A38,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A38,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A38,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H38" s="30">
@@ -16101,7 +16101,7 @@
         <v/>
       </c>
       <c r="C39" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A39,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A39,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A39,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A39,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D39" s="18">
@@ -16117,7 +16117,7 @@
         <v/>
       </c>
       <c r="G39" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A39,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A39,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A39,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A39,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H39" s="20">
@@ -16150,7 +16150,7 @@
         <v/>
       </c>
       <c r="C40" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A40,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A40,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A40,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A40,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D40" s="31">
@@ -16166,7 +16166,7 @@
         <v/>
       </c>
       <c r="G40" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A40,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A40,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A40,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A40,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H40" s="30">
@@ -16199,7 +16199,7 @@
         <v/>
       </c>
       <c r="C41" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A41,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A41,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A41,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A41,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D41" s="18">
@@ -16215,7 +16215,7 @@
         <v/>
       </c>
       <c r="G41" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A41,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A41,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A41,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A41,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H41" s="20">
@@ -16248,7 +16248,7 @@
         <v/>
       </c>
       <c r="C42" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A42,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A42,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A42,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A42,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D42" s="31">
@@ -16264,7 +16264,7 @@
         <v/>
       </c>
       <c r="G42" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A42,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A42,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A42,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A42,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H42" s="30">
@@ -16297,7 +16297,7 @@
         <v/>
       </c>
       <c r="C43" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A43,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A43,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A43,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A43,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D43" s="18">
@@ -16313,7 +16313,7 @@
         <v/>
       </c>
       <c r="G43" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A43,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A43,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A43,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A43,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H43" s="20">
@@ -16346,7 +16346,7 @@
         <v/>
       </c>
       <c r="C44" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A44,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A44,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A44,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A44,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D44" s="31">
@@ -16362,7 +16362,7 @@
         <v/>
       </c>
       <c r="G44" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A44,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A44,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A44,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A44,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H44" s="30">
@@ -16395,7 +16395,7 @@
         <v/>
       </c>
       <c r="C45" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A45,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A45,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A45,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A45,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D45" s="18">
@@ -16411,7 +16411,7 @@
         <v/>
       </c>
       <c r="G45" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A45,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A45,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A45,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A45,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H45" s="20">
@@ -16444,7 +16444,7 @@
         <v/>
       </c>
       <c r="C46" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A46,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A46,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A46,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A46,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D46" s="31">
@@ -16460,7 +16460,7 @@
         <v/>
       </c>
       <c r="G46" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A46,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A46,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A46,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A46,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H46" s="30">
@@ -16493,7 +16493,7 @@
         <v/>
       </c>
       <c r="C47" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A47,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A47,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A47,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A47,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D47" s="18">
@@ -16509,7 +16509,7 @@
         <v/>
       </c>
       <c r="G47" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A47,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A47,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A47,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A47,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H47" s="20">
@@ -16542,7 +16542,7 @@
         <v/>
       </c>
       <c r="C48" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A48,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A48,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A48,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A48,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D48" s="31">
@@ -16558,7 +16558,7 @@
         <v/>
       </c>
       <c r="G48" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A48,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A48,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A48,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A48,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H48" s="30">
@@ -16591,7 +16591,7 @@
         <v/>
       </c>
       <c r="C49" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A49,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A49,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A49,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A49,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D49" s="18">
@@ -16607,7 +16607,7 @@
         <v/>
       </c>
       <c r="G49" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A49,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A49,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A49,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A49,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H49" s="20">
@@ -16640,7 +16640,7 @@
         <v/>
       </c>
       <c r="C50" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A50,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A50,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A50,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A50,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D50" s="31">
@@ -16656,7 +16656,7 @@
         <v/>
       </c>
       <c r="G50" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A50,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A50,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A50,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A50,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H50" s="30">
@@ -16689,7 +16689,7 @@
         <v/>
       </c>
       <c r="C51" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A51,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A51,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A51,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A51,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D51" s="18">
@@ -16705,7 +16705,7 @@
         <v/>
       </c>
       <c r="G51" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A51,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A51,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A51,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A51,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H51" s="20">
@@ -16738,7 +16738,7 @@
         <v/>
       </c>
       <c r="C52" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A52,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A52,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A52,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A52,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D52" s="31">
@@ -16754,7 +16754,7 @@
         <v/>
       </c>
       <c r="G52" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A52,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A52,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A52,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A52,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H52" s="30">
@@ -16787,7 +16787,7 @@
         <v/>
       </c>
       <c r="C53" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A53,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A53,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A53,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A53,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D53" s="18">
@@ -16803,7 +16803,7 @@
         <v/>
       </c>
       <c r="G53" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A53,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A53,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A53,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A53,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H53" s="20">
@@ -16836,7 +16836,7 @@
         <v/>
       </c>
       <c r="C54" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A54,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A54,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A54,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A54,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D54" s="31">
@@ -16852,7 +16852,7 @@
         <v/>
       </c>
       <c r="G54" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A54,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A54,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A54,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A54,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H54" s="30">
@@ -16885,7 +16885,7 @@
         <v/>
       </c>
       <c r="C55" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A55,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A55,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A55,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A55,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D55" s="18">
@@ -16901,7 +16901,7 @@
         <v/>
       </c>
       <c r="G55" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A55,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A55,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A55,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A55,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H55" s="20">
@@ -16934,7 +16934,7 @@
         <v/>
       </c>
       <c r="C56" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A56,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A56,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A56,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A56,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D56" s="31">
@@ -16950,7 +16950,7 @@
         <v/>
       </c>
       <c r="G56" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A56,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A56,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A56,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A56,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H56" s="30">
@@ -16983,7 +16983,7 @@
         <v/>
       </c>
       <c r="C57" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A57,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A57,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A57,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A57,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D57" s="18">
@@ -16999,7 +16999,7 @@
         <v/>
       </c>
       <c r="G57" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A57,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A57,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A57,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A57,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H57" s="20">
@@ -17032,7 +17032,7 @@
         <v/>
       </c>
       <c r="C58" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A58,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A58,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A58,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A58,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D58" s="31">
@@ -17048,7 +17048,7 @@
         <v/>
       </c>
       <c r="G58" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A58,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A58,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A58,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A58,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H58" s="30">
@@ -17081,7 +17081,7 @@
         <v/>
       </c>
       <c r="C59" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A59,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A59,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A59,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A59,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D59" s="18">
@@ -17097,7 +17097,7 @@
         <v/>
       </c>
       <c r="G59" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A59,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A59,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A59,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A59,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H59" s="20">
@@ -17130,7 +17130,7 @@
         <v/>
       </c>
       <c r="C60" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A60,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A60,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A60,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A60,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D60" s="31">
@@ -17146,7 +17146,7 @@
         <v/>
       </c>
       <c r="G60" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A60,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A60,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A60,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A60,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H60" s="30">
@@ -17179,7 +17179,7 @@
         <v/>
       </c>
       <c r="C61" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A61,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A61,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A61,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A61,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D61" s="18">
@@ -17195,7 +17195,7 @@
         <v/>
       </c>
       <c r="G61" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A61,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A61,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A61,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A61,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H61" s="20">
@@ -17228,7 +17228,7 @@
         <v/>
       </c>
       <c r="C62" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A62,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A62,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A62,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A62,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D62" s="31">
@@ -17244,7 +17244,7 @@
         <v/>
       </c>
       <c r="G62" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A62,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A62,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A62,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A62,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H62" s="30">
@@ -17277,7 +17277,7 @@
         <v/>
       </c>
       <c r="C63" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A63,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A63,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A63,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A63,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D63" s="18">
@@ -17293,7 +17293,7 @@
         <v/>
       </c>
       <c r="G63" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A63,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A63,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A63,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A63,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H63" s="20">
@@ -17326,7 +17326,7 @@
         <v/>
       </c>
       <c r="C64" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A64,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A64,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A64,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A64,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D64" s="31">
@@ -17342,7 +17342,7 @@
         <v/>
       </c>
       <c r="G64" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A64,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A64,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A64,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A64,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H64" s="30">
@@ -17375,7 +17375,7 @@
         <v/>
       </c>
       <c r="C65" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A65,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A65,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A65,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A65,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D65" s="18">
@@ -17391,7 +17391,7 @@
         <v/>
       </c>
       <c r="G65" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A65,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A65,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A65,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A65,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H65" s="20">
@@ -17424,7 +17424,7 @@
         <v/>
       </c>
       <c r="C66" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A66,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A66,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A66,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A66,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D66" s="31">
@@ -17440,7 +17440,7 @@
         <v/>
       </c>
       <c r="G66" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A66,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A66,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A66,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A66,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H66" s="30">
@@ -17473,7 +17473,7 @@
         <v/>
       </c>
       <c r="C67" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A67,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A67,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A67,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A67,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D67" s="18">
@@ -17489,7 +17489,7 @@
         <v/>
       </c>
       <c r="G67" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A67,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A67,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A67,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A67,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H67" s="20">
@@ -17522,7 +17522,7 @@
         <v/>
       </c>
       <c r="C68" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A68,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A68,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A68,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A68,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D68" s="31">
@@ -17538,7 +17538,7 @@
         <v/>
       </c>
       <c r="G68" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A68,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A68,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A68,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A68,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H68" s="30">
@@ -17571,7 +17571,7 @@
         <v/>
       </c>
       <c r="C69" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A69,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A69,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A69,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A69,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D69" s="18">
@@ -17587,7 +17587,7 @@
         <v/>
       </c>
       <c r="G69" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A69,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A69,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A69,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A69,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H69" s="20">
@@ -17620,7 +17620,7 @@
         <v/>
       </c>
       <c r="C70" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A70,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A70,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A70,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A70,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D70" s="31">
@@ -17636,7 +17636,7 @@
         <v/>
       </c>
       <c r="G70" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A70,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A70,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A70,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A70,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H70" s="30">
@@ -17669,7 +17669,7 @@
         <v/>
       </c>
       <c r="C71" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A71,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A71,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A71,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A71,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D71" s="18">
@@ -17685,7 +17685,7 @@
         <v/>
       </c>
       <c r="G71" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A71,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A71,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A71,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A71,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H71" s="20">
@@ -17718,7 +17718,7 @@
         <v/>
       </c>
       <c r="C72" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A72,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A72,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A72,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A72,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D72" s="31">
@@ -17734,7 +17734,7 @@
         <v/>
       </c>
       <c r="G72" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A72,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A72,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A72,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A72,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H72" s="30">
@@ -17767,7 +17767,7 @@
         <v/>
       </c>
       <c r="C73" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A73,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A73,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A73,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A73,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D73" s="18">
@@ -17783,7 +17783,7 @@
         <v/>
       </c>
       <c r="G73" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A73,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A73,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A73,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A73,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H73" s="20">
@@ -17816,7 +17816,7 @@
         <v/>
       </c>
       <c r="C74" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A74,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A74,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A74,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A74,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D74" s="31">
@@ -17832,7 +17832,7 @@
         <v/>
       </c>
       <c r="G74" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A74,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A74,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A74,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A74,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H74" s="30">
@@ -17865,7 +17865,7 @@
         <v/>
       </c>
       <c r="C75" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A75,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A75,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A75,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A75,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D75" s="18">
@@ -17881,7 +17881,7 @@
         <v/>
       </c>
       <c r="G75" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A75,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A75,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A75,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A75,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H75" s="20">
@@ -17914,7 +17914,7 @@
         <v/>
       </c>
       <c r="C76" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A76,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A76,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A76,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A76,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D76" s="31">
@@ -17930,7 +17930,7 @@
         <v/>
       </c>
       <c r="G76" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A76,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A76,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A76,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A76,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H76" s="30">
@@ -17963,7 +17963,7 @@
         <v/>
       </c>
       <c r="C77" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A77,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A77,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A77,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A77,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D77" s="18">
@@ -17979,7 +17979,7 @@
         <v/>
       </c>
       <c r="G77" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A77,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A77,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A77,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A77,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H77" s="20">
@@ -18012,7 +18012,7 @@
         <v/>
       </c>
       <c r="C78" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A78,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A78,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A78,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A78,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D78" s="31">
@@ -18028,7 +18028,7 @@
         <v/>
       </c>
       <c r="G78" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A78,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A78,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A78,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A78,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H78" s="30">
@@ -18061,7 +18061,7 @@
         <v/>
       </c>
       <c r="C79" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A79,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A79,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A79,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A79,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D79" s="18">
@@ -18077,7 +18077,7 @@
         <v/>
       </c>
       <c r="G79" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A79,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A79,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A79,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A79,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H79" s="20">
@@ -18110,7 +18110,7 @@
         <v/>
       </c>
       <c r="C80" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A80,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A80,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A80,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A80,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D80" s="31">
@@ -18126,7 +18126,7 @@
         <v/>
       </c>
       <c r="G80" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A80,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A80,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A80,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A80,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H80" s="30">
@@ -18159,7 +18159,7 @@
         <v/>
       </c>
       <c r="C81" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A81,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A81,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A81,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A81,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D81" s="18">
@@ -18175,7 +18175,7 @@
         <v/>
       </c>
       <c r="G81" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A81,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A81,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A81,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A81,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H81" s="20">
@@ -18208,7 +18208,7 @@
         <v/>
       </c>
       <c r="C82" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A82,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A82,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A82,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A82,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D82" s="31">
@@ -18224,7 +18224,7 @@
         <v/>
       </c>
       <c r="G82" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A82,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A82,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A82,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A82,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H82" s="30">
@@ -18257,7 +18257,7 @@
         <v/>
       </c>
       <c r="C83" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A83,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A83,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A83,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A83,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D83" s="18">
@@ -18273,7 +18273,7 @@
         <v/>
       </c>
       <c r="G83" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A83,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A83,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A83,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A83,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H83" s="20">
@@ -18306,7 +18306,7 @@
         <v/>
       </c>
       <c r="C84" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A84,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A84,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A84,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A84,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D84" s="31">
@@ -18322,7 +18322,7 @@
         <v/>
       </c>
       <c r="G84" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A84,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A84,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A84,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A84,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H84" s="30">
@@ -18355,7 +18355,7 @@
         <v/>
       </c>
       <c r="C85" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A85,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A85,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A85,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A85,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D85" s="18">
@@ -18371,7 +18371,7 @@
         <v/>
       </c>
       <c r="G85" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A85,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A85,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A85,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A85,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H85" s="20">
@@ -18404,7 +18404,7 @@
         <v/>
       </c>
       <c r="C86" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A86,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A86,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A86,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A86,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D86" s="31">
@@ -18420,7 +18420,7 @@
         <v/>
       </c>
       <c r="G86" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A86,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A86,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A86,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A86,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H86" s="30">
@@ -18453,7 +18453,7 @@
         <v/>
       </c>
       <c r="C87" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A87,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A87,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A87,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A87,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D87" s="18">
@@ -18469,7 +18469,7 @@
         <v/>
       </c>
       <c r="G87" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A87,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A87,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A87,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A87,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H87" s="20">
@@ -18502,7 +18502,7 @@
         <v/>
       </c>
       <c r="C88" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A88,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A88,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A88,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A88,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D88" s="31">
@@ -18518,7 +18518,7 @@
         <v/>
       </c>
       <c r="G88" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A88,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A88,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A88,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A88,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H88" s="30">
@@ -18551,7 +18551,7 @@
         <v/>
       </c>
       <c r="C89" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A89,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A89,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A89,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A89,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D89" s="18">
@@ -18567,7 +18567,7 @@
         <v/>
       </c>
       <c r="G89" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A89,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A89,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A89,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A89,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H89" s="20">
@@ -18600,7 +18600,7 @@
         <v/>
       </c>
       <c r="C90" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A90,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A90,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A90,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A90,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D90" s="31">
@@ -18616,7 +18616,7 @@
         <v/>
       </c>
       <c r="G90" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A90,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A90,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A90,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A90,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H90" s="30">
@@ -18649,7 +18649,7 @@
         <v/>
       </c>
       <c r="C91" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A91,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A91,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A91,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A91,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D91" s="18">
@@ -18665,7 +18665,7 @@
         <v/>
       </c>
       <c r="G91" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A91,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A91,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A91,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A91,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H91" s="20">
@@ -18698,7 +18698,7 @@
         <v/>
       </c>
       <c r="C92" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A92,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A92,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A92,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A92,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D92" s="31">
@@ -18714,7 +18714,7 @@
         <v/>
       </c>
       <c r="G92" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A92,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A92,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A92,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A92,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H92" s="30">
@@ -18747,7 +18747,7 @@
         <v/>
       </c>
       <c r="C93" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A93,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A93,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A93,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A93,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D93" s="18">
@@ -18763,7 +18763,7 @@
         <v/>
       </c>
       <c r="G93" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A93,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A93,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A93,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A93,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H93" s="20">
@@ -18796,7 +18796,7 @@
         <v/>
       </c>
       <c r="C94" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A94,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A94,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A94,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A94,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D94" s="31">
@@ -18812,7 +18812,7 @@
         <v/>
       </c>
       <c r="G94" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A94,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A94,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A94,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A94,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H94" s="30">
@@ -18845,7 +18845,7 @@
         <v/>
       </c>
       <c r="C95" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A95,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A95,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A95,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A95,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D95" s="18">
@@ -18861,7 +18861,7 @@
         <v/>
       </c>
       <c r="G95" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A95,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A95,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A95,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A95,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H95" s="20">
@@ -18894,7 +18894,7 @@
         <v/>
       </c>
       <c r="C96" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A96,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A96,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A96,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A96,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D96" s="31">
@@ -18910,7 +18910,7 @@
         <v/>
       </c>
       <c r="G96" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A96,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A96,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A96,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A96,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H96" s="30">
@@ -18943,7 +18943,7 @@
         <v/>
       </c>
       <c r="C97" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A97,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A97,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A97,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A97,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D97" s="18">
@@ -18959,7 +18959,7 @@
         <v/>
       </c>
       <c r="G97" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A97,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A97,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A97,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A97,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H97" s="20">
@@ -18992,7 +18992,7 @@
         <v/>
       </c>
       <c r="C98" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A98,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A98,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A98,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A98,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D98" s="31">
@@ -19008,7 +19008,7 @@
         <v/>
       </c>
       <c r="G98" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A98,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A98,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A98,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A98,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H98" s="30">
@@ -19041,7 +19041,7 @@
         <v/>
       </c>
       <c r="C99" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A99,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A99,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A99,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A99,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D99" s="18">
@@ -19057,7 +19057,7 @@
         <v/>
       </c>
       <c r="G99" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A99,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A99,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A99,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A99,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H99" s="20">
@@ -19090,7 +19090,7 @@
         <v/>
       </c>
       <c r="C100" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A100,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A100,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A100,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A100,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D100" s="31">
@@ -19106,7 +19106,7 @@
         <v/>
       </c>
       <c r="G100" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A100,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A100,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A100,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A100,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H100" s="30">
@@ -19139,7 +19139,7 @@
         <v/>
       </c>
       <c r="C101" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A101,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A101,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A101,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A101,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D101" s="18">
@@ -19155,7 +19155,7 @@
         <v/>
       </c>
       <c r="G101" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A101,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A101,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A101,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A101,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H101" s="20">
@@ -19188,7 +19188,7 @@
         <v/>
       </c>
       <c r="C102" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A102,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A102,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A102,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A102,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D102" s="31">
@@ -19204,7 +19204,7 @@
         <v/>
       </c>
       <c r="G102" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A102,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A102,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A102,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A102,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H102" s="30">
@@ -19237,7 +19237,7 @@
         <v/>
       </c>
       <c r="C103" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A103,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A103,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A103,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A103,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D103" s="18">
@@ -19253,7 +19253,7 @@
         <v/>
       </c>
       <c r="G103" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A103,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A103,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A103,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A103,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H103" s="20">
@@ -19286,7 +19286,7 @@
         <v/>
       </c>
       <c r="C104" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A104,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A104,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A104,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A104,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D104" s="31">
@@ -19302,7 +19302,7 @@
         <v/>
       </c>
       <c r="G104" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A104,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A104,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A104,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A104,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H104" s="30">
@@ -19335,7 +19335,7 @@
         <v/>
       </c>
       <c r="C105" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A105,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A105,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A105,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A105,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D105" s="18">
@@ -19351,7 +19351,7 @@
         <v/>
       </c>
       <c r="G105" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A105,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A105,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A105,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A105,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H105" s="20">
@@ -19384,7 +19384,7 @@
         <v/>
       </c>
       <c r="C106" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A106,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A106,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A106,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A106,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D106" s="31">
@@ -19400,7 +19400,7 @@
         <v/>
       </c>
       <c r="G106" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A106,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A106,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A106,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A106,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H106" s="30">
@@ -19433,7 +19433,7 @@
         <v/>
       </c>
       <c r="C107" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A107,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A107,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A107,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A107,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D107" s="18">
@@ -19449,7 +19449,7 @@
         <v/>
       </c>
       <c r="G107" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A107,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A107,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A107,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A107,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H107" s="20">
@@ -19482,7 +19482,7 @@
         <v/>
       </c>
       <c r="C108" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A108,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A108,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A108,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A108,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D108" s="31">
@@ -19498,7 +19498,7 @@
         <v/>
       </c>
       <c r="G108" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A108,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A108,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A108,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A108,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H108" s="30">
@@ -19531,7 +19531,7 @@
         <v/>
       </c>
       <c r="C109" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A109,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A109,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A109,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A109,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D109" s="18">
@@ -19547,7 +19547,7 @@
         <v/>
       </c>
       <c r="G109" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A109,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A109,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A109,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A109,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H109" s="20">
@@ -19580,7 +19580,7 @@
         <v/>
       </c>
       <c r="C110" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A110,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A110,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A110,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A110,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D110" s="31">
@@ -19596,7 +19596,7 @@
         <v/>
       </c>
       <c r="G110" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A110,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A110,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A110,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A110,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H110" s="30">
@@ -19629,7 +19629,7 @@
         <v/>
       </c>
       <c r="C111" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A111,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A111,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A111,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A111,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D111" s="18">
@@ -19645,7 +19645,7 @@
         <v/>
       </c>
       <c r="G111" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A111,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A111,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A111,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A111,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H111" s="20">
@@ -19678,7 +19678,7 @@
         <v/>
       </c>
       <c r="C112" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A112,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A112,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A112,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A112,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D112" s="31">
@@ -19694,7 +19694,7 @@
         <v/>
       </c>
       <c r="G112" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A112,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A112,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A112,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A112,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H112" s="30">
@@ -19727,7 +19727,7 @@
         <v/>
       </c>
       <c r="C113" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A113,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A113,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A113,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A113,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D113" s="18">
@@ -19743,7 +19743,7 @@
         <v/>
       </c>
       <c r="G113" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A113,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A113,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A113,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A113,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H113" s="20">
@@ -19776,7 +19776,7 @@
         <v/>
       </c>
       <c r="C114" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A114,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A114,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A114,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A114,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D114" s="31">
@@ -19792,7 +19792,7 @@
         <v/>
       </c>
       <c r="G114" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A114,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A114,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A114,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A114,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H114" s="30">
@@ -19825,7 +19825,7 @@
         <v/>
       </c>
       <c r="C115" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A115,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A115,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A115,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A115,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D115" s="18">
@@ -19841,7 +19841,7 @@
         <v/>
       </c>
       <c r="G115" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A115,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A115,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A115,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A115,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H115" s="20">
@@ -19874,7 +19874,7 @@
         <v/>
       </c>
       <c r="C116" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A116,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A116,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A116,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A116,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D116" s="31">
@@ -19890,7 +19890,7 @@
         <v/>
       </c>
       <c r="G116" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A116,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A116,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A116,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A116,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H116" s="30">
@@ -19923,7 +19923,7 @@
         <v/>
       </c>
       <c r="C117" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A117,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A117,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A117,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A117,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D117" s="18">
@@ -19939,7 +19939,7 @@
         <v/>
       </c>
       <c r="G117" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A117,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A117,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A117,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A117,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H117" s="20">
@@ -19972,7 +19972,7 @@
         <v/>
       </c>
       <c r="C118" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A118,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A118,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A118,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A118,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D118" s="31">
@@ -19988,7 +19988,7 @@
         <v/>
       </c>
       <c r="G118" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A118,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A118,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A118,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A118,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H118" s="30">
@@ -20021,7 +20021,7 @@
         <v/>
       </c>
       <c r="C119" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A119,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A119,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A119,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A119,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D119" s="18">
@@ -20037,7 +20037,7 @@
         <v/>
       </c>
       <c r="G119" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A119,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A119,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A119,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A119,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H119" s="20">
@@ -20070,7 +20070,7 @@
         <v/>
       </c>
       <c r="C120" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A120,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A120,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A120,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A120,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D120" s="31">
@@ -20086,7 +20086,7 @@
         <v/>
       </c>
       <c r="G120" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A120,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A120,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A120,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A120,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H120" s="30">
@@ -20119,7 +20119,7 @@
         <v/>
       </c>
       <c r="C121" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A121,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A121,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A121,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A121,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D121" s="18">
@@ -20135,7 +20135,7 @@
         <v/>
       </c>
       <c r="G121" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A121,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A121,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A121,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A121,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H121" s="20">
@@ -20168,7 +20168,7 @@
         <v/>
       </c>
       <c r="C122" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A122,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A122,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A122,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A122,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D122" s="31">
@@ -20184,7 +20184,7 @@
         <v/>
       </c>
       <c r="G122" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A122,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A122,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A122,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A122,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H122" s="30">
@@ -20217,7 +20217,7 @@
         <v/>
       </c>
       <c r="C123" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A123,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A123,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A123,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A123,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D123" s="18">
@@ -20233,7 +20233,7 @@
         <v/>
       </c>
       <c r="G123" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A123,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A123,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A123,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A123,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H123" s="20">
@@ -20266,7 +20266,7 @@
         <v/>
       </c>
       <c r="C124" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A124,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A124,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A124,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A124,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D124" s="31">
@@ -20282,7 +20282,7 @@
         <v/>
       </c>
       <c r="G124" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A124,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A124,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A124,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A124,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H124" s="30">
@@ -20315,7 +20315,7 @@
         <v/>
       </c>
       <c r="C125" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A125,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A125,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A125,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A125,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D125" s="18">
@@ -20331,7 +20331,7 @@
         <v/>
       </c>
       <c r="G125" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A125,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A125,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A125,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A125,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H125" s="20">
@@ -20364,7 +20364,7 @@
         <v/>
       </c>
       <c r="C126" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A126,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A126,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A126,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A126,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D126" s="31">
@@ -20380,7 +20380,7 @@
         <v/>
       </c>
       <c r="G126" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A126,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A126,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A126,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A126,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H126" s="30">
@@ -20413,7 +20413,7 @@
         <v/>
       </c>
       <c r="C127" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A127,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A127,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A127,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A127,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D127" s="18">
@@ -20429,7 +20429,7 @@
         <v/>
       </c>
       <c r="G127" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A127,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A127,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A127,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A127,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H127" s="20">
@@ -20462,7 +20462,7 @@
         <v/>
       </c>
       <c r="C128" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A128,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A128,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A128,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A128,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D128" s="31">
@@ -20478,7 +20478,7 @@
         <v/>
       </c>
       <c r="G128" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A128,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A128,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A128,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A128,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H128" s="30">
@@ -20511,7 +20511,7 @@
         <v/>
       </c>
       <c r="C129" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A129,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A129,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A129,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A129,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D129" s="18">
@@ -20527,7 +20527,7 @@
         <v/>
       </c>
       <c r="G129" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A129,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A129,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A129,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A129,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H129" s="20">
@@ -20560,7 +20560,7 @@
         <v/>
       </c>
       <c r="C130" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A130,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A130,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A130,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A130,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D130" s="31">
@@ -20576,7 +20576,7 @@
         <v/>
       </c>
       <c r="G130" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A130,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A130,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A130,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A130,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H130" s="30">
@@ -20609,7 +20609,7 @@
         <v/>
       </c>
       <c r="C131" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A131,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A131,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A131,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A131,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D131" s="18">
@@ -20625,7 +20625,7 @@
         <v/>
       </c>
       <c r="G131" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A131,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A131,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A131,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A131,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H131" s="20">
@@ -20658,7 +20658,7 @@
         <v/>
       </c>
       <c r="C132" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A132,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A132,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A132,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A132,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D132" s="31">
@@ -20674,7 +20674,7 @@
         <v/>
       </c>
       <c r="G132" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A132,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A132,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A132,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A132,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H132" s="30">
@@ -20707,7 +20707,7 @@
         <v/>
       </c>
       <c r="C133" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A133,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A133,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A133,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A133,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D133" s="18">
@@ -20723,7 +20723,7 @@
         <v/>
       </c>
       <c r="G133" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A133,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A133,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A133,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A133,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H133" s="20">
@@ -20756,7 +20756,7 @@
         <v/>
       </c>
       <c r="C134" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A134,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A134,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A134,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A134,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D134" s="31">
@@ -20772,7 +20772,7 @@
         <v/>
       </c>
       <c r="G134" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A134,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A134,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A134,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A134,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H134" s="30">
@@ -20805,7 +20805,7 @@
         <v/>
       </c>
       <c r="C135" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A135,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A135,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A135,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A135,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D135" s="18">
@@ -20821,7 +20821,7 @@
         <v/>
       </c>
       <c r="G135" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A135,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A135,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A135,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A135,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H135" s="20">
@@ -20854,7 +20854,7 @@
         <v/>
       </c>
       <c r="C136" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A136,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A136,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A136,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A136,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D136" s="31">
@@ -20870,7 +20870,7 @@
         <v/>
       </c>
       <c r="G136" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A136,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A136,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A136,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A136,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H136" s="30">
@@ -20903,7 +20903,7 @@
         <v/>
       </c>
       <c r="C137" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A137,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A137,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A137,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A137,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D137" s="18">
@@ -20919,7 +20919,7 @@
         <v/>
       </c>
       <c r="G137" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A137,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A137,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A137,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A137,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H137" s="20">
@@ -20952,7 +20952,7 @@
         <v/>
       </c>
       <c r="C138" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A138,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A138,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A138,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A138,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D138" s="31">
@@ -20968,7 +20968,7 @@
         <v/>
       </c>
       <c r="G138" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A138,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A138,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A138,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A138,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H138" s="30">
@@ -21001,7 +21001,7 @@
         <v/>
       </c>
       <c r="C139" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A139,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A139,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A139,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A139,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D139" s="18">
@@ -21017,7 +21017,7 @@
         <v/>
       </c>
       <c r="G139" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A139,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A139,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A139,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A139,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H139" s="20">
@@ -21050,7 +21050,7 @@
         <v/>
       </c>
       <c r="C140" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A140,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A140,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A140,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A140,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D140" s="31">
@@ -21066,7 +21066,7 @@
         <v/>
       </c>
       <c r="G140" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A140,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A140,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A140,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A140,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H140" s="30">
@@ -21099,7 +21099,7 @@
         <v/>
       </c>
       <c r="C141" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A141,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A141,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A141,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A141,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D141" s="18">
@@ -21115,7 +21115,7 @@
         <v/>
       </c>
       <c r="G141" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A141,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A141,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A141,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A141,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H141" s="20">
@@ -21148,7 +21148,7 @@
         <v/>
       </c>
       <c r="C142" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A142,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A142,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A142,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A142,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D142" s="31">
@@ -21164,7 +21164,7 @@
         <v/>
       </c>
       <c r="G142" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A142,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A142,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A142,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A142,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H142" s="30">
@@ -21197,7 +21197,7 @@
         <v/>
       </c>
       <c r="C143" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A143,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A143,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A143,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A143,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D143" s="18">
@@ -21213,7 +21213,7 @@
         <v/>
       </c>
       <c r="G143" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A143,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A143,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A143,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A143,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H143" s="20">
@@ -21246,7 +21246,7 @@
         <v/>
       </c>
       <c r="C144" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A144,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A144,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A144,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A144,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D144" s="31">
@@ -21262,7 +21262,7 @@
         <v/>
       </c>
       <c r="G144" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A144,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A144,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A144,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A144,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H144" s="30">
@@ -21295,7 +21295,7 @@
         <v/>
       </c>
       <c r="C145" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A145,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A145,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A145,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A145,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D145" s="18">
@@ -21311,7 +21311,7 @@
         <v/>
       </c>
       <c r="G145" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A145,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A145,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A145,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A145,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H145" s="20">
@@ -21344,7 +21344,7 @@
         <v/>
       </c>
       <c r="C146" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A146,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A146,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A146,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A146,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D146" s="31">
@@ -21360,7 +21360,7 @@
         <v/>
       </c>
       <c r="G146" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A146,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A146,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A146,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A146,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H146" s="30">
@@ -21393,7 +21393,7 @@
         <v/>
       </c>
       <c r="C147" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A147,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A147,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A147,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A147,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D147" s="18">
@@ -21409,7 +21409,7 @@
         <v/>
       </c>
       <c r="G147" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A147,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A147,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A147,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A147,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H147" s="20">
@@ -21442,7 +21442,7 @@
         <v/>
       </c>
       <c r="C148" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A148,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A148,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A148,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A148,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D148" s="31">
@@ -21458,7 +21458,7 @@
         <v/>
       </c>
       <c r="G148" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A148,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A148,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A148,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A148,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H148" s="30">
@@ -21491,7 +21491,7 @@
         <v/>
       </c>
       <c r="C149" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A149,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A149,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A149,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A149,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D149" s="18">
@@ -21507,7 +21507,7 @@
         <v/>
       </c>
       <c r="G149" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A149,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A149,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A149,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A149,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H149" s="20">
@@ -21540,7 +21540,7 @@
         <v/>
       </c>
       <c r="C150" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A150,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A150,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A150,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A150,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D150" s="31">
@@ -21556,7 +21556,7 @@
         <v/>
       </c>
       <c r="G150" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A150,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A150,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A150,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A150,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H150" s="30">
@@ -21589,7 +21589,7 @@
         <v/>
       </c>
       <c r="C151" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A151,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A151,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A151,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A151,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D151" s="18">
@@ -21605,7 +21605,7 @@
         <v/>
       </c>
       <c r="G151" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A151,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A151,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A151,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A151,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H151" s="20">
@@ -21638,7 +21638,7 @@
         <v/>
       </c>
       <c r="C152" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A152,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A152,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A152,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A152,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D152" s="31">
@@ -21654,7 +21654,7 @@
         <v/>
       </c>
       <c r="G152" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A152,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A152,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A152,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A152,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H152" s="30">
@@ -21687,7 +21687,7 @@
         <v/>
       </c>
       <c r="C153" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A153,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A153,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A153,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A153,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D153" s="18">
@@ -21703,7 +21703,7 @@
         <v/>
       </c>
       <c r="G153" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A153,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A153,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A153,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A153,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H153" s="20">
@@ -21736,7 +21736,7 @@
         <v/>
       </c>
       <c r="C154" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A154,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A154,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A154,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A154,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D154" s="31">
@@ -21752,7 +21752,7 @@
         <v/>
       </c>
       <c r="G154" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A154,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A154,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A154,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A154,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H154" s="30">
@@ -21785,7 +21785,7 @@
         <v/>
       </c>
       <c r="C155" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A155,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A155,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A155,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A155,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D155" s="18">
@@ -21801,7 +21801,7 @@
         <v/>
       </c>
       <c r="G155" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A155,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A155,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A155,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A155,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H155" s="20">
@@ -21834,7 +21834,7 @@
         <v/>
       </c>
       <c r="C156" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A156,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A156,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A156,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A156,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D156" s="31">
@@ -21850,7 +21850,7 @@
         <v/>
       </c>
       <c r="G156" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A156,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A156,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A156,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A156,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H156" s="30">
@@ -21883,7 +21883,7 @@
         <v/>
       </c>
       <c r="C157" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A157,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A157,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A157,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A157,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D157" s="18">
@@ -21899,7 +21899,7 @@
         <v/>
       </c>
       <c r="G157" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A157,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A157,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A157,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A157,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H157" s="20">
@@ -21932,7 +21932,7 @@
         <v/>
       </c>
       <c r="C158" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A158,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A158,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A158,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A158,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D158" s="31">
@@ -21948,7 +21948,7 @@
         <v/>
       </c>
       <c r="G158" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A158,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A158,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A158,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A158,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H158" s="30">
@@ -21981,7 +21981,7 @@
         <v/>
       </c>
       <c r="C159" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A159,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A159,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A159,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A159,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D159" s="18">
@@ -21997,7 +21997,7 @@
         <v/>
       </c>
       <c r="G159" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A159,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A159,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A159,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A159,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H159" s="20">
@@ -22030,7 +22030,7 @@
         <v/>
       </c>
       <c r="C160" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A160,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A160,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A160,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A160,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D160" s="31">
@@ -22046,7 +22046,7 @@
         <v/>
       </c>
       <c r="G160" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A160,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A160,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A160,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A160,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H160" s="30">
@@ -22079,7 +22079,7 @@
         <v/>
       </c>
       <c r="C161" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A161,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A161,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A161,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A161,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D161" s="18">
@@ -22095,7 +22095,7 @@
         <v/>
       </c>
       <c r="G161" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A161,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A161,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A161,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A161,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H161" s="20">
@@ -22128,7 +22128,7 @@
         <v/>
       </c>
       <c r="C162" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A162,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A162,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A162,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A162,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D162" s="31">
@@ -22144,7 +22144,7 @@
         <v/>
       </c>
       <c r="G162" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A162,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A162,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A162,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A162,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H162" s="30">
@@ -22177,7 +22177,7 @@
         <v/>
       </c>
       <c r="C163" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A163,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A163,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A163,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A163,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D163" s="18">
@@ -22193,7 +22193,7 @@
         <v/>
       </c>
       <c r="G163" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A163,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A163,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A163,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A163,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H163" s="20">
@@ -22226,7 +22226,7 @@
         <v/>
       </c>
       <c r="C164" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A164,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A164,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A164,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A164,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D164" s="31">
@@ -22242,7 +22242,7 @@
         <v/>
       </c>
       <c r="G164" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A164,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A164,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A164,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A164,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H164" s="30">
@@ -22275,7 +22275,7 @@
         <v/>
       </c>
       <c r="C165" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A165,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A165,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A165,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A165,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D165" s="18">
@@ -22291,7 +22291,7 @@
         <v/>
       </c>
       <c r="G165" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A165,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A165,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A165,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A165,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H165" s="20">
@@ -22324,7 +22324,7 @@
         <v/>
       </c>
       <c r="C166" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A166,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A166,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A166,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A166,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D166" s="31">
@@ -22340,7 +22340,7 @@
         <v/>
       </c>
       <c r="G166" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A166,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A166,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A166,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A166,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H166" s="30">
@@ -22373,7 +22373,7 @@
         <v/>
       </c>
       <c r="C167" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A167,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A167,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A167,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A167,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D167" s="18">
@@ -22389,7 +22389,7 @@
         <v/>
       </c>
       <c r="G167" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A167,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A167,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A167,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A167,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H167" s="20">
@@ -22422,7 +22422,7 @@
         <v/>
       </c>
       <c r="C168" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A168,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A168,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A168,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A168,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D168" s="31">
@@ -22438,7 +22438,7 @@
         <v/>
       </c>
       <c r="G168" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A168,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A168,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A168,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A168,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H168" s="30">
@@ -22471,7 +22471,7 @@
         <v/>
       </c>
       <c r="C169" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A169,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A169,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A169,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A169,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D169" s="18">
@@ -22487,7 +22487,7 @@
         <v/>
       </c>
       <c r="G169" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A169,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A169,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A169,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A169,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H169" s="20">
@@ -22520,7 +22520,7 @@
         <v/>
       </c>
       <c r="C170" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A170,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A170,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A170,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A170,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D170" s="31">
@@ -22536,7 +22536,7 @@
         <v/>
       </c>
       <c r="G170" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A170,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A170,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A170,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A170,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H170" s="30">
@@ -22569,7 +22569,7 @@
         <v/>
       </c>
       <c r="C171" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A171,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A171,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A171,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A171,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D171" s="18">
@@ -22585,7 +22585,7 @@
         <v/>
       </c>
       <c r="G171" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A171,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A171,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A171,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A171,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H171" s="20">
@@ -22618,7 +22618,7 @@
         <v/>
       </c>
       <c r="C172" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A172,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A172,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A172,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A172,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D172" s="31">
@@ -22634,7 +22634,7 @@
         <v/>
       </c>
       <c r="G172" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A172,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A172,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A172,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A172,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H172" s="30">
@@ -22667,7 +22667,7 @@
         <v/>
       </c>
       <c r="C173" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A173,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A173,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A173,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A173,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D173" s="18">
@@ -22683,7 +22683,7 @@
         <v/>
       </c>
       <c r="G173" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A173,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A173,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A173,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A173,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H173" s="20">
@@ -22716,7 +22716,7 @@
         <v/>
       </c>
       <c r="C174" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A174,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A174,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A174,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A174,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D174" s="31">
@@ -22732,7 +22732,7 @@
         <v/>
       </c>
       <c r="G174" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A174,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A174,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A174,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A174,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H174" s="30">
@@ -22765,7 +22765,7 @@
         <v/>
       </c>
       <c r="C175" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A175,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A175,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A175,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A175,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D175" s="18">
@@ -22781,7 +22781,7 @@
         <v/>
       </c>
       <c r="G175" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A175,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A175,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A175,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A175,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H175" s="20">
@@ -22814,7 +22814,7 @@
         <v/>
       </c>
       <c r="C176" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A176,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A176,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A176,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A176,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D176" s="31">
@@ -22830,7 +22830,7 @@
         <v/>
       </c>
       <c r="G176" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A176,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A176,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A176,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A176,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H176" s="30">
@@ -22863,7 +22863,7 @@
         <v/>
       </c>
       <c r="C177" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A177,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A177,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A177,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A177,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D177" s="18">
@@ -22879,7 +22879,7 @@
         <v/>
       </c>
       <c r="G177" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A177,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A177,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A177,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A177,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H177" s="20">
@@ -22912,7 +22912,7 @@
         <v/>
       </c>
       <c r="C178" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A178,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A178,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A178,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A178,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D178" s="31">
@@ -22928,7 +22928,7 @@
         <v/>
       </c>
       <c r="G178" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A178,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A178,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A178,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A178,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H178" s="30">
@@ -22961,7 +22961,7 @@
         <v/>
       </c>
       <c r="C179" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A179,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A179,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A179,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A179,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D179" s="18">
@@ -22977,7 +22977,7 @@
         <v/>
       </c>
       <c r="G179" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A179,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A179,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A179,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A179,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H179" s="20">
@@ -23010,7 +23010,7 @@
         <v/>
       </c>
       <c r="C180" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A180,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A180,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A180,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A180,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D180" s="31">
@@ -23026,7 +23026,7 @@
         <v/>
       </c>
       <c r="G180" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A180,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A180,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A180,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A180,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H180" s="30">
@@ -23059,7 +23059,7 @@
         <v/>
       </c>
       <c r="C181" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A181,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A181,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A181,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A181,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D181" s="18">
@@ -23075,7 +23075,7 @@
         <v/>
       </c>
       <c r="G181" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A181,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A181,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A181,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A181,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H181" s="20">
@@ -23108,7 +23108,7 @@
         <v/>
       </c>
       <c r="C182" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A182,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A182,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A182,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A182,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D182" s="31">
@@ -23124,7 +23124,7 @@
         <v/>
       </c>
       <c r="G182" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A182,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A182,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A182,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A182,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H182" s="30">
@@ -23157,7 +23157,7 @@
         <v/>
       </c>
       <c r="C183" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A183,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A183,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A183,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A183,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D183" s="18">
@@ -23173,7 +23173,7 @@
         <v/>
       </c>
       <c r="G183" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A183,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A183,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A183,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A183,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H183" s="20">
@@ -23206,7 +23206,7 @@
         <v/>
       </c>
       <c r="C184" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A184,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A184,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A184,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A184,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D184" s="31">
@@ -23222,7 +23222,7 @@
         <v/>
       </c>
       <c r="G184" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A184,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A184,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A184,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A184,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H184" s="30">
@@ -23255,7 +23255,7 @@
         <v/>
       </c>
       <c r="C185" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A185,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A185,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A185,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A185,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D185" s="18">
@@ -23271,7 +23271,7 @@
         <v/>
       </c>
       <c r="G185" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A185,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A185,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A185,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A185,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H185" s="20">
@@ -23304,7 +23304,7 @@
         <v/>
       </c>
       <c r="C186" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A186,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A186,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A186,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A186,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D186" s="31">
@@ -23320,7 +23320,7 @@
         <v/>
       </c>
       <c r="G186" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A186,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A186,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A186,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A186,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H186" s="30">
@@ -23353,7 +23353,7 @@
         <v/>
       </c>
       <c r="C187" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A187,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A187,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A187,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A187,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D187" s="18">
@@ -23369,7 +23369,7 @@
         <v/>
       </c>
       <c r="G187" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A187,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A187,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A187,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A187,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H187" s="20">
@@ -23402,7 +23402,7 @@
         <v/>
       </c>
       <c r="C188" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A188,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A188,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A188,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A188,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D188" s="31">
@@ -23418,7 +23418,7 @@
         <v/>
       </c>
       <c r="G188" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A188,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A188,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A188,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A188,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H188" s="30">
@@ -23451,7 +23451,7 @@
         <v/>
       </c>
       <c r="C189" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A189,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A189,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A189,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A189,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D189" s="18">
@@ -23467,7 +23467,7 @@
         <v/>
       </c>
       <c r="G189" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A189,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A189,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A189,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A189,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H189" s="20">
@@ -23500,7 +23500,7 @@
         <v/>
       </c>
       <c r="C190" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A190,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A190,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A190,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A190,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D190" s="31">
@@ -23516,7 +23516,7 @@
         <v/>
       </c>
       <c r="G190" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A190,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A190,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A190,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A190,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H190" s="30">
@@ -23549,7 +23549,7 @@
         <v/>
       </c>
       <c r="C191" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A191,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A191,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A191,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A191,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D191" s="18">
@@ -23565,7 +23565,7 @@
         <v/>
       </c>
       <c r="G191" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A191,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A191,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A191,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A191,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H191" s="20">
@@ -23598,7 +23598,7 @@
         <v/>
       </c>
       <c r="C192" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A192,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A192,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A192,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A192,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D192" s="31">
@@ -23614,7 +23614,7 @@
         <v/>
       </c>
       <c r="G192" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A192,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A192,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A192,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A192,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H192" s="30">
@@ -23647,7 +23647,7 @@
         <v/>
       </c>
       <c r="C193" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A193,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A193,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A193,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A193,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D193" s="18">
@@ -23663,7 +23663,7 @@
         <v/>
       </c>
       <c r="G193" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A193,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A193,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A193,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A193,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H193" s="20">
@@ -23696,7 +23696,7 @@
         <v/>
       </c>
       <c r="C194" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A194,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A194,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A194,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A194,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D194" s="31">
@@ -23712,7 +23712,7 @@
         <v/>
       </c>
       <c r="G194" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A194,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A194,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A194,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A194,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H194" s="30">
@@ -23745,7 +23745,7 @@
         <v/>
       </c>
       <c r="C195" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A195,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A195,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A195,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A195,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D195" s="18">
@@ -23761,7 +23761,7 @@
         <v/>
       </c>
       <c r="G195" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A195,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A195,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A195,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A195,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H195" s="20">
@@ -23794,7 +23794,7 @@
         <v/>
       </c>
       <c r="C196" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A196,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A196,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A196,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A196,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D196" s="31">
@@ -23810,7 +23810,7 @@
         <v/>
       </c>
       <c r="G196" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A196,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A196,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A196,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A196,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H196" s="30">
@@ -23843,7 +23843,7 @@
         <v/>
       </c>
       <c r="C197" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A197,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A197,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A197,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A197,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D197" s="18">
@@ -23859,7 +23859,7 @@
         <v/>
       </c>
       <c r="G197" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A197,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A197,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A197,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A197,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H197" s="20">
@@ -23892,7 +23892,7 @@
         <v/>
       </c>
       <c r="C198" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A198,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A198,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A198,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A198,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D198" s="31">
@@ -23908,7 +23908,7 @@
         <v/>
       </c>
       <c r="G198" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A198,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A198,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A198,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A198,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H198" s="30">
@@ -23941,7 +23941,7 @@
         <v/>
       </c>
       <c r="C199" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A199,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A199,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A199,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A199,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D199" s="18">
@@ -23957,7 +23957,7 @@
         <v/>
       </c>
       <c r="G199" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A199,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A199,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A199,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A199,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H199" s="20">
@@ -23990,7 +23990,7 @@
         <v/>
       </c>
       <c r="C200" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A200,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A200,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A200,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A200,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D200" s="31">
@@ -24006,7 +24006,7 @@
         <v/>
       </c>
       <c r="G200" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A200,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A200,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A200,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A200,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H200" s="30">
@@ -24039,7 +24039,7 @@
         <v/>
       </c>
       <c r="C201" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A201,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A201,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A201,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A201,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D201" s="18">
@@ -24055,7 +24055,7 @@
         <v/>
       </c>
       <c r="G201" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A201,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A201,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A201,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A201,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H201" s="20">
@@ -24088,7 +24088,7 @@
         <v/>
       </c>
       <c r="C202" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A202,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A202,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A202,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A202,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D202" s="31">
@@ -24104,7 +24104,7 @@
         <v/>
       </c>
       <c r="G202" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A202,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A202,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A202,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A202,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H202" s="30">
@@ -24137,7 +24137,7 @@
         <v/>
       </c>
       <c r="C203" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A203,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A203,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A203,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A203,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D203" s="18">
@@ -24153,7 +24153,7 @@
         <v/>
       </c>
       <c r="G203" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A203,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A203,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A203,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A203,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H203" s="20">
@@ -24186,7 +24186,7 @@
         <v/>
       </c>
       <c r="C204" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A204,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A204,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A204,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A204,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D204" s="31">
@@ -24202,7 +24202,7 @@
         <v/>
       </c>
       <c r="G204" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A204,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A204,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A204,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A204,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H204" s="30">
@@ -24235,7 +24235,7 @@
         <v/>
       </c>
       <c r="C205" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A205,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A205,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A205,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A205,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D205" s="18">
@@ -24251,7 +24251,7 @@
         <v/>
       </c>
       <c r="G205" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A205,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A205,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A205,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A205,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H205" s="20">
@@ -24284,7 +24284,7 @@
         <v/>
       </c>
       <c r="C206" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A206,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A206,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A206,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A206,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D206" s="31">
@@ -24300,7 +24300,7 @@
         <v/>
       </c>
       <c r="G206" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A206,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A206,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A206,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A206,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H206" s="30">
@@ -24333,7 +24333,7 @@
         <v/>
       </c>
       <c r="C207" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A207,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A207,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A207,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A207,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D207" s="18">
@@ -24349,7 +24349,7 @@
         <v/>
       </c>
       <c r="G207" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A207,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A207,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A207,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A207,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H207" s="20">
@@ -24382,7 +24382,7 @@
         <v/>
       </c>
       <c r="C208" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A208,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A208,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A208,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A208,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D208" s="31">
@@ -24398,7 +24398,7 @@
         <v/>
       </c>
       <c r="G208" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A208,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A208,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A208,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A208,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H208" s="30">
@@ -24431,7 +24431,7 @@
         <v/>
       </c>
       <c r="C209" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A209,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A209,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A209,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A209,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D209" s="18">
@@ -24447,7 +24447,7 @@
         <v/>
       </c>
       <c r="G209" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A209,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A209,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A209,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A209,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H209" s="20">
@@ -24480,7 +24480,7 @@
         <v/>
       </c>
       <c r="C210" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A210,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A210,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A210,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A210,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D210" s="31">
@@ -24496,7 +24496,7 @@
         <v/>
       </c>
       <c r="G210" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A210,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A210,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A210,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A210,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H210" s="30">
@@ -24529,7 +24529,7 @@
         <v/>
       </c>
       <c r="C211" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A211,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A211,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A211,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A211,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D211" s="18">
@@ -24545,7 +24545,7 @@
         <v/>
       </c>
       <c r="G211" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A211,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A211,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A211,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A211,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H211" s="20">
@@ -24578,7 +24578,7 @@
         <v/>
       </c>
       <c r="C212" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A212,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A212,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A212,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A212,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D212" s="31">
@@ -24594,7 +24594,7 @@
         <v/>
       </c>
       <c r="G212" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A212,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A212,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A212,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A212,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H212" s="30">
@@ -24627,7 +24627,7 @@
         <v/>
       </c>
       <c r="C213" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A213,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A213,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A213,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A213,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D213" s="18">
@@ -24643,7 +24643,7 @@
         <v/>
       </c>
       <c r="G213" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A213,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A213,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A213,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A213,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H213" s="20">
@@ -24676,7 +24676,7 @@
         <v/>
       </c>
       <c r="C214" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A214,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A214,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A214,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A214,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D214" s="31">
@@ -24692,7 +24692,7 @@
         <v/>
       </c>
       <c r="G214" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A214,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A214,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A214,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A214,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H214" s="30">
@@ -24725,7 +24725,7 @@
         <v/>
       </c>
       <c r="C215" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A215,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A215,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A215,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A215,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D215" s="18">
@@ -24741,7 +24741,7 @@
         <v/>
       </c>
       <c r="G215" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A215,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A215,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A215,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A215,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H215" s="20">
@@ -24774,7 +24774,7 @@
         <v/>
       </c>
       <c r="C216" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A216,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A216,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A216,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A216,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D216" s="31">
@@ -24790,7 +24790,7 @@
         <v/>
       </c>
       <c r="G216" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A216,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A216,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A216,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A216,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H216" s="30">
@@ -24823,7 +24823,7 @@
         <v/>
       </c>
       <c r="C217" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A217,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A217,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A217,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A217,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D217" s="18">
@@ -24839,7 +24839,7 @@
         <v/>
       </c>
       <c r="G217" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A217,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A217,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A217,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A217,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H217" s="20">
@@ -24872,7 +24872,7 @@
         <v/>
       </c>
       <c r="C218" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A218,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A218,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A218,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A218,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D218" s="31">
@@ -24888,7 +24888,7 @@
         <v/>
       </c>
       <c r="G218" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A218,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A218,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A218,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A218,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H218" s="30">
@@ -24921,7 +24921,7 @@
         <v/>
       </c>
       <c r="C219" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A219,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A219,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A219,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A219,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D219" s="18">
@@ -24937,7 +24937,7 @@
         <v/>
       </c>
       <c r="G219" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A219,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A219,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A219,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A219,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H219" s="20">
@@ -24970,7 +24970,7 @@
         <v/>
       </c>
       <c r="C220" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A220,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A220,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A220,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A220,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D220" s="31">
@@ -24986,7 +24986,7 @@
         <v/>
       </c>
       <c r="G220" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A220,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A220,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A220,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A220,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H220" s="30">
@@ -25019,7 +25019,7 @@
         <v/>
       </c>
       <c r="C221" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A221,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A221,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A221,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A221,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D221" s="18">
@@ -25035,7 +25035,7 @@
         <v/>
       </c>
       <c r="G221" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A221,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A221,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A221,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A221,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H221" s="20">
@@ -25068,7 +25068,7 @@
         <v/>
       </c>
       <c r="C222" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A222,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A222,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A222,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A222,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D222" s="31">
@@ -25084,7 +25084,7 @@
         <v/>
       </c>
       <c r="G222" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A222,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A222,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A222,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A222,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H222" s="30">
@@ -25117,7 +25117,7 @@
         <v/>
       </c>
       <c r="C223" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A223,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A223,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A223,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A223,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D223" s="18">
@@ -25133,7 +25133,7 @@
         <v/>
       </c>
       <c r="G223" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A223,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A223,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A223,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A223,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H223" s="20">
@@ -25166,7 +25166,7 @@
         <v/>
       </c>
       <c r="C224" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A224,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A224,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A224,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A224,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D224" s="31">
@@ -25182,7 +25182,7 @@
         <v/>
       </c>
       <c r="G224" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A224,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A224,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A224,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A224,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H224" s="30">
@@ -25215,7 +25215,7 @@
         <v/>
       </c>
       <c r="C225" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A225,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A225,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A225,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A225,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D225" s="18">
@@ -25231,7 +25231,7 @@
         <v/>
       </c>
       <c r="G225" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A225,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A225,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A225,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A225,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H225" s="20">
@@ -25264,7 +25264,7 @@
         <v/>
       </c>
       <c r="C226" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A226,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A226,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A226,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A226,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D226" s="31">
@@ -25280,7 +25280,7 @@
         <v/>
       </c>
       <c r="G226" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A226,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A226,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A226,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A226,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H226" s="30">
@@ -25313,7 +25313,7 @@
         <v/>
       </c>
       <c r="C227" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A227,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A227,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A227,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A227,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D227" s="18">
@@ -25329,7 +25329,7 @@
         <v/>
       </c>
       <c r="G227" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A227,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A227,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A227,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A227,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H227" s="20">
@@ -25362,7 +25362,7 @@
         <v/>
       </c>
       <c r="C228" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A228,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A228,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A228,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A228,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D228" s="31">
@@ -25378,7 +25378,7 @@
         <v/>
       </c>
       <c r="G228" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A228,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A228,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A228,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A228,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H228" s="30">
@@ -25411,7 +25411,7 @@
         <v/>
       </c>
       <c r="C229" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A229,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A229,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A229,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A229,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D229" s="18">
@@ -25427,7 +25427,7 @@
         <v/>
       </c>
       <c r="G229" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A229,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A229,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A229,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A229,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H229" s="20">
@@ -25460,7 +25460,7 @@
         <v/>
       </c>
       <c r="C230" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A230,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A230,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A230,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A230,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D230" s="31">
@@ -25476,7 +25476,7 @@
         <v/>
       </c>
       <c r="G230" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A230,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A230,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A230,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A230,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H230" s="30">
@@ -25509,7 +25509,7 @@
         <v/>
       </c>
       <c r="C231" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A231,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A231,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A231,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A231,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D231" s="18">
@@ -25525,7 +25525,7 @@
         <v/>
       </c>
       <c r="G231" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A231,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A231,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A231,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A231,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H231" s="20">
@@ -25558,7 +25558,7 @@
         <v/>
       </c>
       <c r="C232" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A232,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A232,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A232,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A232,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D232" s="31">
@@ -25574,7 +25574,7 @@
         <v/>
       </c>
       <c r="G232" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A232,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A232,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A232,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A232,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H232" s="30">
@@ -25607,7 +25607,7 @@
         <v/>
       </c>
       <c r="C233" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A233,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A233,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A233,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A233,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D233" s="18">
@@ -25623,7 +25623,7 @@
         <v/>
       </c>
       <c r="G233" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A233,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A233,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A233,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A233,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H233" s="20">
@@ -25656,7 +25656,7 @@
         <v/>
       </c>
       <c r="C234" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A234,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A234,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A234,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A234,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D234" s="31">
@@ -25672,7 +25672,7 @@
         <v/>
       </c>
       <c r="G234" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A234,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A234,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A234,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A234,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H234" s="30">
@@ -25705,7 +25705,7 @@
         <v/>
       </c>
       <c r="C235" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A235,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A235,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A235,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A235,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D235" s="18">
@@ -25721,7 +25721,7 @@
         <v/>
       </c>
       <c r="G235" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A235,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A235,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A235,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A235,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H235" s="20">
@@ -25754,7 +25754,7 @@
         <v/>
       </c>
       <c r="C236" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A236,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A236,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A236,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A236,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D236" s="31">
@@ -25770,7 +25770,7 @@
         <v/>
       </c>
       <c r="G236" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A236,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A236,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A236,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A236,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H236" s="30">
@@ -25803,7 +25803,7 @@
         <v/>
       </c>
       <c r="C237" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A237,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A237,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A237,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A237,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D237" s="18">
@@ -25819,7 +25819,7 @@
         <v/>
       </c>
       <c r="G237" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A237,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A237,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A237,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A237,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H237" s="20">
@@ -25852,7 +25852,7 @@
         <v/>
       </c>
       <c r="C238" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A238,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A238,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A238,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A238,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D238" s="31">
@@ -25868,7 +25868,7 @@
         <v/>
       </c>
       <c r="G238" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A238,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A238,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A238,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A238,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H238" s="30">
@@ -25901,7 +25901,7 @@
         <v/>
       </c>
       <c r="C239" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A239,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A239,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A239,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A239,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D239" s="18">
@@ -25917,7 +25917,7 @@
         <v/>
       </c>
       <c r="G239" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A239,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A239,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A239,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A239,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H239" s="20">
@@ -25950,7 +25950,7 @@
         <v/>
       </c>
       <c r="C240" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A240,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A240,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A240,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A240,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D240" s="31">
@@ -25966,7 +25966,7 @@
         <v/>
       </c>
       <c r="G240" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A240,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A240,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A240,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A240,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H240" s="30">
@@ -25999,7 +25999,7 @@
         <v/>
       </c>
       <c r="C241" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A241,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A241,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A241,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A241,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D241" s="18">
@@ -26015,7 +26015,7 @@
         <v/>
       </c>
       <c r="G241" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A241,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A241,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A241,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A241,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H241" s="20">
@@ -26048,7 +26048,7 @@
         <v/>
       </c>
       <c r="C242" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A242,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A242,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A242,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A242,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D242" s="31">
@@ -26064,7 +26064,7 @@
         <v/>
       </c>
       <c r="G242" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A242,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A242,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A242,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A242,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H242" s="30">
@@ -26097,7 +26097,7 @@
         <v/>
       </c>
       <c r="C243" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A243,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A243,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A243,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A243,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D243" s="18">
@@ -26113,7 +26113,7 @@
         <v/>
       </c>
       <c r="G243" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A243,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A243,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A243,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A243,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H243" s="20">
@@ -26146,7 +26146,7 @@
         <v/>
       </c>
       <c r="C244" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A244,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A244,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A244,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A244,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D244" s="31">
@@ -26162,7 +26162,7 @@
         <v/>
       </c>
       <c r="G244" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A244,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A244,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A244,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A244,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H244" s="30">
@@ -26195,7 +26195,7 @@
         <v/>
       </c>
       <c r="C245" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A245,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A245,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A245,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A245,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D245" s="18">
@@ -26211,7 +26211,7 @@
         <v/>
       </c>
       <c r="G245" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A245,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A245,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A245,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A245,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H245" s="20">
@@ -26244,7 +26244,7 @@
         <v/>
       </c>
       <c r="C246" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A246,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A246,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A246,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A246,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D246" s="31">
@@ -26260,7 +26260,7 @@
         <v/>
       </c>
       <c r="G246" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A246,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A246,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A246,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A246,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H246" s="30">
@@ -26293,7 +26293,7 @@
         <v/>
       </c>
       <c r="C247" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A247,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A247,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A247,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A247,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D247" s="18">
@@ -26309,7 +26309,7 @@
         <v/>
       </c>
       <c r="G247" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A247,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A247,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A247,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A247,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H247" s="20">
@@ -26342,7 +26342,7 @@
         <v/>
       </c>
       <c r="C248" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A248,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A248,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A248,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A248,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D248" s="31">
@@ -26358,7 +26358,7 @@
         <v/>
       </c>
       <c r="G248" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A248,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A248,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A248,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A248,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H248" s="30">
@@ -26391,7 +26391,7 @@
         <v/>
       </c>
       <c r="C249" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A249,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A249,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A249,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A249,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D249" s="18">
@@ -26407,7 +26407,7 @@
         <v/>
       </c>
       <c r="G249" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A249,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A249,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A249,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A249,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H249" s="20">
@@ -26440,7 +26440,7 @@
         <v/>
       </c>
       <c r="C250" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A250,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A250,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A250,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A250,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D250" s="31">
@@ -26456,7 +26456,7 @@
         <v/>
       </c>
       <c r="G250" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A250,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A250,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A250,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A250,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H250" s="30">
@@ -26489,7 +26489,7 @@
         <v/>
       </c>
       <c r="C251" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A251,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A251,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A251,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A251,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D251" s="18">
@@ -26505,7 +26505,7 @@
         <v/>
       </c>
       <c r="G251" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A251,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A251,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A251,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A251,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H251" s="20">
@@ -26538,7 +26538,7 @@
         <v/>
       </c>
       <c r="C252" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A252,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A252,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A252,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A252,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D252" s="31">
@@ -26554,7 +26554,7 @@
         <v/>
       </c>
       <c r="G252" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A252,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A252,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A252,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A252,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H252" s="30">
@@ -26587,7 +26587,7 @@
         <v/>
       </c>
       <c r="C253" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A253,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A253,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A253,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A253,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D253" s="18">
@@ -26603,7 +26603,7 @@
         <v/>
       </c>
       <c r="G253" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A253,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A253,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A253,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A253,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H253" s="20">
@@ -26636,7 +26636,7 @@
         <v/>
       </c>
       <c r="C254" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A254,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A254,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A254,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A254,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D254" s="31">
@@ -26652,7 +26652,7 @@
         <v/>
       </c>
       <c r="G254" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A254,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A254,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A254,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A254,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H254" s="30">
@@ -26685,7 +26685,7 @@
         <v/>
       </c>
       <c r="C255" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A255,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A255,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A255,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A255,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D255" s="18">
@@ -26701,7 +26701,7 @@
         <v/>
       </c>
       <c r="G255" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A255,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A255,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A255,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A255,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H255" s="20">
@@ -26734,7 +26734,7 @@
         <v/>
       </c>
       <c r="C256" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A256,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A256,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A256,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A256,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D256" s="31">
@@ -26750,7 +26750,7 @@
         <v/>
       </c>
       <c r="G256" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A256,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A256,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A256,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A256,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H256" s="30">
@@ -26783,7 +26783,7 @@
         <v/>
       </c>
       <c r="C257" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A257,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A257,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A257,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A257,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D257" s="18">
@@ -26799,7 +26799,7 @@
         <v/>
       </c>
       <c r="G257" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A257,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A257,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A257,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A257,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H257" s="20">
@@ -26832,7 +26832,7 @@
         <v/>
       </c>
       <c r="C258" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A258,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A258,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A258,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A258,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D258" s="31">
@@ -26848,7 +26848,7 @@
         <v/>
       </c>
       <c r="G258" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A258,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A258,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A258,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A258,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H258" s="30">
@@ -26881,7 +26881,7 @@
         <v/>
       </c>
       <c r="C259" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A259,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A259,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A259,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A259,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D259" s="18">
@@ -26897,7 +26897,7 @@
         <v/>
       </c>
       <c r="G259" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A259,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A259,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A259,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A259,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H259" s="20">
@@ -26930,7 +26930,7 @@
         <v/>
       </c>
       <c r="C260" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A260,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A260,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A260,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A260,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D260" s="31">
@@ -26946,7 +26946,7 @@
         <v/>
       </c>
       <c r="G260" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A260,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A260,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A260,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A260,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H260" s="30">
@@ -26979,7 +26979,7 @@
         <v/>
       </c>
       <c r="C261" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A261,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A261,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A261,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A261,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D261" s="18">
@@ -26995,7 +26995,7 @@
         <v/>
       </c>
       <c r="G261" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A261,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A261,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A261,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A261,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H261" s="20">
@@ -27028,7 +27028,7 @@
         <v/>
       </c>
       <c r="C262" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A262,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A262,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A262,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A262,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D262" s="31">
@@ -27044,7 +27044,7 @@
         <v/>
       </c>
       <c r="G262" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A262,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A262,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A262,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A262,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H262" s="30">
@@ -27077,7 +27077,7 @@
         <v/>
       </c>
       <c r="C263" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A263,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A263,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A263,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A263,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D263" s="18">
@@ -27093,7 +27093,7 @@
         <v/>
       </c>
       <c r="G263" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A263,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A263,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A263,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A263,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H263" s="20">
@@ -27126,7 +27126,7 @@
         <v/>
       </c>
       <c r="C264" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A264,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A264,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A264,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A264,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D264" s="31">
@@ -27142,7 +27142,7 @@
         <v/>
       </c>
       <c r="G264" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A264,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A264,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A264,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A264,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H264" s="30">
@@ -27175,7 +27175,7 @@
         <v/>
       </c>
       <c r="C265" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A265,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A265,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A265,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A265,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D265" s="18">
@@ -27191,7 +27191,7 @@
         <v/>
       </c>
       <c r="G265" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A265,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A265,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A265,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A265,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H265" s="20">
@@ -27224,7 +27224,7 @@
         <v/>
       </c>
       <c r="C266" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A266,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A266,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A266,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A266,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D266" s="31">
@@ -27240,7 +27240,7 @@
         <v/>
       </c>
       <c r="G266" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A266,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A266,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A266,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A266,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H266" s="30">
@@ -27273,7 +27273,7 @@
         <v/>
       </c>
       <c r="C267" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A267,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A267,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A267,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A267,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D267" s="18">
@@ -27289,7 +27289,7 @@
         <v/>
       </c>
       <c r="G267" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A267,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A267,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A267,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A267,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H267" s="20">
@@ -27322,7 +27322,7 @@
         <v/>
       </c>
       <c r="C268" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A268,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A268,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A268,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A268,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D268" s="31">
@@ -27338,7 +27338,7 @@
         <v/>
       </c>
       <c r="G268" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A268,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A268,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A268,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A268,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H268" s="30">
@@ -27371,7 +27371,7 @@
         <v/>
       </c>
       <c r="C269" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A269,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A269,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A269,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A269,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D269" s="18">
@@ -27387,7 +27387,7 @@
         <v/>
       </c>
       <c r="G269" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A269,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A269,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A269,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A269,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H269" s="20">
@@ -27420,7 +27420,7 @@
         <v/>
       </c>
       <c r="C270" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A270,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A270,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A270,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A270,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D270" s="31">
@@ -27436,7 +27436,7 @@
         <v/>
       </c>
       <c r="G270" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A270,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A270,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A270,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A270,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H270" s="30">
@@ -27469,7 +27469,7 @@
         <v/>
       </c>
       <c r="C271" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$463,MATCH($A271,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$D$31:$D$463,MATCH($A271,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A271,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A271,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="D271" s="18">
@@ -27485,7 +27485,7 @@
         <v/>
       </c>
       <c r="G271" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$463,MATCH($A271,Kalshi!$A$31:$A$463,0))=0,"",INDEX(Kalshi!$G$31:$G$463,MATCH($A271,Kalshi!$A$31:$A$463,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A271,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A271,Kalshi!$A$31:$A$464,0))),"")</f>
         <v/>
       </c>
       <c r="H271" s="20">
@@ -27538,7 +27538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-20 01:08 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -28698,7 +28698,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-20 01:08 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -28779,7 +28779,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-20 01:08 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -28963,7 +28963,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 01:08 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -29116,7 +29116,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>24454.333615</v>
+        <v>24599.333615</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>6070.959802000001</v>
@@ -29129,10 +29129,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>11037.3545</v>
+        <v>11244.1615</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>14243.5465</v>
+        <v>13815.798</v>
       </c>
     </row>
     <row r="14">
@@ -29155,7 +29155,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>-0.005</v>
@@ -29228,7 +29228,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0.8</v>
@@ -29242,10 +29242,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>246</v>
+        <v>218.17</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>5</v>
+        <v>346.79</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29273,10 +29273,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>7299</v>
+        <v>7119</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40640,7 +40640,7 @@
         <v>46285</v>
       </c>
       <c r="B281" s="16" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="C281" s="16" t="n">
         <v>0.205</v>
@@ -40691,7 +40691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M463"/>
+  <dimension ref="A1:M464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40718,7 +40718,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 01:08 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -40892,10 +40892,10 @@
         </is>
       </c>
       <c r="B13" s="43" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C13" s="44" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15">
@@ -40987,7 +40987,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>6.9</v>
+        <v>87.52</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -41019,7 +41019,7 @@
         <v/>
       </c>
       <c r="G18" s="19" t="n">
-        <v>1154.86</v>
+        <v>1142.93</v>
       </c>
       <c r="H18" s="20">
         <f>IFERROR(E18/$E$19,"")</f>
@@ -41121,25 +41121,25 @@
         <v>0.79</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>6.9</v>
+        <v>87.52</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>10772.7</v>
+        <v>576.03</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>1154.86</v>
+        <v>1142.93</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>0.79</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>170.41</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="24">
@@ -41150,25 +41150,25 @@
         <v>0.78</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.18</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>200</v>
+        <v>535.59</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.17</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>0.78</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>58.34</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="25">
@@ -41179,25 +41179,25 @@
         <v>0.77</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>538</v>
+        <v>50907</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>496.44</v>
+        <v>50496.44</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>207</v>
+        <v>10870</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>0.77</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>284</v>
+        <v>50628</v>
       </c>
     </row>
     <row r="26">
@@ -41208,7 +41208,7 @@
         <v>0.76</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>669.3</v>
+        <v>431.3</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.14</v>
@@ -41217,16 +41217,16 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.12</v>
+        <v>0.027</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>5870</v>
+        <v>45</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>0.76</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>629.4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27">
@@ -41240,16 +41240,16 @@
         <v>100</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>5870</v>
+        <v>5000</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>1.08</v>
+        <v>46</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>0.75</v>
@@ -61968,6 +61968,54 @@
       <c r="M463" s="26" t="inlineStr">
         <is>
           <t>19 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="41" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B464" s="28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C464" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D464" s="29">
+        <f>IF(COUNT(B464:C464)=2,(B464+C464)/2,"")</f>
+        <v/>
+      </c>
+      <c r="E464" s="28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F464" s="28" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G464" s="29">
+        <f>IF(COUNT(E464:F464)=2,(E464+F464)/2,"")</f>
+        <v/>
+      </c>
+      <c r="H464" s="29">
+        <f>IF(AND(ISNUMBER(D464),ISNUMBER(G464)),D464+G464,"")</f>
+        <v/>
+      </c>
+      <c r="I464" s="30">
+        <f>IFERROR(D464/H464,"")</f>
+        <v/>
+      </c>
+      <c r="J464" s="31">
+        <f>IF(AND(ISNUMBER(D464),ISNUMBER(G464)),D464-G464,"")</f>
+        <v/>
+      </c>
+      <c r="K464" s="46" t="n">
+        <v>533.63</v>
+      </c>
+      <c r="L464" s="46" t="n">
+        <v>70507.13</v>
+      </c>
+      <c r="M464" s="38" t="inlineStr">
+        <is>
+          <t>20 Sep</t>
         </is>
       </c>
     </row>
@@ -62009,7 +62057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-20 01:08 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -62114,7 +62162,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>2503.077581</v>
+        <v>2818.077581</v>
       </c>
       <c r="C10" s="66" t="n"/>
       <c r="D10" s="66" t="n"/>
@@ -62128,7 +62176,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>54244.4535</v>
+        <v>46538.92486</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -62227,10 +62275,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -62245,10 +62293,10 @@
         <v/>
       </c>
       <c r="H16" s="19" t="n">
-        <v>756.9541730000001</v>
+        <v>756.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>536.8973</v>
+        <v>310.8028</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62265,10 +62313,10 @@
         <v>-4.5</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.1</v>
+        <v>0.022</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.131</v>
+        <v>0.128</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62283,10 +62331,10 @@
         <v/>
       </c>
       <c r="H17" s="19" t="n">
-        <v>179.32</v>
+        <v>199.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>8813.09101</v>
+        <v>372.00254</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62303,10 +62351,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -62321,10 +62369,10 @@
         <v/>
       </c>
       <c r="H18" s="19" t="n">
-        <v>156.333332</v>
+        <v>161.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>8682.998</v>
+        <v>413.718</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62362,7 +62410,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8767.0573</v>
+        <v>8822.350700000001</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62400,7 +62448,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8768.0798</v>
+        <v>8736.617899999999</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62417,10 +62465,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.128</v>
+        <v>0.101</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.209</v>
+        <v>0.52</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62438,7 +62486,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>534.01116</v>
+        <v>306.2137</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62455,10 +62503,10 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.034</v>
+        <v>0.005</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.095</v>
+        <v>0.074</v>
       </c>
       <c r="E22" s="17">
         <f>IF(COUNT(C22:D22)=2,(C22+D22)/2,"")</f>
@@ -62476,7 +62524,7 @@
         <v>162.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>732.8140100000001</v>
+        <v>8373.396839999999</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62492,9 +62540,7 @@
       <c r="B23" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="C23" s="16" t="n"/>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
       </c>
@@ -62514,7 +62560,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>8582.8621</v>
+        <v>8341.6121</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62531,7 +62577,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62552,7 +62598,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>374.69576</v>
+        <v>459.63455</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62572,7 +62618,7 @@
         <v>0.1</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E25" s="17">
         <f>IF(COUNT(C25:D25)=2,(C25+D25)/2,"")</f>
@@ -62587,10 +62633,10 @@
         <v/>
       </c>
       <c r="H25" s="19" t="n">
-        <v>115.63526</v>
+        <v>405.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>8836.7649</v>
+        <v>10321.2635</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -64195,13 +64241,13 @@
         <v>46285</v>
       </c>
       <c r="B82" s="28" t="n">
-        <v>0.125</v>
+        <v>0.105</v>
       </c>
       <c r="C82" s="28" t="n">
-        <v>0.1155</v>
+        <v>0.075</v>
       </c>
       <c r="D82" s="28" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E82" s="28" t="n">
         <v>0.155</v>
@@ -64210,19 +64256,19 @@
         <v>0.135</v>
       </c>
       <c r="G82" s="28" t="n">
-        <v>0.1685</v>
+        <v>0.295</v>
       </c>
       <c r="H82" s="28" t="n">
-        <v>0.0645</v>
+        <v>0.0395</v>
       </c>
       <c r="I82" s="28" t="n">
         <v>0.045</v>
       </c>
       <c r="J82" s="28" t="n">
-        <v>0.0525</v>
+        <v>0.052</v>
       </c>
       <c r="K82" s="28" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="83">
@@ -64256,7 +64302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -64281,7 +64327,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-20 01:08 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -65502,7 +65548,27 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="39" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B69" s="16" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F69" s="16" t="n">
+        <v>0.255</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Columns are nested, not exclusive: each is P(turnout ≥ that threshold), so within a row they must fall from left to right. Kalshi began quoting this ladder on 2026-05-08.</t>
         </is>
@@ -65511,10 +65577,10 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A70:J70"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A69:J69"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
@@ -65529,7 +65595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -65554,7 +65620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-20 01:08 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -65837,7 +65903,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.67</v>
@@ -65873,10 +65939,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="E17" s="20">
         <f>IF(ISNUMBER(D17),1-D17,"")</f>
@@ -65912,7 +65978,7 @@
         <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -66950,9 +67016,33 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Kalshi began quoting this ladder on 20 Aug 2026, so the history is only 31 days long. Values are the mid of the daily closing YES bid and the ask derived from the closing NO bid; where only one side closed, the same fallback as the live ladder applies.</t>
+      <c r="A64" s="41" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B64" s="28" t="n"/>
+      <c r="C64" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D64" s="28" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E64" s="28" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="F64" s="28" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G64" s="28" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H64" s="28" t="n"/>
+      <c r="I64" s="28" t="n"/>
+      <c r="J64" s="88" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Kalshi began quoting this ladder on 20 Aug 2026, so the history is only 32 days long. Values are the mid of the daily closing YES bid and the ask derived from the closing NO bid; where only one side closed, the same fallback as the live ladder applies.</t>
         </is>
       </c>
     </row>
@@ -66962,7 +67052,7 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="A65:J65"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
@@ -67007,7 +67097,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-20 01:08 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-20 14:41 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-20 14:41 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-20 14:41 UTC</t>
+          <t>2026-09-20 19:27 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-20 14:41 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-20 14:41 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-20 14:41 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -27538,7 +27538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-20 14:41 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -28698,7 +28698,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-20 14:41 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -28779,7 +28779,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-20 14:41 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -28963,7 +28963,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 14:41 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -29129,10 +29129,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>11244.1615</v>
+        <v>10974.7843</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>13815.798</v>
+        <v>13146.7949</v>
       </c>
     </row>
     <row r="14">
@@ -29155,11 +29155,9 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="C15" s="14" t="n">
         <v>-0.005</v>
       </c>
+      <c r="C15" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -29242,10 +29240,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>218.17</v>
+        <v>149.2</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>346.79</v>
+        <v>326.79</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29273,10 +29271,10 @@
         <v/>
       </c>
       <c r="F20" s="19" t="n">
-        <v>7119</v>
+        <v>7099</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40718,7 +40716,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 14:41 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -40969,7 +40967,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>0.19</v>
@@ -40987,7 +40985,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>87.52</v>
+        <v>7.25</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -41004,7 +41002,7 @@
         <v>0.19</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="D18" s="20">
         <f>1-C18</f>
@@ -41118,10 +41116,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>87.52</v>
+        <v>7.25</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.19</v>
@@ -41136,10 +41134,10 @@
         <v>1142.93</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>215.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
@@ -41147,16 +41145,16 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.18</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>535.59</v>
+        <v>499.54</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.17</v>
@@ -41165,10 +41163,10 @@
         <v>50500</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>50.06</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25">
@@ -41176,10 +41174,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="16" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>50907</v>
+        <v>67</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
@@ -41194,10 +41192,10 @@
         <v>10870</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>50628</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="26">
@@ -41205,10 +41203,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>431.3</v>
+        <v>50776</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.14</v>
@@ -41217,16 +41215,16 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>150</v>
+        <v>50550</v>
       </c>
     </row>
     <row r="27">
@@ -41234,10 +41232,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>100</v>
+        <v>431.3</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>0.13</v>
@@ -41246,16 +41244,16 @@
         <v>5000</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
@@ -62057,7 +62055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-20 14:41 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -62176,7 +62174,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>46538.92486</v>
+        <v>81562.37809</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -62275,10 +62273,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -62296,7 +62294,7 @@
         <v>756.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>310.8028</v>
+        <v>10042.7052</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62313,10 +62311,10 @@
         <v>-4.5</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.022</v>
+        <v>0.082</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.128</v>
+        <v>0.112</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62334,7 +62332,7 @@
         <v>199.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>372.00254</v>
+        <v>9068.77981</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62351,10 +62349,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -62372,7 +62370,7 @@
         <v>161.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>413.718</v>
+        <v>8629.859700000001</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62389,7 +62387,7 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>0.17</v>
@@ -62410,7 +62408,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8822.350700000001</v>
+        <v>8972.6404</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62448,7 +62446,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8736.617899999999</v>
+        <v>8983.109399999999</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62465,10 +62463,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.101</v>
+        <v>0.163</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.52</v>
+        <v>0.199</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62486,7 +62484,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>306.2137</v>
+        <v>9075.055759999999</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62503,7 +62501,7 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>0.074</v>
@@ -62524,7 +62522,7 @@
         <v>162.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>8373.396839999999</v>
+        <v>8511.84491</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62560,7 +62558,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>8341.6121</v>
+        <v>8260.801299999999</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62577,7 +62575,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62598,7 +62596,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>459.63455</v>
+        <v>90.06983</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62636,7 +62634,7 @@
         <v>405.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>10321.2635</v>
+        <v>9893.4674</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -64241,28 +64239,28 @@
         <v>46285</v>
       </c>
       <c r="B82" s="28" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="C82" s="28" t="n">
-        <v>0.075</v>
+        <v>0.097</v>
       </c>
       <c r="D82" s="28" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E82" s="28" t="n">
-        <v>0.155</v>
+        <v>0.16</v>
       </c>
       <c r="F82" s="28" t="n">
         <v>0.135</v>
       </c>
       <c r="G82" s="28" t="n">
-        <v>0.295</v>
+        <v>0.181</v>
       </c>
       <c r="H82" s="28" t="n">
-        <v>0.0395</v>
+        <v>0.039</v>
       </c>
       <c r="I82" s="28" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="J82" s="28" t="n">
         <v>0.052</v>
@@ -64327,7 +64325,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-20 14:41 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -65620,7 +65618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-20 14:41 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>
@@ -65978,7 +65976,7 @@
         <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -67097,7 +67095,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-20 14:41 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-20 19:27 UTC.</t>
         </is>
       </c>
     </row>

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -538,12 +538,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$271</f>
+              <f>'Venue Comparison'!$L$15:$L$272</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$B$15:$B$271</f>
+              <f>'Venue Comparison'!$B$15:$B$272</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -574,12 +574,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$271</f>
+              <f>'Venue Comparison'!$L$15:$L$272</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$C$15:$C$271</f>
+              <f>'Venue Comparison'!$C$15:$C$272</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -610,12 +610,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$271</f>
+              <f>'Venue Comparison'!$L$15:$L$272</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$K$15:$K$271</f>
+              <f>'Venue Comparison'!$K$15:$K$272</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1396,12 +1396,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Venue Comparison'!$L$15:$L$271</f>
+              <f>'Venue Comparison'!$L$15:$L$272</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Venue Comparison'!$D$15:$D$271</f>
+              <f>'Venue Comparison'!$D$15:$D$272</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2101,12 +2101,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$281</f>
+              <f>'Polymarket'!$K$25:$K$282</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$D$25:$D$281</f>
+              <f>'Polymarket'!$D$25:$D$282</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2325,12 +2325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$281</f>
+              <f>'Polymarket'!$K$25:$K$282</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$B$25:$B$281</f>
+              <f>'Polymarket'!$B$25:$B$282</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2361,12 +2361,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Polymarket'!$K$25:$K$281</f>
+              <f>'Polymarket'!$K$25:$K$282</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Polymarket'!$C$25:$C$281</f>
+              <f>'Polymarket'!$C$25:$C$282</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-20 19:27 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="B48" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-0,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-0,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="D48" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-0,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-0,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-0,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="B49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-7,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-7,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
       <c r="C49" s="18">
@@ -4813,7 +4813,7 @@
         <v/>
       </c>
       <c r="D49" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-7,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-7,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-7,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="B50" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-30,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-30,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
       <c r="C50" s="18">
@@ -4832,7 +4832,7 @@
         <v/>
       </c>
       <c r="D50" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-30,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-30,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-30,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-90,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH(Polymarket!$A$282-90,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
       <c r="C51" s="18">
@@ -4851,7 +4851,7 @@
         <v/>
       </c>
       <c r="D51" s="124">
-        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))=0,"",INDEX(Polymarket!$A$25:$A$281,MATCH(Polymarket!$A$281-90,Polymarket!$A$25:$A$281,1))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-90,Polymarket!$A$25:$A$282,1))=0,"",INDEX(Polymarket!$A$25:$A$282,MATCH(Polymarket!$A$282-90,Polymarket!$A$25:$A$282,1))),"")</f>
         <v/>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="B52" s="20">
-        <f>MAX(Polymarket!B25:B281)</f>
+        <f>MAX(Polymarket!B25:B282)</f>
         <v/>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B53" s="20">
-        <f>MIN(Polymarket!B25:B281)</f>
+        <f>MIN(Polymarket!B25:B282)</f>
         <v/>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-20 19:27 UTC</t>
+          <t>2026-09-21 01:05 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="B69" s="59">
-        <f>TEXT(Polymarket!A25,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Polymarket!A281,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Polymarket!A25:A281)&amp;" days)"</f>
+        <f>TEXT(Polymarket!A25,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Polymarket!A282,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Polymarket!A25:A282)&amp;" days)"</f>
         <v/>
       </c>
       <c r="C69" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-20 19:27 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A36,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A36,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H36" s="18">
@@ -5660,7 +5660,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A37,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A37,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H37" s="31">
@@ -5693,7 +5693,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A38,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A38,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H38" s="18">
@@ -5726,7 +5726,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A39,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A39,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H39" s="31">
@@ -5759,7 +5759,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A40,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A40,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H40" s="18">
@@ -5792,7 +5792,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A41,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A41,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H41" s="31">
@@ -5825,7 +5825,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A42,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A42,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H42" s="18">
@@ -5858,7 +5858,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A43,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A43,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H43" s="31">
@@ -5891,7 +5891,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A44,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A44,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H44" s="18">
@@ -5924,7 +5924,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A45,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A45,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H45" s="31">
@@ -5957,7 +5957,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A46,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A46,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H46" s="18">
@@ -5990,7 +5990,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A47,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A47,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H47" s="31">
@@ -6023,7 +6023,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A48,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A48,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H48" s="18">
@@ -6056,7 +6056,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A49,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A49,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H49" s="31">
@@ -6089,7 +6089,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A50,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A50,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H50" s="18">
@@ -6122,7 +6122,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A51,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A51,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H51" s="31">
@@ -6155,7 +6155,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A52,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A52,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H52" s="18">
@@ -6188,7 +6188,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A53,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A53,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H53" s="31">
@@ -6221,7 +6221,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A54,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A54,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H54" s="18">
@@ -6254,7 +6254,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A55,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A55,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H55" s="31">
@@ -6287,7 +6287,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A56,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A56,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H56" s="18">
@@ -6320,7 +6320,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A57,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A57,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H57" s="31">
@@ -6353,7 +6353,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A58,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A58,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H58" s="18">
@@ -6386,7 +6386,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A59,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A59,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H59" s="31">
@@ -6419,7 +6419,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A60,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A60,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H60" s="18">
@@ -6452,7 +6452,7 @@
         <v>0.499</v>
       </c>
       <c r="G61" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A61,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A61,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H61" s="31">
@@ -6485,7 +6485,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A62,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A62,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H62" s="18">
@@ -6518,7 +6518,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A63,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A63,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H63" s="31">
@@ -6551,7 +6551,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A64,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A64,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H64" s="18">
@@ -6584,7 +6584,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A65,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A65,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H65" s="31">
@@ -6617,7 +6617,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A66,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A66,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H66" s="18">
@@ -6650,7 +6650,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A67,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A67,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H67" s="31">
@@ -6683,7 +6683,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A68,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A68,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H68" s="18">
@@ -6716,7 +6716,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A69,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A69,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H69" s="31">
@@ -6749,7 +6749,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A70,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A70,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H70" s="18">
@@ -6782,7 +6782,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A71,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A71,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H71" s="31">
@@ -6815,7 +6815,7 @@
         <v>0.499</v>
       </c>
       <c r="G72" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A72,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A72,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H72" s="18">
@@ -6848,7 +6848,7 @@
         <v>0.499</v>
       </c>
       <c r="G73" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A73,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A73,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H73" s="31">
@@ -6881,7 +6881,7 @@
         <v>0.499</v>
       </c>
       <c r="G74" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A74,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A74,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H74" s="18">
@@ -6914,7 +6914,7 @@
         <v>0.499</v>
       </c>
       <c r="G75" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A75,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A75,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H75" s="31">
@@ -6947,7 +6947,7 @@
         <v>0.499</v>
       </c>
       <c r="G76" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A76,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A76,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H76" s="18">
@@ -6980,7 +6980,7 @@
         <v>0.499</v>
       </c>
       <c r="G77" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A77,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A77,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H77" s="31">
@@ -7013,7 +7013,7 @@
         <v>0.499</v>
       </c>
       <c r="G78" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A78,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A78,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H78" s="18">
@@ -7046,7 +7046,7 @@
         <v>0.499</v>
       </c>
       <c r="G79" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A79,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A79,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H79" s="31">
@@ -7079,7 +7079,7 @@
         <v>0.499</v>
       </c>
       <c r="G80" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A80,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A80,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H80" s="18">
@@ -7112,7 +7112,7 @@
         <v>0.499</v>
       </c>
       <c r="G81" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A81,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A81,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H81" s="31">
@@ -7145,7 +7145,7 @@
         <v>0.499</v>
       </c>
       <c r="G82" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A82,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A82,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H82" s="18">
@@ -7178,7 +7178,7 @@
         <v>0.499</v>
       </c>
       <c r="G83" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A83,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A83,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H83" s="31">
@@ -7211,7 +7211,7 @@
         <v>0.499</v>
       </c>
       <c r="G84" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A84,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A84,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H84" s="18">
@@ -7244,7 +7244,7 @@
         <v>0.499</v>
       </c>
       <c r="G85" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A85,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A85,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H85" s="31">
@@ -7277,7 +7277,7 @@
         <v>0.499</v>
       </c>
       <c r="G86" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A86,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A86,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H86" s="18">
@@ -7310,7 +7310,7 @@
         <v>0.499</v>
       </c>
       <c r="G87" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A87,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A87,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H87" s="31">
@@ -7343,7 +7343,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A88,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A88,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H88" s="18">
@@ -7376,7 +7376,7 @@
         <v>0.499</v>
       </c>
       <c r="G89" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A89,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A89,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H89" s="31">
@@ -7409,7 +7409,7 @@
         <v>0.499</v>
       </c>
       <c r="G90" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A90,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A90,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H90" s="18">
@@ -7442,7 +7442,7 @@
         <v>0.5</v>
       </c>
       <c r="G91" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A91,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A91,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H91" s="31">
@@ -7475,7 +7475,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A92,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A92,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H92" s="18">
@@ -7508,7 +7508,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A93,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A93,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H93" s="31">
@@ -7541,7 +7541,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A94,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A94,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H94" s="18">
@@ -7574,7 +7574,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A95,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A95,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H95" s="31">
@@ -7607,7 +7607,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A96,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A96,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H96" s="18">
@@ -7640,7 +7640,7 @@
         <v>0.499</v>
       </c>
       <c r="G97" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A97,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A97,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H97" s="31">
@@ -7673,7 +7673,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A98,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A98,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H98" s="18">
@@ -7706,7 +7706,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A99,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A99,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H99" s="31">
@@ -7739,7 +7739,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A100,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A100,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H100" s="18">
@@ -7772,7 +7772,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A101,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A101,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H101" s="31">
@@ -7805,7 +7805,7 @@
         <v>0.5</v>
       </c>
       <c r="G102" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A102,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A102,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H102" s="18">
@@ -7838,7 +7838,7 @@
         <v>0.5</v>
       </c>
       <c r="G103" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A103,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A103,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H103" s="31">
@@ -7871,7 +7871,7 @@
         <v>0.5</v>
       </c>
       <c r="G104" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A104,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A104,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H104" s="18">
@@ -7904,7 +7904,7 @@
         <v>0.5</v>
       </c>
       <c r="G105" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A105,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A105,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H105" s="31">
@@ -7937,7 +7937,7 @@
         <v>0.5</v>
       </c>
       <c r="G106" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A106,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A106,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H106" s="18">
@@ -7970,7 +7970,7 @@
         <v>0.5</v>
       </c>
       <c r="G107" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A107,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A107,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H107" s="31">
@@ -8003,7 +8003,7 @@
         <v>0.5</v>
       </c>
       <c r="G108" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A108,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A108,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H108" s="18">
@@ -8036,7 +8036,7 @@
         <v>0.5</v>
       </c>
       <c r="G109" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A109,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A109,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H109" s="31">
@@ -8069,7 +8069,7 @@
         <v>0.5</v>
       </c>
       <c r="G110" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A110,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A110,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H110" s="18">
@@ -8102,7 +8102,7 @@
         <v>0.5</v>
       </c>
       <c r="G111" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A111,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A111,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H111" s="31">
@@ -8135,7 +8135,7 @@
         <v>0.5</v>
       </c>
       <c r="G112" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A112,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A112,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H112" s="18">
@@ -8168,7 +8168,7 @@
         <v>0.5</v>
       </c>
       <c r="G113" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A113,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A113,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H113" s="31">
@@ -8201,7 +8201,7 @@
         <v>0.5</v>
       </c>
       <c r="G114" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A114,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A114,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H114" s="18">
@@ -8234,7 +8234,7 @@
         <v>0.5</v>
       </c>
       <c r="G115" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A115,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A115,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H115" s="31">
@@ -8267,7 +8267,7 @@
         <v>0.5</v>
       </c>
       <c r="G116" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A116,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A116,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H116" s="18">
@@ -8300,7 +8300,7 @@
         <v>0.499</v>
       </c>
       <c r="G117" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A117,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A117,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H117" s="31">
@@ -8333,7 +8333,7 @@
         <v>0.499</v>
       </c>
       <c r="G118" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A118,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A118,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H118" s="18">
@@ -8366,7 +8366,7 @@
         <v>0.499</v>
       </c>
       <c r="G119" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A119,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A119,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H119" s="31">
@@ -8399,7 +8399,7 @@
         <v>0.499</v>
       </c>
       <c r="G120" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A120,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A120,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H120" s="18">
@@ -8432,7 +8432,7 @@
         <v>0.499</v>
       </c>
       <c r="G121" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A121,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A121,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H121" s="31">
@@ -8465,7 +8465,7 @@
         <v>0.499</v>
       </c>
       <c r="G122" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A122,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A122,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H122" s="18">
@@ -8498,7 +8498,7 @@
         <v>0.499</v>
       </c>
       <c r="G123" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A123,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A123,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H123" s="31">
@@ -8531,7 +8531,7 @@
         <v>0.499</v>
       </c>
       <c r="G124" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A124,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A124,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H124" s="18">
@@ -8564,7 +8564,7 @@
         <v>0.499</v>
       </c>
       <c r="G125" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A125,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A125,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H125" s="31">
@@ -8597,7 +8597,7 @@
         <v>0.499</v>
       </c>
       <c r="G126" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A126,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A126,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H126" s="18">
@@ -8630,7 +8630,7 @@
         <v>0.499</v>
       </c>
       <c r="G127" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A127,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A127,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H127" s="31">
@@ -8663,7 +8663,7 @@
         <v>0.499</v>
       </c>
       <c r="G128" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A128,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A128,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H128" s="18">
@@ -8696,7 +8696,7 @@
         <v>0.499</v>
       </c>
       <c r="G129" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A129,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A129,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H129" s="31">
@@ -8729,7 +8729,7 @@
         <v>0.499</v>
       </c>
       <c r="G130" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A130,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A130,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H130" s="18">
@@ -8762,7 +8762,7 @@
         <v>0.499</v>
       </c>
       <c r="G131" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A131,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A131,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H131" s="31">
@@ -8795,7 +8795,7 @@
         <v>0.5</v>
       </c>
       <c r="G132" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A132,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A132,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H132" s="18">
@@ -8828,7 +8828,7 @@
         <v>0.499</v>
       </c>
       <c r="G133" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A133,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A133,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H133" s="31">
@@ -8861,7 +8861,7 @@
         <v>0.5</v>
       </c>
       <c r="G134" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A134,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A134,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H134" s="18">
@@ -8894,7 +8894,7 @@
         <v>0.499</v>
       </c>
       <c r="G135" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A135,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A135,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H135" s="31">
@@ -8927,7 +8927,7 @@
         <v>0.499</v>
       </c>
       <c r="G136" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A136,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A136,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H136" s="18">
@@ -8960,7 +8960,7 @@
         <v>0.5</v>
       </c>
       <c r="G137" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A137,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A137,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H137" s="31">
@@ -8993,7 +8993,7 @@
         <v>0.498</v>
       </c>
       <c r="G138" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A138,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A138,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H138" s="18">
@@ -9026,7 +9026,7 @@
         <v>0.498</v>
       </c>
       <c r="G139" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A139,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A139,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H139" s="31">
@@ -9059,7 +9059,7 @@
         <v>0.498</v>
       </c>
       <c r="G140" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A140,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A140,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H140" s="18">
@@ -9092,7 +9092,7 @@
         <v>0.498</v>
       </c>
       <c r="G141" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A141,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A141,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H141" s="31">
@@ -9125,7 +9125,7 @@
         <v>0.498</v>
       </c>
       <c r="G142" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A142,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A142,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H142" s="18">
@@ -9158,7 +9158,7 @@
         <v>0.498</v>
       </c>
       <c r="G143" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A143,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A143,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H143" s="31">
@@ -9191,7 +9191,7 @@
         <v>0.498</v>
       </c>
       <c r="G144" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A144,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A144,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H144" s="18">
@@ -9224,7 +9224,7 @@
         <v>0.498</v>
       </c>
       <c r="G145" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A145,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A145,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H145" s="31">
@@ -9257,7 +9257,7 @@
         <v>0.498</v>
       </c>
       <c r="G146" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A146,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A146,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H146" s="18">
@@ -9290,7 +9290,7 @@
         <v>0.498</v>
       </c>
       <c r="G147" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A147,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A147,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H147" s="31">
@@ -9323,7 +9323,7 @@
         <v>0.498</v>
       </c>
       <c r="G148" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A148,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A148,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H148" s="18">
@@ -9356,7 +9356,7 @@
         <v>0.498</v>
       </c>
       <c r="G149" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A149,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A149,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H149" s="31">
@@ -9389,7 +9389,7 @@
         <v>0.498</v>
       </c>
       <c r="G150" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A150,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A150,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H150" s="18">
@@ -9422,7 +9422,7 @@
         <v>0.498</v>
       </c>
       <c r="G151" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A151,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A151,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H151" s="31">
@@ -9455,7 +9455,7 @@
         <v>0.498</v>
       </c>
       <c r="G152" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A152,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A152,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H152" s="18">
@@ -9488,7 +9488,7 @@
         <v>0.498</v>
       </c>
       <c r="G153" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A153,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A153,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H153" s="31">
@@ -9521,7 +9521,7 @@
         <v>0.498</v>
       </c>
       <c r="G154" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A154,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A154,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H154" s="18">
@@ -9554,7 +9554,7 @@
         <v>0.498</v>
       </c>
       <c r="G155" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A155,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A155,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H155" s="31">
@@ -9587,7 +9587,7 @@
         <v>0.498</v>
       </c>
       <c r="G156" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A156,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A156,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H156" s="18">
@@ -9620,7 +9620,7 @@
         <v>0.498</v>
       </c>
       <c r="G157" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A157,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A157,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H157" s="31">
@@ -9653,7 +9653,7 @@
         <v>0.498</v>
       </c>
       <c r="G158" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A158,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A158,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H158" s="18">
@@ -9686,7 +9686,7 @@
         <v>0.498</v>
       </c>
       <c r="G159" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A159,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A159,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H159" s="31">
@@ -9719,7 +9719,7 @@
         <v>0.498</v>
       </c>
       <c r="G160" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A160,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A160,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H160" s="18">
@@ -9752,7 +9752,7 @@
         <v>0.498</v>
       </c>
       <c r="G161" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A161,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A161,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H161" s="31">
@@ -9785,7 +9785,7 @@
         <v>0.498</v>
       </c>
       <c r="G162" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A162,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A162,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H162" s="18">
@@ -9818,7 +9818,7 @@
         <v>0.498</v>
       </c>
       <c r="G163" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A163,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A163,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H163" s="31">
@@ -9851,7 +9851,7 @@
         <v>0.498</v>
       </c>
       <c r="G164" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A164,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A164,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H164" s="18">
@@ -9884,7 +9884,7 @@
         <v>0.498</v>
       </c>
       <c r="G165" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A165,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A165,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H165" s="31">
@@ -9917,7 +9917,7 @@
         <v>0.498</v>
       </c>
       <c r="G166" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A166,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A166,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H166" s="18">
@@ -9950,7 +9950,7 @@
         <v>0.498</v>
       </c>
       <c r="G167" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A167,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A167,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H167" s="31">
@@ -9983,7 +9983,7 @@
         <v>0.498</v>
       </c>
       <c r="G168" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A168,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A168,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H168" s="18">
@@ -10016,7 +10016,7 @@
         <v>0.498</v>
       </c>
       <c r="G169" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A169,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A169,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H169" s="31">
@@ -10049,7 +10049,7 @@
         <v>0.498</v>
       </c>
       <c r="G170" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A170,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A170,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H170" s="18">
@@ -10082,7 +10082,7 @@
         <v>0.498</v>
       </c>
       <c r="G171" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A171,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A171,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H171" s="31">
@@ -10115,7 +10115,7 @@
         <v>0.498</v>
       </c>
       <c r="G172" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A172,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A172,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H172" s="18">
@@ -10148,7 +10148,7 @@
         <v>0.498</v>
       </c>
       <c r="G173" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A173,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A173,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H173" s="31">
@@ -10181,7 +10181,7 @@
         <v>0.498</v>
       </c>
       <c r="G174" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A174,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A174,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H174" s="18">
@@ -10214,7 +10214,7 @@
         <v>0.498</v>
       </c>
       <c r="G175" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A175,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A175,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H175" s="31">
@@ -10247,7 +10247,7 @@
         <v>0.498</v>
       </c>
       <c r="G176" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A176,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A176,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H176" s="18">
@@ -10280,7 +10280,7 @@
         <v>0.498</v>
       </c>
       <c r="G177" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A177,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A177,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H177" s="31">
@@ -10313,7 +10313,7 @@
         <v>0.498</v>
       </c>
       <c r="G178" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A178,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A178,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H178" s="18">
@@ -10346,7 +10346,7 @@
         <v>0.498</v>
       </c>
       <c r="G179" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A179,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A179,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H179" s="31">
@@ -10379,7 +10379,7 @@
         <v>0.498</v>
       </c>
       <c r="G180" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A180,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A180,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H180" s="18">
@@ -10412,7 +10412,7 @@
         <v>0.498</v>
       </c>
       <c r="G181" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A181,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A181,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H181" s="31">
@@ -10445,7 +10445,7 @@
         <v>0.498</v>
       </c>
       <c r="G182" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A182,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A182,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H182" s="18">
@@ -10478,7 +10478,7 @@
         <v>0.498</v>
       </c>
       <c r="G183" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A183,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A183,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H183" s="31">
@@ -10511,7 +10511,7 @@
         <v>0.498</v>
       </c>
       <c r="G184" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A184,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A184,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H184" s="18">
@@ -10544,7 +10544,7 @@
         <v>0.498</v>
       </c>
       <c r="G185" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A185,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A185,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H185" s="31">
@@ -10577,7 +10577,7 @@
         <v>0.498</v>
       </c>
       <c r="G186" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A186,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A186,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H186" s="18">
@@ -10610,7 +10610,7 @@
         <v>0.498</v>
       </c>
       <c r="G187" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A187,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A187,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H187" s="31">
@@ -10643,7 +10643,7 @@
         <v>0.498</v>
       </c>
       <c r="G188" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A188,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A188,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H188" s="18">
@@ -10676,7 +10676,7 @@
         <v>0.4970000000000001</v>
       </c>
       <c r="G189" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A189,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A189,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H189" s="31">
@@ -10709,7 +10709,7 @@
         <v>0.498</v>
       </c>
       <c r="G190" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A190,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A190,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H190" s="18">
@@ -10742,7 +10742,7 @@
         <v>0.498</v>
       </c>
       <c r="G191" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A191,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A191,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H191" s="31">
@@ -10775,7 +10775,7 @@
         <v>0.498</v>
       </c>
       <c r="G192" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A192,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A192,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H192" s="18">
@@ -10808,7 +10808,7 @@
         <v>0.498</v>
       </c>
       <c r="G193" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A193,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A193,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H193" s="31">
@@ -10841,7 +10841,7 @@
         <v>0.498</v>
       </c>
       <c r="G194" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A194,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A194,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H194" s="18">
@@ -10874,7 +10874,7 @@
         <v>0.498</v>
       </c>
       <c r="G195" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A195,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A195,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H195" s="31">
@@ -10907,7 +10907,7 @@
         <v>0.498</v>
       </c>
       <c r="G196" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A196,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A196,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H196" s="18">
@@ -10940,7 +10940,7 @@
         <v>0.498</v>
       </c>
       <c r="G197" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A197,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A197,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H197" s="31">
@@ -10973,7 +10973,7 @@
         <v>0.498</v>
       </c>
       <c r="G198" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A198,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A198,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H198" s="18">
@@ -11006,7 +11006,7 @@
         <v>0.498</v>
       </c>
       <c r="G199" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A199,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A199,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H199" s="31">
@@ -11039,7 +11039,7 @@
         <v>0.498</v>
       </c>
       <c r="G200" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A200,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A200,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H200" s="18">
@@ -11072,7 +11072,7 @@
         <v>0.498</v>
       </c>
       <c r="G201" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A201,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A201,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H201" s="31">
@@ -11105,7 +11105,7 @@
         <v>0.498</v>
       </c>
       <c r="G202" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A202,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A202,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H202" s="18">
@@ -11138,7 +11138,7 @@
         <v>0.498</v>
       </c>
       <c r="G203" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A203,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A203,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H203" s="31">
@@ -11171,7 +11171,7 @@
         <v>0.498</v>
       </c>
       <c r="G204" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A204,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A204,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H204" s="18">
@@ -11204,7 +11204,7 @@
         <v>0.498</v>
       </c>
       <c r="G205" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A205,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A205,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H205" s="31">
@@ -11237,7 +11237,7 @@
         <v>0.498</v>
       </c>
       <c r="G206" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A206,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A206,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H206" s="18">
@@ -11270,7 +11270,7 @@
         <v>0.498</v>
       </c>
       <c r="G207" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A207,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A207,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H207" s="31">
@@ -11303,7 +11303,7 @@
         <v>0.498</v>
       </c>
       <c r="G208" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A208,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A208,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H208" s="18">
@@ -11336,7 +11336,7 @@
         <v>0.498</v>
       </c>
       <c r="G209" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A209,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A209,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H209" s="31">
@@ -11369,7 +11369,7 @@
         <v>0.498</v>
       </c>
       <c r="G210" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A210,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A210,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H210" s="18">
@@ -11402,7 +11402,7 @@
         <v>0.498</v>
       </c>
       <c r="G211" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A211,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A211,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H211" s="31">
@@ -11435,7 +11435,7 @@
         <v>0.498</v>
       </c>
       <c r="G212" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A212,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A212,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H212" s="18">
@@ -11468,7 +11468,7 @@
         <v>0.498</v>
       </c>
       <c r="G213" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A213,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A213,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H213" s="31">
@@ -11501,7 +11501,7 @@
         <v>0.498</v>
       </c>
       <c r="G214" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A214,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A214,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H214" s="18">
@@ -11534,7 +11534,7 @@
         <v>0.499</v>
       </c>
       <c r="G215" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A215,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A215,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H215" s="31">
@@ -11567,7 +11567,7 @@
         <v>0.498</v>
       </c>
       <c r="G216" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A216,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A216,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H216" s="18">
@@ -11600,7 +11600,7 @@
         <v>0.498</v>
       </c>
       <c r="G217" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A217,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A217,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H217" s="31">
@@ -11633,7 +11633,7 @@
         <v>0.498</v>
       </c>
       <c r="G218" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A218,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A218,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H218" s="18">
@@ -11666,7 +11666,7 @@
         <v>0.498</v>
       </c>
       <c r="G219" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A219,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A219,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H219" s="31">
@@ -11699,7 +11699,7 @@
         <v>0.498</v>
       </c>
       <c r="G220" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A220,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A220,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H220" s="18">
@@ -11732,7 +11732,7 @@
         <v>0.498</v>
       </c>
       <c r="G221" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A221,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A221,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H221" s="31">
@@ -11765,7 +11765,7 @@
         <v>0.498</v>
       </c>
       <c r="G222" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A222,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A222,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H222" s="18">
@@ -11798,7 +11798,7 @@
         <v>0.499</v>
       </c>
       <c r="G223" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A223,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A223,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H223" s="31">
@@ -11831,7 +11831,7 @@
         <v>0.498</v>
       </c>
       <c r="G224" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A224,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A224,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H224" s="18">
@@ -11864,7 +11864,7 @@
         <v>0.498</v>
       </c>
       <c r="G225" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A225,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A225,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H225" s="31">
@@ -11897,7 +11897,7 @@
         <v>0.498</v>
       </c>
       <c r="G226" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A226,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A226,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H226" s="18">
@@ -11930,7 +11930,7 @@
         <v>0.499</v>
       </c>
       <c r="G227" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A227,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A227,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H227" s="31">
@@ -11963,7 +11963,7 @@
         <v>0.498</v>
       </c>
       <c r="G228" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A228,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A228,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H228" s="18">
@@ -11996,7 +11996,7 @@
         <v>0.498</v>
       </c>
       <c r="G229" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A229,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A229,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H229" s="31">
@@ -12029,7 +12029,7 @@
         <v>0.498</v>
       </c>
       <c r="G230" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A230,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A230,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H230" s="18">
@@ -12062,7 +12062,7 @@
         <v>0.498</v>
       </c>
       <c r="G231" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A231,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A231,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H231" s="31">
@@ -12095,7 +12095,7 @@
         <v>0.498</v>
       </c>
       <c r="G232" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A232,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A232,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H232" s="18">
@@ -12128,7 +12128,7 @@
         <v>0.498</v>
       </c>
       <c r="G233" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A233,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A233,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H233" s="31">
@@ -12161,7 +12161,7 @@
         <v>0.498</v>
       </c>
       <c r="G234" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A234,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A234,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H234" s="18">
@@ -12194,7 +12194,7 @@
         <v>0.499</v>
       </c>
       <c r="G235" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A235,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A235,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H235" s="31">
@@ -12227,7 +12227,7 @@
         <v>0.498</v>
       </c>
       <c r="G236" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A236,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A236,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H236" s="18">
@@ -12260,7 +12260,7 @@
         <v>0.498</v>
       </c>
       <c r="G237" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A237,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A237,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H237" s="31">
@@ -12293,7 +12293,7 @@
         <v>0.498</v>
       </c>
       <c r="G238" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A238,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A238,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H238" s="18">
@@ -12326,7 +12326,7 @@
         <v>0.498</v>
       </c>
       <c r="G239" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A239,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A239,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H239" s="31">
@@ -12359,7 +12359,7 @@
         <v>0.498</v>
       </c>
       <c r="G240" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A240,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A240,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H240" s="18">
@@ -12392,7 +12392,7 @@
         <v>0.498</v>
       </c>
       <c r="G241" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A241,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A241,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H241" s="31">
@@ -12425,7 +12425,7 @@
         <v>0.498</v>
       </c>
       <c r="G242" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A242,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A242,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H242" s="18">
@@ -12458,7 +12458,7 @@
         <v>0.498</v>
       </c>
       <c r="G243" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A243,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A243,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H243" s="31">
@@ -12491,7 +12491,7 @@
         <v>0.498</v>
       </c>
       <c r="G244" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A244,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A244,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H244" s="18">
@@ -12524,7 +12524,7 @@
         <v>0.498</v>
       </c>
       <c r="G245" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A245,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A245,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H245" s="31">
@@ -12557,7 +12557,7 @@
         <v>0.498</v>
       </c>
       <c r="G246" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A246,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A246,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H246" s="18">
@@ -12590,7 +12590,7 @@
         <v>0.498</v>
       </c>
       <c r="G247" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A247,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A247,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H247" s="31">
@@ -12623,7 +12623,7 @@
         <v>0.498</v>
       </c>
       <c r="G248" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A248,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A248,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H248" s="18">
@@ -12656,7 +12656,7 @@
         <v>0.498</v>
       </c>
       <c r="G249" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A249,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A249,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H249" s="31">
@@ -12689,7 +12689,7 @@
         <v>0.498</v>
       </c>
       <c r="G250" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A250,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A250,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H250" s="18">
@@ -12722,7 +12722,7 @@
         <v>0.498</v>
       </c>
       <c r="G251" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A251,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A251,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H251" s="31">
@@ -12755,7 +12755,7 @@
         <v>0.498</v>
       </c>
       <c r="G252" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A252,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A252,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H252" s="18">
@@ -12788,7 +12788,7 @@
         <v>0.498</v>
       </c>
       <c r="G253" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A253,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A253,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H253" s="31">
@@ -12821,7 +12821,7 @@
         <v>0.498</v>
       </c>
       <c r="G254" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A254,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A254,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H254" s="18">
@@ -12854,7 +12854,7 @@
         <v>0.498</v>
       </c>
       <c r="G255" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A255,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A255,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H255" s="31">
@@ -12887,7 +12887,7 @@
         <v>0.498</v>
       </c>
       <c r="G256" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A256,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A256,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H256" s="18">
@@ -12920,7 +12920,7 @@
         <v>0.498</v>
       </c>
       <c r="G257" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A257,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A257,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H257" s="31">
@@ -12953,7 +12953,7 @@
         <v>0.498</v>
       </c>
       <c r="G258" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A258,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A258,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H258" s="18">
@@ -12986,7 +12986,7 @@
         <v>0.498</v>
       </c>
       <c r="G259" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A259,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A259,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H259" s="31">
@@ -13019,7 +13019,7 @@
         <v>0.498</v>
       </c>
       <c r="G260" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A260,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A260,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H260" s="18">
@@ -13052,7 +13052,7 @@
         <v>0.498</v>
       </c>
       <c r="G261" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A261,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A261,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H261" s="31">
@@ -13085,7 +13085,7 @@
         <v>0.498</v>
       </c>
       <c r="G262" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A262,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A262,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H262" s="18">
@@ -13118,7 +13118,7 @@
         <v>0.498</v>
       </c>
       <c r="G263" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A263,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A263,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H263" s="31">
@@ -13151,7 +13151,7 @@
         <v>0.498</v>
       </c>
       <c r="G264" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A264,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A264,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H264" s="18">
@@ -13184,7 +13184,7 @@
         <v>0.498</v>
       </c>
       <c r="G265" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A265,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A265,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H265" s="31">
@@ -13217,7 +13217,7 @@
         <v>0.4970000000000001</v>
       </c>
       <c r="G266" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A266,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A266,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="H266" s="18">
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-20 19:27 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L271"/>
+  <dimension ref="A1:L272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-20 19:27 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>IFERROR(AVERAGE(E15:E271),"")</f>
+        <f>IFERROR(AVERAGE(E15:E272),"")</f>
         <v/>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>IFERROR(MAX(E15:E271),"")</f>
+        <f>IFERROR(MAX(E15:E272),"")</f>
         <v/>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
         </is>
       </c>
       <c r="B10" s="40">
-        <f>COUNT(D15:D271)</f>
+        <f>COUNT(D15:D272)</f>
         <v/>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
         </is>
       </c>
       <c r="B11" s="40">
-        <f>COUNT(A15:A271)-COUNT(D15:D271)</f>
+        <f>COUNT(A15:A272)-COUNT(D15:D272)</f>
         <v/>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         <v>46008</v>
       </c>
       <c r="B15" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A15,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A15,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A15,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A15,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C15" s="100">
@@ -14937,7 +14937,7 @@
         <v/>
       </c>
       <c r="F15" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A15,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A15,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A15,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A15,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G15" s="100">
@@ -14970,7 +14970,7 @@
         <v>46009</v>
       </c>
       <c r="B16" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A16,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A16,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A16,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A16,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C16" s="101">
@@ -14986,7 +14986,7 @@
         <v/>
       </c>
       <c r="F16" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A16,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A16,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A16,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A16,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G16" s="101">
@@ -15019,7 +15019,7 @@
         <v>46010</v>
       </c>
       <c r="B17" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A17,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A17,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A17,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A17,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C17" s="100">
@@ -15035,7 +15035,7 @@
         <v/>
       </c>
       <c r="F17" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A17,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A17,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A17,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A17,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G17" s="100">
@@ -15068,7 +15068,7 @@
         <v>46011</v>
       </c>
       <c r="B18" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A18,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A18,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A18,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A18,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C18" s="101">
@@ -15084,7 +15084,7 @@
         <v/>
       </c>
       <c r="F18" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A18,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A18,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A18,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A18,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G18" s="101">
@@ -15117,7 +15117,7 @@
         <v>46012</v>
       </c>
       <c r="B19" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A19,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A19,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A19,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A19,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C19" s="100">
@@ -15133,7 +15133,7 @@
         <v/>
       </c>
       <c r="F19" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A19,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A19,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A19,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A19,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G19" s="100">
@@ -15166,7 +15166,7 @@
         <v>46013</v>
       </c>
       <c r="B20" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A20,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A20,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A20,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A20,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C20" s="101">
@@ -15182,7 +15182,7 @@
         <v/>
       </c>
       <c r="F20" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A20,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A20,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A20,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A20,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G20" s="101">
@@ -15215,7 +15215,7 @@
         <v>46014</v>
       </c>
       <c r="B21" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A21,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A21,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A21,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A21,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C21" s="100">
@@ -15231,7 +15231,7 @@
         <v/>
       </c>
       <c r="F21" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A21,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A21,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A21,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A21,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G21" s="100">
@@ -15264,7 +15264,7 @@
         <v>46015</v>
       </c>
       <c r="B22" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A22,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A22,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A22,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A22,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C22" s="101">
@@ -15280,7 +15280,7 @@
         <v/>
       </c>
       <c r="F22" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A22,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A22,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A22,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A22,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G22" s="101">
@@ -15313,7 +15313,7 @@
         <v>46016</v>
       </c>
       <c r="B23" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A23,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A23,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A23,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A23,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C23" s="100">
@@ -15329,7 +15329,7 @@
         <v/>
       </c>
       <c r="F23" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A23,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A23,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A23,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A23,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G23" s="100">
@@ -15362,7 +15362,7 @@
         <v>46017</v>
       </c>
       <c r="B24" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A24,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A24,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A24,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A24,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C24" s="101">
@@ -15378,7 +15378,7 @@
         <v/>
       </c>
       <c r="F24" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A24,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A24,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A24,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A24,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G24" s="101">
@@ -15411,7 +15411,7 @@
         <v>46018</v>
       </c>
       <c r="B25" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A25,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A25,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A25,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A25,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C25" s="100">
@@ -15427,7 +15427,7 @@
         <v/>
       </c>
       <c r="F25" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A25,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A25,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A25,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A25,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G25" s="100">
@@ -15460,7 +15460,7 @@
         <v>46019</v>
       </c>
       <c r="B26" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A26,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A26,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A26,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A26,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C26" s="101">
@@ -15476,7 +15476,7 @@
         <v/>
       </c>
       <c r="F26" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A26,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A26,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A26,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A26,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G26" s="101">
@@ -15509,7 +15509,7 @@
         <v>46020</v>
       </c>
       <c r="B27" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A27,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A27,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A27,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A27,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C27" s="100">
@@ -15525,7 +15525,7 @@
         <v/>
       </c>
       <c r="F27" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A27,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A27,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A27,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A27,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G27" s="100">
@@ -15558,7 +15558,7 @@
         <v>46021</v>
       </c>
       <c r="B28" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A28,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A28,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A28,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A28,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C28" s="101">
@@ -15574,7 +15574,7 @@
         <v/>
       </c>
       <c r="F28" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A28,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A28,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A28,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A28,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G28" s="101">
@@ -15607,7 +15607,7 @@
         <v>46022</v>
       </c>
       <c r="B29" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A29,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A29,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A29,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A29,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C29" s="100">
@@ -15623,7 +15623,7 @@
         <v/>
       </c>
       <c r="F29" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A29,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A29,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A29,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A29,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G29" s="100">
@@ -15656,7 +15656,7 @@
         <v>46023</v>
       </c>
       <c r="B30" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A30,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A30,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A30,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A30,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C30" s="101">
@@ -15672,7 +15672,7 @@
         <v/>
       </c>
       <c r="F30" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A30,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A30,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A30,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A30,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G30" s="101">
@@ -15705,7 +15705,7 @@
         <v>46024</v>
       </c>
       <c r="B31" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A31,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A31,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A31,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A31,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C31" s="100">
@@ -15721,7 +15721,7 @@
         <v/>
       </c>
       <c r="F31" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A31,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A31,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A31,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A31,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G31" s="100">
@@ -15754,7 +15754,7 @@
         <v>46025</v>
       </c>
       <c r="B32" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A32,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A32,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A32,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A32,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C32" s="101">
@@ -15770,7 +15770,7 @@
         <v/>
       </c>
       <c r="F32" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A32,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A32,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A32,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A32,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G32" s="101">
@@ -15803,7 +15803,7 @@
         <v>46026</v>
       </c>
       <c r="B33" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A33,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A33,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A33,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A33,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C33" s="100">
@@ -15819,7 +15819,7 @@
         <v/>
       </c>
       <c r="F33" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A33,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A33,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A33,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A33,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G33" s="100">
@@ -15852,7 +15852,7 @@
         <v>46027</v>
       </c>
       <c r="B34" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A34,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A34,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A34,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A34,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C34" s="101">
@@ -15868,7 +15868,7 @@
         <v/>
       </c>
       <c r="F34" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A34,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A34,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A34,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A34,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G34" s="101">
@@ -15901,7 +15901,7 @@
         <v>46028</v>
       </c>
       <c r="B35" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A35,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A35,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A35,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A35,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C35" s="100">
@@ -15917,7 +15917,7 @@
         <v/>
       </c>
       <c r="F35" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A35,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A35,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A35,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A35,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G35" s="100">
@@ -15950,7 +15950,7 @@
         <v>46029</v>
       </c>
       <c r="B36" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A36,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A36,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A36,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C36" s="101">
@@ -15966,7 +15966,7 @@
         <v/>
       </c>
       <c r="F36" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A36,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A36,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A36,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A36,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G36" s="101">
@@ -15999,7 +15999,7 @@
         <v>46030</v>
       </c>
       <c r="B37" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A37,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A37,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A37,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C37" s="100">
@@ -16015,7 +16015,7 @@
         <v/>
       </c>
       <c r="F37" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A37,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A37,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A37,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A37,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G37" s="100">
@@ -16048,7 +16048,7 @@
         <v>46031</v>
       </c>
       <c r="B38" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A38,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A38,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A38,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C38" s="101">
@@ -16064,7 +16064,7 @@
         <v/>
       </c>
       <c r="F38" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A38,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A38,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A38,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A38,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G38" s="101">
@@ -16097,7 +16097,7 @@
         <v>46032</v>
       </c>
       <c r="B39" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A39,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A39,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A39,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C39" s="100">
@@ -16113,7 +16113,7 @@
         <v/>
       </c>
       <c r="F39" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A39,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A39,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A39,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A39,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G39" s="100">
@@ -16146,7 +16146,7 @@
         <v>46033</v>
       </c>
       <c r="B40" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A40,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A40,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A40,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C40" s="101">
@@ -16162,7 +16162,7 @@
         <v/>
       </c>
       <c r="F40" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A40,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A40,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A40,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A40,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G40" s="101">
@@ -16195,7 +16195,7 @@
         <v>46034</v>
       </c>
       <c r="B41" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A41,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A41,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A41,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C41" s="100">
@@ -16211,7 +16211,7 @@
         <v/>
       </c>
       <c r="F41" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A41,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A41,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A41,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A41,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G41" s="100">
@@ -16244,7 +16244,7 @@
         <v>46035</v>
       </c>
       <c r="B42" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A42,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A42,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A42,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C42" s="101">
@@ -16260,7 +16260,7 @@
         <v/>
       </c>
       <c r="F42" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A42,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A42,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A42,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A42,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G42" s="101">
@@ -16293,7 +16293,7 @@
         <v>46036</v>
       </c>
       <c r="B43" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A43,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A43,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A43,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C43" s="100">
@@ -16309,7 +16309,7 @@
         <v/>
       </c>
       <c r="F43" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A43,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A43,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A43,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A43,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G43" s="100">
@@ -16342,7 +16342,7 @@
         <v>46037</v>
       </c>
       <c r="B44" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A44,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A44,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A44,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C44" s="101">
@@ -16358,7 +16358,7 @@
         <v/>
       </c>
       <c r="F44" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A44,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A44,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A44,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A44,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G44" s="101">
@@ -16391,7 +16391,7 @@
         <v>46038</v>
       </c>
       <c r="B45" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A45,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A45,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A45,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C45" s="100">
@@ -16407,7 +16407,7 @@
         <v/>
       </c>
       <c r="F45" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A45,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A45,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A45,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A45,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G45" s="100">
@@ -16440,7 +16440,7 @@
         <v>46039</v>
       </c>
       <c r="B46" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A46,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A46,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A46,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C46" s="101">
@@ -16456,7 +16456,7 @@
         <v/>
       </c>
       <c r="F46" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A46,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A46,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A46,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A46,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G46" s="101">
@@ -16489,7 +16489,7 @@
         <v>46040</v>
       </c>
       <c r="B47" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A47,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A47,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A47,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C47" s="100">
@@ -16505,7 +16505,7 @@
         <v/>
       </c>
       <c r="F47" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A47,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A47,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A47,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A47,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G47" s="100">
@@ -16538,7 +16538,7 @@
         <v>46041</v>
       </c>
       <c r="B48" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A48,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A48,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A48,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C48" s="101">
@@ -16554,7 +16554,7 @@
         <v/>
       </c>
       <c r="F48" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A48,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A48,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A48,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A48,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G48" s="101">
@@ -16587,7 +16587,7 @@
         <v>46042</v>
       </c>
       <c r="B49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A49,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A49,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A49,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C49" s="100">
@@ -16603,7 +16603,7 @@
         <v/>
       </c>
       <c r="F49" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A49,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A49,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A49,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A49,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G49" s="100">
@@ -16636,7 +16636,7 @@
         <v>46043</v>
       </c>
       <c r="B50" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A50,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A50,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A50,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C50" s="101">
@@ -16652,7 +16652,7 @@
         <v/>
       </c>
       <c r="F50" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A50,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A50,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A50,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A50,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G50" s="101">
@@ -16685,7 +16685,7 @@
         <v>46044</v>
       </c>
       <c r="B51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A51,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A51,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A51,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C51" s="100">
@@ -16701,7 +16701,7 @@
         <v/>
       </c>
       <c r="F51" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A51,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A51,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A51,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A51,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G51" s="100">
@@ -16734,7 +16734,7 @@
         <v>46045</v>
       </c>
       <c r="B52" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A52,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A52,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A52,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C52" s="101">
@@ -16750,7 +16750,7 @@
         <v/>
       </c>
       <c r="F52" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A52,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A52,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A52,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A52,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G52" s="101">
@@ -16783,7 +16783,7 @@
         <v>46046</v>
       </c>
       <c r="B53" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A53,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A53,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A53,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C53" s="100">
@@ -16799,7 +16799,7 @@
         <v/>
       </c>
       <c r="F53" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A53,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A53,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A53,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A53,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G53" s="100">
@@ -16832,7 +16832,7 @@
         <v>46047</v>
       </c>
       <c r="B54" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A54,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A54,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A54,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C54" s="101">
@@ -16848,7 +16848,7 @@
         <v/>
       </c>
       <c r="F54" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A54,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A54,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A54,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A54,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G54" s="101">
@@ -16881,7 +16881,7 @@
         <v>46048</v>
       </c>
       <c r="B55" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A55,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A55,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A55,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C55" s="100">
@@ -16897,7 +16897,7 @@
         <v/>
       </c>
       <c r="F55" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A55,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A55,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A55,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A55,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G55" s="100">
@@ -16930,7 +16930,7 @@
         <v>46049</v>
       </c>
       <c r="B56" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A56,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A56,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A56,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C56" s="101">
@@ -16946,7 +16946,7 @@
         <v/>
       </c>
       <c r="F56" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A56,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A56,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A56,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A56,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G56" s="101">
@@ -16979,7 +16979,7 @@
         <v>46050</v>
       </c>
       <c r="B57" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A57,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A57,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A57,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C57" s="100">
@@ -16995,7 +16995,7 @@
         <v/>
       </c>
       <c r="F57" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A57,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A57,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A57,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A57,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G57" s="100">
@@ -17028,7 +17028,7 @@
         <v>46051</v>
       </c>
       <c r="B58" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A58,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A58,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A58,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C58" s="101">
@@ -17044,7 +17044,7 @@
         <v/>
       </c>
       <c r="F58" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A58,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A58,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A58,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A58,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G58" s="101">
@@ -17077,7 +17077,7 @@
         <v>46052</v>
       </c>
       <c r="B59" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A59,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A59,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A59,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C59" s="100">
@@ -17093,7 +17093,7 @@
         <v/>
       </c>
       <c r="F59" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A59,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A59,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A59,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A59,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G59" s="100">
@@ -17126,7 +17126,7 @@
         <v>46053</v>
       </c>
       <c r="B60" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A60,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A60,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A60,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C60" s="101">
@@ -17142,7 +17142,7 @@
         <v/>
       </c>
       <c r="F60" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A60,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A60,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A60,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A60,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G60" s="101">
@@ -17175,7 +17175,7 @@
         <v>46054</v>
       </c>
       <c r="B61" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A61,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A61,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A61,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C61" s="100">
@@ -17191,7 +17191,7 @@
         <v/>
       </c>
       <c r="F61" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A61,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A61,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A61,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A61,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G61" s="100">
@@ -17224,7 +17224,7 @@
         <v>46055</v>
       </c>
       <c r="B62" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A62,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A62,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A62,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C62" s="101">
@@ -17240,7 +17240,7 @@
         <v/>
       </c>
       <c r="F62" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A62,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A62,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A62,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A62,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G62" s="101">
@@ -17273,7 +17273,7 @@
         <v>46056</v>
       </c>
       <c r="B63" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A63,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A63,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A63,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C63" s="100">
@@ -17289,7 +17289,7 @@
         <v/>
       </c>
       <c r="F63" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A63,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A63,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A63,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A63,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G63" s="100">
@@ -17322,7 +17322,7 @@
         <v>46057</v>
       </c>
       <c r="B64" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A64,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A64,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A64,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C64" s="101">
@@ -17338,7 +17338,7 @@
         <v/>
       </c>
       <c r="F64" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A64,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A64,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A64,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A64,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G64" s="101">
@@ -17371,7 +17371,7 @@
         <v>46058</v>
       </c>
       <c r="B65" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A65,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A65,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A65,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C65" s="100">
@@ -17387,7 +17387,7 @@
         <v/>
       </c>
       <c r="F65" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A65,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A65,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A65,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A65,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G65" s="100">
@@ -17420,7 +17420,7 @@
         <v>46059</v>
       </c>
       <c r="B66" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A66,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A66,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A66,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C66" s="101">
@@ -17436,7 +17436,7 @@
         <v/>
       </c>
       <c r="F66" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A66,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A66,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A66,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A66,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G66" s="101">
@@ -17469,7 +17469,7 @@
         <v>46060</v>
       </c>
       <c r="B67" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A67,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A67,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A67,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C67" s="100">
@@ -17485,7 +17485,7 @@
         <v/>
       </c>
       <c r="F67" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A67,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A67,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A67,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A67,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G67" s="100">
@@ -17518,7 +17518,7 @@
         <v>46061</v>
       </c>
       <c r="B68" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A68,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A68,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A68,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C68" s="101">
@@ -17534,7 +17534,7 @@
         <v/>
       </c>
       <c r="F68" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A68,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A68,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A68,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A68,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G68" s="101">
@@ -17567,7 +17567,7 @@
         <v>46062</v>
       </c>
       <c r="B69" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A69,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A69,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A69,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C69" s="100">
@@ -17583,7 +17583,7 @@
         <v/>
       </c>
       <c r="F69" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A69,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A69,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A69,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A69,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G69" s="100">
@@ -17616,7 +17616,7 @@
         <v>46063</v>
       </c>
       <c r="B70" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A70,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A70,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A70,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C70" s="101">
@@ -17632,7 +17632,7 @@
         <v/>
       </c>
       <c r="F70" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A70,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A70,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A70,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A70,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G70" s="101">
@@ -17665,7 +17665,7 @@
         <v>46064</v>
       </c>
       <c r="B71" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A71,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A71,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A71,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C71" s="100">
@@ -17681,7 +17681,7 @@
         <v/>
       </c>
       <c r="F71" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A71,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A71,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A71,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A71,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G71" s="100">
@@ -17714,7 +17714,7 @@
         <v>46065</v>
       </c>
       <c r="B72" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A72,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A72,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A72,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C72" s="101">
@@ -17730,7 +17730,7 @@
         <v/>
       </c>
       <c r="F72" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A72,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A72,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A72,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A72,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G72" s="101">
@@ -17763,7 +17763,7 @@
         <v>46066</v>
       </c>
       <c r="B73" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A73,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A73,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A73,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C73" s="100">
@@ -17779,7 +17779,7 @@
         <v/>
       </c>
       <c r="F73" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A73,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A73,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A73,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A73,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G73" s="100">
@@ -17812,7 +17812,7 @@
         <v>46067</v>
       </c>
       <c r="B74" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A74,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A74,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A74,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C74" s="101">
@@ -17828,7 +17828,7 @@
         <v/>
       </c>
       <c r="F74" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A74,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A74,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A74,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A74,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G74" s="101">
@@ -17861,7 +17861,7 @@
         <v>46068</v>
       </c>
       <c r="B75" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A75,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A75,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A75,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C75" s="100">
@@ -17877,7 +17877,7 @@
         <v/>
       </c>
       <c r="F75" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A75,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A75,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A75,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A75,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G75" s="100">
@@ -17910,7 +17910,7 @@
         <v>46069</v>
       </c>
       <c r="B76" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A76,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A76,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A76,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C76" s="101">
@@ -17926,7 +17926,7 @@
         <v/>
       </c>
       <c r="F76" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A76,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A76,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A76,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A76,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G76" s="101">
@@ -17959,7 +17959,7 @@
         <v>46070</v>
       </c>
       <c r="B77" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A77,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A77,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A77,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C77" s="100">
@@ -17975,7 +17975,7 @@
         <v/>
       </c>
       <c r="F77" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A77,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A77,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A77,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A77,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G77" s="100">
@@ -18008,7 +18008,7 @@
         <v>46071</v>
       </c>
       <c r="B78" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A78,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A78,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A78,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C78" s="101">
@@ -18024,7 +18024,7 @@
         <v/>
       </c>
       <c r="F78" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A78,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A78,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A78,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A78,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G78" s="101">
@@ -18057,7 +18057,7 @@
         <v>46072</v>
       </c>
       <c r="B79" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A79,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A79,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A79,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C79" s="100">
@@ -18073,7 +18073,7 @@
         <v/>
       </c>
       <c r="F79" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A79,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A79,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A79,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A79,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G79" s="100">
@@ -18106,7 +18106,7 @@
         <v>46073</v>
       </c>
       <c r="B80" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A80,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A80,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A80,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C80" s="101">
@@ -18122,7 +18122,7 @@
         <v/>
       </c>
       <c r="F80" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A80,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A80,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A80,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A80,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G80" s="101">
@@ -18155,7 +18155,7 @@
         <v>46074</v>
       </c>
       <c r="B81" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A81,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A81,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A81,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C81" s="100">
@@ -18171,7 +18171,7 @@
         <v/>
       </c>
       <c r="F81" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A81,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A81,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A81,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A81,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G81" s="100">
@@ -18204,7 +18204,7 @@
         <v>46075</v>
       </c>
       <c r="B82" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A82,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A82,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A82,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C82" s="101">
@@ -18220,7 +18220,7 @@
         <v/>
       </c>
       <c r="F82" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A82,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A82,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A82,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A82,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G82" s="101">
@@ -18253,7 +18253,7 @@
         <v>46076</v>
       </c>
       <c r="B83" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A83,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A83,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A83,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C83" s="100">
@@ -18269,7 +18269,7 @@
         <v/>
       </c>
       <c r="F83" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A83,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A83,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A83,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A83,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G83" s="100">
@@ -18302,7 +18302,7 @@
         <v>46077</v>
       </c>
       <c r="B84" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A84,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A84,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A84,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C84" s="101">
@@ -18318,7 +18318,7 @@
         <v/>
       </c>
       <c r="F84" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A84,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A84,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A84,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A84,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G84" s="101">
@@ -18351,7 +18351,7 @@
         <v>46078</v>
       </c>
       <c r="B85" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A85,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A85,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A85,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C85" s="100">
@@ -18367,7 +18367,7 @@
         <v/>
       </c>
       <c r="F85" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A85,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A85,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A85,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A85,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G85" s="100">
@@ -18400,7 +18400,7 @@
         <v>46079</v>
       </c>
       <c r="B86" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A86,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A86,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A86,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C86" s="101">
@@ -18416,7 +18416,7 @@
         <v/>
       </c>
       <c r="F86" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A86,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A86,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A86,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A86,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G86" s="101">
@@ -18449,7 +18449,7 @@
         <v>46080</v>
       </c>
       <c r="B87" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A87,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A87,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A87,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C87" s="100">
@@ -18465,7 +18465,7 @@
         <v/>
       </c>
       <c r="F87" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A87,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A87,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A87,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A87,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G87" s="100">
@@ -18498,7 +18498,7 @@
         <v>46081</v>
       </c>
       <c r="B88" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A88,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A88,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A88,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C88" s="101">
@@ -18514,7 +18514,7 @@
         <v/>
       </c>
       <c r="F88" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A88,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A88,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A88,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A88,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G88" s="101">
@@ -18547,7 +18547,7 @@
         <v>46082</v>
       </c>
       <c r="B89" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A89,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A89,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A89,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C89" s="100">
@@ -18563,7 +18563,7 @@
         <v/>
       </c>
       <c r="F89" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A89,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A89,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A89,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A89,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G89" s="100">
@@ -18596,7 +18596,7 @@
         <v>46083</v>
       </c>
       <c r="B90" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A90,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A90,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A90,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C90" s="101">
@@ -18612,7 +18612,7 @@
         <v/>
       </c>
       <c r="F90" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A90,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A90,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A90,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A90,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G90" s="101">
@@ -18645,7 +18645,7 @@
         <v>46084</v>
       </c>
       <c r="B91" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A91,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A91,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A91,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C91" s="100">
@@ -18661,7 +18661,7 @@
         <v/>
       </c>
       <c r="F91" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A91,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A91,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A91,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A91,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G91" s="100">
@@ -18694,7 +18694,7 @@
         <v>46085</v>
       </c>
       <c r="B92" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A92,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A92,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A92,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C92" s="101">
@@ -18710,7 +18710,7 @@
         <v/>
       </c>
       <c r="F92" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A92,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A92,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A92,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A92,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G92" s="101">
@@ -18743,7 +18743,7 @@
         <v>46086</v>
       </c>
       <c r="B93" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A93,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A93,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A93,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C93" s="100">
@@ -18759,7 +18759,7 @@
         <v/>
       </c>
       <c r="F93" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A93,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A93,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A93,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A93,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G93" s="100">
@@ -18792,7 +18792,7 @@
         <v>46087</v>
       </c>
       <c r="B94" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A94,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A94,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A94,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C94" s="101">
@@ -18808,7 +18808,7 @@
         <v/>
       </c>
       <c r="F94" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A94,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A94,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A94,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A94,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G94" s="101">
@@ -18841,7 +18841,7 @@
         <v>46088</v>
       </c>
       <c r="B95" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A95,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A95,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A95,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C95" s="100">
@@ -18857,7 +18857,7 @@
         <v/>
       </c>
       <c r="F95" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A95,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A95,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A95,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A95,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G95" s="100">
@@ -18890,7 +18890,7 @@
         <v>46089</v>
       </c>
       <c r="B96" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A96,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A96,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A96,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C96" s="101">
@@ -18906,7 +18906,7 @@
         <v/>
       </c>
       <c r="F96" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A96,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A96,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A96,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A96,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G96" s="101">
@@ -18939,7 +18939,7 @@
         <v>46090</v>
       </c>
       <c r="B97" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A97,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A97,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A97,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C97" s="100">
@@ -18955,7 +18955,7 @@
         <v/>
       </c>
       <c r="F97" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A97,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A97,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A97,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A97,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G97" s="100">
@@ -18988,7 +18988,7 @@
         <v>46091</v>
       </c>
       <c r="B98" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A98,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A98,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A98,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C98" s="101">
@@ -19004,7 +19004,7 @@
         <v/>
       </c>
       <c r="F98" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A98,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A98,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A98,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A98,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G98" s="101">
@@ -19037,7 +19037,7 @@
         <v>46092</v>
       </c>
       <c r="B99" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A99,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A99,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A99,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C99" s="100">
@@ -19053,7 +19053,7 @@
         <v/>
       </c>
       <c r="F99" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A99,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A99,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A99,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A99,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G99" s="100">
@@ -19086,7 +19086,7 @@
         <v>46093</v>
       </c>
       <c r="B100" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A100,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A100,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A100,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C100" s="101">
@@ -19102,7 +19102,7 @@
         <v/>
       </c>
       <c r="F100" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A100,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A100,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A100,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A100,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G100" s="101">
@@ -19135,7 +19135,7 @@
         <v>46094</v>
       </c>
       <c r="B101" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A101,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A101,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A101,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C101" s="100">
@@ -19151,7 +19151,7 @@
         <v/>
       </c>
       <c r="F101" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A101,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A101,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A101,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A101,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G101" s="100">
@@ -19184,7 +19184,7 @@
         <v>46095</v>
       </c>
       <c r="B102" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A102,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A102,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A102,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C102" s="101">
@@ -19200,7 +19200,7 @@
         <v/>
       </c>
       <c r="F102" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A102,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A102,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A102,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A102,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G102" s="101">
@@ -19233,7 +19233,7 @@
         <v>46096</v>
       </c>
       <c r="B103" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A103,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A103,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A103,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C103" s="100">
@@ -19249,7 +19249,7 @@
         <v/>
       </c>
       <c r="F103" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A103,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A103,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A103,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A103,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G103" s="100">
@@ -19282,7 +19282,7 @@
         <v>46097</v>
       </c>
       <c r="B104" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A104,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A104,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A104,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C104" s="101">
@@ -19298,7 +19298,7 @@
         <v/>
       </c>
       <c r="F104" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A104,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A104,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A104,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A104,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G104" s="101">
@@ -19331,7 +19331,7 @@
         <v>46098</v>
       </c>
       <c r="B105" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A105,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A105,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A105,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C105" s="100">
@@ -19347,7 +19347,7 @@
         <v/>
       </c>
       <c r="F105" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A105,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A105,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A105,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A105,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G105" s="100">
@@ -19380,7 +19380,7 @@
         <v>46099</v>
       </c>
       <c r="B106" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A106,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A106,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A106,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C106" s="101">
@@ -19396,7 +19396,7 @@
         <v/>
       </c>
       <c r="F106" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A106,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A106,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A106,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A106,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G106" s="101">
@@ -19429,7 +19429,7 @@
         <v>46100</v>
       </c>
       <c r="B107" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A107,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A107,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A107,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C107" s="100">
@@ -19445,7 +19445,7 @@
         <v/>
       </c>
       <c r="F107" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A107,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A107,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A107,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A107,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G107" s="100">
@@ -19478,7 +19478,7 @@
         <v>46101</v>
       </c>
       <c r="B108" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A108,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A108,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A108,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C108" s="101">
@@ -19494,7 +19494,7 @@
         <v/>
       </c>
       <c r="F108" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A108,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A108,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A108,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A108,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G108" s="101">
@@ -19527,7 +19527,7 @@
         <v>46102</v>
       </c>
       <c r="B109" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A109,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A109,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A109,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C109" s="100">
@@ -19543,7 +19543,7 @@
         <v/>
       </c>
       <c r="F109" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A109,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A109,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A109,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A109,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G109" s="100">
@@ -19576,7 +19576,7 @@
         <v>46103</v>
       </c>
       <c r="B110" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A110,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A110,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A110,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C110" s="101">
@@ -19592,7 +19592,7 @@
         <v/>
       </c>
       <c r="F110" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A110,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A110,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A110,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A110,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G110" s="101">
@@ -19625,7 +19625,7 @@
         <v>46104</v>
       </c>
       <c r="B111" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A111,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A111,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A111,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C111" s="100">
@@ -19641,7 +19641,7 @@
         <v/>
       </c>
       <c r="F111" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A111,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A111,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A111,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A111,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G111" s="100">
@@ -19674,7 +19674,7 @@
         <v>46105</v>
       </c>
       <c r="B112" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A112,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A112,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A112,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C112" s="101">
@@ -19690,7 +19690,7 @@
         <v/>
       </c>
       <c r="F112" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A112,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A112,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A112,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A112,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G112" s="101">
@@ -19723,7 +19723,7 @@
         <v>46106</v>
       </c>
       <c r="B113" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A113,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A113,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A113,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C113" s="100">
@@ -19739,7 +19739,7 @@
         <v/>
       </c>
       <c r="F113" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A113,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A113,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A113,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A113,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G113" s="100">
@@ -19772,7 +19772,7 @@
         <v>46107</v>
       </c>
       <c r="B114" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A114,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A114,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A114,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C114" s="101">
@@ -19788,7 +19788,7 @@
         <v/>
       </c>
       <c r="F114" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A114,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A114,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A114,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A114,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G114" s="101">
@@ -19821,7 +19821,7 @@
         <v>46108</v>
       </c>
       <c r="B115" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A115,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A115,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A115,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C115" s="100">
@@ -19837,7 +19837,7 @@
         <v/>
       </c>
       <c r="F115" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A115,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A115,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A115,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A115,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G115" s="100">
@@ -19870,7 +19870,7 @@
         <v>46109</v>
       </c>
       <c r="B116" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A116,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A116,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A116,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C116" s="101">
@@ -19886,7 +19886,7 @@
         <v/>
       </c>
       <c r="F116" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A116,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A116,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A116,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A116,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G116" s="101">
@@ -19919,7 +19919,7 @@
         <v>46110</v>
       </c>
       <c r="B117" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A117,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A117,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A117,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C117" s="100">
@@ -19935,7 +19935,7 @@
         <v/>
       </c>
       <c r="F117" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A117,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A117,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A117,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A117,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G117" s="100">
@@ -19968,7 +19968,7 @@
         <v>46121</v>
       </c>
       <c r="B118" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A118,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A118,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A118,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C118" s="101">
@@ -19984,7 +19984,7 @@
         <v/>
       </c>
       <c r="F118" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A118,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A118,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A118,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A118,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G118" s="101">
@@ -20017,7 +20017,7 @@
         <v>46130</v>
       </c>
       <c r="B119" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A119,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A119,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A119,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C119" s="100">
@@ -20033,7 +20033,7 @@
         <v/>
       </c>
       <c r="F119" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A119,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A119,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A119,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A119,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G119" s="100">
@@ -20066,7 +20066,7 @@
         <v>46134</v>
       </c>
       <c r="B120" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A120,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A120,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A120,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C120" s="101">
@@ -20082,7 +20082,7 @@
         <v/>
       </c>
       <c r="F120" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A120,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A120,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A120,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A120,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G120" s="101">
@@ -20115,7 +20115,7 @@
         <v>46135</v>
       </c>
       <c r="B121" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A121,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A121,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A121,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C121" s="100">
@@ -20131,7 +20131,7 @@
         <v/>
       </c>
       <c r="F121" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A121,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A121,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A121,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A121,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G121" s="100">
@@ -20164,7 +20164,7 @@
         <v>46136</v>
       </c>
       <c r="B122" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A122,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A122,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A122,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C122" s="101">
@@ -20180,7 +20180,7 @@
         <v/>
       </c>
       <c r="F122" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A122,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A122,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A122,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A122,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G122" s="101">
@@ -20213,7 +20213,7 @@
         <v>46137</v>
       </c>
       <c r="B123" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A123,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A123,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A123,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C123" s="100">
@@ -20229,7 +20229,7 @@
         <v/>
       </c>
       <c r="F123" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A123,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A123,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A123,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A123,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G123" s="100">
@@ -20262,7 +20262,7 @@
         <v>46138</v>
       </c>
       <c r="B124" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A124,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A124,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A124,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C124" s="101">
@@ -20278,7 +20278,7 @@
         <v/>
       </c>
       <c r="F124" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A124,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A124,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A124,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A124,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G124" s="101">
@@ -20311,7 +20311,7 @@
         <v>46139</v>
       </c>
       <c r="B125" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A125,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A125,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A125,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C125" s="100">
@@ -20327,7 +20327,7 @@
         <v/>
       </c>
       <c r="F125" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A125,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A125,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A125,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A125,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G125" s="100">
@@ -20360,7 +20360,7 @@
         <v>46140</v>
       </c>
       <c r="B126" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A126,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A126,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A126,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C126" s="101">
@@ -20376,7 +20376,7 @@
         <v/>
       </c>
       <c r="F126" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A126,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A126,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A126,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A126,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G126" s="101">
@@ -20409,7 +20409,7 @@
         <v>46141</v>
       </c>
       <c r="B127" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A127,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A127,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A127,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C127" s="100">
@@ -20425,7 +20425,7 @@
         <v/>
       </c>
       <c r="F127" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A127,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A127,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A127,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A127,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G127" s="100">
@@ -20458,7 +20458,7 @@
         <v>46142</v>
       </c>
       <c r="B128" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A128,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A128,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A128,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C128" s="101">
@@ -20474,7 +20474,7 @@
         <v/>
       </c>
       <c r="F128" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A128,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A128,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A128,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A128,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G128" s="101">
@@ -20507,7 +20507,7 @@
         <v>46143</v>
       </c>
       <c r="B129" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A129,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A129,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A129,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C129" s="100">
@@ -20523,7 +20523,7 @@
         <v/>
       </c>
       <c r="F129" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A129,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A129,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A129,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A129,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G129" s="100">
@@ -20556,7 +20556,7 @@
         <v>46144</v>
       </c>
       <c r="B130" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A130,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A130,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A130,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C130" s="101">
@@ -20572,7 +20572,7 @@
         <v/>
       </c>
       <c r="F130" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A130,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A130,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A130,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A130,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G130" s="101">
@@ -20605,7 +20605,7 @@
         <v>46145</v>
       </c>
       <c r="B131" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A131,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A131,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A131,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C131" s="100">
@@ -20621,7 +20621,7 @@
         <v/>
       </c>
       <c r="F131" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A131,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A131,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A131,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A131,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G131" s="100">
@@ -20654,7 +20654,7 @@
         <v>46146</v>
       </c>
       <c r="B132" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A132,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A132,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A132,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C132" s="101">
@@ -20670,7 +20670,7 @@
         <v/>
       </c>
       <c r="F132" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A132,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A132,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A132,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A132,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G132" s="101">
@@ -20703,7 +20703,7 @@
         <v>46147</v>
       </c>
       <c r="B133" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A133,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A133,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A133,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C133" s="100">
@@ -20719,7 +20719,7 @@
         <v/>
       </c>
       <c r="F133" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A133,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A133,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A133,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A133,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G133" s="100">
@@ -20752,7 +20752,7 @@
         <v>46148</v>
       </c>
       <c r="B134" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A134,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A134,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A134,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C134" s="101">
@@ -20768,7 +20768,7 @@
         <v/>
       </c>
       <c r="F134" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A134,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A134,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A134,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A134,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G134" s="101">
@@ -20801,7 +20801,7 @@
         <v>46149</v>
       </c>
       <c r="B135" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A135,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A135,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A135,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C135" s="100">
@@ -20817,7 +20817,7 @@
         <v/>
       </c>
       <c r="F135" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A135,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A135,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A135,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A135,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G135" s="100">
@@ -20850,7 +20850,7 @@
         <v>46150</v>
       </c>
       <c r="B136" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A136,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A136,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A136,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C136" s="101">
@@ -20866,7 +20866,7 @@
         <v/>
       </c>
       <c r="F136" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A136,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A136,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A136,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A136,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G136" s="101">
@@ -20899,7 +20899,7 @@
         <v>46151</v>
       </c>
       <c r="B137" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A137,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A137,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A137,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C137" s="100">
@@ -20915,7 +20915,7 @@
         <v/>
       </c>
       <c r="F137" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A137,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A137,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A137,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A137,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G137" s="100">
@@ -20948,7 +20948,7 @@
         <v>46152</v>
       </c>
       <c r="B138" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A138,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A138,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A138,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C138" s="101">
@@ -20964,7 +20964,7 @@
         <v/>
       </c>
       <c r="F138" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A138,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A138,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A138,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A138,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G138" s="101">
@@ -20997,7 +20997,7 @@
         <v>46153</v>
       </c>
       <c r="B139" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A139,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A139,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A139,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C139" s="100">
@@ -21013,7 +21013,7 @@
         <v/>
       </c>
       <c r="F139" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A139,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A139,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A139,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A139,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G139" s="100">
@@ -21046,7 +21046,7 @@
         <v>46154</v>
       </c>
       <c r="B140" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A140,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A140,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A140,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C140" s="101">
@@ -21062,7 +21062,7 @@
         <v/>
       </c>
       <c r="F140" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A140,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A140,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A140,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A140,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G140" s="101">
@@ -21095,7 +21095,7 @@
         <v>46155</v>
       </c>
       <c r="B141" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A141,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A141,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A141,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C141" s="100">
@@ -21111,7 +21111,7 @@
         <v/>
       </c>
       <c r="F141" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A141,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A141,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A141,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A141,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G141" s="100">
@@ -21144,7 +21144,7 @@
         <v>46156</v>
       </c>
       <c r="B142" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A142,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A142,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A142,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C142" s="101">
@@ -21160,7 +21160,7 @@
         <v/>
       </c>
       <c r="F142" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A142,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A142,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A142,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A142,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G142" s="101">
@@ -21193,7 +21193,7 @@
         <v>46157</v>
       </c>
       <c r="B143" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A143,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A143,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A143,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C143" s="100">
@@ -21209,7 +21209,7 @@
         <v/>
       </c>
       <c r="F143" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A143,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A143,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A143,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A143,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G143" s="100">
@@ -21242,7 +21242,7 @@
         <v>46158</v>
       </c>
       <c r="B144" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A144,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A144,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A144,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C144" s="101">
@@ -21258,7 +21258,7 @@
         <v/>
       </c>
       <c r="F144" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A144,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A144,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A144,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A144,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G144" s="101">
@@ -21291,7 +21291,7 @@
         <v>46159</v>
       </c>
       <c r="B145" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A145,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A145,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A145,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C145" s="100">
@@ -21307,7 +21307,7 @@
         <v/>
       </c>
       <c r="F145" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A145,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A145,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A145,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A145,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G145" s="100">
@@ -21340,7 +21340,7 @@
         <v>46160</v>
       </c>
       <c r="B146" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A146,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A146,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A146,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C146" s="101">
@@ -21356,7 +21356,7 @@
         <v/>
       </c>
       <c r="F146" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A146,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A146,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A146,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A146,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G146" s="101">
@@ -21389,7 +21389,7 @@
         <v>46161</v>
       </c>
       <c r="B147" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A147,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A147,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A147,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C147" s="100">
@@ -21405,7 +21405,7 @@
         <v/>
       </c>
       <c r="F147" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A147,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A147,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A147,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A147,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G147" s="100">
@@ -21438,7 +21438,7 @@
         <v>46162</v>
       </c>
       <c r="B148" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A148,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A148,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A148,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C148" s="101">
@@ -21454,7 +21454,7 @@
         <v/>
       </c>
       <c r="F148" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A148,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A148,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A148,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A148,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G148" s="101">
@@ -21487,7 +21487,7 @@
         <v>46163</v>
       </c>
       <c r="B149" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A149,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A149,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A149,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C149" s="100">
@@ -21503,7 +21503,7 @@
         <v/>
       </c>
       <c r="F149" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A149,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A149,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A149,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A149,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G149" s="100">
@@ -21536,7 +21536,7 @@
         <v>46164</v>
       </c>
       <c r="B150" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A150,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A150,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A150,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C150" s="101">
@@ -21552,7 +21552,7 @@
         <v/>
       </c>
       <c r="F150" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A150,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A150,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A150,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A150,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G150" s="101">
@@ -21585,7 +21585,7 @@
         <v>46165</v>
       </c>
       <c r="B151" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A151,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A151,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A151,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C151" s="100">
@@ -21601,7 +21601,7 @@
         <v/>
       </c>
       <c r="F151" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A151,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A151,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A151,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A151,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G151" s="100">
@@ -21634,7 +21634,7 @@
         <v>46166</v>
       </c>
       <c r="B152" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A152,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A152,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A152,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C152" s="101">
@@ -21650,7 +21650,7 @@
         <v/>
       </c>
       <c r="F152" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A152,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A152,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A152,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A152,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G152" s="101">
@@ -21683,7 +21683,7 @@
         <v>46167</v>
       </c>
       <c r="B153" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A153,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A153,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A153,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C153" s="100">
@@ -21699,7 +21699,7 @@
         <v/>
       </c>
       <c r="F153" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A153,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A153,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A153,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A153,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G153" s="100">
@@ -21732,7 +21732,7 @@
         <v>46168</v>
       </c>
       <c r="B154" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A154,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A154,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A154,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C154" s="101">
@@ -21748,7 +21748,7 @@
         <v/>
       </c>
       <c r="F154" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A154,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A154,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A154,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A154,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G154" s="101">
@@ -21781,7 +21781,7 @@
         <v>46169</v>
       </c>
       <c r="B155" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A155,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A155,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A155,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C155" s="100">
@@ -21797,7 +21797,7 @@
         <v/>
       </c>
       <c r="F155" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A155,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A155,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A155,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A155,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G155" s="100">
@@ -21830,7 +21830,7 @@
         <v>46170</v>
       </c>
       <c r="B156" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A156,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A156,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A156,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C156" s="101">
@@ -21846,7 +21846,7 @@
         <v/>
       </c>
       <c r="F156" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A156,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A156,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A156,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A156,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G156" s="101">
@@ -21879,7 +21879,7 @@
         <v>46171</v>
       </c>
       <c r="B157" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A157,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A157,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A157,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C157" s="100">
@@ -21895,7 +21895,7 @@
         <v/>
       </c>
       <c r="F157" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A157,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A157,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A157,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A157,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G157" s="100">
@@ -21928,7 +21928,7 @@
         <v>46172</v>
       </c>
       <c r="B158" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A158,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A158,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A158,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C158" s="101">
@@ -21944,7 +21944,7 @@
         <v/>
       </c>
       <c r="F158" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A158,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A158,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A158,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A158,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G158" s="101">
@@ -21977,7 +21977,7 @@
         <v>46173</v>
       </c>
       <c r="B159" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A159,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A159,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A159,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C159" s="100">
@@ -21993,7 +21993,7 @@
         <v/>
       </c>
       <c r="F159" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A159,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A159,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A159,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A159,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G159" s="100">
@@ -22026,7 +22026,7 @@
         <v>46174</v>
       </c>
       <c r="B160" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A160,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A160,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A160,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C160" s="101">
@@ -22042,7 +22042,7 @@
         <v/>
       </c>
       <c r="F160" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A160,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A160,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A160,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A160,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G160" s="101">
@@ -22075,7 +22075,7 @@
         <v>46175</v>
       </c>
       <c r="B161" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A161,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A161,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A161,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C161" s="100">
@@ -22091,7 +22091,7 @@
         <v/>
       </c>
       <c r="F161" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A161,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A161,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A161,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A161,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G161" s="100">
@@ -22124,7 +22124,7 @@
         <v>46176</v>
       </c>
       <c r="B162" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A162,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A162,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A162,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C162" s="101">
@@ -22140,7 +22140,7 @@
         <v/>
       </c>
       <c r="F162" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A162,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A162,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A162,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A162,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G162" s="101">
@@ -22173,7 +22173,7 @@
         <v>46177</v>
       </c>
       <c r="B163" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A163,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A163,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A163,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C163" s="100">
@@ -22189,7 +22189,7 @@
         <v/>
       </c>
       <c r="F163" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A163,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A163,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A163,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A163,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G163" s="100">
@@ -22222,7 +22222,7 @@
         <v>46178</v>
       </c>
       <c r="B164" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A164,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A164,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A164,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C164" s="101">
@@ -22238,7 +22238,7 @@
         <v/>
       </c>
       <c r="F164" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A164,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A164,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A164,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A164,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G164" s="101">
@@ -22271,7 +22271,7 @@
         <v>46179</v>
       </c>
       <c r="B165" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A165,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A165,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A165,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C165" s="100">
@@ -22287,7 +22287,7 @@
         <v/>
       </c>
       <c r="F165" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A165,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A165,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A165,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A165,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G165" s="100">
@@ -22320,7 +22320,7 @@
         <v>46180</v>
       </c>
       <c r="B166" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A166,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A166,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A166,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C166" s="101">
@@ -22336,7 +22336,7 @@
         <v/>
       </c>
       <c r="F166" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A166,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A166,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A166,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A166,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G166" s="101">
@@ -22369,7 +22369,7 @@
         <v>46181</v>
       </c>
       <c r="B167" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A167,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A167,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A167,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C167" s="100">
@@ -22385,7 +22385,7 @@
         <v/>
       </c>
       <c r="F167" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A167,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A167,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A167,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A167,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G167" s="100">
@@ -22418,7 +22418,7 @@
         <v>46182</v>
       </c>
       <c r="B168" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A168,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A168,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A168,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C168" s="101">
@@ -22434,7 +22434,7 @@
         <v/>
       </c>
       <c r="F168" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A168,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A168,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A168,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A168,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G168" s="101">
@@ -22467,7 +22467,7 @@
         <v>46183</v>
       </c>
       <c r="B169" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A169,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A169,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A169,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C169" s="100">
@@ -22483,7 +22483,7 @@
         <v/>
       </c>
       <c r="F169" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A169,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A169,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A169,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A169,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G169" s="100">
@@ -22516,7 +22516,7 @@
         <v>46184</v>
       </c>
       <c r="B170" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A170,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A170,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A170,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C170" s="101">
@@ -22532,7 +22532,7 @@
         <v/>
       </c>
       <c r="F170" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A170,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A170,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A170,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A170,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G170" s="101">
@@ -22565,7 +22565,7 @@
         <v>46185</v>
       </c>
       <c r="B171" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A171,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A171,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A171,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C171" s="100">
@@ -22581,7 +22581,7 @@
         <v/>
       </c>
       <c r="F171" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A171,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A171,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A171,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A171,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G171" s="100">
@@ -22614,7 +22614,7 @@
         <v>46186</v>
       </c>
       <c r="B172" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A172,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A172,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A172,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C172" s="101">
@@ -22630,7 +22630,7 @@
         <v/>
       </c>
       <c r="F172" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A172,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A172,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A172,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A172,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G172" s="101">
@@ -22663,7 +22663,7 @@
         <v>46187</v>
       </c>
       <c r="B173" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A173,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A173,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A173,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C173" s="100">
@@ -22679,7 +22679,7 @@
         <v/>
       </c>
       <c r="F173" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A173,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A173,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A173,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A173,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G173" s="100">
@@ -22712,7 +22712,7 @@
         <v>46188</v>
       </c>
       <c r="B174" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A174,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A174,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A174,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C174" s="101">
@@ -22728,7 +22728,7 @@
         <v/>
       </c>
       <c r="F174" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A174,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A174,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A174,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A174,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G174" s="101">
@@ -22761,7 +22761,7 @@
         <v>46189</v>
       </c>
       <c r="B175" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A175,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A175,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A175,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C175" s="100">
@@ -22777,7 +22777,7 @@
         <v/>
       </c>
       <c r="F175" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A175,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A175,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A175,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A175,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G175" s="100">
@@ -22810,7 +22810,7 @@
         <v>46190</v>
       </c>
       <c r="B176" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A176,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A176,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A176,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C176" s="101">
@@ -22826,7 +22826,7 @@
         <v/>
       </c>
       <c r="F176" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A176,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A176,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A176,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A176,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G176" s="101">
@@ -22859,7 +22859,7 @@
         <v>46191</v>
       </c>
       <c r="B177" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A177,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A177,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A177,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C177" s="100">
@@ -22875,7 +22875,7 @@
         <v/>
       </c>
       <c r="F177" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A177,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A177,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A177,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A177,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G177" s="100">
@@ -22908,7 +22908,7 @@
         <v>46192</v>
       </c>
       <c r="B178" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A178,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A178,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A178,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C178" s="101">
@@ -22924,7 +22924,7 @@
         <v/>
       </c>
       <c r="F178" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A178,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A178,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A178,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A178,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G178" s="101">
@@ -22957,7 +22957,7 @@
         <v>46193</v>
       </c>
       <c r="B179" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A179,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A179,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A179,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C179" s="100">
@@ -22973,7 +22973,7 @@
         <v/>
       </c>
       <c r="F179" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A179,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A179,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A179,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A179,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G179" s="100">
@@ -23006,7 +23006,7 @@
         <v>46194</v>
       </c>
       <c r="B180" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A180,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A180,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A180,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C180" s="101">
@@ -23022,7 +23022,7 @@
         <v/>
       </c>
       <c r="F180" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A180,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A180,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A180,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A180,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G180" s="101">
@@ -23055,7 +23055,7 @@
         <v>46195</v>
       </c>
       <c r="B181" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A181,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A181,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A181,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C181" s="100">
@@ -23071,7 +23071,7 @@
         <v/>
       </c>
       <c r="F181" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A181,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A181,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A181,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A181,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G181" s="100">
@@ -23104,7 +23104,7 @@
         <v>46196</v>
       </c>
       <c r="B182" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A182,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A182,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A182,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C182" s="101">
@@ -23120,7 +23120,7 @@
         <v/>
       </c>
       <c r="F182" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A182,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A182,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A182,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A182,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G182" s="101">
@@ -23153,7 +23153,7 @@
         <v>46197</v>
       </c>
       <c r="B183" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A183,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A183,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A183,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C183" s="100">
@@ -23169,7 +23169,7 @@
         <v/>
       </c>
       <c r="F183" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A183,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A183,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A183,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A183,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G183" s="100">
@@ -23202,7 +23202,7 @@
         <v>46198</v>
       </c>
       <c r="B184" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A184,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A184,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A184,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C184" s="101">
@@ -23218,7 +23218,7 @@
         <v/>
       </c>
       <c r="F184" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A184,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A184,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A184,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A184,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G184" s="101">
@@ -23251,7 +23251,7 @@
         <v>46199</v>
       </c>
       <c r="B185" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A185,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A185,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A185,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C185" s="100">
@@ -23267,7 +23267,7 @@
         <v/>
       </c>
       <c r="F185" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A185,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A185,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A185,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A185,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G185" s="100">
@@ -23300,7 +23300,7 @@
         <v>46200</v>
       </c>
       <c r="B186" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A186,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A186,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A186,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C186" s="101">
@@ -23316,7 +23316,7 @@
         <v/>
       </c>
       <c r="F186" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A186,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A186,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A186,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A186,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G186" s="101">
@@ -23349,7 +23349,7 @@
         <v>46201</v>
       </c>
       <c r="B187" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A187,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A187,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A187,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C187" s="100">
@@ -23365,7 +23365,7 @@
         <v/>
       </c>
       <c r="F187" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A187,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A187,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A187,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A187,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G187" s="100">
@@ -23398,7 +23398,7 @@
         <v>46202</v>
       </c>
       <c r="B188" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A188,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A188,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A188,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C188" s="101">
@@ -23414,7 +23414,7 @@
         <v/>
       </c>
       <c r="F188" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A188,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A188,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A188,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A188,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G188" s="101">
@@ -23447,7 +23447,7 @@
         <v>46203</v>
       </c>
       <c r="B189" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A189,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A189,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A189,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C189" s="100">
@@ -23463,7 +23463,7 @@
         <v/>
       </c>
       <c r="F189" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A189,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A189,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A189,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A189,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G189" s="100">
@@ -23496,7 +23496,7 @@
         <v>46204</v>
       </c>
       <c r="B190" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A190,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A190,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A190,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C190" s="101">
@@ -23512,7 +23512,7 @@
         <v/>
       </c>
       <c r="F190" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A190,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A190,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A190,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A190,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G190" s="101">
@@ -23545,7 +23545,7 @@
         <v>46205</v>
       </c>
       <c r="B191" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A191,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A191,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A191,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C191" s="100">
@@ -23561,7 +23561,7 @@
         <v/>
       </c>
       <c r="F191" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A191,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A191,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A191,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A191,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G191" s="100">
@@ -23594,7 +23594,7 @@
         <v>46206</v>
       </c>
       <c r="B192" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A192,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A192,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A192,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C192" s="101">
@@ -23610,7 +23610,7 @@
         <v/>
       </c>
       <c r="F192" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A192,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A192,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A192,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A192,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G192" s="101">
@@ -23643,7 +23643,7 @@
         <v>46207</v>
       </c>
       <c r="B193" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A193,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A193,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A193,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C193" s="100">
@@ -23659,7 +23659,7 @@
         <v/>
       </c>
       <c r="F193" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A193,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A193,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A193,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A193,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G193" s="100">
@@ -23692,7 +23692,7 @@
         <v>46208</v>
       </c>
       <c r="B194" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A194,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A194,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A194,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C194" s="101">
@@ -23708,7 +23708,7 @@
         <v/>
       </c>
       <c r="F194" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A194,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A194,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A194,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A194,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G194" s="101">
@@ -23741,7 +23741,7 @@
         <v>46209</v>
       </c>
       <c r="B195" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A195,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A195,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A195,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C195" s="100">
@@ -23757,7 +23757,7 @@
         <v/>
       </c>
       <c r="F195" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A195,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A195,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A195,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A195,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G195" s="100">
@@ -23790,7 +23790,7 @@
         <v>46210</v>
       </c>
       <c r="B196" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A196,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A196,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A196,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C196" s="101">
@@ -23806,7 +23806,7 @@
         <v/>
       </c>
       <c r="F196" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A196,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A196,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A196,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A196,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G196" s="101">
@@ -23839,7 +23839,7 @@
         <v>46211</v>
       </c>
       <c r="B197" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A197,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A197,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A197,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C197" s="100">
@@ -23855,7 +23855,7 @@
         <v/>
       </c>
       <c r="F197" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A197,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A197,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A197,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A197,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G197" s="100">
@@ -23888,7 +23888,7 @@
         <v>46212</v>
       </c>
       <c r="B198" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A198,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A198,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A198,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C198" s="101">
@@ -23904,7 +23904,7 @@
         <v/>
       </c>
       <c r="F198" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A198,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A198,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A198,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A198,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G198" s="101">
@@ -23937,7 +23937,7 @@
         <v>46213</v>
       </c>
       <c r="B199" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A199,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A199,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A199,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C199" s="100">
@@ -23953,7 +23953,7 @@
         <v/>
       </c>
       <c r="F199" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A199,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A199,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A199,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A199,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G199" s="100">
@@ -23986,7 +23986,7 @@
         <v>46214</v>
       </c>
       <c r="B200" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A200,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A200,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A200,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C200" s="101">
@@ -24002,7 +24002,7 @@
         <v/>
       </c>
       <c r="F200" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A200,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A200,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A200,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A200,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G200" s="101">
@@ -24035,7 +24035,7 @@
         <v>46215</v>
       </c>
       <c r="B201" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A201,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A201,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A201,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C201" s="100">
@@ -24051,7 +24051,7 @@
         <v/>
       </c>
       <c r="F201" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A201,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A201,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A201,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A201,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G201" s="100">
@@ -24084,7 +24084,7 @@
         <v>46216</v>
       </c>
       <c r="B202" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A202,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A202,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A202,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C202" s="101">
@@ -24100,7 +24100,7 @@
         <v/>
       </c>
       <c r="F202" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A202,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A202,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A202,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A202,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G202" s="101">
@@ -24133,7 +24133,7 @@
         <v>46217</v>
       </c>
       <c r="B203" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A203,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A203,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A203,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C203" s="100">
@@ -24149,7 +24149,7 @@
         <v/>
       </c>
       <c r="F203" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A203,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A203,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A203,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A203,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G203" s="100">
@@ -24182,7 +24182,7 @@
         <v>46218</v>
       </c>
       <c r="B204" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A204,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A204,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A204,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C204" s="101">
@@ -24198,7 +24198,7 @@
         <v/>
       </c>
       <c r="F204" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A204,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A204,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A204,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A204,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G204" s="101">
@@ -24231,7 +24231,7 @@
         <v>46219</v>
       </c>
       <c r="B205" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A205,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A205,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A205,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C205" s="100">
@@ -24247,7 +24247,7 @@
         <v/>
       </c>
       <c r="F205" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A205,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A205,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A205,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A205,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G205" s="100">
@@ -24280,7 +24280,7 @@
         <v>46220</v>
       </c>
       <c r="B206" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A206,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A206,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A206,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C206" s="101">
@@ -24296,7 +24296,7 @@
         <v/>
       </c>
       <c r="F206" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A206,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A206,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A206,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A206,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G206" s="101">
@@ -24329,7 +24329,7 @@
         <v>46221</v>
       </c>
       <c r="B207" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A207,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A207,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A207,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C207" s="100">
@@ -24345,7 +24345,7 @@
         <v/>
       </c>
       <c r="F207" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A207,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A207,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A207,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A207,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G207" s="100">
@@ -24378,7 +24378,7 @@
         <v>46222</v>
       </c>
       <c r="B208" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A208,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A208,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A208,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C208" s="101">
@@ -24394,7 +24394,7 @@
         <v/>
       </c>
       <c r="F208" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A208,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A208,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A208,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A208,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G208" s="101">
@@ -24427,7 +24427,7 @@
         <v>46223</v>
       </c>
       <c r="B209" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A209,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A209,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A209,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C209" s="100">
@@ -24443,7 +24443,7 @@
         <v/>
       </c>
       <c r="F209" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A209,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A209,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A209,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A209,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G209" s="100">
@@ -24476,7 +24476,7 @@
         <v>46224</v>
       </c>
       <c r="B210" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A210,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A210,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A210,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C210" s="101">
@@ -24492,7 +24492,7 @@
         <v/>
       </c>
       <c r="F210" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A210,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A210,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A210,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A210,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G210" s="101">
@@ -24525,7 +24525,7 @@
         <v>46225</v>
       </c>
       <c r="B211" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A211,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A211,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A211,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C211" s="100">
@@ -24541,7 +24541,7 @@
         <v/>
       </c>
       <c r="F211" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A211,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A211,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A211,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A211,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G211" s="100">
@@ -24574,7 +24574,7 @@
         <v>46226</v>
       </c>
       <c r="B212" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A212,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A212,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A212,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C212" s="101">
@@ -24590,7 +24590,7 @@
         <v/>
       </c>
       <c r="F212" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A212,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A212,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A212,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A212,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G212" s="101">
@@ -24623,7 +24623,7 @@
         <v>46227</v>
       </c>
       <c r="B213" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A213,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A213,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A213,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C213" s="100">
@@ -24639,7 +24639,7 @@
         <v/>
       </c>
       <c r="F213" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A213,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A213,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A213,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A213,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G213" s="100">
@@ -24672,7 +24672,7 @@
         <v>46228</v>
       </c>
       <c r="B214" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A214,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A214,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A214,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C214" s="101">
@@ -24688,7 +24688,7 @@
         <v/>
       </c>
       <c r="F214" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A214,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A214,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A214,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A214,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G214" s="101">
@@ -24721,7 +24721,7 @@
         <v>46229</v>
       </c>
       <c r="B215" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A215,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A215,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A215,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C215" s="100">
@@ -24737,7 +24737,7 @@
         <v/>
       </c>
       <c r="F215" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A215,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A215,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A215,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A215,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G215" s="100">
@@ -24770,7 +24770,7 @@
         <v>46230</v>
       </c>
       <c r="B216" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A216,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A216,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A216,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C216" s="101">
@@ -24786,7 +24786,7 @@
         <v/>
       </c>
       <c r="F216" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A216,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A216,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A216,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A216,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G216" s="101">
@@ -24819,7 +24819,7 @@
         <v>46231</v>
       </c>
       <c r="B217" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A217,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A217,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A217,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C217" s="100">
@@ -24835,7 +24835,7 @@
         <v/>
       </c>
       <c r="F217" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A217,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A217,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A217,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A217,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G217" s="100">
@@ -24868,7 +24868,7 @@
         <v>46232</v>
       </c>
       <c r="B218" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A218,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A218,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A218,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C218" s="101">
@@ -24884,7 +24884,7 @@
         <v/>
       </c>
       <c r="F218" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A218,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A218,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A218,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A218,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G218" s="101">
@@ -24917,7 +24917,7 @@
         <v>46233</v>
       </c>
       <c r="B219" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A219,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A219,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A219,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C219" s="100">
@@ -24933,7 +24933,7 @@
         <v/>
       </c>
       <c r="F219" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A219,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A219,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A219,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A219,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G219" s="100">
@@ -24966,7 +24966,7 @@
         <v>46234</v>
       </c>
       <c r="B220" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A220,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A220,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A220,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C220" s="101">
@@ -24982,7 +24982,7 @@
         <v/>
       </c>
       <c r="F220" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A220,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A220,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A220,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A220,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G220" s="101">
@@ -25015,7 +25015,7 @@
         <v>46235</v>
       </c>
       <c r="B221" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A221,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A221,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A221,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C221" s="100">
@@ -25031,7 +25031,7 @@
         <v/>
       </c>
       <c r="F221" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A221,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A221,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A221,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A221,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G221" s="100">
@@ -25064,7 +25064,7 @@
         <v>46236</v>
       </c>
       <c r="B222" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A222,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A222,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A222,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C222" s="101">
@@ -25080,7 +25080,7 @@
         <v/>
       </c>
       <c r="F222" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A222,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A222,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A222,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A222,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G222" s="101">
@@ -25113,7 +25113,7 @@
         <v>46237</v>
       </c>
       <c r="B223" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A223,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A223,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A223,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C223" s="100">
@@ -25129,7 +25129,7 @@
         <v/>
       </c>
       <c r="F223" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A223,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A223,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A223,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A223,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G223" s="100">
@@ -25162,7 +25162,7 @@
         <v>46238</v>
       </c>
       <c r="B224" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A224,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A224,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A224,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C224" s="101">
@@ -25178,7 +25178,7 @@
         <v/>
       </c>
       <c r="F224" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A224,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A224,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A224,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A224,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G224" s="101">
@@ -25211,7 +25211,7 @@
         <v>46239</v>
       </c>
       <c r="B225" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A225,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A225,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A225,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C225" s="100">
@@ -25227,7 +25227,7 @@
         <v/>
       </c>
       <c r="F225" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A225,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A225,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A225,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A225,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G225" s="100">
@@ -25260,7 +25260,7 @@
         <v>46240</v>
       </c>
       <c r="B226" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A226,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A226,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A226,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C226" s="101">
@@ -25276,7 +25276,7 @@
         <v/>
       </c>
       <c r="F226" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A226,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A226,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A226,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A226,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G226" s="101">
@@ -25309,7 +25309,7 @@
         <v>46241</v>
       </c>
       <c r="B227" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A227,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A227,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A227,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C227" s="100">
@@ -25325,7 +25325,7 @@
         <v/>
       </c>
       <c r="F227" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A227,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A227,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A227,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A227,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G227" s="100">
@@ -25358,7 +25358,7 @@
         <v>46242</v>
       </c>
       <c r="B228" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A228,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A228,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A228,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C228" s="101">
@@ -25374,7 +25374,7 @@
         <v/>
       </c>
       <c r="F228" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A228,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A228,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A228,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A228,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G228" s="101">
@@ -25407,7 +25407,7 @@
         <v>46243</v>
       </c>
       <c r="B229" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A229,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A229,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A229,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C229" s="100">
@@ -25423,7 +25423,7 @@
         <v/>
       </c>
       <c r="F229" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A229,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A229,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A229,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A229,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G229" s="100">
@@ -25456,7 +25456,7 @@
         <v>46244</v>
       </c>
       <c r="B230" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A230,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A230,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A230,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C230" s="101">
@@ -25472,7 +25472,7 @@
         <v/>
       </c>
       <c r="F230" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A230,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A230,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A230,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A230,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G230" s="101">
@@ -25505,7 +25505,7 @@
         <v>46245</v>
       </c>
       <c r="B231" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A231,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A231,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A231,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C231" s="100">
@@ -25521,7 +25521,7 @@
         <v/>
       </c>
       <c r="F231" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A231,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A231,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A231,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A231,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G231" s="100">
@@ -25554,7 +25554,7 @@
         <v>46246</v>
       </c>
       <c r="B232" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A232,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A232,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A232,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C232" s="101">
@@ -25570,7 +25570,7 @@
         <v/>
       </c>
       <c r="F232" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A232,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A232,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A232,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A232,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G232" s="101">
@@ -25603,7 +25603,7 @@
         <v>46247</v>
       </c>
       <c r="B233" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A233,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A233,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A233,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C233" s="100">
@@ -25619,7 +25619,7 @@
         <v/>
       </c>
       <c r="F233" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A233,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A233,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A233,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A233,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G233" s="100">
@@ -25652,7 +25652,7 @@
         <v>46248</v>
       </c>
       <c r="B234" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A234,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A234,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A234,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C234" s="101">
@@ -25668,7 +25668,7 @@
         <v/>
       </c>
       <c r="F234" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A234,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A234,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A234,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A234,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G234" s="101">
@@ -25701,7 +25701,7 @@
         <v>46249</v>
       </c>
       <c r="B235" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A235,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A235,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A235,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C235" s="100">
@@ -25717,7 +25717,7 @@
         <v/>
       </c>
       <c r="F235" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A235,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A235,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A235,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A235,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G235" s="100">
@@ -25750,7 +25750,7 @@
         <v>46250</v>
       </c>
       <c r="B236" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A236,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A236,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A236,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C236" s="101">
@@ -25766,7 +25766,7 @@
         <v/>
       </c>
       <c r="F236" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A236,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A236,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A236,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A236,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G236" s="101">
@@ -25799,7 +25799,7 @@
         <v>46251</v>
       </c>
       <c r="B237" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A237,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A237,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A237,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C237" s="100">
@@ -25815,7 +25815,7 @@
         <v/>
       </c>
       <c r="F237" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A237,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A237,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A237,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A237,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G237" s="100">
@@ -25848,7 +25848,7 @@
         <v>46252</v>
       </c>
       <c r="B238" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A238,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A238,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A238,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C238" s="101">
@@ -25864,7 +25864,7 @@
         <v/>
       </c>
       <c r="F238" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A238,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A238,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A238,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A238,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G238" s="101">
@@ -25897,7 +25897,7 @@
         <v>46253</v>
       </c>
       <c r="B239" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A239,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A239,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A239,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C239" s="100">
@@ -25913,7 +25913,7 @@
         <v/>
       </c>
       <c r="F239" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A239,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A239,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A239,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A239,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G239" s="100">
@@ -25946,7 +25946,7 @@
         <v>46254</v>
       </c>
       <c r="B240" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A240,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A240,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A240,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C240" s="101">
@@ -25962,7 +25962,7 @@
         <v/>
       </c>
       <c r="F240" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A240,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A240,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A240,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A240,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G240" s="101">
@@ -25995,7 +25995,7 @@
         <v>46255</v>
       </c>
       <c r="B241" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A241,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A241,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A241,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C241" s="100">
@@ -26011,7 +26011,7 @@
         <v/>
       </c>
       <c r="F241" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A241,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A241,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A241,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A241,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G241" s="100">
@@ -26044,7 +26044,7 @@
         <v>46256</v>
       </c>
       <c r="B242" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A242,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A242,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A242,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C242" s="101">
@@ -26060,7 +26060,7 @@
         <v/>
       </c>
       <c r="F242" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A242,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A242,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A242,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A242,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G242" s="101">
@@ -26093,7 +26093,7 @@
         <v>46257</v>
       </c>
       <c r="B243" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A243,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A243,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A243,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C243" s="100">
@@ -26109,7 +26109,7 @@
         <v/>
       </c>
       <c r="F243" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A243,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A243,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A243,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A243,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G243" s="100">
@@ -26142,7 +26142,7 @@
         <v>46258</v>
       </c>
       <c r="B244" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A244,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A244,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A244,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C244" s="101">
@@ -26158,7 +26158,7 @@
         <v/>
       </c>
       <c r="F244" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A244,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A244,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A244,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A244,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G244" s="101">
@@ -26191,7 +26191,7 @@
         <v>46259</v>
       </c>
       <c r="B245" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A245,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A245,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A245,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C245" s="100">
@@ -26207,7 +26207,7 @@
         <v/>
       </c>
       <c r="F245" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A245,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A245,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A245,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A245,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G245" s="100">
@@ -26240,7 +26240,7 @@
         <v>46260</v>
       </c>
       <c r="B246" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A246,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A246,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A246,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C246" s="101">
@@ -26256,7 +26256,7 @@
         <v/>
       </c>
       <c r="F246" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A246,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A246,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A246,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A246,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G246" s="101">
@@ -26289,7 +26289,7 @@
         <v>46261</v>
       </c>
       <c r="B247" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A247,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A247,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A247,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C247" s="100">
@@ -26305,7 +26305,7 @@
         <v/>
       </c>
       <c r="F247" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A247,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A247,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A247,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A247,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G247" s="100">
@@ -26338,7 +26338,7 @@
         <v>46262</v>
       </c>
       <c r="B248" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A248,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A248,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A248,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C248" s="101">
@@ -26354,7 +26354,7 @@
         <v/>
       </c>
       <c r="F248" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A248,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A248,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A248,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A248,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G248" s="101">
@@ -26387,7 +26387,7 @@
         <v>46263</v>
       </c>
       <c r="B249" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A249,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A249,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A249,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C249" s="100">
@@ -26403,7 +26403,7 @@
         <v/>
       </c>
       <c r="F249" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A249,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A249,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A249,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A249,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G249" s="100">
@@ -26436,7 +26436,7 @@
         <v>46264</v>
       </c>
       <c r="B250" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A250,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A250,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A250,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C250" s="101">
@@ -26452,7 +26452,7 @@
         <v/>
       </c>
       <c r="F250" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A250,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A250,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A250,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A250,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G250" s="101">
@@ -26485,7 +26485,7 @@
         <v>46265</v>
       </c>
       <c r="B251" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A251,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A251,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A251,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C251" s="100">
@@ -26501,7 +26501,7 @@
         <v/>
       </c>
       <c r="F251" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A251,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A251,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A251,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A251,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G251" s="100">
@@ -26534,7 +26534,7 @@
         <v>46266</v>
       </c>
       <c r="B252" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A252,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A252,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A252,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C252" s="101">
@@ -26550,7 +26550,7 @@
         <v/>
       </c>
       <c r="F252" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A252,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A252,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A252,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A252,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G252" s="101">
@@ -26583,7 +26583,7 @@
         <v>46267</v>
       </c>
       <c r="B253" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A253,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A253,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A253,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C253" s="100">
@@ -26599,7 +26599,7 @@
         <v/>
       </c>
       <c r="F253" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A253,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A253,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A253,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A253,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G253" s="100">
@@ -26632,7 +26632,7 @@
         <v>46268</v>
       </c>
       <c r="B254" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A254,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A254,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A254,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C254" s="101">
@@ -26648,7 +26648,7 @@
         <v/>
       </c>
       <c r="F254" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A254,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A254,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A254,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A254,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G254" s="101">
@@ -26681,7 +26681,7 @@
         <v>46269</v>
       </c>
       <c r="B255" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A255,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A255,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A255,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C255" s="100">
@@ -26697,7 +26697,7 @@
         <v/>
       </c>
       <c r="F255" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A255,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A255,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A255,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A255,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G255" s="100">
@@ -26730,7 +26730,7 @@
         <v>46270</v>
       </c>
       <c r="B256" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A256,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A256,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A256,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C256" s="101">
@@ -26746,7 +26746,7 @@
         <v/>
       </c>
       <c r="F256" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A256,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A256,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A256,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A256,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G256" s="101">
@@ -26779,7 +26779,7 @@
         <v>46271</v>
       </c>
       <c r="B257" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A257,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A257,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A257,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C257" s="100">
@@ -26795,7 +26795,7 @@
         <v/>
       </c>
       <c r="F257" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A257,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A257,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A257,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A257,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G257" s="100">
@@ -26828,7 +26828,7 @@
         <v>46272</v>
       </c>
       <c r="B258" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A258,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A258,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A258,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C258" s="101">
@@ -26844,7 +26844,7 @@
         <v/>
       </c>
       <c r="F258" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A258,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A258,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A258,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A258,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G258" s="101">
@@ -26877,7 +26877,7 @@
         <v>46273</v>
       </c>
       <c r="B259" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A259,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A259,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A259,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C259" s="100">
@@ -26893,7 +26893,7 @@
         <v/>
       </c>
       <c r="F259" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A259,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A259,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A259,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A259,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G259" s="100">
@@ -26926,7 +26926,7 @@
         <v>46274</v>
       </c>
       <c r="B260" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A260,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A260,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A260,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C260" s="101">
@@ -26942,7 +26942,7 @@
         <v/>
       </c>
       <c r="F260" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A260,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A260,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A260,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A260,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G260" s="101">
@@ -26975,7 +26975,7 @@
         <v>46275</v>
       </c>
       <c r="B261" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A261,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A261,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A261,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C261" s="100">
@@ -26991,7 +26991,7 @@
         <v/>
       </c>
       <c r="F261" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A261,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A261,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A261,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A261,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G261" s="100">
@@ -27024,7 +27024,7 @@
         <v>46276</v>
       </c>
       <c r="B262" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A262,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A262,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A262,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C262" s="101">
@@ -27040,7 +27040,7 @@
         <v/>
       </c>
       <c r="F262" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A262,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A262,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A262,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A262,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G262" s="101">
@@ -27073,7 +27073,7 @@
         <v>46277</v>
       </c>
       <c r="B263" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A263,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A263,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A263,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C263" s="100">
@@ -27089,7 +27089,7 @@
         <v/>
       </c>
       <c r="F263" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A263,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A263,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A263,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A263,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G263" s="100">
@@ -27122,7 +27122,7 @@
         <v>46278</v>
       </c>
       <c r="B264" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A264,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A264,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A264,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C264" s="101">
@@ -27138,7 +27138,7 @@
         <v/>
       </c>
       <c r="F264" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A264,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A264,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A264,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A264,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G264" s="101">
@@ -27171,7 +27171,7 @@
         <v>46279</v>
       </c>
       <c r="B265" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A265,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A265,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A265,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C265" s="100">
@@ -27187,7 +27187,7 @@
         <v/>
       </c>
       <c r="F265" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A265,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A265,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A265,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A265,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G265" s="100">
@@ -27220,7 +27220,7 @@
         <v>46280</v>
       </c>
       <c r="B266" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A266,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A266,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A266,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C266" s="101">
@@ -27236,7 +27236,7 @@
         <v/>
       </c>
       <c r="F266" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A266,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A266,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A266,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A266,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G266" s="101">
@@ -27269,7 +27269,7 @@
         <v>46281</v>
       </c>
       <c r="B267" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A267,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A267,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A267,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A267,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C267" s="100">
@@ -27285,7 +27285,7 @@
         <v/>
       </c>
       <c r="F267" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A267,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A267,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A267,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A267,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G267" s="100">
@@ -27318,7 +27318,7 @@
         <v>46282</v>
       </c>
       <c r="B268" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A268,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A268,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A268,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A268,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C268" s="101">
@@ -27334,7 +27334,7 @@
         <v/>
       </c>
       <c r="F268" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A268,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A268,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A268,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A268,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G268" s="101">
@@ -27367,7 +27367,7 @@
         <v>46283</v>
       </c>
       <c r="B269" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A269,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A269,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A269,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A269,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C269" s="100">
@@ -27383,7 +27383,7 @@
         <v/>
       </c>
       <c r="F269" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A269,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A269,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A269,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A269,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G269" s="100">
@@ -27416,7 +27416,7 @@
         <v>46284</v>
       </c>
       <c r="B270" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A270,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A270,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A270,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A270,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C270" s="101">
@@ -27432,7 +27432,7 @@
         <v/>
       </c>
       <c r="F270" s="101">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A270,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A270,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A270,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A270,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G270" s="101">
@@ -27465,7 +27465,7 @@
         <v>46285</v>
       </c>
       <c r="B271" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$281,MATCH($A271,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$B$25:$B$281,MATCH($A271,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A271,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A271,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="C271" s="100">
@@ -27481,7 +27481,7 @@
         <v/>
       </c>
       <c r="F271" s="100">
-        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$281,MATCH($A271,Polymarket!$A$25:$A$281,0))=0,"",INDEX(Polymarket!$C$25:$C$281,MATCH($A271,Polymarket!$A$25:$A$281,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A271,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A271,Polymarket!$A$25:$A$282,0))),"")</f>
         <v/>
       </c>
       <c r="G271" s="100">
@@ -27506,6 +27506,55 @@
       <c r="L271" s="26" t="inlineStr">
         <is>
           <t>20 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="41" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B272" s="101">
+        <f>IFERROR(IF(INDEX(Polymarket!$B$25:$B$282,MATCH($A272,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$B$25:$B$282,MATCH($A272,Polymarket!$A$25:$A$282,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C272" s="101">
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A272,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A272,Kalshi!$A$31:$A$464,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D272" s="31">
+        <f>IF(AND(ISNUMBER(B272),ISNUMBER(C272)),B272-C272,"")</f>
+        <v/>
+      </c>
+      <c r="E272" s="29">
+        <f>IF(ISNUMBER(D272),ABS(D272),"")</f>
+        <v/>
+      </c>
+      <c r="F272" s="101">
+        <f>IFERROR(IF(INDEX(Polymarket!$C$25:$C$282,MATCH($A272,Polymarket!$A$25:$A$282,0))=0,"",INDEX(Polymarket!$C$25:$C$282,MATCH($A272,Polymarket!$A$25:$A$282,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G272" s="101">
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A272,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A272,Kalshi!$A$31:$A$464,0))),"")</f>
+        <v/>
+      </c>
+      <c r="H272" s="30">
+        <f>IF(AND(ISNUMBER(B272),ISNUMBER(C272)),MIN(B272,C272),"")</f>
+        <v/>
+      </c>
+      <c r="I272" s="30">
+        <f>IF(AND(ISNUMBER(F272),ISNUMBER(G272)),MIN(F272,G272),"")</f>
+        <v/>
+      </c>
+      <c r="J272" s="29">
+        <f>IF(AND(ISNUMBER(H272),ISNUMBER(I272)),H272+I272,"")</f>
+        <v/>
+      </c>
+      <c r="K272" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L272" s="38" t="inlineStr">
+        <is>
+          <t>21 Sep</t>
         </is>
       </c>
     </row>
@@ -27538,7 +27587,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-20 19:27 UTC.</t>
+          <t>Everything behind the numbers: where each cell came from, what is assumed, and how to pull it again. Built 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -28698,7 +28747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-20 19:27 UTC.</t>
+          <t>Every chart is bound to the cell ranges on the data sheets, so all of them redraw automatically each time the tracker refreshes. Built 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -28779,7 +28828,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-20 19:27 UTC.</t>
+          <t>What the market thinks the result will look like, and how that squares with the polling. Built 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K281"/>
+  <dimension ref="A1:K282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28963,7 +29012,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 19:27 UTC.</t>
+          <t>Source: Polymarket CLOB API (clob.polymarket.com) + Gamma API. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -29129,10 +29178,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10974.7843</v>
+        <v>11284.5843</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>13146.7949</v>
+        <v>13473.5624</v>
       </c>
     </row>
     <row r="14">
@@ -29240,10 +29289,10 @@
         <v/>
       </c>
       <c r="F19" s="19" t="n">
-        <v>149.2</v>
+        <v>306.2</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>326.79</v>
+        <v>644.79</v>
       </c>
       <c r="H19" s="20">
         <f>IFERROR(D19/$D$21,"")</f>
@@ -29274,7 +29323,7 @@
         <v>7099</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>360</v>
+        <v>422</v>
       </c>
       <c r="H20" s="20">
         <f>IFERROR(D20/$D$21,"")</f>
@@ -40638,7 +40687,7 @@
         <v>46285</v>
       </c>
       <c r="B281" s="16" t="n">
-        <v>0.79</v>
+        <v>0.795</v>
       </c>
       <c r="C281" s="16" t="n">
         <v>0.205</v>
@@ -40674,6 +40723,50 @@
       <c r="K281" s="26" t="inlineStr">
         <is>
           <t>20 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="41" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B282" s="28" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C282" s="28" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="D282" s="29">
+        <f>IF(COUNT(B282:C282)=2,B282+C282,"")</f>
+        <v/>
+      </c>
+      <c r="E282" s="30">
+        <f>IF(ISNUMBER(B282),IFERROR(B282/$D282,""),"")</f>
+        <v/>
+      </c>
+      <c r="F282" s="30">
+        <f>IF(ISNUMBER(C282),IFERROR(C282/$D282,""),"")</f>
+        <v/>
+      </c>
+      <c r="G282" s="31">
+        <f>IF(COUNT(B282:C282)=2,B282-C282,"")</f>
+        <v/>
+      </c>
+      <c r="H282" s="31">
+        <f>IFERROR(IF(AND(ISNUMBER(B282),INDEX($B$25:$B282,MATCH($A282-7,$A$25:$A282,1))&lt;&gt;0,INDEX($A$25:$A282,MATCH($A282-7,$A$25:$A282,1))&lt;&gt;0,$A282-INDEX($A$25:$A282,MATCH($A282-7,$A$25:$A282,1))&lt;=10),B282-INDEX($B$25:$B282,MATCH($A282-7,$A$25:$A282,1)),""),"")</f>
+        <v/>
+      </c>
+      <c r="I282" s="31">
+        <f>IFERROR(IF(AND(ISNUMBER(B282),INDEX($B$25:$B282,MATCH($A282-30,$A$25:$A282,1))&lt;&gt;0,INDEX($A$25:$A282,MATCH($A282-30,$A$25:$A282,1))&lt;&gt;0,$A282-INDEX($A$25:$A282,MATCH($A282-30,$A$25:$A282,1))&lt;=33),B282-INDEX($B$25:$B282,MATCH($A282-30,$A$25:$A282,1)),""),"")</f>
+        <v/>
+      </c>
+      <c r="J282" s="42">
+        <f>DATE(2026,11,3)-A282</f>
+        <v/>
+      </c>
+      <c r="K282" s="26" t="inlineStr">
+        <is>
+          <t>21 Sep</t>
         </is>
       </c>
     </row>
@@ -40716,7 +40809,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-20 19:27 UTC.</t>
+          <t>Source: Kalshi Trade API v2 (api.elections.kalshi.com), RSA-signed requests. Prices are per-$1 contracts; price = implied probability. Pulled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -40985,7 +41078,7 @@
         <v/>
       </c>
       <c r="G17" s="19" t="n">
-        <v>7.25</v>
+        <v>6.33</v>
       </c>
       <c r="H17" s="20">
         <f>IFERROR(E17/$E$19,"")</f>
@@ -41119,13 +41212,13 @@
         <v>0.8</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>7.25</v>
+        <v>6.33</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>576.03</v>
+        <v>517.03</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0.19</v>
@@ -41137,7 +41230,7 @@
         <v>0.8</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>42</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="24">
@@ -41148,13 +41241,13 @@
         <v>0.79</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>59</v>
+        <v>79.03</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.18</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>499.54</v>
+        <v>531.85</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>0.17</v>
@@ -41166,7 +41259,7 @@
         <v>0.79</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>166</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25">
@@ -41177,7 +41270,7 @@
         <v>0.78</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>67</v>
+        <v>160.97</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>0.17</v>
@@ -41195,7 +41288,7 @@
         <v>0.78</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>56.06</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="26">
@@ -41206,7 +41299,7 @@
         <v>0.77</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>50776</v>
+        <v>50976</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>0.14</v>
@@ -41215,10 +41308,10 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>0.77</v>
@@ -41235,7 +41328,7 @@
         <v>0.76</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>431.3</v>
+        <v>100</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>0.13</v>
@@ -41244,10 +41337,10 @@
         <v>5000</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0.027</v>
+        <v>0.011</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>45</v>
+        <v>3644</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>0.76</v>
@@ -62029,7 +62122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -62055,7 +62148,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-20 19:27 UTC.</t>
+          <t>The PA-07 winning margin, quoted on BOTH venues: Polymarket as exclusive brackets (below) and Kalshi as nested thresholds (further down, with the two compared). Pulled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -62174,7 +62267,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>81562.37809</v>
+        <v>83840.06031</v>
       </c>
       <c r="C11" s="66" t="n"/>
       <c r="D11" s="66" t="n"/>
@@ -62273,10 +62366,10 @@
         <v>-8</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E16" s="17">
         <f>IF(COUNT(C16:D16)=2,(C16+D16)/2,"")</f>
@@ -62294,7 +62387,7 @@
         <v>756.954173</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>10042.7052</v>
+        <v>9773.551100000001</v>
       </c>
       <c r="J16" s="75">
         <f>IFERROR(F16*B16,"")</f>
@@ -62311,10 +62404,10 @@
         <v>-4.5</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.082</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.112</v>
+        <v>0.104</v>
       </c>
       <c r="E17" s="17">
         <f>IF(COUNT(C17:D17)=2,(C17+D17)/2,"")</f>
@@ -62332,7 +62425,7 @@
         <v>199.32</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>9068.77981</v>
+        <v>8879.931549999999</v>
       </c>
       <c r="J17" s="75">
         <f>IFERROR(F17*B17,"")</f>
@@ -62349,10 +62442,10 @@
         <v>-1.5</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="E18" s="17">
         <f>IF(COUNT(C18:D18)=2,(C18+D18)/2,"")</f>
@@ -62370,7 +62463,7 @@
         <v>161.333332</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>8629.859700000001</v>
+        <v>8649.346</v>
       </c>
       <c r="J18" s="75">
         <f>IFERROR(F18*B18,"")</f>
@@ -62387,7 +62480,7 @@
         <v>1.5</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>0.17</v>
@@ -62408,7 +62501,7 @@
         <v>211.03</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>8972.6404</v>
+        <v>8999.900600000001</v>
       </c>
       <c r="J19" s="75">
         <f>IFERROR(F19*B19,"")</f>
@@ -62446,7 +62539,7 @@
         <v>329.176665</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>8983.109399999999</v>
+        <v>8719.717000000001</v>
       </c>
       <c r="J20" s="75">
         <f>IFERROR(F20*B20,"")</f>
@@ -62463,10 +62556,10 @@
         <v>7.5</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.199</v>
+        <v>0.2</v>
       </c>
       <c r="E21" s="17">
         <f>IF(COUNT(C21:D21)=2,(C21+D21)/2,"")</f>
@@ -62484,7 +62577,7 @@
         <v>295.538151</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>9075.055759999999</v>
+        <v>12386.28493</v>
       </c>
       <c r="J21" s="75">
         <f>IFERROR(F21*B21,"")</f>
@@ -62501,7 +62594,7 @@
         <v>10.5</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>0.074</v>
@@ -62522,7 +62615,7 @@
         <v>162.03</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>8511.84491</v>
+        <v>8160.97936</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(F22*B22,"")</f>
@@ -62538,7 +62631,9 @@
       <c r="B23" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="C23" s="16" t="n"/>
+      <c r="C23" s="16" t="n">
+        <v>0.01</v>
+      </c>
       <c r="D23" s="16" t="n">
         <v>0.08</v>
       </c>
@@ -62558,7 +62653,7 @@
         <v>143.03</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>8260.801299999999</v>
+        <v>8220.6855</v>
       </c>
       <c r="J23" s="75">
         <f>IFERROR(F23*B23,"")</f>
@@ -62575,7 +62670,7 @@
         <v>16.5</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>0.099</v>
@@ -62596,7 +62691,7 @@
         <v>154.03</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>90.06983</v>
+        <v>167.72889</v>
       </c>
       <c r="J24" s="75">
         <f>IFERROR(F24*B24,"")</f>
@@ -62634,7 +62729,7 @@
         <v>405.63526</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>9893.4674</v>
+        <v>9684.518899999999</v>
       </c>
       <c r="J25" s="75">
         <f>IFERROR(F25*B25,"")</f>
@@ -64239,53 +64334,88 @@
         <v>46285</v>
       </c>
       <c r="B82" s="28" t="n">
-        <v>0.1</v>
+        <v>0.115</v>
       </c>
       <c r="C82" s="28" t="n">
-        <v>0.097</v>
+        <v>0.1165</v>
       </c>
       <c r="D82" s="28" t="n">
-        <v>0.08</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E82" s="28" t="n">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="F82" s="28" t="n">
         <v>0.135</v>
       </c>
       <c r="G82" s="28" t="n">
-        <v>0.181</v>
+        <v>0.166</v>
       </c>
       <c r="H82" s="28" t="n">
-        <v>0.039</v>
+        <v>0.067</v>
       </c>
       <c r="I82" s="28" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="J82" s="28" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="K82" s="28" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="39" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B83" s="16" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="C83" s="16" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="F83" s="16" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="H83" s="16" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="I83" s="16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J83" s="16" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="K83" s="16" t="n">
         <v>0.11</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>All ten brackets, daily closes from CLOB /prices-history at fidelity=1440. The market opened 11 Aug 2026, so the series is only 40 days long and the brackets are thin — read it as a sanity check on the ladder above, not as a trend.</t>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>All ten brackets, daily closes from CLOB /prices-history at fidelity=1440. The market opened 11 Aug 2026, so the series is only 41 days long and the brackets are thin — read it as a sanity check on the ladder above, not as a trend.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A84:K84"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
   </mergeCells>
@@ -64325,7 +64455,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-20 19:27 UTC.</t>
+          <t>Kalshi KXMIDTERMVOTETURN-PA07: how many ballots the PA-07 House race draws on 3 Nov 2026, quoted as thresholds. Pulled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -65618,7 +65748,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-20 19:27 UTC.</t>
+          <t>How many of Pennsylvania's 17 House seats Democrats win on 3 Nov 2026. PA-07 is one of the seats in this count, so the ladder is a state-level read on the same question. Pulled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -65832,7 +65962,7 @@
         <v>0.04</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="E14" s="20">
         <f>IF(ISNUMBER(D14),1-D14,"")</f>
@@ -65865,7 +65995,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0.9</v>
@@ -65901,7 +66031,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>0.67</v>
@@ -65976,7 +66106,7 @@
         <v>0.28</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="E18" s="20">
         <f>IF(ISNUMBER(D18),1-D18,"")</f>
@@ -67095,7 +67225,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-20 19:27 UTC.</t>
+          <t>General-election and Democratic-primary polling for Pennsylvania's 7th, from the NYT/538 house-poll file (house.csv), plus the district and incumbent profile from GovTrack. Percentages stored as fractions. Compiled 2026-09-21 01:05 UTC.</t>
         </is>
       </c>
     </row>
@@ -67670,7 +67800,7 @@
         </is>
       </c>
       <c r="B28" s="50" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="29">

--- a/site/PA-07_House_Election_Tracker.xlsx
+++ b/site/PA-07_House_Election_Tracker.xlsx
@@ -1620,12 +1620,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$464</f>
+              <f>'Kalshi'!$M$31:$M$465</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$B$31:$B$464</f>
+              <f>'Kalshi'!$B$31:$B$465</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1656,12 +1656,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$464</f>
+              <f>'Kalshi'!$M$31:$M$465</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$C$31:$C$464</f>
+              <f>'Kalshi'!$C$31:$C$465</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1880,12 +1880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Kalshi'!$M$31:$M$464</f>
+              <f>'Kalshi'!$M$31:$M$465</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Kalshi'!$L$31:$L$464</f>
+              <f>'Kalshi'!$L$31:$L$465</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-21 01:05 UTC.</t>
+          <t>Pennsylvania's 7th Congressional District, general election 3 Nov 2026. Green = pulled from another sheet, black = calculated, blue = entered fact, yellow = key output or assumption. Built 2026-09-21 17:04 UTC.</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>2026-09-21 01:05 UTC</t>
+          <t>2026-09-21 17:04 UTC</t>
         </is>
       </c>
       <c r="C68" s="66" t="n"/>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="B70" s="59">
-        <f>TEXT(Kalshi!A31,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Kalshi!A464,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Kalshi!A31:A464)&amp;" days)"</f>
+        <f>TEXT(Kalshi!A31,"yyyy-mm-dd")&amp;" to "&amp;TEXT(Kalshi!A465,"yyyy-mm-dd")&amp;"  ("&amp;COUNT(Kalshi!A31:A465)&amp;" days)"</f>
         <v/>
       </c>
       <c r="C70" s="66" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-21 01:05 UTC.</t>
+          <t>Outside views of PA-07: a statistical forecast, a third-party odds tracker, and what each disagrees with the markets about. Compiled 2026-09-21 17:04 UTC.</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-21 01:05 UTC.</t>
+          <t>Money raised and spent in the 2026 PA-07 race, from the OpenFEC API. This is finance, not polling. Compiled 2026-09-21 17:04 UTC.</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-21 01:05 UTC.</t>
+          <t>Daily Democratic win probability on both venues, joined on date with INDEX/MATCH so the join survives a data refresh. Built 2026-09-21 17:04 UTC.</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v/>
       </c>
       <c r="C15" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A15,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A15,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A15,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A15,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D15" s="18">
@@ -14941,7 +14941,7 @@
         <v/>
       </c>
       <c r="G15" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A15,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A15,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A15,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A15,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H15" s="20">
@@ -14974,7 +14974,7 @@
         <v/>
       </c>
       <c r="C16" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A16,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A16,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A16,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A16,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D16" s="31">
@@ -14990,7 +14990,7 @@
         <v/>
       </c>
       <c r="G16" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A16,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A16,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A16,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A16,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H16" s="30">
@@ -15023,7 +15023,7 @@
         <v/>
       </c>
       <c r="C17" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A17,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A17,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A17,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A17,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D17" s="18">
@@ -15039,7 +15039,7 @@
         <v/>
       </c>
       <c r="G17" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A17,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A17,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A17,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A17,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H17" s="20">
@@ -15072,7 +15072,7 @@
         <v/>
       </c>
       <c r="C18" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A18,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A18,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A18,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A18,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D18" s="31">
@@ -15088,7 +15088,7 @@
         <v/>
       </c>
       <c r="G18" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A18,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A18,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A18,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A18,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H18" s="30">
@@ -15121,7 +15121,7 @@
         <v/>
       </c>
       <c r="C19" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A19,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A19,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A19,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A19,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D19" s="18">
@@ -15137,7 +15137,7 @@
         <v/>
       </c>
       <c r="G19" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A19,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A19,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A19,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A19,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H19" s="20">
@@ -15170,7 +15170,7 @@
         <v/>
       </c>
       <c r="C20" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A20,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A20,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A20,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A20,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D20" s="31">
@@ -15186,7 +15186,7 @@
         <v/>
       </c>
       <c r="G20" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A20,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A20,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A20,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A20,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H20" s="30">
@@ -15219,7 +15219,7 @@
         <v/>
       </c>
       <c r="C21" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A21,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A21,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A21,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A21,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D21" s="18">
@@ -15235,7 +15235,7 @@
         <v/>
       </c>
       <c r="G21" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A21,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A21,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A21,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A21,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
@@ -15268,7 +15268,7 @@
         <v/>
       </c>
       <c r="C22" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A22,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A22,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A22,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A22,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D22" s="31">
@@ -15284,7 +15284,7 @@
         <v/>
       </c>
       <c r="G22" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A22,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A22,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A22,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A22,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H22" s="30">
@@ -15317,7 +15317,7 @@
         <v/>
       </c>
       <c r="C23" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A23,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A23,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A23,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A23,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D23" s="18">
@@ -15333,7 +15333,7 @@
         <v/>
       </c>
       <c r="G23" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A23,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A23,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A23,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A23,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
@@ -15366,7 +15366,7 @@
         <v/>
       </c>
       <c r="C24" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A24,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A24,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A24,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A24,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D24" s="31">
@@ -15382,7 +15382,7 @@
         <v/>
       </c>
       <c r="G24" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A24,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A24,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A24,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A24,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H24" s="30">
@@ -15415,7 +15415,7 @@
         <v/>
       </c>
       <c r="C25" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A25,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A25,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A25,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A25,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D25" s="18">
@@ -15431,7 +15431,7 @@
         <v/>
       </c>
       <c r="G25" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A25,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A25,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A25,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A25,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
@@ -15464,7 +15464,7 @@
         <v/>
       </c>
       <c r="C26" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A26,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A26,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A26,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A26,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D26" s="31">
@@ -15480,7 +15480,7 @@
         <v/>
       </c>
       <c r="G26" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A26,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A26,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A26,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A26,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H26" s="30">
@@ -15513,7 +15513,7 @@
         <v/>
       </c>
       <c r="C27" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A27,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A27,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A27,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A27,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D27" s="18">
@@ -15529,7 +15529,7 @@
         <v/>
       </c>
       <c r="G27" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A27,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A27,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A27,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A27,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H27" s="20">
@@ -15562,7 +15562,7 @@
         <v/>
       </c>
       <c r="C28" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A28,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A28,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A28,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A28,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D28" s="31">
@@ -15578,7 +15578,7 @@
         <v/>
       </c>
       <c r="G28" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A28,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A28,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A28,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A28,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H28" s="30">
@@ -15611,7 +15611,7 @@
         <v/>
       </c>
       <c r="C29" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A29,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A29,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A29,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A29,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D29" s="18">
@@ -15627,7 +15627,7 @@
         <v/>
       </c>
       <c r="G29" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A29,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A29,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A29,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A29,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H29" s="20">
@@ -15660,7 +15660,7 @@
         <v/>
       </c>
       <c r="C30" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A30,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A30,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A30,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A30,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D30" s="31">
@@ -15676,7 +15676,7 @@
         <v/>
       </c>
       <c r="G30" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A30,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A30,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A30,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A30,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H30" s="30">
@@ -15709,7 +15709,7 @@
         <v/>
       </c>
       <c r="C31" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A31,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A31,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A31,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A31,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D31" s="18">
@@ -15725,7 +15725,7 @@
         <v/>
       </c>
       <c r="G31" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A31,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A31,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A31,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A31,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H31" s="20">
@@ -15758,7 +15758,7 @@
         <v/>
       </c>
       <c r="C32" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A32,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A32,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A32,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A32,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D32" s="31">
@@ -15774,7 +15774,7 @@
         <v/>
       </c>
       <c r="G32" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A32,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A32,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A32,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A32,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H32" s="30">
@@ -15807,7 +15807,7 @@
         <v/>
       </c>
       <c r="C33" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A33,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A33,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A33,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A33,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="D33" s="18">
@@ -15823,7 +15823,7 @@
         <v/>
       </c>
       <c r="G33" s="100">
-        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$464,MATCH($A33,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$G$31:$G$464,MATCH($A33,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$G$31:$G$465,MATCH($A33,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$G$31:$G$465,MATCH($A33,Kalshi!$A$31:$A$465,0))),"")</f>
         <v/>
       </c>
       <c r="H33" s="20">
@@ -15856,7 +15856,7 @@
         <v/>
       </c>
       <c r="C34" s="101">
-        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$464,MATCH($A34,Kalshi!$A$31:$A$464,0))=0,"",INDEX(Kalshi!$D$31:$D$464,MATCH($A34,Kalshi!$A$31:$A$464,0))),"")</f>
+        <f>IFERROR(IF(INDEX(Kalshi!$D$31:$D$465,MATCH($A34,Kalshi!$A$31:$A$465,0))=0,"",INDEX(Kalshi!$D$31:$D$465,MATCH($A